--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J91" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J91"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J92" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J92"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -497,9 +497,9 @@
         <v>شناسه ثبت</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" s="16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,42 +508,48 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:32</t>
+          <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G6" s="22">
-        <v>4</v>
-      </c>
-      <c r="H6" s="22">
-        <v>0</v>
-      </c>
-      <c r="I6" s="20">
-        <v>4</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">371938f24f</t>
+          <t xml:space="preserve">2688d62325</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -552,7 +558,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -562,12 +568,12 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G7" s="23">
@@ -581,13 +587,13 @@
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -596,7 +602,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -606,12 +612,12 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G8" s="22">
@@ -625,13 +631,13 @@
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -640,7 +646,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -650,32 +656,32 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9" s="23">
         <v>0</v>
       </c>
       <c r="I9" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -684,7 +690,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -694,32 +700,32 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G10" s="22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H10" s="22">
         <v>0</v>
       </c>
       <c r="I10" s="20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
@@ -728,7 +734,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -738,32 +744,32 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G11" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H11" s="23">
         <v>0</v>
       </c>
       <c r="I11" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -772,7 +778,7 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
@@ -782,32 +788,32 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G12" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H12" s="22">
         <v>0</v>
       </c>
       <c r="I12" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -816,7 +822,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -826,32 +832,32 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G13" s="23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H13" s="23">
         <v>0</v>
       </c>
       <c r="I13" s="21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -860,7 +866,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
@@ -870,32 +876,32 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G14" s="22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="22">
         <v>0</v>
       </c>
       <c r="I14" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
@@ -904,7 +910,7 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -914,32 +920,32 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G15" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H15" s="23">
         <v>0</v>
       </c>
       <c r="I15" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
@@ -948,7 +954,7 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
@@ -958,32 +964,32 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G16" s="22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="22">
         <v>0</v>
       </c>
       <c r="I16" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
@@ -992,7 +998,7 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -1002,32 +1008,32 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G17" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H17" s="23">
         <v>0</v>
       </c>
       <c r="I17" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
@@ -1036,7 +1042,7 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
@@ -1046,32 +1052,32 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G18" s="22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H18" s="22">
         <v>0</v>
       </c>
       <c r="I18" s="20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
@@ -1080,7 +1086,7 @@
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -1090,32 +1096,32 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G19" s="23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H19" s="23">
         <v>0</v>
       </c>
       <c r="I19" s="21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
@@ -1124,7 +1130,7 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
@@ -1134,32 +1140,32 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G20" s="22">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H20" s="22">
         <v>0</v>
       </c>
       <c r="I20" s="20">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
@@ -1168,7 +1174,7 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -1178,32 +1184,32 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G21" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H21" s="23">
         <v>0</v>
       </c>
       <c r="I21" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
@@ -1212,7 +1218,7 @@
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D22" s="17" t="inlineStr">
@@ -1222,32 +1228,32 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G22" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H22" s="22">
         <v>0</v>
       </c>
       <c r="I22" s="20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
@@ -1256,7 +1262,7 @@
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
@@ -1266,46 +1272,46 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G23" s="23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H23" s="23">
         <v>0</v>
       </c>
       <c r="I23" s="21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
@@ -1319,19 +1325,17 @@
         </is>
       </c>
       <c r="G24" s="22">
+        <v>5</v>
+      </c>
+      <c r="H24" s="22">
         <v>0</v>
       </c>
-      <c r="H24" s="22">
+      <c r="I24" s="20">
         <v>5</v>
       </c>
-      <c r="I24" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -1356,19 +1360,19 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G25" s="23">
         <v>0</v>
       </c>
       <c r="H25" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
@@ -1397,7 +1401,7 @@
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E26" s="17" t="inlineStr">
@@ -1410,15 +1414,11 @@
           <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H26" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+      <c r="G26" s="22">
+        <v>0</v>
+      </c>
+      <c r="H26" s="22">
+        <v>3</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
@@ -1447,24 +1447,28 @@
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G27" s="23">
-        <v>0</v>
-      </c>
-      <c r="H27" s="23">
-        <v>6</v>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
@@ -1493,7 +1497,7 @@
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
@@ -1506,15 +1510,11 @@
           <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H28" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
+      <c r="G28" s="22">
+        <v>0</v>
+      </c>
+      <c r="H28" s="22">
+        <v>6</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="H29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -1598,22 +1598,22 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="H31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="H32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -1743,24 +1743,28 @@
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G33" s="23">
-        <v>0</v>
-      </c>
-      <c r="H33" s="23">
-        <v>3</v>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
@@ -1789,7 +1793,7 @@
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E34" s="17" t="inlineStr">
@@ -1802,15 +1806,11 @@
           <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H34" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
+      <c r="G34" s="22">
+        <v>0</v>
+      </c>
+      <c r="H34" s="22">
+        <v>3</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
@@ -1839,24 +1839,28 @@
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G35" s="23">
-        <v>0</v>
-      </c>
-      <c r="H35" s="23">
-        <v>3</v>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1885,7 +1889,7 @@
       </c>
       <c r="D36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E36" s="17" t="inlineStr">
@@ -1898,15 +1902,11 @@
           <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
-      <c r="G36" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H36" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
+      <c r="G36" s="22">
+        <v>0</v>
+      </c>
+      <c r="H36" s="22">
+        <v>3</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1935,24 +1935,28 @@
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G37" s="23">
-        <v>0</v>
-      </c>
-      <c r="H37" s="23">
-        <v>5</v>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H37" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1981,7 +1985,7 @@
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
@@ -1994,15 +1998,11 @@
           <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
-      <c r="G38" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H38" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
+      <c r="G38" s="22">
+        <v>0</v>
+      </c>
+      <c r="H38" s="22">
+        <v>5</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -2031,24 +2031,28 @@
       </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="G39" s="23">
-        <v>0</v>
-      </c>
-      <c r="H39" s="23">
-        <v>9</v>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H39" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
@@ -2077,7 +2081,7 @@
       </c>
       <c r="D40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E40" s="17" t="inlineStr">
@@ -2090,15 +2094,11 @@
           <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
-      <c r="G40" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H40" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
+      <c r="G40" s="22">
+        <v>0</v>
+      </c>
+      <c r="H40" s="22">
+        <v>9</v>
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G41" s="23" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="H41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I41" s="21" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G42" s="22" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="H42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I42" s="20" t="inlineStr">
@@ -2227,24 +2227,28 @@
       </c>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G43" s="23">
-        <v>0</v>
-      </c>
-      <c r="H43" s="23">
-        <v>6</v>
+          <t xml:space="preserve">وافل</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H43" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وافل</t>
+        </is>
       </c>
       <c r="I43" s="21" t="inlineStr">
         <is>
@@ -2273,7 +2277,7 @@
       </c>
       <c r="D44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E44" s="17" t="inlineStr">
@@ -2286,15 +2290,11 @@
           <t xml:space="preserve">کوکی</t>
         </is>
       </c>
-      <c r="G44" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H44" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
+      <c r="G44" s="22">
+        <v>0</v>
+      </c>
+      <c r="H44" s="22">
+        <v>6</v>
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
@@ -2323,24 +2323,28 @@
       </c>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="G45" s="23">
-        <v>0</v>
-      </c>
-      <c r="H45" s="23">
-        <v>3</v>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
       </c>
       <c r="I45" s="21" t="inlineStr">
         <is>
@@ -2369,7 +2373,7 @@
       </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
@@ -2382,15 +2386,11 @@
           <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
-      <c r="G46" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H46" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
+      <c r="G46" s="22">
+        <v>0</v>
+      </c>
+      <c r="H46" s="22">
+        <v>3</v>
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
@@ -2424,12 +2424,12 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="H47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="I47" s="21" t="inlineStr">
@@ -2469,24 +2469,28 @@
       </c>
       <c r="D48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G48" s="22">
-        <v>0</v>
-      </c>
-      <c r="H48" s="22">
-        <v>4</v>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H48" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
       </c>
       <c r="I48" s="20" t="inlineStr">
         <is>
@@ -2515,7 +2519,7 @@
       </c>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
@@ -2528,15 +2532,11 @@
           <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
-      <c r="G49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
+      <c r="G49" s="23">
+        <v>0</v>
+      </c>
+      <c r="H49" s="23">
+        <v>4</v>
       </c>
       <c r="I49" s="21" t="inlineStr">
         <is>
@@ -2565,24 +2565,28 @@
       </c>
       <c r="D50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G50" s="22">
-        <v>0</v>
-      </c>
-      <c r="H50" s="22">
-        <v>6</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H50" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I50" s="20" t="inlineStr">
         <is>
@@ -2611,7 +2615,7 @@
       </c>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
@@ -2624,15 +2628,11 @@
           <t xml:space="preserve">آجیل</t>
         </is>
       </c>
-      <c r="G51" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H51" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+      <c r="G51" s="23">
+        <v>0</v>
+      </c>
+      <c r="H51" s="23">
+        <v>6</v>
       </c>
       <c r="I51" s="21" t="inlineStr">
         <is>
@@ -2661,24 +2661,28 @@
       </c>
       <c r="D52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
-      </c>
-      <c r="G52" s="22">
-        <v>0</v>
-      </c>
-      <c r="H52" s="22">
-        <v>7</v>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H52" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
       </c>
       <c r="I52" s="20" t="inlineStr">
         <is>
@@ -2707,7 +2711,7 @@
       </c>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
@@ -2720,15 +2724,11 @@
           <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
-      <c r="G53" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H53" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
+      <c r="G53" s="23">
+        <v>0</v>
+      </c>
+      <c r="H53" s="23">
+        <v>7</v>
       </c>
       <c r="I53" s="21" t="inlineStr">
         <is>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G54" s="22" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="H54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I54" s="20" t="inlineStr">
@@ -2807,24 +2807,28 @@
       </c>
       <c r="D55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G55" s="23">
-        <v>0</v>
-      </c>
-      <c r="H55" s="23">
-        <v>3</v>
+          <t xml:space="preserve">رول رول</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H55" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول</t>
+        </is>
       </c>
       <c r="I55" s="21" t="inlineStr">
         <is>
@@ -2853,7 +2857,7 @@
       </c>
       <c r="D56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E56" s="17" t="inlineStr">
@@ -2866,15 +2870,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G56" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H56" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G56" s="22">
+        <v>0</v>
+      </c>
+      <c r="H56" s="22">
+        <v>3</v>
       </c>
       <c r="I56" s="20" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G60" s="22" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="H60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I60" s="20" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="H61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I61" s="21" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="G62" s="22" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="H62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="I62" s="20" t="inlineStr">
@@ -3203,24 +3203,28 @@
       </c>
       <c r="D63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G63" s="23">
-        <v>0</v>
-      </c>
-      <c r="H63" s="23">
-        <v>5</v>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H63" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
       </c>
       <c r="I63" s="21" t="inlineStr">
         <is>
@@ -3249,7 +3253,7 @@
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
@@ -3262,15 +3266,11 @@
           <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
-      <c r="G64" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H64" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
+      <c r="G64" s="22">
+        <v>0</v>
+      </c>
+      <c r="H64" s="22">
+        <v>5</v>
       </c>
       <c r="I64" s="20" t="inlineStr">
         <is>
@@ -3299,24 +3299,28 @@
       </c>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G65" s="23">
-        <v>0</v>
-      </c>
-      <c r="H65" s="23">
-        <v>2</v>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H65" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
       </c>
       <c r="I65" s="21" t="inlineStr">
         <is>
@@ -3345,7 +3349,7 @@
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
@@ -3358,15 +3362,11 @@
           <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
-      <c r="G66" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H66" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
+      <c r="G66" s="22">
+        <v>0</v>
+      </c>
+      <c r="H66" s="22">
+        <v>2</v>
       </c>
       <c r="I66" s="20" t="inlineStr">
         <is>
@@ -3395,24 +3395,28 @@
       </c>
       <c r="D67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G67" s="23">
-        <v>0</v>
-      </c>
-      <c r="H67" s="23">
-        <v>4</v>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H67" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
       </c>
       <c r="I67" s="21" t="inlineStr">
         <is>
@@ -3441,7 +3445,7 @@
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
@@ -3454,15 +3458,11 @@
           <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
-      <c r="G68" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H68" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
+      <c r="G68" s="22">
+        <v>0</v>
+      </c>
+      <c r="H68" s="22">
+        <v>4</v>
       </c>
       <c r="I68" s="20" t="inlineStr">
         <is>
@@ -3496,12 +3496,12 @@
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="H69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I69" s="21" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G70" s="22" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="H70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I70" s="20" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="H71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I71" s="21" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G72" s="22" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="H72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I72" s="20" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="H73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I73" s="21" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G74" s="22" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="H74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="H75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="I75" s="21" t="inlineStr">
@@ -3841,24 +3841,28 @@
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G76" s="22">
-        <v>0</v>
-      </c>
-      <c r="H76" s="22">
-        <v>4</v>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H76" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
@@ -3887,7 +3891,7 @@
       </c>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
@@ -3900,15 +3904,11 @@
           <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
-      <c r="G77" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H77" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
+      <c r="G77" s="23">
+        <v>0</v>
+      </c>
+      <c r="H77" s="23">
+        <v>4</v>
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G78" s="22" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="H78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="H79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I79" s="21" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G80" s="22" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="H80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="H81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="I81" s="21" t="inlineStr">
@@ -4137,24 +4137,28 @@
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G82" s="22">
-        <v>0</v>
-      </c>
-      <c r="H82" s="22">
-        <v>4</v>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H82" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
@@ -4183,7 +4187,7 @@
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
@@ -4196,15 +4200,11 @@
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G83" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H83" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
+      <c r="G83" s="23">
+        <v>0</v>
+      </c>
+      <c r="H83" s="23">
+        <v>4</v>
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
@@ -4238,132 +4238,138 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F84" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H84" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="I84" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J84" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="18">
+        <v>3</v>
+      </c>
+      <c r="B85" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C85" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D85" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E85" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">68</t>
         </is>
       </c>
-      <c r="F84" s="22" t="inlineStr">
+      <c r="F85" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="G84" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H84" s="22" t="inlineStr">
+      <c r="G85" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H85" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="I84" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J84" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="48" customHeight="1">
-      <c r="A85" s="18">
-        <v>3</v>
-      </c>
-      <c r="B85" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/24</t>
-        </is>
-      </c>
-      <c r="C85" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12:39:32</t>
-        </is>
-      </c>
-      <c r="D85" s="19" t="inlineStr">
+      <c r="I85" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J85" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="48" customHeight="1">
+      <c r="A86" s="16">
+        <v>3</v>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C86" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E85" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F85" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G85" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H85" s="23" t="inlineStr">
+      <c r="E86" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F86" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H86" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="I85" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J85" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="28" customHeight="1">
-      <c r="A86" s="16">
-        <v>2</v>
-      </c>
-      <c r="B86" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/23</t>
-        </is>
-      </c>
-      <c r="C86" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23:16:19</t>
-        </is>
-      </c>
-      <c r="D86" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E86" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="F86" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G86" s="22">
-        <v>4</v>
-      </c>
-      <c r="H86" s="22">
-        <v>0</v>
-      </c>
-      <c r="I86" s="20">
-        <v>4</v>
+      <c r="I86" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">deac82c691</t>
+          <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
     <row r="87" ht="28" customHeight="1">
       <c r="A87" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B87" s="19" t="inlineStr">
         <is>
@@ -4372,12 +4378,12 @@
       </c>
       <c r="C87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">23:16:19</t>
         </is>
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
@@ -4391,19 +4397,17 @@
         </is>
       </c>
       <c r="G87" s="23">
+        <v>4</v>
+      </c>
+      <c r="H87" s="23">
         <v>0</v>
       </c>
-      <c r="H87" s="23">
+      <c r="I87" s="21">
         <v>4</v>
       </c>
-      <c r="I87" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4427,7 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
@@ -4436,15 +4440,11 @@
           <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
-      <c r="G88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
+      <c r="G88" s="22">
+        <v>0</v>
+      </c>
+      <c r="H88" s="22">
+        <v>4</v>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="H89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="I89" s="21" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
@@ -4578,30 +4578,80 @@
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H91" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I91" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J91" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="28" customHeight="1">
+      <c r="A92" s="16">
+        <v>1</v>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C92" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E92" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F91" s="23" t="inlineStr">
+      <c r="F92" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G91" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H91" s="23" t="inlineStr">
+      <c r="G92" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H92" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I91" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J91" s="19" t="inlineStr">
+      <c r="I92" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J92" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J92" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J92"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J98" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J98"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -497,9 +497,9 @@
         <v>شناسه ثبت</v>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1">
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,33 +508,29 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11:25:59</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">یادداشت و آمار قهوه</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G6" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
-        </is>
-      </c>
-      <c r="H6" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G6" s="22">
+        <v>0</v>
+      </c>
+      <c r="H6" s="22">
+        <v>2</v>
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
@@ -543,13 +539,13 @@
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2688d62325</t>
+          <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -558,42 +554,44 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:32</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G7" s="23">
+        <v>0</v>
+      </c>
+      <c r="H7" s="23">
         <v>4</v>
       </c>
-      <c r="H7" s="23">
-        <v>0</v>
-      </c>
-      <c r="I7" s="21">
-        <v>4</v>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">371938f24f</t>
+          <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -602,42 +600,44 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G8" s="22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H8" s="22">
-        <v>0</v>
-      </c>
-      <c r="I8" s="20">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="18">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -646,42 +646,44 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H9" s="23">
-        <v>0</v>
-      </c>
-      <c r="I9" s="21">
-        <v>4</v>
+        <v>12</v>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -690,42 +692,44 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G10" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="22">
-        <v>0</v>
-      </c>
-      <c r="I10" s="20">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="18">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
@@ -734,42 +738,44 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G11" s="23">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H11" s="23">
-        <v>0</v>
-      </c>
-      <c r="I11" s="21">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="16">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -778,42 +784,48 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G12" s="22">
-        <v>3</v>
-      </c>
-      <c r="H12" s="22">
-        <v>0</v>
-      </c>
-      <c r="I12" s="20">
-        <v>3</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">2688d62325</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="18">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -822,7 +834,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -832,32 +844,32 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G13" s="23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H13" s="23">
         <v>0</v>
       </c>
       <c r="I13" s="21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -866,7 +878,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
@@ -876,12 +888,12 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G14" s="22">
@@ -895,13 +907,13 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="18">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
@@ -910,7 +922,7 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -920,32 +932,32 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G15" s="23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="23">
         <v>0</v>
       </c>
       <c r="I15" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="16">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
@@ -954,7 +966,7 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
@@ -964,32 +976,32 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G16" s="22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H16" s="22">
         <v>0</v>
       </c>
       <c r="I16" s="20">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="18">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
@@ -998,7 +1010,7 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -1008,12 +1020,12 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G17" s="23">
@@ -1027,13 +1039,13 @@
       </c>
       <c r="J17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
@@ -1042,7 +1054,7 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
@@ -1052,12 +1064,12 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G18" s="22">
@@ -1071,13 +1083,13 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="18">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
@@ -1086,7 +1098,7 @@
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -1096,32 +1108,32 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G19" s="23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" s="23">
         <v>0</v>
       </c>
       <c r="I19" s="21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="16">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
@@ -1130,7 +1142,7 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
@@ -1140,32 +1152,32 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G20" s="22">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H20" s="22">
         <v>0</v>
       </c>
       <c r="I20" s="20">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="18">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
@@ -1174,7 +1186,7 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -1184,12 +1196,12 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G21" s="23">
@@ -1203,13 +1215,13 @@
       </c>
       <c r="J21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="16">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
@@ -1218,7 +1230,7 @@
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D22" s="17" t="inlineStr">
@@ -1228,12 +1240,12 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G22" s="22">
@@ -1247,57 +1259,57 @@
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="18">
+        <v>11</v>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:18:11</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G23" s="23">
         <v>5</v>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:17:58</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
-      </c>
-      <c r="G23" s="23">
-        <v>3</v>
       </c>
       <c r="H23" s="23">
         <v>0</v>
       </c>
       <c r="I23" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="16">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
@@ -1306,7 +1318,7 @@
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
@@ -1316,188 +1328,178 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G24" s="22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H24" s="22">
         <v>0</v>
       </c>
       <c r="I24" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="18">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G25" s="23">
+        <v>7</v>
+      </c>
+      <c r="H25" s="23">
         <v>0</v>
       </c>
-      <c r="H25" s="23">
-        <v>5</v>
-      </c>
-      <c r="I25" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I25" s="21">
+        <v>7</v>
       </c>
       <c r="J25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="16">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G26" s="22">
+        <v>9</v>
+      </c>
+      <c r="H26" s="22">
         <v>0</v>
       </c>
-      <c r="H26" s="22">
-        <v>3</v>
-      </c>
-      <c r="I26" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I26" s="20">
+        <v>9</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="18">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
-      </c>
-      <c r="G27" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H27" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
-      </c>
-      <c r="I27" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G27" s="23">
+        <v>3</v>
+      </c>
+      <c r="H27" s="23">
+        <v>0</v>
+      </c>
+      <c r="I27" s="21">
+        <v>3</v>
       </c>
       <c r="J27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
@@ -1511,119 +1513,105 @@
         </is>
       </c>
       <c r="G28" s="22">
+        <v>6</v>
+      </c>
+      <c r="H28" s="22">
         <v>0</v>
       </c>
-      <c r="H28" s="22">
+      <c r="I28" s="20">
         <v>6</v>
       </c>
-      <c r="I28" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H29" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="I29" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G29" s="23">
+        <v>3</v>
+      </c>
+      <c r="H29" s="23">
+        <v>0</v>
+      </c>
+      <c r="I29" s="21">
+        <v>3</v>
       </c>
       <c r="J29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
-        </is>
-      </c>
-      <c r="G30" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H30" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
-        </is>
-      </c>
-      <c r="I30" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">تیتاپ نادری</t>
+        </is>
+      </c>
+      <c r="G30" s="22">
+        <v>5</v>
+      </c>
+      <c r="H30" s="22">
+        <v>0</v>
+      </c>
+      <c r="I30" s="20">
+        <v>5</v>
       </c>
       <c r="J30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -1643,28 +1631,24 @@
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H31" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
-        </is>
+          <t xml:space="preserve">تیتاپ نادری</t>
+        </is>
+      </c>
+      <c r="G31" s="23">
+        <v>0</v>
+      </c>
+      <c r="H31" s="23">
+        <v>5</v>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
@@ -1693,28 +1677,24 @@
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
-        </is>
-      </c>
-      <c r="G32" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H32" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">نات بار زرد</t>
-        </is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G32" s="22">
+        <v>0</v>
+      </c>
+      <c r="H32" s="22">
+        <v>3</v>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
@@ -1748,22 +1728,22 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -1798,19 +1778,19 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G34" s="22">
         <v>0</v>
       </c>
       <c r="H34" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
@@ -1844,22 +1824,22 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
@@ -1889,24 +1869,28 @@
       </c>
       <c r="D36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G36" s="22">
-        <v>0</v>
-      </c>
-      <c r="H36" s="22">
-        <v>3</v>
+          <t xml:space="preserve">ساندویچ بندری</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ بندری</t>
+        </is>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1940,12 +1924,12 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G37" s="23" t="inlineStr">
@@ -1955,7 +1939,7 @@
       </c>
       <c r="H37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I37" s="21" t="inlineStr">
@@ -1985,24 +1969,28 @@
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G38" s="22">
-        <v>0</v>
-      </c>
-      <c r="H38" s="22">
-        <v>5</v>
+          <t xml:space="preserve">نات بار زرد</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">نات بار زرد</t>
+        </is>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -2036,12 +2024,12 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
         </is>
       </c>
       <c r="G39" s="23" t="inlineStr">
@@ -2051,7 +2039,7 @@
       </c>
       <c r="H39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
         </is>
       </c>
       <c r="I39" s="21" t="inlineStr">
@@ -2086,19 +2074,19 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G40" s="22">
         <v>0</v>
       </c>
       <c r="H40" s="22">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
@@ -2132,12 +2120,12 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G41" s="23" t="inlineStr">
@@ -2147,7 +2135,7 @@
       </c>
       <c r="H41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="I41" s="21" t="inlineStr">
@@ -2177,28 +2165,24 @@
       </c>
       <c r="D42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
-        </is>
-      </c>
-      <c r="G42" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H42" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کروسان</t>
-        </is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G42" s="22">
+        <v>0</v>
+      </c>
+      <c r="H42" s="22">
+        <v>3</v>
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
@@ -2232,12 +2216,12 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G43" s="23" t="inlineStr">
@@ -2247,7 +2231,7 @@
       </c>
       <c r="H43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="I43" s="21" t="inlineStr">
@@ -2282,19 +2266,19 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G44" s="22">
         <v>0</v>
       </c>
       <c r="H44" s="22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
@@ -2328,12 +2312,12 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr">
@@ -2343,7 +2327,7 @@
       </c>
       <c r="H45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="I45" s="21" t="inlineStr">
@@ -2378,19 +2362,19 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G46" s="22">
         <v>0</v>
       </c>
       <c r="H46" s="22">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
@@ -2424,12 +2408,12 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr">
@@ -2439,7 +2423,7 @@
       </c>
       <c r="H47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I47" s="21" t="inlineStr">
@@ -2474,12 +2458,12 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G48" s="22" t="inlineStr">
@@ -2489,7 +2473,7 @@
       </c>
       <c r="H48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I48" s="20" t="inlineStr">
@@ -2519,24 +2503,28 @@
       </c>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G49" s="23">
-        <v>0</v>
-      </c>
-      <c r="H49" s="23">
-        <v>4</v>
+          <t xml:space="preserve">وافل</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وافل</t>
+        </is>
       </c>
       <c r="I49" s="21" t="inlineStr">
         <is>
@@ -2565,28 +2553,24 @@
       </c>
       <c r="D50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G50" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H50" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G50" s="22">
+        <v>0</v>
+      </c>
+      <c r="H50" s="22">
+        <v>6</v>
       </c>
       <c r="I50" s="20" t="inlineStr">
         <is>
@@ -2615,24 +2599,28 @@
       </c>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G51" s="23">
-        <v>0</v>
-      </c>
-      <c r="H51" s="23">
-        <v>6</v>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H51" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
       </c>
       <c r="I51" s="21" t="inlineStr">
         <is>
@@ -2661,28 +2649,24 @@
       </c>
       <c r="D52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G52" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H52" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+          <t xml:space="preserve">پاستیل</t>
+        </is>
+      </c>
+      <c r="G52" s="22">
+        <v>0</v>
+      </c>
+      <c r="H52" s="22">
+        <v>3</v>
       </c>
       <c r="I52" s="20" t="inlineStr">
         <is>
@@ -2711,24 +2695,28 @@
       </c>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
-      </c>
-      <c r="G53" s="23">
-        <v>0</v>
-      </c>
-      <c r="H53" s="23">
-        <v>7</v>
+          <t xml:space="preserve">پاستیل</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H53" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پاستیل</t>
+        </is>
       </c>
       <c r="I53" s="21" t="inlineStr">
         <is>
@@ -2762,12 +2750,12 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G54" s="22" t="inlineStr">
@@ -2777,7 +2765,7 @@
       </c>
       <c r="H54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="I54" s="20" t="inlineStr">
@@ -2807,28 +2795,24 @@
       </c>
       <c r="D55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
-        </is>
-      </c>
-      <c r="G55" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H55" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">رول رول</t>
-        </is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G55" s="23">
+        <v>0</v>
+      </c>
+      <c r="H55" s="23">
+        <v>4</v>
       </c>
       <c r="I55" s="21" t="inlineStr">
         <is>
@@ -2857,24 +2841,28 @@
       </c>
       <c r="D56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G56" s="22">
-        <v>0</v>
-      </c>
-      <c r="H56" s="22">
-        <v>3</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H56" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I56" s="20" t="inlineStr">
         <is>
@@ -2903,28 +2891,24 @@
       </c>
       <c r="D57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H57" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G57" s="23">
+        <v>0</v>
+      </c>
+      <c r="H57" s="23">
+        <v>6</v>
       </c>
       <c r="I57" s="21" t="inlineStr">
         <is>
@@ -2958,12 +2942,12 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G58" s="22" t="inlineStr">
@@ -2973,7 +2957,7 @@
       </c>
       <c r="H58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="I58" s="20" t="inlineStr">
@@ -3003,28 +2987,24 @@
       </c>
       <c r="D59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G59" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H59" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
+        </is>
+      </c>
+      <c r="G59" s="23">
+        <v>0</v>
+      </c>
+      <c r="H59" s="23">
+        <v>7</v>
       </c>
       <c r="I59" s="21" t="inlineStr">
         <is>
@@ -3058,12 +3038,12 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G60" s="22" t="inlineStr">
@@ -3073,7 +3053,7 @@
       </c>
       <c r="H60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I60" s="20" t="inlineStr">
@@ -3108,12 +3088,12 @@
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr">
@@ -3123,7 +3103,7 @@
       </c>
       <c r="H61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="I61" s="21" t="inlineStr">
@@ -3153,28 +3133,24 @@
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
-        </is>
-      </c>
-      <c r="G62" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H62" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">توینکلز</t>
-        </is>
+          <t xml:space="preserve">اب معدنی</t>
+        </is>
+      </c>
+      <c r="G62" s="22">
+        <v>0</v>
+      </c>
+      <c r="H62" s="22">
+        <v>3</v>
       </c>
       <c r="I62" s="20" t="inlineStr">
         <is>
@@ -3208,12 +3184,12 @@
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr">
@@ -3223,7 +3199,7 @@
       </c>
       <c r="H63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I63" s="21" t="inlineStr">
@@ -3253,24 +3229,28 @@
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G64" s="22">
-        <v>0</v>
-      </c>
-      <c r="H64" s="22">
-        <v>5</v>
+          <t xml:space="preserve">اب معدنی</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H64" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اب معدنی</t>
+        </is>
       </c>
       <c r="I64" s="20" t="inlineStr">
         <is>
@@ -3304,12 +3284,12 @@
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr">
@@ -3319,7 +3299,7 @@
       </c>
       <c r="H65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I65" s="21" t="inlineStr">
@@ -3349,24 +3329,28 @@
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G66" s="22">
-        <v>0</v>
-      </c>
-      <c r="H66" s="22">
-        <v>2</v>
+          <t xml:space="preserve">اب معدنی</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H66" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اب معدنی</t>
+        </is>
       </c>
       <c r="I66" s="20" t="inlineStr">
         <is>
@@ -3400,12 +3384,12 @@
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
@@ -3415,7 +3399,7 @@
       </c>
       <c r="H67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I67" s="21" t="inlineStr">
@@ -3445,24 +3429,28 @@
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G68" s="22">
-        <v>0</v>
-      </c>
-      <c r="H68" s="22">
-        <v>4</v>
+          <t xml:space="preserve">توینکلز</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H68" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">توینکلز</t>
+        </is>
       </c>
       <c r="I68" s="20" t="inlineStr">
         <is>
@@ -3496,12 +3484,12 @@
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
@@ -3511,7 +3499,7 @@
       </c>
       <c r="H69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="I69" s="21" t="inlineStr">
@@ -3541,28 +3529,24 @@
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
-        </is>
-      </c>
-      <c r="G70" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H70" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شیر شکلات</t>
-        </is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G70" s="22">
+        <v>0</v>
+      </c>
+      <c r="H70" s="22">
+        <v>5</v>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
@@ -3596,12 +3580,12 @@
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
@@ -3611,7 +3595,7 @@
       </c>
       <c r="H71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="I71" s="21" t="inlineStr">
@@ -3641,28 +3625,24 @@
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
-        </is>
-      </c>
-      <c r="G72" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H72" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شیر قهوه</t>
-        </is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G72" s="22">
+        <v>0</v>
+      </c>
+      <c r="H72" s="22">
+        <v>2</v>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
@@ -3696,12 +3676,12 @@
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -3711,7 +3691,7 @@
       </c>
       <c r="H73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="I73" s="21" t="inlineStr">
@@ -3741,28 +3721,24 @@
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
-        </is>
-      </c>
-      <c r="G74" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H74" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
-        </is>
+          <t xml:space="preserve">تیتو مزمز</t>
+        </is>
+      </c>
+      <c r="G74" s="22">
+        <v>0</v>
+      </c>
+      <c r="H74" s="22">
+        <v>4</v>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
@@ -3796,12 +3772,12 @@
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -3811,7 +3787,7 @@
       </c>
       <c r="H75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I75" s="21" t="inlineStr">
@@ -3846,12 +3822,12 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G76" s="22" t="inlineStr">
@@ -3861,7 +3837,7 @@
       </c>
       <c r="H76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
@@ -3891,24 +3867,28 @@
       </c>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G77" s="23">
-        <v>0</v>
-      </c>
-      <c r="H77" s="23">
-        <v>4</v>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H77" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
@@ -3942,12 +3922,12 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G78" s="22" t="inlineStr">
@@ -3957,7 +3937,7 @@
       </c>
       <c r="H78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
@@ -3992,12 +3972,12 @@
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -4007,7 +3987,7 @@
       </c>
       <c r="H79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I79" s="21" t="inlineStr">
@@ -4042,12 +4022,12 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G80" s="22" t="inlineStr">
@@ -4057,7 +4037,7 @@
       </c>
       <c r="H80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
@@ -4092,12 +4072,12 @@
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -4107,7 +4087,7 @@
       </c>
       <c r="H81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="I81" s="21" t="inlineStr">
@@ -4142,12 +4122,12 @@
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G82" s="22" t="inlineStr">
@@ -4157,7 +4137,7 @@
       </c>
       <c r="H82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
@@ -4192,12 +4172,12 @@
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G83" s="23">
@@ -4238,12 +4218,12 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G84" s="22" t="inlineStr">
@@ -4253,7 +4233,7 @@
       </c>
       <c r="H84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I84" s="20" t="inlineStr">
@@ -4288,12 +4268,12 @@
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">68</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف بدون قند</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -4303,7 +4283,7 @@
       </c>
       <c r="H85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف بدون قند</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I85" s="21" t="inlineStr">
@@ -4317,7 +4297,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="48" customHeight="1">
+    <row r="86" ht="28" customHeight="1">
       <c r="A86" s="16">
         <v>3</v>
       </c>
@@ -4333,17 +4313,17 @@
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">یادداشت و آمار قهوه</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G86" s="22" t="inlineStr">
@@ -4353,7 +4333,7 @@
       </c>
       <c r="H86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
@@ -4369,82 +4349,92 @@
     </row>
     <row r="87" ht="28" customHeight="1">
       <c r="A87" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/23</t>
+          <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
       <c r="C87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">23:16:19</t>
+          <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G87" s="23">
-        <v>4</v>
-      </c>
-      <c r="H87" s="23">
-        <v>0</v>
-      </c>
-      <c r="I87" s="21">
-        <v>4</v>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
+        </is>
+      </c>
+      <c r="I87" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">deac82c691</t>
+          <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
     <row r="88" ht="28" customHeight="1">
       <c r="A88" s="16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/23</t>
+          <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G88" s="22">
-        <v>0</v>
-      </c>
-      <c r="H88" s="22">
-        <v>4</v>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H88" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
@@ -4453,48 +4443,44 @@
       </c>
       <c r="J88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
     <row r="89" ht="28" customHeight="1">
       <c r="A89" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/23</t>
+          <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
       <c r="C89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
       <c r="D89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H89" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G89" s="23">
+        <v>0</v>
+      </c>
+      <c r="H89" s="23">
+        <v>4</v>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
@@ -4503,22 +4489,22 @@
       </c>
       <c r="J89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
     <row r="90" ht="28" customHeight="1">
       <c r="A90" s="16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/23</t>
+          <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
       <c r="D90" s="17" t="inlineStr">
@@ -4528,12 +4514,12 @@
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G90" s="22" t="inlineStr">
@@ -4543,7 +4529,7 @@
       </c>
       <c r="H90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="I90" s="20" t="inlineStr">
@@ -4553,105 +4539,395 @@
       </c>
       <c r="J90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
     <row r="91" ht="28" customHeight="1">
       <c r="A91" s="18">
+        <v>3</v>
+      </c>
+      <c r="B91" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D91" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E91" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف بدون قند</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H91" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف بدون قند</t>
+        </is>
+      </c>
+      <c r="I91" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J91" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="48" customHeight="1">
+      <c r="A92" s="16">
+        <v>3</v>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C92" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">یادداشت و آمار قهوه</t>
+        </is>
+      </c>
+      <c r="E92" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F92" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G92" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H92" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
+        </is>
+      </c>
+      <c r="I92" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J92" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="28" customHeight="1">
+      <c r="A93" s="18">
+        <v>2</v>
+      </c>
+      <c r="B93" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:16:19</t>
+        </is>
+      </c>
+      <c r="D93" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
+        </is>
+      </c>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تیتاپ نادری</t>
+        </is>
+      </c>
+      <c r="G93" s="23">
+        <v>4</v>
+      </c>
+      <c r="H93" s="23">
+        <v>0</v>
+      </c>
+      <c r="I93" s="21">
+        <v>4</v>
+      </c>
+      <c r="J93" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deac82c691</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="28" customHeight="1">
+      <c r="A94" s="16">
         <v>1</v>
       </c>
-      <c r="B91" s="19" t="inlineStr">
+      <c r="B94" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/23</t>
         </is>
       </c>
-      <c r="C91" s="19" t="inlineStr">
+      <c r="C94" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">22:41:53</t>
         </is>
       </c>
-      <c r="D91" s="19" t="inlineStr">
+      <c r="D94" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E94" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="F94" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تیتاپ نادری</t>
+        </is>
+      </c>
+      <c r="G94" s="22">
+        <v>0</v>
+      </c>
+      <c r="H94" s="22">
+        <v>4</v>
+      </c>
+      <c r="I94" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J94" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="28" customHeight="1">
+      <c r="A95" s="18">
+        <v>1</v>
+      </c>
+      <c r="B95" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C95" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D95" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
-      <c r="E91" s="19" t="inlineStr">
+      <c r="E95" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="F95" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تیتاپ نادری</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H95" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تیتاپ نادری</t>
+        </is>
+      </c>
+      <c r="I95" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J95" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="28" customHeight="1">
+      <c r="A96" s="16">
+        <v>1</v>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C96" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D96" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E96" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="F96" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H96" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I96" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J96" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="28" customHeight="1">
+      <c r="A97" s="18">
+        <v>1</v>
+      </c>
+      <c r="B97" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C97" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D97" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E97" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F91" s="23" t="inlineStr">
+      <c r="F97" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G91" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H91" s="23" t="inlineStr">
+      <c r="G97" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H97" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I91" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J91" s="19" t="inlineStr">
+      <c r="I97" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J97" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="28" customHeight="1">
-      <c r="A92" s="16">
+    <row r="98" ht="28" customHeight="1">
+      <c r="A98" s="16">
         <v>1</v>
       </c>
-      <c r="B92" s="17" t="inlineStr">
+      <c r="B98" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/23</t>
         </is>
       </c>
-      <c r="C92" s="17" t="inlineStr">
+      <c r="C98" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">22:41:53</t>
         </is>
       </c>
-      <c r="D92" s="17" t="inlineStr">
+      <c r="D98" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
-      <c r="E92" s="17" t="inlineStr">
+      <c r="E98" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F92" s="22" t="inlineStr">
+      <c r="F98" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G92" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H92" s="22" t="inlineStr">
+      <c r="G98" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H98" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I92" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J92" s="17" t="inlineStr">
+      <c r="I98" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J98" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J98" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J98"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J125" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J125"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -527,10 +527,10 @@
         </is>
       </c>
       <c r="G6" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
@@ -539,13 +539,13 @@
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="G7" s="23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I7" s="21" t="inlineStr">
         <is>
@@ -585,13 +585,13 @@
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="G8" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="20" t="inlineStr">
         <is>
@@ -631,13 +631,13 @@
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -656,19 +656,19 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G9" s="23">
         <v>0</v>
       </c>
       <c r="H9" s="23">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I9" s="21" t="inlineStr">
         <is>
@@ -677,13 +677,13 @@
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -702,19 +702,19 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G10" s="22">
         <v>0</v>
       </c>
       <c r="H10" s="22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
@@ -723,13 +723,13 @@
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -748,19 +748,19 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G11" s="23">
         <v>0</v>
       </c>
       <c r="H11" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" s="21" t="inlineStr">
         <is>
@@ -769,13 +769,13 @@
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
+          <t xml:space="preserve">ea4946ef39</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -784,33 +784,29 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11:25:59</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">یادداشت و آمار قهوه</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G12" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
-        </is>
-      </c>
-      <c r="H12" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G12" s="22">
+        <v>0</v>
+      </c>
+      <c r="H12" s="22">
+        <v>2</v>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
@@ -819,13 +815,13 @@
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2688d62325</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="18">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -834,42 +830,44 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:32</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G13" s="23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H13" s="23">
-        <v>0</v>
-      </c>
-      <c r="I13" s="21">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">371938f24f</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -878,42 +876,44 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G14" s="22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H14" s="22">
-        <v>0</v>
-      </c>
-      <c r="I14" s="20">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="18">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
@@ -922,42 +922,44 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G15" s="23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H15" s="23">
-        <v>0</v>
-      </c>
-      <c r="I15" s="21">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="16">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
@@ -966,42 +968,44 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G16" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16" s="22">
-        <v>0</v>
-      </c>
-      <c r="I16" s="20">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="18">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
@@ -1010,42 +1014,44 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G17" s="23">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H17" s="23">
-        <v>0</v>
-      </c>
-      <c r="I17" s="21">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
@@ -1054,12 +1060,12 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E18" s="17" t="inlineStr">
@@ -1073,23 +1079,25 @@
         </is>
       </c>
       <c r="G18" s="22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" s="22">
-        <v>0</v>
-      </c>
-      <c r="I18" s="20">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="18">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
@@ -1098,42 +1106,44 @@
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G19" s="23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H19" s="23">
-        <v>0</v>
-      </c>
-      <c r="I19" s="21">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="16">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
@@ -1142,42 +1152,44 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G20" s="22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" s="22">
-        <v>0</v>
-      </c>
-      <c r="I20" s="20">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="18">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
@@ -1186,42 +1198,44 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G21" s="23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H21" s="23">
-        <v>0</v>
-      </c>
-      <c r="I21" s="21">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="16">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
@@ -1230,42 +1244,44 @@
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G22" s="22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H22" s="22">
-        <v>0</v>
-      </c>
-      <c r="I22" s="20">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="18">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
@@ -1274,42 +1290,44 @@
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G23" s="23">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H23" s="23">
-        <v>0</v>
-      </c>
-      <c r="I23" s="21">
-        <v>5</v>
+        <v>21</v>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="16">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
@@ -1318,42 +1336,44 @@
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G24" s="22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H24" s="22">
-        <v>0</v>
-      </c>
-      <c r="I24" s="20">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="18">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
@@ -1362,42 +1382,44 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G25" s="23">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H25" s="23">
-        <v>0</v>
-      </c>
-      <c r="I25" s="21">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="16">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
@@ -1406,42 +1428,44 @@
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G26" s="22">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H26" s="22">
-        <v>0</v>
-      </c>
-      <c r="I26" s="20">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="18">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
@@ -1450,42 +1474,44 @@
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G27" s="23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H27" s="23">
-        <v>0</v>
-      </c>
-      <c r="I27" s="21">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="16">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
@@ -1494,42 +1520,44 @@
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G28" s="22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H28" s="22">
-        <v>0</v>
-      </c>
-      <c r="I28" s="20">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="18">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
@@ -1538,42 +1566,44 @@
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G29" s="23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H29" s="23">
-        <v>0</v>
-      </c>
-      <c r="I29" s="21">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="16">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
@@ -1582,51 +1612,53 @@
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G30" s="22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30" s="22">
-        <v>0</v>
-      </c>
-      <c r="I30" s="20">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="18">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
@@ -1636,19 +1668,19 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G31" s="23">
         <v>0</v>
       </c>
       <c r="H31" s="23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
@@ -1657,22 +1689,22 @@
       </c>
       <c r="J31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="16">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
@@ -1682,19 +1714,19 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G32" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
@@ -1703,27 +1735,27 @@
       </c>
       <c r="J32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="18">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
@@ -1736,15 +1768,11 @@
           <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
-      <c r="G33" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H33" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+      <c r="G33" s="23">
+        <v>0</v>
+      </c>
+      <c r="H33" s="23">
+        <v>2</v>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
@@ -1753,22 +1781,22 @@
       </c>
       <c r="J33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="16">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
@@ -1790,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
@@ -1799,48 +1827,44 @@
       </c>
       <c r="J34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="18">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G35" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H35" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
+          <t xml:space="preserve">ساندویچ بندری</t>
+        </is>
+      </c>
+      <c r="G35" s="23">
+        <v>0</v>
+      </c>
+      <c r="H35" s="23">
+        <v>2</v>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1849,48 +1873,44 @@
       </c>
       <c r="J35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="16">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
-        </is>
-      </c>
-      <c r="G36" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H36" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
-        </is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G36" s="22">
+        <v>0</v>
+      </c>
+      <c r="H36" s="22">
+        <v>12</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1899,48 +1919,44 @@
       </c>
       <c r="J36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="18">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H37" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
-        </is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G37" s="23">
+        <v>0</v>
+      </c>
+      <c r="H37" s="23">
+        <v>4</v>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1949,48 +1965,44 @@
       </c>
       <c r="J37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="16">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
-        </is>
-      </c>
-      <c r="G38" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H38" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">نات بار زرد</t>
-        </is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G38" s="22">
+        <v>0</v>
+      </c>
+      <c r="H38" s="22">
+        <v>1</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -1999,47 +2011,47 @@
       </c>
       <c r="J38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1">
       <c r="A39" s="18">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
       <c r="H39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I39" s="21" t="inlineStr">
@@ -2049,875 +2061,799 @@
       </c>
       <c r="J39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">2688d62325</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="16">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G40" s="22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40" s="22">
-        <v>3</v>
-      </c>
-      <c r="I40" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I40" s="20">
+        <v>4</v>
       </c>
       <c r="J40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="18">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H41" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="I41" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G41" s="23">
+        <v>4</v>
+      </c>
+      <c r="H41" s="23">
+        <v>0</v>
+      </c>
+      <c r="I41" s="21">
+        <v>4</v>
       </c>
       <c r="J41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="16">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G42" s="22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H42" s="22">
-        <v>3</v>
-      </c>
-      <c r="I42" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I42" s="20">
+        <v>4</v>
       </c>
       <c r="J42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="18">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G43" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H43" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="I43" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G43" s="23">
+        <v>2</v>
+      </c>
+      <c r="H43" s="23">
+        <v>0</v>
+      </c>
+      <c r="I43" s="21">
+        <v>2</v>
       </c>
       <c r="J43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="16">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G44" s="22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H44" s="22">
+        <v>0</v>
+      </c>
+      <c r="I44" s="20">
         <v>5</v>
       </c>
-      <c r="I44" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="18">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G45" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H45" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="I45" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">اب معدنی</t>
+        </is>
+      </c>
+      <c r="G45" s="23">
+        <v>3</v>
+      </c>
+      <c r="H45" s="23">
+        <v>0</v>
+      </c>
+      <c r="I45" s="21">
+        <v>3</v>
       </c>
       <c r="J45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="16">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G46" s="22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H46" s="22">
-        <v>9</v>
-      </c>
-      <c r="I46" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I46" s="20">
+        <v>6</v>
       </c>
       <c r="J46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="18">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H47" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="I47" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G47" s="23">
+        <v>4</v>
+      </c>
+      <c r="H47" s="23">
+        <v>0</v>
+      </c>
+      <c r="I47" s="21">
+        <v>4</v>
       </c>
       <c r="J47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="16">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
-        </is>
-      </c>
-      <c r="G48" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H48" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کروسان</t>
-        </is>
-      </c>
-      <c r="I48" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">پاستیل</t>
+        </is>
+      </c>
+      <c r="G48" s="22">
+        <v>3</v>
+      </c>
+      <c r="H48" s="22">
+        <v>0</v>
+      </c>
+      <c r="I48" s="20">
+        <v>3</v>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="18">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">وافل</t>
-        </is>
-      </c>
-      <c r="I49" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G49" s="23">
+        <v>6</v>
+      </c>
+      <c r="H49" s="23">
+        <v>0</v>
+      </c>
+      <c r="I49" s="21">
+        <v>6</v>
       </c>
       <c r="J49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="16">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G50" s="22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H50" s="22">
-        <v>6</v>
-      </c>
-      <c r="I50" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I50" s="20">
+        <v>5</v>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="18">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H51" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="I51" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G51" s="23">
+        <v>3</v>
+      </c>
+      <c r="H51" s="23">
+        <v>0</v>
+      </c>
+      <c r="I51" s="21">
+        <v>3</v>
       </c>
       <c r="J51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="16">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G52" s="22">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H52" s="22">
-        <v>3</v>
-      </c>
-      <c r="I52" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I52" s="20">
+        <v>7</v>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="18">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="G53" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H53" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="I53" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
+        </is>
+      </c>
+      <c r="G53" s="23">
+        <v>9</v>
+      </c>
+      <c r="H53" s="23">
+        <v>0</v>
+      </c>
+      <c r="I53" s="21">
+        <v>9</v>
       </c>
       <c r="J53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
-        </is>
-      </c>
-      <c r="G54" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H54" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
-        </is>
-      </c>
-      <c r="I54" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G54" s="22">
+        <v>3</v>
+      </c>
+      <c r="H54" s="22">
+        <v>0</v>
+      </c>
+      <c r="I54" s="20">
+        <v>3</v>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G55" s="23">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H55" s="23">
-        <v>4</v>
-      </c>
-      <c r="I55" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I55" s="21">
+        <v>6</v>
       </c>
       <c r="J55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G56" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H56" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="I56" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G56" s="22">
+        <v>3</v>
+      </c>
+      <c r="H56" s="22">
+        <v>0</v>
+      </c>
+      <c r="I56" s="20">
+        <v>3</v>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G57" s="23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H57" s="23">
-        <v>6</v>
-      </c>
-      <c r="I57" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I57" s="21">
+        <v>5</v>
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -2937,28 +2873,24 @@
       </c>
       <c r="D58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G58" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H58" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+          <t xml:space="preserve">تیتاپ نادری</t>
+        </is>
+      </c>
+      <c r="G58" s="22">
+        <v>0</v>
+      </c>
+      <c r="H58" s="22">
+        <v>5</v>
       </c>
       <c r="I58" s="20" t="inlineStr">
         <is>
@@ -2992,19 +2924,19 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G59" s="23">
         <v>0</v>
       </c>
       <c r="H59" s="23">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I59" s="21" t="inlineStr">
         <is>
@@ -3038,22 +2970,22 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="I60" s="20" t="inlineStr">
@@ -3083,28 +3015,24 @@
       </c>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
-        </is>
-      </c>
-      <c r="G61" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H61" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">رول رول</t>
-        </is>
+          <t xml:space="preserve">ساندویچ مرغ</t>
+        </is>
+      </c>
+      <c r="G61" s="23">
+        <v>0</v>
+      </c>
+      <c r="H61" s="23">
+        <v>6</v>
       </c>
       <c r="I61" s="21" t="inlineStr">
         <is>
@@ -3133,24 +3061,28 @@
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G62" s="22">
-        <v>0</v>
-      </c>
-      <c r="H62" s="22">
-        <v>3</v>
+          <t xml:space="preserve">ساندویچ مرغ</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H62" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ مرغ</t>
+        </is>
       </c>
       <c r="I62" s="20" t="inlineStr">
         <is>
@@ -3184,22 +3116,22 @@
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I63" s="21" t="inlineStr">
@@ -3234,12 +3166,12 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G64" s="22" t="inlineStr">
@@ -3249,7 +3181,7 @@
       </c>
       <c r="H64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I64" s="20" t="inlineStr">
@@ -3284,12 +3216,12 @@
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr">
@@ -3299,7 +3231,7 @@
       </c>
       <c r="H65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="I65" s="21" t="inlineStr">
@@ -3334,12 +3266,12 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
         </is>
       </c>
       <c r="G66" s="22" t="inlineStr">
@@ -3349,7 +3281,7 @@
       </c>
       <c r="H66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
         </is>
       </c>
       <c r="I66" s="20" t="inlineStr">
@@ -3379,28 +3311,24 @@
       </c>
       <c r="D67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H67" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">های بای نادری</t>
-        </is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G67" s="23">
+        <v>0</v>
+      </c>
+      <c r="H67" s="23">
+        <v>3</v>
       </c>
       <c r="I67" s="21" t="inlineStr">
         <is>
@@ -3434,12 +3362,12 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G68" s="22" t="inlineStr">
@@ -3449,7 +3377,7 @@
       </c>
       <c r="H68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="I68" s="20" t="inlineStr">
@@ -3479,28 +3407,24 @@
       </c>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H69" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">معینی پور</t>
-        </is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G69" s="23">
+        <v>0</v>
+      </c>
+      <c r="H69" s="23">
+        <v>3</v>
       </c>
       <c r="I69" s="21" t="inlineStr">
         <is>
@@ -3529,24 +3453,28 @@
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G70" s="22">
-        <v>0</v>
-      </c>
-      <c r="H70" s="22">
-        <v>5</v>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H70" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
@@ -3575,28 +3503,24 @@
       </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H71" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G71" s="23">
+        <v>0</v>
+      </c>
+      <c r="H71" s="23">
+        <v>5</v>
       </c>
       <c r="I71" s="21" t="inlineStr">
         <is>
@@ -3625,24 +3549,28 @@
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G72" s="22">
-        <v>0</v>
-      </c>
-      <c r="H72" s="22">
-        <v>2</v>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H72" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
@@ -3671,28 +3599,24 @@
       </c>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G73" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H73" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
+        </is>
+      </c>
+      <c r="G73" s="23">
+        <v>0</v>
+      </c>
+      <c r="H73" s="23">
+        <v>9</v>
       </c>
       <c r="I73" s="21" t="inlineStr">
         <is>
@@ -3721,24 +3645,28 @@
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G74" s="22">
-        <v>0</v>
-      </c>
-      <c r="H74" s="22">
-        <v>4</v>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H74" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
+        </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
@@ -3772,12 +3700,12 @@
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -3787,7 +3715,7 @@
       </c>
       <c r="H75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I75" s="21" t="inlineStr">
@@ -3822,12 +3750,12 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">وافل</t>
         </is>
       </c>
       <c r="G76" s="22" t="inlineStr">
@@ -3837,7 +3765,7 @@
       </c>
       <c r="H76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">وافل</t>
         </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
@@ -3867,28 +3795,24 @@
       </c>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
-        </is>
-      </c>
-      <c r="G77" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H77" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
-        </is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G77" s="23">
+        <v>0</v>
+      </c>
+      <c r="H77" s="23">
+        <v>6</v>
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
@@ -3922,12 +3846,12 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G78" s="22" t="inlineStr">
@@ -3937,7 +3861,7 @@
       </c>
       <c r="H78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
@@ -3967,28 +3891,24 @@
       </c>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
-        </is>
-      </c>
-      <c r="G79" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H79" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">سان استار انبه</t>
-        </is>
+          <t xml:space="preserve">پاستیل</t>
+        </is>
+      </c>
+      <c r="G79" s="23">
+        <v>0</v>
+      </c>
+      <c r="H79" s="23">
+        <v>3</v>
       </c>
       <c r="I79" s="21" t="inlineStr">
         <is>
@@ -4022,12 +3942,12 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G80" s="22" t="inlineStr">
@@ -4037,7 +3957,7 @@
       </c>
       <c r="H80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
@@ -4072,12 +3992,12 @@
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -4087,7 +4007,7 @@
       </c>
       <c r="H81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="I81" s="21" t="inlineStr">
@@ -4117,28 +4037,24 @@
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
-        </is>
-      </c>
-      <c r="G82" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H82" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الوئه ورا</t>
-        </is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G82" s="22">
+        <v>0</v>
+      </c>
+      <c r="H82" s="22">
+        <v>4</v>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
@@ -4167,24 +4083,28 @@
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G83" s="23">
-        <v>0</v>
-      </c>
-      <c r="H83" s="23">
-        <v>4</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H83" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
@@ -4213,28 +4133,24 @@
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G84" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H84" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G84" s="22">
+        <v>0</v>
+      </c>
+      <c r="H84" s="22">
+        <v>6</v>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
@@ -4268,12 +4184,12 @@
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -4283,7 +4199,7 @@
       </c>
       <c r="H85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="I85" s="21" t="inlineStr">
@@ -4313,28 +4229,24 @@
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
-        </is>
-      </c>
-      <c r="G86" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H86" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
-        </is>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
+        </is>
+      </c>
+      <c r="G86" s="22">
+        <v>0</v>
+      </c>
+      <c r="H86" s="22">
+        <v>7</v>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
@@ -4368,12 +4280,12 @@
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -4383,7 +4295,7 @@
       </c>
       <c r="H87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I87" s="21" t="inlineStr">
@@ -4418,12 +4330,12 @@
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G88" s="22" t="inlineStr">
@@ -4433,7 +4345,7 @@
       </c>
       <c r="H88" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="I88" s="20" t="inlineStr">
@@ -4468,19 +4380,19 @@
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G89" s="23">
         <v>0</v>
       </c>
       <c r="H89" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
@@ -4514,12 +4426,12 @@
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G90" s="22" t="inlineStr">
@@ -4529,7 +4441,7 @@
       </c>
       <c r="H90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I90" s="20" t="inlineStr">
@@ -4564,12 +4476,12 @@
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">68</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف بدون قند</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -4579,7 +4491,7 @@
       </c>
       <c r="H91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف بدون قند</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I91" s="21" t="inlineStr">
@@ -4593,7 +4505,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="48" customHeight="1">
+    <row r="92" ht="28" customHeight="1">
       <c r="A92" s="16">
         <v>3</v>
       </c>
@@ -4609,17 +4521,17 @@
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">یادداشت و آمار قهوه</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F92" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G92" s="22" t="inlineStr">
@@ -4629,7 +4541,7 @@
       </c>
       <c r="H92" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I92" s="20" t="inlineStr">
@@ -4645,82 +4557,92 @@
     </row>
     <row r="93" ht="28" customHeight="1">
       <c r="A93" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/23</t>
+          <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
       <c r="C93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">23:16:19</t>
+          <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
       <c r="D93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G93" s="23">
-        <v>4</v>
-      </c>
-      <c r="H93" s="23">
-        <v>0</v>
-      </c>
-      <c r="I93" s="21">
-        <v>4</v>
+          <t xml:space="preserve">اب معدنی</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H93" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اب معدنی</t>
+        </is>
+      </c>
+      <c r="I93" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">deac82c691</t>
+          <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
     <row r="94" ht="28" customHeight="1">
       <c r="A94" s="16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/23</t>
+          <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F94" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G94" s="22">
-        <v>0</v>
-      </c>
-      <c r="H94" s="22">
-        <v>4</v>
+          <t xml:space="preserve">های بای نادری</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H94" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">های بای نادری</t>
+        </is>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
@@ -4729,22 +4651,22 @@
       </c>
       <c r="J94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
     <row r="95" ht="28" customHeight="1">
       <c r="A95" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/23</t>
+          <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
       <c r="C95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
       <c r="D95" s="19" t="inlineStr">
@@ -4754,12 +4676,12 @@
       </c>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -4769,7 +4691,7 @@
       </c>
       <c r="H95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="I95" s="21" t="inlineStr">
@@ -4779,22 +4701,22 @@
       </c>
       <c r="J95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
     <row r="96" ht="28" customHeight="1">
       <c r="A96" s="16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/23</t>
+          <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
       <c r="D96" s="17" t="inlineStr">
@@ -4804,12 +4726,12 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G96" s="22" t="inlineStr">
@@ -4819,7 +4741,7 @@
       </c>
       <c r="H96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="I96" s="20" t="inlineStr">
@@ -4829,48 +4751,44 @@
       </c>
       <c r="J96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
     <row r="97" ht="28" customHeight="1">
       <c r="A97" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/23</t>
+          <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
       <c r="C97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
       <c r="D97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="G97" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H97" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G97" s="23">
+        <v>0</v>
+      </c>
+      <c r="H97" s="23">
+        <v>5</v>
       </c>
       <c r="I97" s="21" t="inlineStr">
         <is>
@@ -4879,55 +4797,1379 @@
       </c>
       <c r="J97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
     <row r="98" ht="28" customHeight="1">
       <c r="A98" s="16">
+        <v>3</v>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E98" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48</t>
+        </is>
+      </c>
+      <c r="F98" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G98" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H98" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="I98" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J98" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="28" customHeight="1">
+      <c r="A99" s="18">
+        <v>3</v>
+      </c>
+      <c r="B99" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C99" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D99" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E99" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51</t>
+        </is>
+      </c>
+      <c r="F99" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G99" s="23">
+        <v>0</v>
+      </c>
+      <c r="H99" s="23">
+        <v>2</v>
+      </c>
+      <c r="I99" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J99" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="28" customHeight="1">
+      <c r="A100" s="16">
+        <v>3</v>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D100" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E100" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51</t>
+        </is>
+      </c>
+      <c r="F100" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G100" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H100" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="I100" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J100" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="18">
+        <v>3</v>
+      </c>
+      <c r="B101" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D101" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E101" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52</t>
+        </is>
+      </c>
+      <c r="F101" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تیتو مزمز</t>
+        </is>
+      </c>
+      <c r="G101" s="23">
+        <v>0</v>
+      </c>
+      <c r="H101" s="23">
+        <v>4</v>
+      </c>
+      <c r="I101" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J101" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="28" customHeight="1">
+      <c r="A102" s="16">
+        <v>3</v>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D102" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E102" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52</t>
+        </is>
+      </c>
+      <c r="F102" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تیتو مزمز</t>
+        </is>
+      </c>
+      <c r="G102" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H102" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تیتو مزمز</t>
+        </is>
+      </c>
+      <c r="I102" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J102" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="28" customHeight="1">
+      <c r="A103" s="18">
+        <v>3</v>
+      </c>
+      <c r="B103" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C103" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D103" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E103" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53</t>
+        </is>
+      </c>
+      <c r="F103" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شیر شکلات</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H103" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شیر شکلات</t>
+        </is>
+      </c>
+      <c r="I103" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J103" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="16">
+        <v>3</v>
+      </c>
+      <c r="B104" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C104" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D104" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E104" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="F104" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G104" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H104" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="I104" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J104" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="28" customHeight="1">
+      <c r="A105" s="18">
+        <v>3</v>
+      </c>
+      <c r="B105" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C105" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D105" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E105" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55</t>
+        </is>
+      </c>
+      <c r="F105" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شیر قهوه</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H105" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شیر قهوه</t>
+        </is>
+      </c>
+      <c r="I105" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J105" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="28" customHeight="1">
+      <c r="A106" s="16">
+        <v>3</v>
+      </c>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D106" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E106" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56</t>
+        </is>
+      </c>
+      <c r="F106" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سان استار انبه</t>
+        </is>
+      </c>
+      <c r="G106" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H106" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سان استار انبه</t>
+        </is>
+      </c>
+      <c r="I106" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J106" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="28" customHeight="1">
+      <c r="A107" s="18">
+        <v>3</v>
+      </c>
+      <c r="B107" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C107" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D107" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E107" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57</t>
+        </is>
+      </c>
+      <c r="F107" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سان استار پرتقال</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H107" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سان استار پرتقال</t>
+        </is>
+      </c>
+      <c r="I107" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J107" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="28" customHeight="1">
+      <c r="A108" s="16">
+        <v>3</v>
+      </c>
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C108" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D108" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E108" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58</t>
+        </is>
+      </c>
+      <c r="F108" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وجین</t>
+        </is>
+      </c>
+      <c r="G108" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H108" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وجین</t>
+        </is>
+      </c>
+      <c r="I108" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J108" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="28" customHeight="1">
+      <c r="A109" s="18">
+        <v>3</v>
+      </c>
+      <c r="B109" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C109" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D109" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E109" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61</t>
+        </is>
+      </c>
+      <c r="F109" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="G109" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H109" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="I109" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J109" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="28" customHeight="1">
+      <c r="A110" s="16">
+        <v>3</v>
+      </c>
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C110" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D110" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62</t>
+        </is>
+      </c>
+      <c r="F110" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پرو شیر</t>
+        </is>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>4</v>
+      </c>
+      <c r="I110" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J110" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="18">
+        <v>3</v>
+      </c>
+      <c r="B111" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C111" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D111" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E111" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62</t>
+        </is>
+      </c>
+      <c r="F111" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پرو شیر</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H111" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پرو شیر</t>
+        </is>
+      </c>
+      <c r="I111" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J111" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="A112" s="16">
+        <v>3</v>
+      </c>
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C112" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D112" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E112" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63</t>
+        </is>
+      </c>
+      <c r="F112" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+        </is>
+      </c>
+      <c r="G112" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H112" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+        </is>
+      </c>
+      <c r="I112" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J112" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="28" customHeight="1">
+      <c r="A113" s="18">
+        <v>3</v>
+      </c>
+      <c r="B113" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C113" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D113" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E113" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64</t>
+        </is>
+      </c>
+      <c r="F113" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+        </is>
+      </c>
+      <c r="G113" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H113" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+        </is>
+      </c>
+      <c r="I113" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J113" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="28" customHeight="1">
+      <c r="A114" s="16">
+        <v>3</v>
+      </c>
+      <c r="B114" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C114" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D114" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E114" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65</t>
+        </is>
+      </c>
+      <c r="F114" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
+        </is>
+      </c>
+      <c r="G114" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H114" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
+        </is>
+      </c>
+      <c r="I114" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J114" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="28" customHeight="1">
+      <c r="A115" s="18">
+        <v>3</v>
+      </c>
+      <c r="B115" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C115" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D115" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E115" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66</t>
+        </is>
+      </c>
+      <c r="F115" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G115" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H115" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="I115" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J115" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="28" customHeight="1">
+      <c r="A116" s="16">
+        <v>3</v>
+      </c>
+      <c r="B116" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C116" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D116" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E116" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F116" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>4</v>
+      </c>
+      <c r="I116" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J116" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="28" customHeight="1">
+      <c r="A117" s="18">
+        <v>3</v>
+      </c>
+      <c r="B117" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D117" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E117" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F117" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G117" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H117" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="I117" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J117" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="28" customHeight="1">
+      <c r="A118" s="16">
+        <v>3</v>
+      </c>
+      <c r="B118" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C118" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D118" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E118" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68</t>
+        </is>
+      </c>
+      <c r="F118" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف بدون قند</t>
+        </is>
+      </c>
+      <c r="G118" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H118" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف بدون قند</t>
+        </is>
+      </c>
+      <c r="I118" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J118" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="48" customHeight="1">
+      <c r="A119" s="18">
+        <v>3</v>
+      </c>
+      <c r="B119" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C119" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D119" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">یادداشت و آمار قهوه</t>
+        </is>
+      </c>
+      <c r="E119" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F119" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G119" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H119" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
+        </is>
+      </c>
+      <c r="I119" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J119" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="28" customHeight="1">
+      <c r="A120" s="16">
+        <v>2</v>
+      </c>
+      <c r="B120" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C120" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:16:19</t>
+        </is>
+      </c>
+      <c r="D120" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
+        </is>
+      </c>
+      <c r="E120" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="F120" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تیتاپ نادری</t>
+        </is>
+      </c>
+      <c r="G120" s="22">
+        <v>4</v>
+      </c>
+      <c r="H120" s="22">
+        <v>0</v>
+      </c>
+      <c r="I120" s="20">
+        <v>4</v>
+      </c>
+      <c r="J120" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deac82c691</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="28" customHeight="1">
+      <c r="A121" s="18">
         <v>1</v>
       </c>
-      <c r="B98" s="17" t="inlineStr">
+      <c r="B121" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/23</t>
         </is>
       </c>
-      <c r="C98" s="17" t="inlineStr">
+      <c r="C121" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">22:41:53</t>
         </is>
       </c>
-      <c r="D98" s="17" t="inlineStr">
+      <c r="D121" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E121" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="F121" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تیتاپ نادری</t>
+        </is>
+      </c>
+      <c r="G121" s="23">
+        <v>0</v>
+      </c>
+      <c r="H121" s="23">
+        <v>4</v>
+      </c>
+      <c r="I121" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J121" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="28" customHeight="1">
+      <c r="A122" s="16">
+        <v>1</v>
+      </c>
+      <c r="B122" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C122" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D122" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
-      <c r="E98" s="17" t="inlineStr">
+      <c r="E122" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="F122" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تیتاپ نادری</t>
+        </is>
+      </c>
+      <c r="G122" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H122" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تیتاپ نادری</t>
+        </is>
+      </c>
+      <c r="I122" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J122" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="28" customHeight="1">
+      <c r="A123" s="18">
+        <v>1</v>
+      </c>
+      <c r="B123" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C123" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D123" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E123" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="F123" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G123" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H123" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I123" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J123" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="28" customHeight="1">
+      <c r="A124" s="16">
+        <v>1</v>
+      </c>
+      <c r="B124" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C124" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D124" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E124" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F124" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G124" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H124" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I124" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J124" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="28" customHeight="1">
+      <c r="A125" s="18">
+        <v>1</v>
+      </c>
+      <c r="B125" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C125" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D125" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E125" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F98" s="22" t="inlineStr">
+      <c r="F125" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G98" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H98" s="22" t="inlineStr">
+      <c r="G125" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H125" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I98" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J98" s="17" t="inlineStr">
+      <c r="I125" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J125" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J125" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J125"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J126" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J126"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,38 +508,36 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:24</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G6" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H6" s="22">
         <v>0</v>
       </c>
-      <c r="I6" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I6" s="20">
+        <v>4</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">bd714591b4</t>
         </is>
       </c>
     </row>
@@ -564,16 +562,16 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G7" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H7" s="23">
         <v>0</v>
@@ -610,16 +608,16 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G8" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H8" s="22">
         <v>0</v>
@@ -656,19 +654,19 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" s="23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I9" s="21" t="inlineStr">
         <is>
@@ -702,19 +700,19 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G10" s="22">
         <v>0</v>
       </c>
       <c r="H10" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
@@ -748,12 +746,12 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G11" s="23">
@@ -794,19 +792,19 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G12" s="22">
         <v>0</v>
       </c>
       <c r="H12" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
@@ -840,19 +838,19 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G13" s="23">
         <v>0</v>
       </c>
       <c r="H13" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" s="21" t="inlineStr">
         <is>
@@ -886,19 +884,19 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G14" s="22">
         <v>0</v>
       </c>
       <c r="H14" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
@@ -932,12 +930,12 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G15" s="23">
@@ -978,19 +976,19 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G16" s="22">
         <v>0</v>
       </c>
       <c r="H16" s="22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
@@ -1024,19 +1022,19 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G17" s="23">
         <v>0</v>
       </c>
       <c r="H17" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
@@ -1070,12 +1068,12 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G18" s="22">
@@ -1116,19 +1114,19 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G19" s="23">
         <v>0</v>
       </c>
       <c r="H19" s="23">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
@@ -1162,19 +1160,19 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G20" s="22">
         <v>0</v>
       </c>
       <c r="H20" s="22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
@@ -1208,19 +1206,19 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G21" s="23">
         <v>0</v>
       </c>
       <c r="H21" s="23">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
@@ -1254,19 +1252,19 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G22" s="22">
         <v>0</v>
       </c>
       <c r="H22" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
@@ -1300,19 +1298,19 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G23" s="23">
         <v>0</v>
       </c>
       <c r="H23" s="23">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
@@ -1346,19 +1344,19 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G24" s="22">
         <v>0</v>
       </c>
       <c r="H24" s="22">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -1392,19 +1390,19 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G25" s="23">
         <v>0</v>
       </c>
       <c r="H25" s="23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
@@ -1438,19 +1436,19 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G26" s="22">
         <v>0</v>
       </c>
       <c r="H26" s="22">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
@@ -1484,19 +1482,19 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G27" s="23">
         <v>0</v>
       </c>
       <c r="H27" s="23">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
@@ -1530,19 +1528,19 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G28" s="22">
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -1576,12 +1574,12 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G29" s="23">
@@ -1622,19 +1620,19 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G30" s="22">
         <v>0</v>
       </c>
       <c r="H30" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
@@ -1668,12 +1666,12 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G31" s="23">
@@ -1714,19 +1712,19 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G32" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
@@ -1741,7 +1739,7 @@
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
@@ -1750,7 +1748,7 @@
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
@@ -1760,19 +1758,19 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G33" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
@@ -1781,7 +1779,7 @@
       </c>
       <c r="J33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
@@ -1806,19 +1804,19 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G34" s="22">
         <v>0</v>
       </c>
       <c r="H34" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
@@ -1852,19 +1850,19 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G35" s="23">
         <v>0</v>
       </c>
       <c r="H35" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1898,19 +1896,19 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G36" s="22">
         <v>0</v>
       </c>
       <c r="H36" s="22">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1944,19 +1942,19 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G37" s="23">
         <v>0</v>
       </c>
       <c r="H37" s="23">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1990,128 +1988,130 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G38" s="22">
+        <v>0</v>
+      </c>
+      <c r="H38" s="22">
+        <v>4</v>
+      </c>
+      <c r="I38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J38" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="18">
+        <v>23</v>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:59:31</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">67</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G38" s="22">
-        <v>0</v>
-      </c>
-      <c r="H38" s="22">
+      <c r="G39" s="23">
+        <v>0</v>
+      </c>
+      <c r="H39" s="23">
         <v>1</v>
       </c>
-      <c r="I38" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J38" s="17" t="inlineStr">
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J39" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="48" customHeight="1">
-      <c r="A39" s="18">
+    <row r="40" ht="48" customHeight="1">
+      <c r="A40" s="16">
         <v>22</v>
       </c>
-      <c r="B39" s="19" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
-      <c r="C39" s="19" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
-      <c r="D39" s="19" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E39" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F39" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G39" s="23" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="H39" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I39" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J39" s="19" t="inlineStr">
+      <c r="H40" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J40" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2688d62325</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="16">
-        <v>21</v>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:18:32</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62</t>
-        </is>
-      </c>
-      <c r="F40" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G40" s="22">
-        <v>4</v>
-      </c>
-      <c r="H40" s="22">
-        <v>0</v>
-      </c>
-      <c r="I40" s="20">
-        <v>4</v>
-      </c>
-      <c r="J40" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D41" s="19" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G41" s="23">
@@ -2149,13 +2149,13 @@
       </c>
       <c r="J41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="16">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D42" s="17" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G42" s="22">
@@ -2193,13 +2193,13 @@
       </c>
       <c r="J42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D43" s="19" t="inlineStr">
@@ -2218,32 +2218,32 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G43" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H43" s="23">
         <v>0</v>
       </c>
       <c r="I43" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
@@ -2262,32 +2262,32 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G44" s="22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H44" s="22">
         <v>0</v>
       </c>
       <c r="I44" s="20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D45" s="19" t="inlineStr">
@@ -2306,32 +2306,32 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G45" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H45" s="23">
         <v>0</v>
       </c>
       <c r="I45" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G46" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H46" s="22">
         <v>0</v>
       </c>
       <c r="I46" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D47" s="19" t="inlineStr">
@@ -2394,32 +2394,32 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G47" s="23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H47" s="23">
         <v>0</v>
       </c>
       <c r="I47" s="21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -2438,32 +2438,32 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G48" s="22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H48" s="22">
         <v>0</v>
       </c>
       <c r="I48" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
@@ -2482,32 +2482,32 @@
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G49" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H49" s="23">
         <v>0</v>
       </c>
       <c r="I49" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G50" s="22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H50" s="22">
         <v>0</v>
       </c>
       <c r="I50" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G51" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H51" s="23">
         <v>0</v>
       </c>
       <c r="I51" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -2614,32 +2614,32 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G52" s="22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H52" s="22">
         <v>0</v>
       </c>
       <c r="I52" s="20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D53" s="19" t="inlineStr">
@@ -2658,32 +2658,32 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G53" s="23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H53" s="23">
         <v>0</v>
       </c>
       <c r="I53" s="21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -2702,32 +2702,32 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G54" s="22">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H54" s="22">
         <v>0</v>
       </c>
       <c r="I54" s="20">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -2746,32 +2746,32 @@
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G55" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H55" s="23">
         <v>0</v>
       </c>
       <c r="I55" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -2790,32 +2790,32 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G56" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H56" s="22">
         <v>0</v>
       </c>
       <c r="I56" s="20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -2834,46 +2834,46 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G57" s="23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H57" s="23">
         <v>0</v>
       </c>
       <c r="I57" s="21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E58" s="17" t="inlineStr">
@@ -2887,19 +2887,17 @@
         </is>
       </c>
       <c r="G58" s="22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H58" s="22">
+        <v>0</v>
+      </c>
+      <c r="I58" s="20">
         <v>5</v>
       </c>
-      <c r="I58" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -2924,19 +2922,19 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G59" s="23">
         <v>0</v>
       </c>
       <c r="H59" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I59" s="21" t="inlineStr">
         <is>
@@ -2965,7 +2963,7 @@
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
@@ -2978,15 +2976,11 @@
           <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
-      <c r="G60" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H60" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+      <c r="G60" s="22">
+        <v>0</v>
+      </c>
+      <c r="H60" s="22">
+        <v>3</v>
       </c>
       <c r="I60" s="20" t="inlineStr">
         <is>
@@ -3015,24 +3009,28 @@
       </c>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G61" s="23">
-        <v>0</v>
-      </c>
-      <c r="H61" s="23">
-        <v>6</v>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H61" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
       </c>
       <c r="I61" s="21" t="inlineStr">
         <is>
@@ -3061,7 +3059,7 @@
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
@@ -3074,15 +3072,11 @@
           <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
-      <c r="G62" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H62" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
+      <c r="G62" s="22">
+        <v>0</v>
+      </c>
+      <c r="H62" s="22">
+        <v>6</v>
       </c>
       <c r="I62" s="20" t="inlineStr">
         <is>
@@ -3116,12 +3110,12 @@
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr">
@@ -3131,7 +3125,7 @@
       </c>
       <c r="H63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I63" s="21" t="inlineStr">
@@ -3166,22 +3160,22 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I64" s="20" t="inlineStr">
@@ -3216,12 +3210,12 @@
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr">
@@ -3231,7 +3225,7 @@
       </c>
       <c r="H65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I65" s="21" t="inlineStr">
@@ -3266,12 +3260,12 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G66" s="22" t="inlineStr">
@@ -3281,7 +3275,7 @@
       </c>
       <c r="H66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="I66" s="20" t="inlineStr">
@@ -3311,24 +3305,28 @@
       </c>
       <c r="D67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G67" s="23">
-        <v>0</v>
-      </c>
-      <c r="H67" s="23">
-        <v>3</v>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H67" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
       </c>
       <c r="I67" s="21" t="inlineStr">
         <is>
@@ -3357,7 +3355,7 @@
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
@@ -3370,15 +3368,11 @@
           <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
-      <c r="G68" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H68" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
+      <c r="G68" s="22">
+        <v>0</v>
+      </c>
+      <c r="H68" s="22">
+        <v>3</v>
       </c>
       <c r="I68" s="20" t="inlineStr">
         <is>
@@ -3407,24 +3401,28 @@
       </c>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G69" s="23">
-        <v>0</v>
-      </c>
-      <c r="H69" s="23">
-        <v>3</v>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H69" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
       </c>
       <c r="I69" s="21" t="inlineStr">
         <is>
@@ -3453,7 +3451,7 @@
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
@@ -3466,15 +3464,11 @@
           <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
-      <c r="G70" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H70" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
+      <c r="G70" s="22">
+        <v>0</v>
+      </c>
+      <c r="H70" s="22">
+        <v>3</v>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
@@ -3503,24 +3497,28 @@
       </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G71" s="23">
-        <v>0</v>
-      </c>
-      <c r="H71" s="23">
-        <v>5</v>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H71" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
       </c>
       <c r="I71" s="21" t="inlineStr">
         <is>
@@ -3549,7 +3547,7 @@
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
@@ -3562,15 +3560,11 @@
           <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
-      <c r="G72" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H72" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
+      <c r="G72" s="22">
+        <v>0</v>
+      </c>
+      <c r="H72" s="22">
+        <v>5</v>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
@@ -3599,24 +3593,28 @@
       </c>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="G73" s="23">
-        <v>0</v>
-      </c>
-      <c r="H73" s="23">
-        <v>9</v>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H73" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
       </c>
       <c r="I73" s="21" t="inlineStr">
         <is>
@@ -3645,7 +3643,7 @@
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
@@ -3658,15 +3656,11 @@
           <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
-      <c r="G74" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H74" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
+      <c r="G74" s="22">
+        <v>0</v>
+      </c>
+      <c r="H74" s="22">
+        <v>9</v>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
@@ -3700,12 +3694,12 @@
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -3715,7 +3709,7 @@
       </c>
       <c r="H75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I75" s="21" t="inlineStr">
@@ -3750,12 +3744,12 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G76" s="22" t="inlineStr">
@@ -3765,7 +3759,7 @@
       </c>
       <c r="H76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
@@ -3795,24 +3789,28 @@
       </c>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G77" s="23">
-        <v>0</v>
-      </c>
-      <c r="H77" s="23">
-        <v>6</v>
+          <t xml:space="preserve">وافل</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H77" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وافل</t>
+        </is>
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
@@ -3841,7 +3839,7 @@
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
@@ -3854,15 +3852,11 @@
           <t xml:space="preserve">کوکی</t>
         </is>
       </c>
-      <c r="G78" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H78" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
+      <c r="G78" s="22">
+        <v>0</v>
+      </c>
+      <c r="H78" s="22">
+        <v>6</v>
       </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
@@ -3891,24 +3885,28 @@
       </c>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="G79" s="23">
-        <v>0</v>
-      </c>
-      <c r="H79" s="23">
-        <v>3</v>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H79" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
       </c>
       <c r="I79" s="21" t="inlineStr">
         <is>
@@ -3937,7 +3935,7 @@
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
@@ -3950,15 +3948,11 @@
           <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
-      <c r="G80" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H80" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
+      <c r="G80" s="22">
+        <v>0</v>
+      </c>
+      <c r="H80" s="22">
+        <v>3</v>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
@@ -3992,12 +3986,12 @@
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -4007,7 +4001,7 @@
       </c>
       <c r="H81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="I81" s="21" t="inlineStr">
@@ -4037,24 +4031,28 @@
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G82" s="22">
-        <v>0</v>
-      </c>
-      <c r="H82" s="22">
-        <v>4</v>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H82" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
@@ -4083,7 +4081,7 @@
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
@@ -4096,15 +4094,11 @@
           <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
-      <c r="G83" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H83" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
+      <c r="G83" s="23">
+        <v>0</v>
+      </c>
+      <c r="H83" s="23">
+        <v>4</v>
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
@@ -4133,24 +4127,28 @@
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G84" s="22">
-        <v>0</v>
-      </c>
-      <c r="H84" s="22">
-        <v>6</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H84" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
@@ -4179,7 +4177,7 @@
       </c>
       <c r="D85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
@@ -4192,15 +4190,11 @@
           <t xml:space="preserve">آجیل</t>
         </is>
       </c>
-      <c r="G85" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H85" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+      <c r="G85" s="23">
+        <v>0</v>
+      </c>
+      <c r="H85" s="23">
+        <v>6</v>
       </c>
       <c r="I85" s="21" t="inlineStr">
         <is>
@@ -4229,24 +4223,28 @@
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
-      </c>
-      <c r="G86" s="22">
-        <v>0</v>
-      </c>
-      <c r="H86" s="22">
-        <v>7</v>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H86" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
@@ -4275,7 +4273,7 @@
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
@@ -4288,15 +4286,11 @@
           <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
-      <c r="G87" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H87" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
+      <c r="G87" s="23">
+        <v>0</v>
+      </c>
+      <c r="H87" s="23">
+        <v>7</v>
       </c>
       <c r="I87" s="21" t="inlineStr">
         <is>
@@ -4330,12 +4324,12 @@
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G88" s="22" t="inlineStr">
@@ -4345,7 +4339,7 @@
       </c>
       <c r="H88" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I88" s="20" t="inlineStr">
@@ -4375,24 +4369,28 @@
       </c>
       <c r="D89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G89" s="23">
-        <v>0</v>
-      </c>
-      <c r="H89" s="23">
-        <v>3</v>
+          <t xml:space="preserve">رول رول</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H89" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول</t>
+        </is>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
@@ -4421,7 +4419,7 @@
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
@@ -4434,15 +4432,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G90" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H90" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G90" s="22">
+        <v>0</v>
+      </c>
+      <c r="H90" s="22">
+        <v>3</v>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
@@ -4476,7 +4470,7 @@
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
@@ -4526,7 +4520,7 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F92" s="22" t="inlineStr">
@@ -4576,7 +4570,7 @@
       </c>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
@@ -4626,12 +4620,12 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F94" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G94" s="22" t="inlineStr">
@@ -4641,7 +4635,7 @@
       </c>
       <c r="H94" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I94" s="20" t="inlineStr">
@@ -4676,12 +4670,12 @@
       </c>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -4691,7 +4685,7 @@
       </c>
       <c r="H95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I95" s="21" t="inlineStr">
@@ -4726,12 +4720,12 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="G96" s="22" t="inlineStr">
@@ -4741,7 +4735,7 @@
       </c>
       <c r="H96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="I96" s="20" t="inlineStr">
@@ -4771,24 +4765,28 @@
       </c>
       <c r="D97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G97" s="23">
-        <v>0</v>
-      </c>
-      <c r="H97" s="23">
-        <v>5</v>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
+      </c>
+      <c r="G97" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H97" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
       </c>
       <c r="I97" s="21" t="inlineStr">
         <is>
@@ -4817,7 +4815,7 @@
       </c>
       <c r="D98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E98" s="17" t="inlineStr">
@@ -4830,15 +4828,11 @@
           <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
-      <c r="G98" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H98" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
+      <c r="G98" s="22">
+        <v>0</v>
+      </c>
+      <c r="H98" s="22">
+        <v>5</v>
       </c>
       <c r="I98" s="20" t="inlineStr">
         <is>
@@ -4867,24 +4861,28 @@
       </c>
       <c r="D99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G99" s="23">
-        <v>0</v>
-      </c>
-      <c r="H99" s="23">
-        <v>2</v>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G99" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H99" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
       </c>
       <c r="I99" s="21" t="inlineStr">
         <is>
@@ -4913,7 +4911,7 @@
       </c>
       <c r="D100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
@@ -4926,15 +4924,11 @@
           <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
-      <c r="G100" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H100" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
+      <c r="G100" s="22">
+        <v>0</v>
+      </c>
+      <c r="H100" s="22">
+        <v>2</v>
       </c>
       <c r="I100" s="20" t="inlineStr">
         <is>
@@ -4963,24 +4957,28 @@
       </c>
       <c r="D101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G101" s="23">
-        <v>0</v>
-      </c>
-      <c r="H101" s="23">
-        <v>4</v>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H101" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
       </c>
       <c r="I101" s="21" t="inlineStr">
         <is>
@@ -5009,7 +5007,7 @@
       </c>
       <c r="D102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E102" s="17" t="inlineStr">
@@ -5022,15 +5020,11 @@
           <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
-      <c r="G102" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H102" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
+      <c r="G102" s="22">
+        <v>0</v>
+      </c>
+      <c r="H102" s="22">
+        <v>4</v>
       </c>
       <c r="I102" s="20" t="inlineStr">
         <is>
@@ -5064,12 +5058,12 @@
       </c>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -5079,7 +5073,7 @@
       </c>
       <c r="H103" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I103" s="21" t="inlineStr">
@@ -5114,12 +5108,12 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G104" s="22" t="inlineStr">
@@ -5129,7 +5123,7 @@
       </c>
       <c r="H104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I104" s="20" t="inlineStr">
@@ -5164,12 +5158,12 @@
       </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -5179,7 +5173,7 @@
       </c>
       <c r="H105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I105" s="21" t="inlineStr">
@@ -5214,12 +5208,12 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G106" s="22" t="inlineStr">
@@ -5229,7 +5223,7 @@
       </c>
       <c r="H106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I106" s="20" t="inlineStr">
@@ -5264,12 +5258,12 @@
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -5279,7 +5273,7 @@
       </c>
       <c r="H107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I107" s="21" t="inlineStr">
@@ -5314,12 +5308,12 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G108" s="22" t="inlineStr">
@@ -5329,7 +5323,7 @@
       </c>
       <c r="H108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I108" s="20" t="inlineStr">
@@ -5364,12 +5358,12 @@
       </c>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -5379,7 +5373,7 @@
       </c>
       <c r="H109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="I109" s="21" t="inlineStr">
@@ -5409,24 +5403,28 @@
       </c>
       <c r="D110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G110" s="22">
-        <v>0</v>
-      </c>
-      <c r="H110" s="22">
-        <v>4</v>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="G110" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H110" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
       </c>
       <c r="I110" s="20" t="inlineStr">
         <is>
@@ -5455,7 +5453,7 @@
       </c>
       <c r="D111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E111" s="19" t="inlineStr">
@@ -5468,15 +5466,11 @@
           <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
-      <c r="G111" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H111" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
+      <c r="G111" s="23">
+        <v>0</v>
+      </c>
+      <c r="H111" s="23">
+        <v>4</v>
       </c>
       <c r="I111" s="21" t="inlineStr">
         <is>
@@ -5510,12 +5504,12 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G112" s="22" t="inlineStr">
@@ -5525,7 +5519,7 @@
       </c>
       <c r="H112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I112" s="20" t="inlineStr">
@@ -5560,12 +5554,12 @@
       </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -5575,7 +5569,7 @@
       </c>
       <c r="H113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I113" s="21" t="inlineStr">
@@ -5610,12 +5604,12 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G114" s="22" t="inlineStr">
@@ -5625,7 +5619,7 @@
       </c>
       <c r="H114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I114" s="20" t="inlineStr">
@@ -5660,12 +5654,12 @@
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -5675,7 +5669,7 @@
       </c>
       <c r="H115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="I115" s="21" t="inlineStr">
@@ -5705,24 +5699,28 @@
       </c>
       <c r="D116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G116" s="22">
-        <v>0</v>
-      </c>
-      <c r="H116" s="22">
-        <v>4</v>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G116" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H116" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
       </c>
       <c r="I116" s="20" t="inlineStr">
         <is>
@@ -5751,7 +5749,7 @@
       </c>
       <c r="D117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E117" s="19" t="inlineStr">
@@ -5764,15 +5762,11 @@
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G117" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H117" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
+      <c r="G117" s="23">
+        <v>0</v>
+      </c>
+      <c r="H117" s="23">
+        <v>4</v>
       </c>
       <c r="I117" s="21" t="inlineStr">
         <is>
@@ -5806,132 +5800,138 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F118" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G118" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H118" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="I118" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J118" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="28" customHeight="1">
+      <c r="A119" s="18">
+        <v>3</v>
+      </c>
+      <c r="B119" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C119" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D119" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E119" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">68</t>
         </is>
       </c>
-      <c r="F118" s="22" t="inlineStr">
+      <c r="F119" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="G118" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H118" s="22" t="inlineStr">
+      <c r="G119" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H119" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="I118" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J118" s="17" t="inlineStr">
+      <c r="I119" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J119" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="48" customHeight="1">
-      <c r="A119" s="18">
-        <v>3</v>
-      </c>
-      <c r="B119" s="19" t="inlineStr">
+    <row r="120" ht="48" customHeight="1">
+      <c r="A120" s="16">
+        <v>3</v>
+      </c>
+      <c r="B120" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
-      <c r="C119" s="19" t="inlineStr">
+      <c r="C120" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
-      <c r="D119" s="19" t="inlineStr">
+      <c r="D120" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E119" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F119" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G119" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H119" s="23" t="inlineStr">
+      <c r="E120" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F120" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G120" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H120" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="I119" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J119" s="19" t="inlineStr">
+      <c r="I120" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J120" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="28" customHeight="1">
-      <c r="A120" s="16">
-        <v>2</v>
-      </c>
-      <c r="B120" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/23</t>
-        </is>
-      </c>
-      <c r="C120" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23:16:19</t>
-        </is>
-      </c>
-      <c r="D120" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E120" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="F120" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G120" s="22">
-        <v>4</v>
-      </c>
-      <c r="H120" s="22">
-        <v>0</v>
-      </c>
-      <c r="I120" s="20">
-        <v>4</v>
-      </c>
-      <c r="J120" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
     <row r="121" ht="28" customHeight="1">
       <c r="A121" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B121" s="19" t="inlineStr">
         <is>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="C121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">23:16:19</t>
         </is>
       </c>
       <c r="D121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E121" s="19" t="inlineStr">
@@ -5959,19 +5959,17 @@
         </is>
       </c>
       <c r="G121" s="23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H121" s="23">
+        <v>0</v>
+      </c>
+      <c r="I121" s="21">
         <v>4</v>
       </c>
-      <c r="I121" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5989,7 @@
       </c>
       <c r="D122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E122" s="17" t="inlineStr">
@@ -6004,15 +6002,11 @@
           <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
-      <c r="G122" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H122" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
+      <c r="G122" s="22">
+        <v>0</v>
+      </c>
+      <c r="H122" s="22">
+        <v>4</v>
       </c>
       <c r="I122" s="20" t="inlineStr">
         <is>
@@ -6046,12 +6040,12 @@
       </c>
       <c r="E123" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -6061,7 +6055,7 @@
       </c>
       <c r="H123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="I123" s="21" t="inlineStr">
@@ -6096,7 +6090,7 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F124" s="22" t="inlineStr">
@@ -6146,30 +6140,80 @@
       </c>
       <c r="E125" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F125" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G125" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H125" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I125" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J125" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="28" customHeight="1">
+      <c r="A126" s="16">
+        <v>1</v>
+      </c>
+      <c r="B126" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C126" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D126" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E126" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F125" s="23" t="inlineStr">
+      <c r="F126" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G125" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H125" s="23" t="inlineStr">
+      <c r="G126" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H126" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I125" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J125" s="19" t="inlineStr">
+      <c r="I126" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J126" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J126" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J126"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J127" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J127"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:24</t>
+          <t xml:space="preserve">15:29:38</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -518,32 +518,32 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G6" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H6" s="22">
         <v>0</v>
       </c>
       <c r="I6" s="20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd714591b4</t>
+          <t xml:space="preserve">19f5f6152e</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -552,38 +552,36 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:24</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G7" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H7" s="23">
         <v>0</v>
       </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I7" s="21">
+        <v>4</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">bd714591b4</t>
         </is>
       </c>
     </row>
@@ -608,16 +606,16 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G8" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H8" s="22">
         <v>0</v>
@@ -654,16 +652,16 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9" s="23">
         <v>0</v>
@@ -700,19 +698,19 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G10" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" s="22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
@@ -746,19 +744,19 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G11" s="23">
         <v>0</v>
       </c>
       <c r="H11" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I11" s="21" t="inlineStr">
         <is>
@@ -792,12 +790,12 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G12" s="22">
@@ -838,19 +836,19 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G13" s="23">
         <v>0</v>
       </c>
       <c r="H13" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" s="21" t="inlineStr">
         <is>
@@ -884,19 +882,19 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G14" s="22">
         <v>0</v>
       </c>
       <c r="H14" s="22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
@@ -930,19 +928,19 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G15" s="23">
         <v>0</v>
       </c>
       <c r="H15" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" s="21" t="inlineStr">
         <is>
@@ -976,12 +974,12 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G16" s="22">
@@ -1022,19 +1020,19 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G17" s="23">
         <v>0</v>
       </c>
       <c r="H17" s="23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
@@ -1068,19 +1066,19 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G18" s="22">
         <v>0</v>
       </c>
       <c r="H18" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
@@ -1114,12 +1112,12 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G19" s="23">
@@ -1160,19 +1158,19 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G20" s="22">
         <v>0</v>
       </c>
       <c r="H20" s="22">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
@@ -1206,19 +1204,19 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G21" s="23">
         <v>0</v>
       </c>
       <c r="H21" s="23">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
@@ -1252,19 +1250,19 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G22" s="22">
         <v>0</v>
       </c>
       <c r="H22" s="22">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
@@ -1298,19 +1296,19 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G23" s="23">
         <v>0</v>
       </c>
       <c r="H23" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
@@ -1344,19 +1342,19 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G24" s="22">
         <v>0</v>
       </c>
       <c r="H24" s="22">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -1390,19 +1388,19 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G25" s="23">
         <v>0</v>
       </c>
       <c r="H25" s="23">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
@@ -1436,19 +1434,19 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G26" s="22">
         <v>0</v>
       </c>
       <c r="H26" s="22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
@@ -1482,19 +1480,19 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G27" s="23">
         <v>0</v>
       </c>
       <c r="H27" s="23">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
@@ -1528,19 +1526,19 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G28" s="22">
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -1574,19 +1572,19 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G29" s="23">
         <v>0</v>
       </c>
       <c r="H29" s="23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
@@ -1620,12 +1618,12 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G30" s="22">
@@ -1666,19 +1664,19 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G31" s="23">
         <v>0</v>
       </c>
       <c r="H31" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
@@ -1712,12 +1710,12 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G32" s="22">
@@ -1758,19 +1756,19 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G33" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
@@ -1785,7 +1783,7 @@
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
@@ -1794,7 +1792,7 @@
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
@@ -1804,19 +1802,19 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G34" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
@@ -1825,7 +1823,7 @@
       </c>
       <c r="J34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
@@ -1850,19 +1848,19 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G35" s="23">
         <v>0</v>
       </c>
       <c r="H35" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1896,19 +1894,19 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G36" s="22">
         <v>0</v>
       </c>
       <c r="H36" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1942,19 +1940,19 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G37" s="23">
         <v>0</v>
       </c>
       <c r="H37" s="23">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1988,19 +1986,19 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G38" s="22">
         <v>0</v>
       </c>
       <c r="H38" s="22">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -2034,128 +2032,130 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G39" s="23">
+        <v>0</v>
+      </c>
+      <c r="H39" s="23">
+        <v>4</v>
+      </c>
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J39" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="16">
+        <v>23</v>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:59:31</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">67</t>
         </is>
       </c>
-      <c r="F39" s="23" t="inlineStr">
+      <c r="F40" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G39" s="23">
-        <v>0</v>
-      </c>
-      <c r="H39" s="23">
+      <c r="G40" s="22">
+        <v>0</v>
+      </c>
+      <c r="H40" s="22">
         <v>1</v>
       </c>
-      <c r="I39" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J39" s="19" t="inlineStr">
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J40" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="48" customHeight="1">
-      <c r="A40" s="16">
+    <row r="41" ht="48" customHeight="1">
+      <c r="A41" s="18">
         <v>22</v>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
-      <c r="C40" s="17" t="inlineStr">
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="D41" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F40" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G40" s="22" t="inlineStr">
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G41" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="H40" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I40" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J40" s="17" t="inlineStr">
+      <c r="H41" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I41" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J41" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">2688d62325</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="18">
-        <v>21</v>
-      </c>
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C41" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:18:32</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E41" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62</t>
-        </is>
-      </c>
-      <c r="F41" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G41" s="23">
-        <v>4</v>
-      </c>
-      <c r="H41" s="23">
-        <v>0</v>
-      </c>
-      <c r="I41" s="21">
-        <v>4</v>
-      </c>
-      <c r="J41" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D42" s="17" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G42" s="22">
@@ -2193,13 +2193,13 @@
       </c>
       <c r="J42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="18">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D43" s="19" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G43" s="23">
@@ -2237,13 +2237,13 @@
       </c>
       <c r="J43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
@@ -2262,32 +2262,32 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G44" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H44" s="22">
         <v>0</v>
       </c>
       <c r="I44" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D45" s="19" t="inlineStr">
@@ -2306,32 +2306,32 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G45" s="23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H45" s="23">
         <v>0</v>
       </c>
       <c r="I45" s="21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G46" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H46" s="22">
         <v>0</v>
       </c>
       <c r="I46" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D47" s="19" t="inlineStr">
@@ -2394,32 +2394,32 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G47" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H47" s="23">
         <v>0</v>
       </c>
       <c r="I47" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -2438,32 +2438,32 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G48" s="22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H48" s="22">
         <v>0</v>
       </c>
       <c r="I48" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
@@ -2482,32 +2482,32 @@
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G49" s="23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H49" s="23">
         <v>0</v>
       </c>
       <c r="I49" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G50" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H50" s="22">
         <v>0</v>
       </c>
       <c r="I50" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G51" s="23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H51" s="23">
         <v>0</v>
       </c>
       <c r="I51" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -2614,32 +2614,32 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G52" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H52" s="22">
         <v>0</v>
       </c>
       <c r="I52" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D53" s="19" t="inlineStr">
@@ -2658,32 +2658,32 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G53" s="23">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H53" s="23">
         <v>0</v>
       </c>
       <c r="I53" s="21">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -2702,32 +2702,32 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G54" s="22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H54" s="22">
         <v>0</v>
       </c>
       <c r="I54" s="20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -2746,32 +2746,32 @@
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G55" s="23">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H55" s="23">
         <v>0</v>
       </c>
       <c r="I55" s="21">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -2790,32 +2790,32 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G56" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H56" s="22">
         <v>0</v>
       </c>
       <c r="I56" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -2834,32 +2834,32 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G57" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H57" s="23">
         <v>0</v>
       </c>
       <c r="I57" s="21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -2878,46 +2878,46 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G58" s="22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H58" s="22">
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
@@ -2931,19 +2931,17 @@
         </is>
       </c>
       <c r="G59" s="23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H59" s="23">
+        <v>0</v>
+      </c>
+      <c r="I59" s="21">
         <v>5</v>
       </c>
-      <c r="I59" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -2968,19 +2966,19 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G60" s="22">
         <v>0</v>
       </c>
       <c r="H60" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I60" s="20" t="inlineStr">
         <is>
@@ -3009,7 +3007,7 @@
       </c>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
@@ -3022,15 +3020,11 @@
           <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
-      <c r="G61" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H61" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+      <c r="G61" s="23">
+        <v>0</v>
+      </c>
+      <c r="H61" s="23">
+        <v>3</v>
       </c>
       <c r="I61" s="21" t="inlineStr">
         <is>
@@ -3059,24 +3053,28 @@
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G62" s="22">
-        <v>0</v>
-      </c>
-      <c r="H62" s="22">
-        <v>6</v>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H62" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
       </c>
       <c r="I62" s="20" t="inlineStr">
         <is>
@@ -3105,7 +3103,7 @@
       </c>
       <c r="D63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
@@ -3118,15 +3116,11 @@
           <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
-      <c r="G63" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H63" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
+      <c r="G63" s="23">
+        <v>0</v>
+      </c>
+      <c r="H63" s="23">
+        <v>6</v>
       </c>
       <c r="I63" s="21" t="inlineStr">
         <is>
@@ -3160,12 +3154,12 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G64" s="22" t="inlineStr">
@@ -3175,7 +3169,7 @@
       </c>
       <c r="H64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I64" s="20" t="inlineStr">
@@ -3210,22 +3204,22 @@
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I65" s="21" t="inlineStr">
@@ -3260,12 +3254,12 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G66" s="22" t="inlineStr">
@@ -3275,7 +3269,7 @@
       </c>
       <c r="H66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I66" s="20" t="inlineStr">
@@ -3310,12 +3304,12 @@
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
@@ -3325,7 +3319,7 @@
       </c>
       <c r="H67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="I67" s="21" t="inlineStr">
@@ -3355,24 +3349,28 @@
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G68" s="22">
-        <v>0</v>
-      </c>
-      <c r="H68" s="22">
-        <v>3</v>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H68" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
       </c>
       <c r="I68" s="20" t="inlineStr">
         <is>
@@ -3401,7 +3399,7 @@
       </c>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
@@ -3414,15 +3412,11 @@
           <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
-      <c r="G69" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H69" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
+      <c r="G69" s="23">
+        <v>0</v>
+      </c>
+      <c r="H69" s="23">
+        <v>3</v>
       </c>
       <c r="I69" s="21" t="inlineStr">
         <is>
@@ -3451,24 +3445,28 @@
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G70" s="22">
-        <v>0</v>
-      </c>
-      <c r="H70" s="22">
-        <v>3</v>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H70" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
@@ -3497,7 +3495,7 @@
       </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
@@ -3510,15 +3508,11 @@
           <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
-      <c r="G71" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H71" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
+      <c r="G71" s="23">
+        <v>0</v>
+      </c>
+      <c r="H71" s="23">
+        <v>3</v>
       </c>
       <c r="I71" s="21" t="inlineStr">
         <is>
@@ -3547,24 +3541,28 @@
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G72" s="22">
-        <v>0</v>
-      </c>
-      <c r="H72" s="22">
-        <v>5</v>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H72" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
@@ -3593,7 +3591,7 @@
       </c>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
@@ -3606,15 +3604,11 @@
           <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
-      <c r="G73" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H73" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
+      <c r="G73" s="23">
+        <v>0</v>
+      </c>
+      <c r="H73" s="23">
+        <v>5</v>
       </c>
       <c r="I73" s="21" t="inlineStr">
         <is>
@@ -3643,24 +3637,28 @@
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="G74" s="22">
-        <v>0</v>
-      </c>
-      <c r="H74" s="22">
-        <v>9</v>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H74" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
@@ -3689,7 +3687,7 @@
       </c>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
@@ -3702,15 +3700,11 @@
           <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
-      <c r="G75" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H75" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
+      <c r="G75" s="23">
+        <v>0</v>
+      </c>
+      <c r="H75" s="23">
+        <v>9</v>
       </c>
       <c r="I75" s="21" t="inlineStr">
         <is>
@@ -3744,12 +3738,12 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G76" s="22" t="inlineStr">
@@ -3759,7 +3753,7 @@
       </c>
       <c r="H76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
@@ -3794,12 +3788,12 @@
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
@@ -3809,7 +3803,7 @@
       </c>
       <c r="H77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I77" s="21" t="inlineStr">
@@ -3839,24 +3833,28 @@
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G78" s="22">
-        <v>0</v>
-      </c>
-      <c r="H78" s="22">
-        <v>6</v>
+          <t xml:space="preserve">وافل</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H78" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وافل</t>
+        </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
@@ -3885,7 +3883,7 @@
       </c>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3898,15 +3896,11 @@
           <t xml:space="preserve">کوکی</t>
         </is>
       </c>
-      <c r="G79" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H79" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
+      <c r="G79" s="23">
+        <v>0</v>
+      </c>
+      <c r="H79" s="23">
+        <v>6</v>
       </c>
       <c r="I79" s="21" t="inlineStr">
         <is>
@@ -3935,24 +3929,28 @@
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="G80" s="22">
-        <v>0</v>
-      </c>
-      <c r="H80" s="22">
-        <v>3</v>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H80" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
@@ -3981,7 +3979,7 @@
       </c>
       <c r="D81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
@@ -3994,15 +3992,11 @@
           <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
-      <c r="G81" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H81" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
+      <c r="G81" s="23">
+        <v>0</v>
+      </c>
+      <c r="H81" s="23">
+        <v>3</v>
       </c>
       <c r="I81" s="21" t="inlineStr">
         <is>
@@ -4036,12 +4030,12 @@
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G82" s="22" t="inlineStr">
@@ -4051,7 +4045,7 @@
       </c>
       <c r="H82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
@@ -4081,24 +4075,28 @@
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G83" s="23">
-        <v>0</v>
-      </c>
-      <c r="H83" s="23">
-        <v>4</v>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H83" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
@@ -4127,7 +4125,7 @@
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
@@ -4140,15 +4138,11 @@
           <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
-      <c r="G84" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H84" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
+      <c r="G84" s="22">
+        <v>0</v>
+      </c>
+      <c r="H84" s="22">
+        <v>4</v>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
@@ -4177,24 +4171,28 @@
       </c>
       <c r="D85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G85" s="23">
-        <v>0</v>
-      </c>
-      <c r="H85" s="23">
-        <v>6</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H85" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I85" s="21" t="inlineStr">
         <is>
@@ -4223,7 +4221,7 @@
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
@@ -4236,15 +4234,11 @@
           <t xml:space="preserve">آجیل</t>
         </is>
       </c>
-      <c r="G86" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H86" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+      <c r="G86" s="22">
+        <v>0</v>
+      </c>
+      <c r="H86" s="22">
+        <v>6</v>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
@@ -4273,24 +4267,28 @@
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
-      </c>
-      <c r="G87" s="23">
-        <v>0</v>
-      </c>
-      <c r="H87" s="23">
-        <v>7</v>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
       </c>
       <c r="I87" s="21" t="inlineStr">
         <is>
@@ -4319,7 +4317,7 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
@@ -4332,15 +4330,11 @@
           <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
-      <c r="G88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
+      <c r="G88" s="22">
+        <v>0</v>
+      </c>
+      <c r="H88" s="22">
+        <v>7</v>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
@@ -4374,12 +4368,12 @@
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -4389,7 +4383,7 @@
       </c>
       <c r="H89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I89" s="21" t="inlineStr">
@@ -4419,24 +4413,28 @@
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G90" s="22">
-        <v>0</v>
-      </c>
-      <c r="H90" s="22">
-        <v>3</v>
+          <t xml:space="preserve">رول رول</t>
+        </is>
+      </c>
+      <c r="G90" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H90" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول</t>
+        </is>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
@@ -4465,7 +4463,7 @@
       </c>
       <c r="D91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E91" s="19" t="inlineStr">
@@ -4478,15 +4476,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G91" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H91" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G91" s="23">
+        <v>0</v>
+      </c>
+      <c r="H91" s="23">
+        <v>3</v>
       </c>
       <c r="I91" s="21" t="inlineStr">
         <is>
@@ -4520,7 +4514,7 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F92" s="22" t="inlineStr">
@@ -4570,7 +4564,7 @@
       </c>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
@@ -4620,7 +4614,7 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F94" s="22" t="inlineStr">
@@ -4670,12 +4664,12 @@
       </c>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -4685,7 +4679,7 @@
       </c>
       <c r="H95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I95" s="21" t="inlineStr">
@@ -4720,12 +4714,12 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G96" s="22" t="inlineStr">
@@ -4735,7 +4729,7 @@
       </c>
       <c r="H96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I96" s="20" t="inlineStr">
@@ -4770,12 +4764,12 @@
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -4785,7 +4779,7 @@
       </c>
       <c r="H97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="I97" s="21" t="inlineStr">
@@ -4815,24 +4809,28 @@
       </c>
       <c r="D98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F98" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G98" s="22">
-        <v>0</v>
-      </c>
-      <c r="H98" s="22">
-        <v>5</v>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
+      </c>
+      <c r="G98" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H98" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
       </c>
       <c r="I98" s="20" t="inlineStr">
         <is>
@@ -4861,7 +4859,7 @@
       </c>
       <c r="D99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E99" s="19" t="inlineStr">
@@ -4874,15 +4872,11 @@
           <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
-      <c r="G99" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H99" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
+      <c r="G99" s="23">
+        <v>0</v>
+      </c>
+      <c r="H99" s="23">
+        <v>5</v>
       </c>
       <c r="I99" s="21" t="inlineStr">
         <is>
@@ -4911,24 +4905,28 @@
       </c>
       <c r="D100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G100" s="22">
-        <v>0</v>
-      </c>
-      <c r="H100" s="22">
-        <v>2</v>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G100" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H100" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
       </c>
       <c r="I100" s="20" t="inlineStr">
         <is>
@@ -4957,7 +4955,7 @@
       </c>
       <c r="D101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E101" s="19" t="inlineStr">
@@ -4970,15 +4968,11 @@
           <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
-      <c r="G101" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H101" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
+      <c r="G101" s="23">
+        <v>0</v>
+      </c>
+      <c r="H101" s="23">
+        <v>2</v>
       </c>
       <c r="I101" s="21" t="inlineStr">
         <is>
@@ -5007,24 +5001,28 @@
       </c>
       <c r="D102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F102" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G102" s="22">
-        <v>0</v>
-      </c>
-      <c r="H102" s="22">
-        <v>4</v>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G102" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H102" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
       </c>
       <c r="I102" s="20" t="inlineStr">
         <is>
@@ -5053,7 +5051,7 @@
       </c>
       <c r="D103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E103" s="19" t="inlineStr">
@@ -5066,15 +5064,11 @@
           <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
-      <c r="G103" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H103" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
+      <c r="G103" s="23">
+        <v>0</v>
+      </c>
+      <c r="H103" s="23">
+        <v>4</v>
       </c>
       <c r="I103" s="21" t="inlineStr">
         <is>
@@ -5108,12 +5102,12 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G104" s="22" t="inlineStr">
@@ -5123,7 +5117,7 @@
       </c>
       <c r="H104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I104" s="20" t="inlineStr">
@@ -5158,12 +5152,12 @@
       </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -5173,7 +5167,7 @@
       </c>
       <c r="H105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I105" s="21" t="inlineStr">
@@ -5208,12 +5202,12 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G106" s="22" t="inlineStr">
@@ -5223,7 +5217,7 @@
       </c>
       <c r="H106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I106" s="20" t="inlineStr">
@@ -5258,12 +5252,12 @@
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -5273,7 +5267,7 @@
       </c>
       <c r="H107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I107" s="21" t="inlineStr">
@@ -5308,12 +5302,12 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G108" s="22" t="inlineStr">
@@ -5323,7 +5317,7 @@
       </c>
       <c r="H108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I108" s="20" t="inlineStr">
@@ -5358,12 +5352,12 @@
       </c>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -5373,7 +5367,7 @@
       </c>
       <c r="H109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I109" s="21" t="inlineStr">
@@ -5408,12 +5402,12 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -5423,7 +5417,7 @@
       </c>
       <c r="H110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="I110" s="20" t="inlineStr">
@@ -5453,24 +5447,28 @@
       </c>
       <c r="D111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G111" s="23">
-        <v>0</v>
-      </c>
-      <c r="H111" s="23">
-        <v>4</v>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H111" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
       </c>
       <c r="I111" s="21" t="inlineStr">
         <is>
@@ -5499,7 +5497,7 @@
       </c>
       <c r="D112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E112" s="17" t="inlineStr">
@@ -5512,15 +5510,11 @@
           <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
-      <c r="G112" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H112" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>4</v>
       </c>
       <c r="I112" s="20" t="inlineStr">
         <is>
@@ -5554,12 +5548,12 @@
       </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -5569,7 +5563,7 @@
       </c>
       <c r="H113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I113" s="21" t="inlineStr">
@@ -5604,12 +5598,12 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G114" s="22" t="inlineStr">
@@ -5619,7 +5613,7 @@
       </c>
       <c r="H114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I114" s="20" t="inlineStr">
@@ -5654,12 +5648,12 @@
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -5669,7 +5663,7 @@
       </c>
       <c r="H115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I115" s="21" t="inlineStr">
@@ -5704,12 +5698,12 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="G116" s="22" t="inlineStr">
@@ -5719,7 +5713,7 @@
       </c>
       <c r="H116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="I116" s="20" t="inlineStr">
@@ -5749,24 +5743,28 @@
       </c>
       <c r="D117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G117" s="23">
-        <v>0</v>
-      </c>
-      <c r="H117" s="23">
-        <v>4</v>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G117" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H117" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
       </c>
       <c r="I117" s="21" t="inlineStr">
         <is>
@@ -5795,7 +5793,7 @@
       </c>
       <c r="D118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E118" s="17" t="inlineStr">
@@ -5808,15 +5806,11 @@
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G118" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H118" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
+      <c r="G118" s="22">
+        <v>0</v>
+      </c>
+      <c r="H118" s="22">
+        <v>4</v>
       </c>
       <c r="I118" s="20" t="inlineStr">
         <is>
@@ -5850,132 +5844,138 @@
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F119" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G119" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H119" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="I119" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J119" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="28" customHeight="1">
+      <c r="A120" s="16">
+        <v>3</v>
+      </c>
+      <c r="B120" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C120" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D120" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E120" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">68</t>
         </is>
       </c>
-      <c r="F119" s="23" t="inlineStr">
+      <c r="F120" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="G119" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H119" s="23" t="inlineStr">
+      <c r="G120" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H120" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="I119" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J119" s="19" t="inlineStr">
+      <c r="I120" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J120" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="48" customHeight="1">
-      <c r="A120" s="16">
-        <v>3</v>
-      </c>
-      <c r="B120" s="17" t="inlineStr">
+    <row r="121" ht="48" customHeight="1">
+      <c r="A121" s="18">
+        <v>3</v>
+      </c>
+      <c r="B121" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
-      <c r="C120" s="17" t="inlineStr">
+      <c r="C121" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
-      <c r="D120" s="17" t="inlineStr">
+      <c r="D121" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E120" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F120" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G120" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H120" s="22" t="inlineStr">
+      <c r="E121" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F121" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G121" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H121" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="I120" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J120" s="17" t="inlineStr">
+      <c r="I121" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J121" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="28" customHeight="1">
-      <c r="A121" s="18">
-        <v>2</v>
-      </c>
-      <c r="B121" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/23</t>
-        </is>
-      </c>
-      <c r="C121" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23:16:19</t>
-        </is>
-      </c>
-      <c r="D121" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E121" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="F121" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G121" s="23">
-        <v>4</v>
-      </c>
-      <c r="H121" s="23">
-        <v>0</v>
-      </c>
-      <c r="I121" s="21">
-        <v>4</v>
-      </c>
-      <c r="J121" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
     <row r="122" ht="28" customHeight="1">
       <c r="A122" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="C122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">23:16:19</t>
         </is>
       </c>
       <c r="D122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E122" s="17" t="inlineStr">
@@ -6003,19 +6003,17 @@
         </is>
       </c>
       <c r="G122" s="22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H122" s="22">
+        <v>0</v>
+      </c>
+      <c r="I122" s="20">
         <v>4</v>
       </c>
-      <c r="I122" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6033,7 @@
       </c>
       <c r="D123" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E123" s="19" t="inlineStr">
@@ -6048,15 +6046,11 @@
           <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
-      <c r="G123" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H123" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
+      <c r="G123" s="23">
+        <v>0</v>
+      </c>
+      <c r="H123" s="23">
+        <v>4</v>
       </c>
       <c r="I123" s="21" t="inlineStr">
         <is>
@@ -6090,12 +6084,12 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F124" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G124" s="22" t="inlineStr">
@@ -6105,7 +6099,7 @@
       </c>
       <c r="H124" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="I124" s="20" t="inlineStr">
@@ -6140,7 +6134,7 @@
       </c>
       <c r="E125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
@@ -6190,30 +6184,80 @@
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F126" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G126" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H126" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I126" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J126" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="28" customHeight="1">
+      <c r="A127" s="18">
+        <v>1</v>
+      </c>
+      <c r="B127" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C127" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D127" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E127" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F126" s="22" t="inlineStr">
+      <c r="F127" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G126" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H126" s="22" t="inlineStr">
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H127" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I126" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J126" s="17" t="inlineStr">
+      <c r="I127" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J127" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J127" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J127"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J128" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J128"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:38</t>
+          <t xml:space="preserve">15:29:59</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -518,12 +518,12 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G6" s="22">
@@ -537,13 +537,13 @@
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">19f5f6152e</t>
+          <t xml:space="preserve">d659616819</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:24</t>
+          <t xml:space="preserve">15:29:38</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -562,32 +562,32 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G7" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H7" s="23">
         <v>0</v>
       </c>
       <c r="I7" s="21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd714591b4</t>
+          <t xml:space="preserve">19f5f6152e</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -596,38 +596,36 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:24</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G8" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H8" s="22">
         <v>0</v>
       </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I8" s="20">
+        <v>4</v>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">bd714591b4</t>
         </is>
       </c>
     </row>
@@ -652,16 +650,16 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9" s="23">
         <v>0</v>
@@ -698,16 +696,16 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G10" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" s="22">
         <v>0</v>
@@ -744,19 +742,19 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G11" s="23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" s="23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I11" s="21" t="inlineStr">
         <is>
@@ -790,19 +788,19 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G12" s="22">
         <v>0</v>
       </c>
       <c r="H12" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
@@ -836,12 +834,12 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G13" s="23">
@@ -882,19 +880,19 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G14" s="22">
         <v>0</v>
       </c>
       <c r="H14" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
@@ -928,19 +926,19 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G15" s="23">
         <v>0</v>
       </c>
       <c r="H15" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15" s="21" t="inlineStr">
         <is>
@@ -974,19 +972,19 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G16" s="22">
         <v>0</v>
       </c>
       <c r="H16" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
@@ -1020,12 +1018,12 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G17" s="23">
@@ -1066,19 +1064,19 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G18" s="22">
         <v>0</v>
       </c>
       <c r="H18" s="22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
@@ -1112,19 +1110,19 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G19" s="23">
         <v>0</v>
       </c>
       <c r="H19" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
@@ -1158,12 +1156,12 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G20" s="22">
@@ -1204,19 +1202,19 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G21" s="23">
         <v>0</v>
       </c>
       <c r="H21" s="23">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
@@ -1250,19 +1248,19 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G22" s="22">
         <v>0</v>
       </c>
       <c r="H22" s="22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
@@ -1296,19 +1294,19 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G23" s="23">
         <v>0</v>
       </c>
       <c r="H23" s="23">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
@@ -1342,19 +1340,19 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G24" s="22">
         <v>0</v>
       </c>
       <c r="H24" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -1388,19 +1386,19 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G25" s="23">
         <v>0</v>
       </c>
       <c r="H25" s="23">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
@@ -1434,19 +1432,19 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G26" s="22">
         <v>0</v>
       </c>
       <c r="H26" s="22">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
@@ -1480,19 +1478,19 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G27" s="23">
         <v>0</v>
       </c>
       <c r="H27" s="23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
@@ -1526,19 +1524,19 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G28" s="22">
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -1572,19 +1570,19 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G29" s="23">
         <v>0</v>
       </c>
       <c r="H29" s="23">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
@@ -1618,19 +1616,19 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G30" s="22">
         <v>0</v>
       </c>
       <c r="H30" s="22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
@@ -1664,12 +1662,12 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G31" s="23">
@@ -1710,19 +1708,19 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G32" s="22">
         <v>0</v>
       </c>
       <c r="H32" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
@@ -1756,12 +1754,12 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G33" s="23">
@@ -1802,19 +1800,19 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G34" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
@@ -1829,7 +1827,7 @@
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
@@ -1838,7 +1836,7 @@
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
@@ -1848,19 +1846,19 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G35" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1869,7 +1867,7 @@
       </c>
       <c r="J35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
@@ -1894,19 +1892,19 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G36" s="22">
         <v>0</v>
       </c>
       <c r="H36" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1940,19 +1938,19 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G37" s="23">
         <v>0</v>
       </c>
       <c r="H37" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1986,19 +1984,19 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G38" s="22">
         <v>0</v>
       </c>
       <c r="H38" s="22">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -2032,19 +2030,19 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G39" s="23">
         <v>0</v>
       </c>
       <c r="H39" s="23">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
@@ -2078,128 +2076,130 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G40" s="22">
+        <v>0</v>
+      </c>
+      <c r="H40" s="22">
+        <v>4</v>
+      </c>
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="18">
+        <v>23</v>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:59:31</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">67</t>
         </is>
       </c>
-      <c r="F40" s="22" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G40" s="22">
-        <v>0</v>
-      </c>
-      <c r="H40" s="22">
+      <c r="G41" s="23">
+        <v>0</v>
+      </c>
+      <c r="H41" s="23">
         <v>1</v>
       </c>
-      <c r="I40" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J40" s="17" t="inlineStr">
+      <c r="I41" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J41" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="48" customHeight="1">
-      <c r="A41" s="18">
+    <row r="42" ht="48" customHeight="1">
+      <c r="A42" s="16">
         <v>22</v>
       </c>
-      <c r="B41" s="19" t="inlineStr">
+      <c r="B42" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
-      <c r="C41" s="19" t="inlineStr">
+      <c r="C42" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
-      <c r="D41" s="19" t="inlineStr">
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E41" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F41" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G41" s="23" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G42" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="H41" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I41" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J41" s="19" t="inlineStr">
+      <c r="H42" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I42" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J42" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2688d62325</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="16">
-        <v>21</v>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:18:32</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E42" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62</t>
-        </is>
-      </c>
-      <c r="F42" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G42" s="22">
-        <v>4</v>
-      </c>
-      <c r="H42" s="22">
-        <v>0</v>
-      </c>
-      <c r="I42" s="20">
-        <v>4</v>
-      </c>
-      <c r="J42" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D43" s="19" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G43" s="23">
@@ -2237,13 +2237,13 @@
       </c>
       <c r="J43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="16">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G44" s="22">
@@ -2281,13 +2281,13 @@
       </c>
       <c r="J44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D45" s="19" t="inlineStr">
@@ -2306,32 +2306,32 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G45" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H45" s="23">
         <v>0</v>
       </c>
       <c r="I45" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G46" s="22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H46" s="22">
         <v>0</v>
       </c>
       <c r="I46" s="20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D47" s="19" t="inlineStr">
@@ -2394,32 +2394,32 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G47" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H47" s="23">
         <v>0</v>
       </c>
       <c r="I47" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -2438,32 +2438,32 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G48" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H48" s="22">
         <v>0</v>
       </c>
       <c r="I48" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
@@ -2482,32 +2482,32 @@
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G49" s="23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H49" s="23">
         <v>0</v>
       </c>
       <c r="I49" s="21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G50" s="22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H50" s="22">
         <v>0</v>
       </c>
       <c r="I50" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G51" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H51" s="23">
         <v>0</v>
       </c>
       <c r="I51" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -2614,32 +2614,32 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G52" s="22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H52" s="22">
         <v>0</v>
       </c>
       <c r="I52" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D53" s="19" t="inlineStr">
@@ -2658,32 +2658,32 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G53" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H53" s="23">
         <v>0</v>
       </c>
       <c r="I53" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -2702,32 +2702,32 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G54" s="22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H54" s="22">
         <v>0</v>
       </c>
       <c r="I54" s="20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -2746,32 +2746,32 @@
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G55" s="23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H55" s="23">
         <v>0</v>
       </c>
       <c r="I55" s="21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -2790,32 +2790,32 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G56" s="22">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H56" s="22">
         <v>0</v>
       </c>
       <c r="I56" s="20">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -2834,32 +2834,32 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G57" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H57" s="23">
         <v>0</v>
       </c>
       <c r="I57" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -2878,32 +2878,32 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G58" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H58" s="22">
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -2922,46 +2922,46 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G59" s="23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H59" s="23">
         <v>0</v>
       </c>
       <c r="I59" s="21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
@@ -2975,19 +2975,17 @@
         </is>
       </c>
       <c r="G60" s="22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H60" s="22">
+        <v>0</v>
+      </c>
+      <c r="I60" s="20">
         <v>5</v>
       </c>
-      <c r="I60" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -3012,19 +3010,19 @@
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G61" s="23">
         <v>0</v>
       </c>
       <c r="H61" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I61" s="21" t="inlineStr">
         <is>
@@ -3053,7 +3051,7 @@
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
@@ -3066,15 +3064,11 @@
           <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
-      <c r="G62" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H62" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+      <c r="G62" s="22">
+        <v>0</v>
+      </c>
+      <c r="H62" s="22">
+        <v>3</v>
       </c>
       <c r="I62" s="20" t="inlineStr">
         <is>
@@ -3103,24 +3097,28 @@
       </c>
       <c r="D63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G63" s="23">
-        <v>0</v>
-      </c>
-      <c r="H63" s="23">
-        <v>6</v>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H63" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
       </c>
       <c r="I63" s="21" t="inlineStr">
         <is>
@@ -3149,7 +3147,7 @@
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
@@ -3162,15 +3160,11 @@
           <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
-      <c r="G64" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H64" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
+      <c r="G64" s="22">
+        <v>0</v>
+      </c>
+      <c r="H64" s="22">
+        <v>6</v>
       </c>
       <c r="I64" s="20" t="inlineStr">
         <is>
@@ -3204,12 +3198,12 @@
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr">
@@ -3219,7 +3213,7 @@
       </c>
       <c r="H65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I65" s="21" t="inlineStr">
@@ -3254,22 +3248,22 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I66" s="20" t="inlineStr">
@@ -3304,12 +3298,12 @@
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
@@ -3319,7 +3313,7 @@
       </c>
       <c r="H67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I67" s="21" t="inlineStr">
@@ -3354,12 +3348,12 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G68" s="22" t="inlineStr">
@@ -3369,7 +3363,7 @@
       </c>
       <c r="H68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="I68" s="20" t="inlineStr">
@@ -3399,24 +3393,28 @@
       </c>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G69" s="23">
-        <v>0</v>
-      </c>
-      <c r="H69" s="23">
-        <v>3</v>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H69" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
       </c>
       <c r="I69" s="21" t="inlineStr">
         <is>
@@ -3445,7 +3443,7 @@
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
@@ -3458,15 +3456,11 @@
           <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
-      <c r="G70" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H70" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
+      <c r="G70" s="22">
+        <v>0</v>
+      </c>
+      <c r="H70" s="22">
+        <v>3</v>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
@@ -3495,24 +3489,28 @@
       </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G71" s="23">
-        <v>0</v>
-      </c>
-      <c r="H71" s="23">
-        <v>3</v>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H71" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
       </c>
       <c r="I71" s="21" t="inlineStr">
         <is>
@@ -3541,7 +3539,7 @@
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
@@ -3554,15 +3552,11 @@
           <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
-      <c r="G72" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H72" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
+      <c r="G72" s="22">
+        <v>0</v>
+      </c>
+      <c r="H72" s="22">
+        <v>3</v>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
@@ -3591,24 +3585,28 @@
       </c>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G73" s="23">
-        <v>0</v>
-      </c>
-      <c r="H73" s="23">
-        <v>5</v>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H73" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
       </c>
       <c r="I73" s="21" t="inlineStr">
         <is>
@@ -3637,7 +3635,7 @@
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
@@ -3650,15 +3648,11 @@
           <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
-      <c r="G74" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H74" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
+      <c r="G74" s="22">
+        <v>0</v>
+      </c>
+      <c r="H74" s="22">
+        <v>5</v>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
@@ -3687,24 +3681,28 @@
       </c>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="G75" s="23">
-        <v>0</v>
-      </c>
-      <c r="H75" s="23">
-        <v>9</v>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H75" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
       </c>
       <c r="I75" s="21" t="inlineStr">
         <is>
@@ -3733,7 +3731,7 @@
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
@@ -3746,15 +3744,11 @@
           <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
-      <c r="G76" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H76" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
+      <c r="G76" s="22">
+        <v>0</v>
+      </c>
+      <c r="H76" s="22">
+        <v>9</v>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
@@ -3788,12 +3782,12 @@
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
@@ -3803,7 +3797,7 @@
       </c>
       <c r="H77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I77" s="21" t="inlineStr">
@@ -3838,12 +3832,12 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G78" s="22" t="inlineStr">
@@ -3853,7 +3847,7 @@
       </c>
       <c r="H78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
@@ -3883,24 +3877,28 @@
       </c>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G79" s="23">
-        <v>0</v>
-      </c>
-      <c r="H79" s="23">
-        <v>6</v>
+          <t xml:space="preserve">وافل</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H79" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وافل</t>
+        </is>
       </c>
       <c r="I79" s="21" t="inlineStr">
         <is>
@@ -3929,7 +3927,7 @@
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
@@ -3942,15 +3940,11 @@
           <t xml:space="preserve">کوکی</t>
         </is>
       </c>
-      <c r="G80" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H80" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
+      <c r="G80" s="22">
+        <v>0</v>
+      </c>
+      <c r="H80" s="22">
+        <v>6</v>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
@@ -3979,24 +3973,28 @@
       </c>
       <c r="D81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="G81" s="23">
-        <v>0</v>
-      </c>
-      <c r="H81" s="23">
-        <v>3</v>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H81" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
       </c>
       <c r="I81" s="21" t="inlineStr">
         <is>
@@ -4025,7 +4023,7 @@
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
@@ -4038,15 +4036,11 @@
           <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
-      <c r="G82" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H82" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
+      <c r="G82" s="22">
+        <v>0</v>
+      </c>
+      <c r="H82" s="22">
+        <v>3</v>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
@@ -4080,12 +4074,12 @@
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -4095,7 +4089,7 @@
       </c>
       <c r="H83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="I83" s="21" t="inlineStr">
@@ -4125,24 +4119,28 @@
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G84" s="22">
-        <v>0</v>
-      </c>
-      <c r="H84" s="22">
-        <v>4</v>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H84" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
@@ -4171,7 +4169,7 @@
       </c>
       <c r="D85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
@@ -4184,15 +4182,11 @@
           <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
-      <c r="G85" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H85" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
+      <c r="G85" s="23">
+        <v>0</v>
+      </c>
+      <c r="H85" s="23">
+        <v>4</v>
       </c>
       <c r="I85" s="21" t="inlineStr">
         <is>
@@ -4221,24 +4215,28 @@
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G86" s="22">
-        <v>0</v>
-      </c>
-      <c r="H86" s="22">
-        <v>6</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H86" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
@@ -4267,7 +4265,7 @@
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
@@ -4280,15 +4278,11 @@
           <t xml:space="preserve">آجیل</t>
         </is>
       </c>
-      <c r="G87" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H87" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+      <c r="G87" s="23">
+        <v>0</v>
+      </c>
+      <c r="H87" s="23">
+        <v>6</v>
       </c>
       <c r="I87" s="21" t="inlineStr">
         <is>
@@ -4317,24 +4311,28 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
-      </c>
-      <c r="G88" s="22">
-        <v>0</v>
-      </c>
-      <c r="H88" s="22">
-        <v>7</v>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H88" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
@@ -4363,7 +4361,7 @@
       </c>
       <c r="D89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
@@ -4376,15 +4374,11 @@
           <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
-      <c r="G89" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H89" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
+      <c r="G89" s="23">
+        <v>0</v>
+      </c>
+      <c r="H89" s="23">
+        <v>7</v>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
@@ -4418,12 +4412,12 @@
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G90" s="22" t="inlineStr">
@@ -4433,7 +4427,7 @@
       </c>
       <c r="H90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I90" s="20" t="inlineStr">
@@ -4463,24 +4457,28 @@
       </c>
       <c r="D91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G91" s="23">
-        <v>0</v>
-      </c>
-      <c r="H91" s="23">
-        <v>3</v>
+          <t xml:space="preserve">رول رول</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H91" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول</t>
+        </is>
       </c>
       <c r="I91" s="21" t="inlineStr">
         <is>
@@ -4509,7 +4507,7 @@
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
@@ -4522,15 +4520,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G92" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H92" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G92" s="22">
+        <v>0</v>
+      </c>
+      <c r="H92" s="22">
+        <v>3</v>
       </c>
       <c r="I92" s="20" t="inlineStr">
         <is>
@@ -4564,7 +4558,7 @@
       </c>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
@@ -4614,7 +4608,7 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F94" s="22" t="inlineStr">
@@ -4664,7 +4658,7 @@
       </c>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
@@ -4714,12 +4708,12 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G96" s="22" t="inlineStr">
@@ -4729,7 +4723,7 @@
       </c>
       <c r="H96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I96" s="20" t="inlineStr">
@@ -4764,12 +4758,12 @@
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -4779,7 +4773,7 @@
       </c>
       <c r="H97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I97" s="21" t="inlineStr">
@@ -4814,12 +4808,12 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F98" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="G98" s="22" t="inlineStr">
@@ -4829,7 +4823,7 @@
       </c>
       <c r="H98" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="I98" s="20" t="inlineStr">
@@ -4859,24 +4853,28 @@
       </c>
       <c r="D99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G99" s="23">
-        <v>0</v>
-      </c>
-      <c r="H99" s="23">
-        <v>5</v>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
+      </c>
+      <c r="G99" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H99" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
       </c>
       <c r="I99" s="21" t="inlineStr">
         <is>
@@ -4905,7 +4903,7 @@
       </c>
       <c r="D100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
@@ -4918,15 +4916,11 @@
           <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
-      <c r="G100" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H100" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
+      <c r="G100" s="22">
+        <v>0</v>
+      </c>
+      <c r="H100" s="22">
+        <v>5</v>
       </c>
       <c r="I100" s="20" t="inlineStr">
         <is>
@@ -4955,24 +4949,28 @@
       </c>
       <c r="D101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G101" s="23">
-        <v>0</v>
-      </c>
-      <c r="H101" s="23">
-        <v>2</v>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H101" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
       </c>
       <c r="I101" s="21" t="inlineStr">
         <is>
@@ -5001,7 +4999,7 @@
       </c>
       <c r="D102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E102" s="17" t="inlineStr">
@@ -5014,15 +5012,11 @@
           <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
-      <c r="G102" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H102" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
+      <c r="G102" s="22">
+        <v>0</v>
+      </c>
+      <c r="H102" s="22">
+        <v>2</v>
       </c>
       <c r="I102" s="20" t="inlineStr">
         <is>
@@ -5051,24 +5045,28 @@
       </c>
       <c r="D103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G103" s="23">
-        <v>0</v>
-      </c>
-      <c r="H103" s="23">
-        <v>4</v>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H103" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
       </c>
       <c r="I103" s="21" t="inlineStr">
         <is>
@@ -5097,7 +5095,7 @@
       </c>
       <c r="D104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E104" s="17" t="inlineStr">
@@ -5110,15 +5108,11 @@
           <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
-      <c r="G104" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H104" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
+      <c r="G104" s="22">
+        <v>0</v>
+      </c>
+      <c r="H104" s="22">
+        <v>4</v>
       </c>
       <c r="I104" s="20" t="inlineStr">
         <is>
@@ -5152,12 +5146,12 @@
       </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -5167,7 +5161,7 @@
       </c>
       <c r="H105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I105" s="21" t="inlineStr">
@@ -5202,12 +5196,12 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G106" s="22" t="inlineStr">
@@ -5217,7 +5211,7 @@
       </c>
       <c r="H106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I106" s="20" t="inlineStr">
@@ -5252,12 +5246,12 @@
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -5267,7 +5261,7 @@
       </c>
       <c r="H107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I107" s="21" t="inlineStr">
@@ -5302,12 +5296,12 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G108" s="22" t="inlineStr">
@@ -5317,7 +5311,7 @@
       </c>
       <c r="H108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I108" s="20" t="inlineStr">
@@ -5352,12 +5346,12 @@
       </c>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -5367,7 +5361,7 @@
       </c>
       <c r="H109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I109" s="21" t="inlineStr">
@@ -5402,12 +5396,12 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -5417,7 +5411,7 @@
       </c>
       <c r="H110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I110" s="20" t="inlineStr">
@@ -5452,12 +5446,12 @@
       </c>
       <c r="E111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -5467,7 +5461,7 @@
       </c>
       <c r="H111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="I111" s="21" t="inlineStr">
@@ -5497,24 +5491,28 @@
       </c>
       <c r="D112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G112" s="22">
-        <v>0</v>
-      </c>
-      <c r="H112" s="22">
-        <v>4</v>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="G112" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H112" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
       </c>
       <c r="I112" s="20" t="inlineStr">
         <is>
@@ -5543,7 +5541,7 @@
       </c>
       <c r="D113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E113" s="19" t="inlineStr">
@@ -5556,15 +5554,11 @@
           <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
-      <c r="G113" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H113" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
+      <c r="G113" s="23">
+        <v>0</v>
+      </c>
+      <c r="H113" s="23">
+        <v>4</v>
       </c>
       <c r="I113" s="21" t="inlineStr">
         <is>
@@ -5598,12 +5592,12 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G114" s="22" t="inlineStr">
@@ -5613,7 +5607,7 @@
       </c>
       <c r="H114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I114" s="20" t="inlineStr">
@@ -5648,12 +5642,12 @@
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -5663,7 +5657,7 @@
       </c>
       <c r="H115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I115" s="21" t="inlineStr">
@@ -5698,12 +5692,12 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G116" s="22" t="inlineStr">
@@ -5713,7 +5707,7 @@
       </c>
       <c r="H116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I116" s="20" t="inlineStr">
@@ -5748,12 +5742,12 @@
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -5763,7 +5757,7 @@
       </c>
       <c r="H117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="I117" s="21" t="inlineStr">
@@ -5793,24 +5787,28 @@
       </c>
       <c r="D118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G118" s="22">
-        <v>0</v>
-      </c>
-      <c r="H118" s="22">
-        <v>4</v>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G118" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H118" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
       </c>
       <c r="I118" s="20" t="inlineStr">
         <is>
@@ -5839,7 +5837,7 @@
       </c>
       <c r="D119" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E119" s="19" t="inlineStr">
@@ -5852,15 +5850,11 @@
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G119" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H119" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
+      <c r="G119" s="23">
+        <v>0</v>
+      </c>
+      <c r="H119" s="23">
+        <v>4</v>
       </c>
       <c r="I119" s="21" t="inlineStr">
         <is>
@@ -5894,132 +5888,138 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F120" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G120" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H120" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="I120" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J120" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="28" customHeight="1">
+      <c r="A121" s="18">
+        <v>3</v>
+      </c>
+      <c r="B121" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C121" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D121" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E121" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">68</t>
         </is>
       </c>
-      <c r="F120" s="22" t="inlineStr">
+      <c r="F121" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="G120" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H120" s="22" t="inlineStr">
+      <c r="G121" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H121" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="I120" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J120" s="17" t="inlineStr">
+      <c r="I121" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J121" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="48" customHeight="1">
-      <c r="A121" s="18">
-        <v>3</v>
-      </c>
-      <c r="B121" s="19" t="inlineStr">
+    <row r="122" ht="48" customHeight="1">
+      <c r="A122" s="16">
+        <v>3</v>
+      </c>
+      <c r="B122" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
-      <c r="C121" s="19" t="inlineStr">
+      <c r="C122" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
-      <c r="D121" s="19" t="inlineStr">
+      <c r="D122" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E121" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F121" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G121" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H121" s="23" t="inlineStr">
+      <c r="E122" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F122" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G122" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H122" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="I121" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J121" s="19" t="inlineStr">
+      <c r="I122" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J122" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="28" customHeight="1">
-      <c r="A122" s="16">
-        <v>2</v>
-      </c>
-      <c r="B122" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/23</t>
-        </is>
-      </c>
-      <c r="C122" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23:16:19</t>
-        </is>
-      </c>
-      <c r="D122" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E122" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="F122" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G122" s="22">
-        <v>4</v>
-      </c>
-      <c r="H122" s="22">
-        <v>0</v>
-      </c>
-      <c r="I122" s="20">
-        <v>4</v>
-      </c>
-      <c r="J122" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
     <row r="123" ht="28" customHeight="1">
       <c r="A123" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B123" s="19" t="inlineStr">
         <is>
@@ -6028,12 +6028,12 @@
       </c>
       <c r="C123" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">23:16:19</t>
         </is>
       </c>
       <c r="D123" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E123" s="19" t="inlineStr">
@@ -6047,19 +6047,17 @@
         </is>
       </c>
       <c r="G123" s="23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H123" s="23">
+        <v>0</v>
+      </c>
+      <c r="I123" s="21">
         <v>4</v>
       </c>
-      <c r="I123" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J123" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6077,7 @@
       </c>
       <c r="D124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E124" s="17" t="inlineStr">
@@ -6092,15 +6090,11 @@
           <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
-      <c r="G124" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H124" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
+      <c r="G124" s="22">
+        <v>0</v>
+      </c>
+      <c r="H124" s="22">
+        <v>4</v>
       </c>
       <c r="I124" s="20" t="inlineStr">
         <is>
@@ -6134,12 +6128,12 @@
       </c>
       <c r="E125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -6149,7 +6143,7 @@
       </c>
       <c r="H125" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="I125" s="21" t="inlineStr">
@@ -6184,7 +6178,7 @@
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F126" s="22" t="inlineStr">
@@ -6234,30 +6228,80 @@
       </c>
       <c r="E127" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F127" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H127" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I127" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J127" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="28" customHeight="1">
+      <c r="A128" s="16">
+        <v>1</v>
+      </c>
+      <c r="B128" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C128" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D128" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E128" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F127" s="23" t="inlineStr">
+      <c r="F128" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G127" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H127" s="23" t="inlineStr">
+      <c r="G128" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H128" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I127" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J127" s="19" t="inlineStr">
+      <c r="I128" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J128" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J128" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J128"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J129" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J129"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:59</t>
+          <t xml:space="preserve">15:30:35</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -518,32 +518,32 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G6" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H6" s="22">
         <v>0</v>
       </c>
       <c r="I6" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">d659616819</t>
+          <t xml:space="preserve">ed45f1ef47</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:38</t>
+          <t xml:space="preserve">15:29:59</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G7" s="23">
@@ -581,13 +581,13 @@
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">19f5f6152e</t>
+          <t xml:space="preserve">d659616819</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:24</t>
+          <t xml:space="preserve">15:29:38</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -606,32 +606,32 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G8" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H8" s="22">
         <v>0</v>
       </c>
       <c r="I8" s="20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd714591b4</t>
+          <t xml:space="preserve">19f5f6152e</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -640,38 +640,36 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:24</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9" s="23">
         <v>0</v>
       </c>
-      <c r="I9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I9" s="21">
+        <v>4</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">bd714591b4</t>
         </is>
       </c>
     </row>
@@ -696,16 +694,16 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G10" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10" s="22">
         <v>0</v>
@@ -742,16 +740,16 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G11" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11" s="23">
         <v>0</v>
@@ -788,19 +786,19 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G12" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" s="22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
@@ -834,19 +832,19 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G13" s="23">
         <v>0</v>
       </c>
       <c r="H13" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I13" s="21" t="inlineStr">
         <is>
@@ -880,12 +878,12 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G14" s="22">
@@ -926,19 +924,19 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G15" s="23">
         <v>0</v>
       </c>
       <c r="H15" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" s="21" t="inlineStr">
         <is>
@@ -972,19 +970,19 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G16" s="22">
         <v>0</v>
       </c>
       <c r="H16" s="22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
@@ -1018,19 +1016,19 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G17" s="23">
         <v>0</v>
       </c>
       <c r="H17" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
@@ -1064,12 +1062,12 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G18" s="22">
@@ -1110,19 +1108,19 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G19" s="23">
         <v>0</v>
       </c>
       <c r="H19" s="23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
@@ -1156,19 +1154,19 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G20" s="22">
         <v>0</v>
       </c>
       <c r="H20" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
@@ -1202,12 +1200,12 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G21" s="23">
@@ -1248,19 +1246,19 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G22" s="22">
         <v>0</v>
       </c>
       <c r="H22" s="22">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
@@ -1294,19 +1292,19 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G23" s="23">
         <v>0</v>
       </c>
       <c r="H23" s="23">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
@@ -1340,19 +1338,19 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G24" s="22">
         <v>0</v>
       </c>
       <c r="H24" s="22">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -1386,19 +1384,19 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G25" s="23">
         <v>0</v>
       </c>
       <c r="H25" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
@@ -1432,19 +1430,19 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G26" s="22">
         <v>0</v>
       </c>
       <c r="H26" s="22">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
@@ -1478,19 +1476,19 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G27" s="23">
         <v>0</v>
       </c>
       <c r="H27" s="23">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
@@ -1524,19 +1522,19 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G28" s="22">
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -1570,19 +1568,19 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G29" s="23">
         <v>0</v>
       </c>
       <c r="H29" s="23">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
@@ -1616,19 +1614,19 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G30" s="22">
         <v>0</v>
       </c>
       <c r="H30" s="22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
@@ -1662,19 +1660,19 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G31" s="23">
         <v>0</v>
       </c>
       <c r="H31" s="23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
@@ -1708,12 +1706,12 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G32" s="22">
@@ -1754,19 +1752,19 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G33" s="23">
         <v>0</v>
       </c>
       <c r="H33" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
@@ -1800,12 +1798,12 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G34" s="22">
@@ -1846,19 +1844,19 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G35" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1873,7 +1871,7 @@
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
@@ -1882,7 +1880,7 @@
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D36" s="17" t="inlineStr">
@@ -1892,19 +1890,19 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G36" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1913,7 +1911,7 @@
       </c>
       <c r="J36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
@@ -1938,19 +1936,19 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G37" s="23">
         <v>0</v>
       </c>
       <c r="H37" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1984,19 +1982,19 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G38" s="22">
         <v>0</v>
       </c>
       <c r="H38" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -2030,19 +2028,19 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G39" s="23">
         <v>0</v>
       </c>
       <c r="H39" s="23">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
@@ -2076,19 +2074,19 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G40" s="22">
         <v>0</v>
       </c>
       <c r="H40" s="22">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
@@ -2122,128 +2120,130 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G41" s="23">
+        <v>0</v>
+      </c>
+      <c r="H41" s="23">
+        <v>4</v>
+      </c>
+      <c r="I41" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J41" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="16">
+        <v>23</v>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:59:31</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">67</t>
         </is>
       </c>
-      <c r="F41" s="23" t="inlineStr">
+      <c r="F42" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G41" s="23">
-        <v>0</v>
-      </c>
-      <c r="H41" s="23">
+      <c r="G42" s="22">
+        <v>0</v>
+      </c>
+      <c r="H42" s="22">
         <v>1</v>
       </c>
-      <c r="I41" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J41" s="19" t="inlineStr">
+      <c r="I42" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J42" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="48" customHeight="1">
-      <c r="A42" s="16">
+    <row r="43" ht="48" customHeight="1">
+      <c r="A43" s="18">
         <v>22</v>
       </c>
-      <c r="B42" s="17" t="inlineStr">
+      <c r="B43" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
-      <c r="C42" s="17" t="inlineStr">
+      <c r="C43" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="D43" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F42" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G42" s="22" t="inlineStr">
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="H42" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I42" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J42" s="17" t="inlineStr">
+      <c r="H43" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I43" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">2688d62325</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="18">
-        <v>21</v>
-      </c>
-      <c r="B43" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C43" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:18:32</t>
-        </is>
-      </c>
-      <c r="D43" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E43" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62</t>
-        </is>
-      </c>
-      <c r="F43" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G43" s="23">
-        <v>4</v>
-      </c>
-      <c r="H43" s="23">
-        <v>0</v>
-      </c>
-      <c r="I43" s="21">
-        <v>4</v>
-      </c>
-      <c r="J43" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G44" s="22">
@@ -2281,13 +2281,13 @@
       </c>
       <c r="J44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="18">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D45" s="19" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G45" s="23">
@@ -2325,13 +2325,13 @@
       </c>
       <c r="J45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G46" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H46" s="22">
         <v>0</v>
       </c>
       <c r="I46" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D47" s="19" t="inlineStr">
@@ -2394,32 +2394,32 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G47" s="23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H47" s="23">
         <v>0</v>
       </c>
       <c r="I47" s="21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -2438,32 +2438,32 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G48" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H48" s="22">
         <v>0</v>
       </c>
       <c r="I48" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
@@ -2482,32 +2482,32 @@
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G49" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H49" s="23">
         <v>0</v>
       </c>
       <c r="I49" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G50" s="22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H50" s="22">
         <v>0</v>
       </c>
       <c r="I50" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G51" s="23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H51" s="23">
         <v>0</v>
       </c>
       <c r="I51" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -2614,32 +2614,32 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G52" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H52" s="22">
         <v>0</v>
       </c>
       <c r="I52" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D53" s="19" t="inlineStr">
@@ -2658,32 +2658,32 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G53" s="23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H53" s="23">
         <v>0</v>
       </c>
       <c r="I53" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -2702,32 +2702,32 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G54" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H54" s="22">
         <v>0</v>
       </c>
       <c r="I54" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -2746,32 +2746,32 @@
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G55" s="23">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H55" s="23">
         <v>0</v>
       </c>
       <c r="I55" s="21">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -2790,32 +2790,32 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G56" s="22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H56" s="22">
         <v>0</v>
       </c>
       <c r="I56" s="20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -2834,32 +2834,32 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G57" s="23">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H57" s="23">
         <v>0</v>
       </c>
       <c r="I57" s="21">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -2878,32 +2878,32 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G58" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H58" s="22">
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -2922,32 +2922,32 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G59" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H59" s="23">
         <v>0</v>
       </c>
       <c r="I59" s="21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
@@ -2966,46 +2966,46 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G60" s="22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H60" s="22">
         <v>0</v>
       </c>
       <c r="I60" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
@@ -3019,19 +3019,17 @@
         </is>
       </c>
       <c r="G61" s="23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H61" s="23">
+        <v>0</v>
+      </c>
+      <c r="I61" s="21">
         <v>5</v>
       </c>
-      <c r="I61" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -3056,19 +3054,19 @@
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G62" s="22">
         <v>0</v>
       </c>
       <c r="H62" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I62" s="20" t="inlineStr">
         <is>
@@ -3097,7 +3095,7 @@
       </c>
       <c r="D63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
@@ -3110,15 +3108,11 @@
           <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
-      <c r="G63" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H63" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+      <c r="G63" s="23">
+        <v>0</v>
+      </c>
+      <c r="H63" s="23">
+        <v>3</v>
       </c>
       <c r="I63" s="21" t="inlineStr">
         <is>
@@ -3147,24 +3141,28 @@
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G64" s="22">
-        <v>0</v>
-      </c>
-      <c r="H64" s="22">
-        <v>6</v>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H64" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
       </c>
       <c r="I64" s="20" t="inlineStr">
         <is>
@@ -3193,7 +3191,7 @@
       </c>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
@@ -3206,15 +3204,11 @@
           <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
-      <c r="G65" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H65" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
+      <c r="G65" s="23">
+        <v>0</v>
+      </c>
+      <c r="H65" s="23">
+        <v>6</v>
       </c>
       <c r="I65" s="21" t="inlineStr">
         <is>
@@ -3248,12 +3242,12 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G66" s="22" t="inlineStr">
@@ -3263,7 +3257,7 @@
       </c>
       <c r="H66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I66" s="20" t="inlineStr">
@@ -3298,22 +3292,22 @@
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I67" s="21" t="inlineStr">
@@ -3348,12 +3342,12 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G68" s="22" t="inlineStr">
@@ -3363,7 +3357,7 @@
       </c>
       <c r="H68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I68" s="20" t="inlineStr">
@@ -3398,12 +3392,12 @@
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
@@ -3413,7 +3407,7 @@
       </c>
       <c r="H69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="I69" s="21" t="inlineStr">
@@ -3443,24 +3437,28 @@
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G70" s="22">
-        <v>0</v>
-      </c>
-      <c r="H70" s="22">
-        <v>3</v>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H70" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
@@ -3489,7 +3487,7 @@
       </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
@@ -3502,15 +3500,11 @@
           <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
-      <c r="G71" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H71" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
+      <c r="G71" s="23">
+        <v>0</v>
+      </c>
+      <c r="H71" s="23">
+        <v>3</v>
       </c>
       <c r="I71" s="21" t="inlineStr">
         <is>
@@ -3539,24 +3533,28 @@
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G72" s="22">
-        <v>0</v>
-      </c>
-      <c r="H72" s="22">
-        <v>3</v>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H72" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
@@ -3585,7 +3583,7 @@
       </c>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
@@ -3598,15 +3596,11 @@
           <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
-      <c r="G73" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H73" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
+      <c r="G73" s="23">
+        <v>0</v>
+      </c>
+      <c r="H73" s="23">
+        <v>3</v>
       </c>
       <c r="I73" s="21" t="inlineStr">
         <is>
@@ -3635,24 +3629,28 @@
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G74" s="22">
-        <v>0</v>
-      </c>
-      <c r="H74" s="22">
-        <v>5</v>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H74" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
@@ -3681,7 +3679,7 @@
       </c>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
@@ -3694,15 +3692,11 @@
           <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
-      <c r="G75" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H75" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
+      <c r="G75" s="23">
+        <v>0</v>
+      </c>
+      <c r="H75" s="23">
+        <v>5</v>
       </c>
       <c r="I75" s="21" t="inlineStr">
         <is>
@@ -3731,24 +3725,28 @@
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="G76" s="22">
-        <v>0</v>
-      </c>
-      <c r="H76" s="22">
-        <v>9</v>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H76" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
@@ -3777,7 +3775,7 @@
       </c>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
@@ -3790,15 +3788,11 @@
           <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
-      <c r="G77" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H77" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
+      <c r="G77" s="23">
+        <v>0</v>
+      </c>
+      <c r="H77" s="23">
+        <v>9</v>
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
@@ -3832,12 +3826,12 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G78" s="22" t="inlineStr">
@@ -3847,7 +3841,7 @@
       </c>
       <c r="H78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
@@ -3882,12 +3876,12 @@
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -3897,7 +3891,7 @@
       </c>
       <c r="H79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I79" s="21" t="inlineStr">
@@ -3927,24 +3921,28 @@
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G80" s="22">
-        <v>0</v>
-      </c>
-      <c r="H80" s="22">
-        <v>6</v>
+          <t xml:space="preserve">وافل</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H80" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وافل</t>
+        </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
@@ -3973,7 +3971,7 @@
       </c>
       <c r="D81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
@@ -3986,15 +3984,11 @@
           <t xml:space="preserve">کوکی</t>
         </is>
       </c>
-      <c r="G81" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H81" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
+      <c r="G81" s="23">
+        <v>0</v>
+      </c>
+      <c r="H81" s="23">
+        <v>6</v>
       </c>
       <c r="I81" s="21" t="inlineStr">
         <is>
@@ -4023,24 +4017,28 @@
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="G82" s="22">
-        <v>0</v>
-      </c>
-      <c r="H82" s="22">
-        <v>3</v>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H82" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
@@ -4069,7 +4067,7 @@
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
@@ -4082,15 +4080,11 @@
           <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
-      <c r="G83" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H83" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
+      <c r="G83" s="23">
+        <v>0</v>
+      </c>
+      <c r="H83" s="23">
+        <v>3</v>
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
@@ -4124,12 +4118,12 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G84" s="22" t="inlineStr">
@@ -4139,7 +4133,7 @@
       </c>
       <c r="H84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="I84" s="20" t="inlineStr">
@@ -4169,24 +4163,28 @@
       </c>
       <c r="D85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G85" s="23">
-        <v>0</v>
-      </c>
-      <c r="H85" s="23">
-        <v>4</v>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H85" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
       </c>
       <c r="I85" s="21" t="inlineStr">
         <is>
@@ -4215,7 +4213,7 @@
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
@@ -4228,15 +4226,11 @@
           <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
-      <c r="G86" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H86" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
+      <c r="G86" s="22">
+        <v>0</v>
+      </c>
+      <c r="H86" s="22">
+        <v>4</v>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
@@ -4265,24 +4259,28 @@
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G87" s="23">
-        <v>0</v>
-      </c>
-      <c r="H87" s="23">
-        <v>6</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I87" s="21" t="inlineStr">
         <is>
@@ -4311,7 +4309,7 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
@@ -4324,15 +4322,11 @@
           <t xml:space="preserve">آجیل</t>
         </is>
       </c>
-      <c r="G88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+      <c r="G88" s="22">
+        <v>0</v>
+      </c>
+      <c r="H88" s="22">
+        <v>6</v>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
@@ -4361,24 +4355,28 @@
       </c>
       <c r="D89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
-      </c>
-      <c r="G89" s="23">
-        <v>0</v>
-      </c>
-      <c r="H89" s="23">
-        <v>7</v>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H89" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
@@ -4407,7 +4405,7 @@
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
@@ -4420,15 +4418,11 @@
           <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
-      <c r="G90" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H90" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
+      <c r="G90" s="22">
+        <v>0</v>
+      </c>
+      <c r="H90" s="22">
+        <v>7</v>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
@@ -4462,12 +4456,12 @@
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -4477,7 +4471,7 @@
       </c>
       <c r="H91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I91" s="21" t="inlineStr">
@@ -4507,24 +4501,28 @@
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F92" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G92" s="22">
-        <v>0</v>
-      </c>
-      <c r="H92" s="22">
-        <v>3</v>
+          <t xml:space="preserve">رول رول</t>
+        </is>
+      </c>
+      <c r="G92" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H92" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول</t>
+        </is>
       </c>
       <c r="I92" s="20" t="inlineStr">
         <is>
@@ -4553,7 +4551,7 @@
       </c>
       <c r="D93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E93" s="19" t="inlineStr">
@@ -4566,15 +4564,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G93" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H93" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G93" s="23">
+        <v>0</v>
+      </c>
+      <c r="H93" s="23">
+        <v>3</v>
       </c>
       <c r="I93" s="21" t="inlineStr">
         <is>
@@ -4608,7 +4602,7 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F94" s="22" t="inlineStr">
@@ -4658,7 +4652,7 @@
       </c>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
@@ -4708,7 +4702,7 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
@@ -4758,12 +4752,12 @@
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -4773,7 +4767,7 @@
       </c>
       <c r="H97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I97" s="21" t="inlineStr">
@@ -4808,12 +4802,12 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F98" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G98" s="22" t="inlineStr">
@@ -4823,7 +4817,7 @@
       </c>
       <c r="H98" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I98" s="20" t="inlineStr">
@@ -4858,12 +4852,12 @@
       </c>
       <c r="E99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -4873,7 +4867,7 @@
       </c>
       <c r="H99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="I99" s="21" t="inlineStr">
@@ -4903,24 +4897,28 @@
       </c>
       <c r="D100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G100" s="22">
-        <v>0</v>
-      </c>
-      <c r="H100" s="22">
-        <v>5</v>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
+      </c>
+      <c r="G100" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H100" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
       </c>
       <c r="I100" s="20" t="inlineStr">
         <is>
@@ -4949,7 +4947,7 @@
       </c>
       <c r="D101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E101" s="19" t="inlineStr">
@@ -4962,15 +4960,11 @@
           <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
-      <c r="G101" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H101" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
+      <c r="G101" s="23">
+        <v>0</v>
+      </c>
+      <c r="H101" s="23">
+        <v>5</v>
       </c>
       <c r="I101" s="21" t="inlineStr">
         <is>
@@ -4999,24 +4993,28 @@
       </c>
       <c r="D102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F102" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G102" s="22">
-        <v>0</v>
-      </c>
-      <c r="H102" s="22">
-        <v>2</v>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G102" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H102" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
       </c>
       <c r="I102" s="20" t="inlineStr">
         <is>
@@ -5045,7 +5043,7 @@
       </c>
       <c r="D103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E103" s="19" t="inlineStr">
@@ -5058,15 +5056,11 @@
           <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
-      <c r="G103" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H103" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
+      <c r="G103" s="23">
+        <v>0</v>
+      </c>
+      <c r="H103" s="23">
+        <v>2</v>
       </c>
       <c r="I103" s="21" t="inlineStr">
         <is>
@@ -5095,24 +5089,28 @@
       </c>
       <c r="D104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G104" s="22">
-        <v>0</v>
-      </c>
-      <c r="H104" s="22">
-        <v>4</v>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G104" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H104" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
       </c>
       <c r="I104" s="20" t="inlineStr">
         <is>
@@ -5141,7 +5139,7 @@
       </c>
       <c r="D105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E105" s="19" t="inlineStr">
@@ -5154,15 +5152,11 @@
           <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
-      <c r="G105" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H105" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
+      <c r="G105" s="23">
+        <v>0</v>
+      </c>
+      <c r="H105" s="23">
+        <v>4</v>
       </c>
       <c r="I105" s="21" t="inlineStr">
         <is>
@@ -5196,12 +5190,12 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G106" s="22" t="inlineStr">
@@ -5211,7 +5205,7 @@
       </c>
       <c r="H106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I106" s="20" t="inlineStr">
@@ -5246,12 +5240,12 @@
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -5261,7 +5255,7 @@
       </c>
       <c r="H107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I107" s="21" t="inlineStr">
@@ -5296,12 +5290,12 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G108" s="22" t="inlineStr">
@@ -5311,7 +5305,7 @@
       </c>
       <c r="H108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I108" s="20" t="inlineStr">
@@ -5346,12 +5340,12 @@
       </c>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -5361,7 +5355,7 @@
       </c>
       <c r="H109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I109" s="21" t="inlineStr">
@@ -5396,12 +5390,12 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -5411,7 +5405,7 @@
       </c>
       <c r="H110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I110" s="20" t="inlineStr">
@@ -5446,12 +5440,12 @@
       </c>
       <c r="E111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -5461,7 +5455,7 @@
       </c>
       <c r="H111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I111" s="21" t="inlineStr">
@@ -5496,12 +5490,12 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G112" s="22" t="inlineStr">
@@ -5511,7 +5505,7 @@
       </c>
       <c r="H112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="I112" s="20" t="inlineStr">
@@ -5541,24 +5535,28 @@
       </c>
       <c r="D113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G113" s="23">
-        <v>0</v>
-      </c>
-      <c r="H113" s="23">
-        <v>4</v>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="G113" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H113" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
       </c>
       <c r="I113" s="21" t="inlineStr">
         <is>
@@ -5587,7 +5585,7 @@
       </c>
       <c r="D114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E114" s="17" t="inlineStr">
@@ -5600,15 +5598,11 @@
           <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
-      <c r="G114" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H114" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
+      <c r="G114" s="22">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22">
+        <v>4</v>
       </c>
       <c r="I114" s="20" t="inlineStr">
         <is>
@@ -5642,12 +5636,12 @@
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -5657,7 +5651,7 @@
       </c>
       <c r="H115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I115" s="21" t="inlineStr">
@@ -5692,12 +5686,12 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G116" s="22" t="inlineStr">
@@ -5707,7 +5701,7 @@
       </c>
       <c r="H116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I116" s="20" t="inlineStr">
@@ -5742,12 +5736,12 @@
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -5757,7 +5751,7 @@
       </c>
       <c r="H117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I117" s="21" t="inlineStr">
@@ -5792,12 +5786,12 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="G118" s="22" t="inlineStr">
@@ -5807,7 +5801,7 @@
       </c>
       <c r="H118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="I118" s="20" t="inlineStr">
@@ -5837,24 +5831,28 @@
       </c>
       <c r="D119" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G119" s="23">
-        <v>0</v>
-      </c>
-      <c r="H119" s="23">
-        <v>4</v>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G119" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H119" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
       </c>
       <c r="I119" s="21" t="inlineStr">
         <is>
@@ -5883,7 +5881,7 @@
       </c>
       <c r="D120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E120" s="17" t="inlineStr">
@@ -5896,15 +5894,11 @@
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G120" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H120" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
+      <c r="G120" s="22">
+        <v>0</v>
+      </c>
+      <c r="H120" s="22">
+        <v>4</v>
       </c>
       <c r="I120" s="20" t="inlineStr">
         <is>
@@ -5938,132 +5932,138 @@
       </c>
       <c r="E121" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F121" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G121" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H121" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="I121" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J121" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="28" customHeight="1">
+      <c r="A122" s="16">
+        <v>3</v>
+      </c>
+      <c r="B122" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C122" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D122" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E122" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">68</t>
         </is>
       </c>
-      <c r="F121" s="23" t="inlineStr">
+      <c r="F122" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="G121" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H121" s="23" t="inlineStr">
+      <c r="G122" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H122" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="I121" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J121" s="19" t="inlineStr">
+      <c r="I122" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J122" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="48" customHeight="1">
-      <c r="A122" s="16">
-        <v>3</v>
-      </c>
-      <c r="B122" s="17" t="inlineStr">
+    <row r="123" ht="48" customHeight="1">
+      <c r="A123" s="18">
+        <v>3</v>
+      </c>
+      <c r="B123" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
-      <c r="C122" s="17" t="inlineStr">
+      <c r="C123" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
-      <c r="D122" s="17" t="inlineStr">
+      <c r="D123" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E122" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F122" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G122" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H122" s="22" t="inlineStr">
+      <c r="E123" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F123" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G123" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H123" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="I122" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J122" s="17" t="inlineStr">
+      <c r="I123" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J123" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="28" customHeight="1">
-      <c r="A123" s="18">
-        <v>2</v>
-      </c>
-      <c r="B123" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/23</t>
-        </is>
-      </c>
-      <c r="C123" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23:16:19</t>
-        </is>
-      </c>
-      <c r="D123" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E123" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="F123" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G123" s="23">
-        <v>4</v>
-      </c>
-      <c r="H123" s="23">
-        <v>0</v>
-      </c>
-      <c r="I123" s="21">
-        <v>4</v>
-      </c>
-      <c r="J123" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
     <row r="124" ht="28" customHeight="1">
       <c r="A124" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
@@ -6072,12 +6072,12 @@
       </c>
       <c r="C124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">23:16:19</t>
         </is>
       </c>
       <c r="D124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E124" s="17" t="inlineStr">
@@ -6091,19 +6091,17 @@
         </is>
       </c>
       <c r="G124" s="22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H124" s="22">
+        <v>0</v>
+      </c>
+      <c r="I124" s="20">
         <v>4</v>
       </c>
-      <c r="I124" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6121,7 @@
       </c>
       <c r="D125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E125" s="19" t="inlineStr">
@@ -6136,15 +6134,11 @@
           <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
-      <c r="G125" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H125" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
+      <c r="G125" s="23">
+        <v>0</v>
+      </c>
+      <c r="H125" s="23">
+        <v>4</v>
       </c>
       <c r="I125" s="21" t="inlineStr">
         <is>
@@ -6178,12 +6172,12 @@
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F126" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G126" s="22" t="inlineStr">
@@ -6193,7 +6187,7 @@
       </c>
       <c r="H126" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="I126" s="20" t="inlineStr">
@@ -6228,7 +6222,7 @@
       </c>
       <c r="E127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
@@ -6278,30 +6272,80 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F128" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G128" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H128" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I128" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J128" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="28" customHeight="1">
+      <c r="A129" s="18">
+        <v>1</v>
+      </c>
+      <c r="B129" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C129" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D129" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E129" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F128" s="22" t="inlineStr">
+      <c r="F129" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G128" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H128" s="22" t="inlineStr">
+      <c r="G129" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H129" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I128" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J128" s="17" t="inlineStr">
+      <c r="I129" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J129" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J129" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J129"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J130" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J130"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:35</t>
+          <t xml:space="preserve">15:30:53</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -518,12 +518,12 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G6" s="22">
@@ -537,13 +537,13 @@
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed45f1ef47</t>
+          <t xml:space="preserve">a1408f9e88</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:59</t>
+          <t xml:space="preserve">15:30:35</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -562,32 +562,32 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G7" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H7" s="23">
         <v>0</v>
       </c>
       <c r="I7" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">d659616819</t>
+          <t xml:space="preserve">ed45f1ef47</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:38</t>
+          <t xml:space="preserve">15:29:59</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G8" s="22">
@@ -625,13 +625,13 @@
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">19f5f6152e</t>
+          <t xml:space="preserve">d659616819</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:24</t>
+          <t xml:space="preserve">15:29:38</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -650,32 +650,32 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9" s="23">
         <v>0</v>
       </c>
       <c r="I9" s="21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd714591b4</t>
+          <t xml:space="preserve">19f5f6152e</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -684,38 +684,36 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:24</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G10" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" s="22">
         <v>0</v>
       </c>
-      <c r="I10" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I10" s="20">
+        <v>4</v>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">bd714591b4</t>
         </is>
       </c>
     </row>
@@ -740,16 +738,16 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G11" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" s="23">
         <v>0</v>
@@ -786,16 +784,16 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G12" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12" s="22">
         <v>0</v>
@@ -832,19 +830,19 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G13" s="23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" s="23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I13" s="21" t="inlineStr">
         <is>
@@ -878,19 +876,19 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G14" s="22">
         <v>0</v>
       </c>
       <c r="H14" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
@@ -924,12 +922,12 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G15" s="23">
@@ -970,19 +968,19 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G16" s="22">
         <v>0</v>
       </c>
       <c r="H16" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
@@ -1016,19 +1014,19 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G17" s="23">
         <v>0</v>
       </c>
       <c r="H17" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
@@ -1062,19 +1060,19 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G18" s="22">
         <v>0</v>
       </c>
       <c r="H18" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
@@ -1108,12 +1106,12 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G19" s="23">
@@ -1154,19 +1152,19 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G20" s="22">
         <v>0</v>
       </c>
       <c r="H20" s="22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
@@ -1200,19 +1198,19 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G21" s="23">
         <v>0</v>
       </c>
       <c r="H21" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
@@ -1246,12 +1244,12 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G22" s="22">
@@ -1292,19 +1290,19 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G23" s="23">
         <v>0</v>
       </c>
       <c r="H23" s="23">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
@@ -1338,19 +1336,19 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G24" s="22">
         <v>0</v>
       </c>
       <c r="H24" s="22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -1384,19 +1382,19 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G25" s="23">
         <v>0</v>
       </c>
       <c r="H25" s="23">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
@@ -1430,19 +1428,19 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G26" s="22">
         <v>0</v>
       </c>
       <c r="H26" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
@@ -1476,19 +1474,19 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G27" s="23">
         <v>0</v>
       </c>
       <c r="H27" s="23">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
@@ -1522,19 +1520,19 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G28" s="22">
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -1568,19 +1566,19 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G29" s="23">
         <v>0</v>
       </c>
       <c r="H29" s="23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
@@ -1614,19 +1612,19 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G30" s="22">
         <v>0</v>
       </c>
       <c r="H30" s="22">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
@@ -1660,19 +1658,19 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G31" s="23">
         <v>0</v>
       </c>
       <c r="H31" s="23">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
@@ -1706,19 +1704,19 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G32" s="22">
         <v>0</v>
       </c>
       <c r="H32" s="22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
@@ -1752,12 +1750,12 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G33" s="23">
@@ -1798,19 +1796,19 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G34" s="22">
         <v>0</v>
       </c>
       <c r="H34" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
@@ -1844,12 +1842,12 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G35" s="23">
@@ -1890,19 +1888,19 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G36" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1917,7 +1915,7 @@
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
@@ -1926,7 +1924,7 @@
       </c>
       <c r="C37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
@@ -1936,19 +1934,19 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G37" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1957,7 +1955,7 @@
       </c>
       <c r="J37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
@@ -1982,19 +1980,19 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G38" s="22">
         <v>0</v>
       </c>
       <c r="H38" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -2028,19 +2026,19 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G39" s="23">
         <v>0</v>
       </c>
       <c r="H39" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
@@ -2074,19 +2072,19 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G40" s="22">
         <v>0</v>
       </c>
       <c r="H40" s="22">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
@@ -2120,19 +2118,19 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G41" s="23">
         <v>0</v>
       </c>
       <c r="H41" s="23">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I41" s="21" t="inlineStr">
         <is>
@@ -2166,128 +2164,130 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G42" s="22">
+        <v>0</v>
+      </c>
+      <c r="H42" s="22">
+        <v>4</v>
+      </c>
+      <c r="I42" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="18">
+        <v>23</v>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:59:31</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">67</t>
         </is>
       </c>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="F43" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G42" s="22">
-        <v>0</v>
-      </c>
-      <c r="H42" s="22">
+      <c r="G43" s="23">
+        <v>0</v>
+      </c>
+      <c r="H43" s="23">
         <v>1</v>
       </c>
-      <c r="I42" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J42" s="17" t="inlineStr">
+      <c r="I43" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="48" customHeight="1">
-      <c r="A43" s="18">
+    <row r="44" ht="48" customHeight="1">
+      <c r="A44" s="16">
         <v>22</v>
       </c>
-      <c r="B43" s="19" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
-      <c r="C43" s="19" t="inlineStr">
+      <c r="C44" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
-      <c r="D43" s="19" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E43" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F43" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G43" s="23" t="inlineStr">
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F44" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="H43" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I43" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J43" s="19" t="inlineStr">
+      <c r="H44" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I44" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J44" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2688d62325</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="16">
-        <v>21</v>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:18:32</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E44" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62</t>
-        </is>
-      </c>
-      <c r="F44" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G44" s="22">
-        <v>4</v>
-      </c>
-      <c r="H44" s="22">
-        <v>0</v>
-      </c>
-      <c r="I44" s="20">
-        <v>4</v>
-      </c>
-      <c r="J44" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D45" s="19" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G45" s="23">
@@ -2325,13 +2325,13 @@
       </c>
       <c r="J45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="16">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G46" s="22">
@@ -2369,13 +2369,13 @@
       </c>
       <c r="J46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D47" s="19" t="inlineStr">
@@ -2394,32 +2394,32 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G47" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H47" s="23">
         <v>0</v>
       </c>
       <c r="I47" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -2438,32 +2438,32 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G48" s="22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H48" s="22">
         <v>0</v>
       </c>
       <c r="I48" s="20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
@@ -2482,32 +2482,32 @@
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G49" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H49" s="23">
         <v>0</v>
       </c>
       <c r="I49" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G50" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H50" s="22">
         <v>0</v>
       </c>
       <c r="I50" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G51" s="23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H51" s="23">
         <v>0</v>
       </c>
       <c r="I51" s="21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -2614,32 +2614,32 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G52" s="22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H52" s="22">
         <v>0</v>
       </c>
       <c r="I52" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D53" s="19" t="inlineStr">
@@ -2658,32 +2658,32 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G53" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H53" s="23">
         <v>0</v>
       </c>
       <c r="I53" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -2702,32 +2702,32 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G54" s="22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H54" s="22">
         <v>0</v>
       </c>
       <c r="I54" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -2746,32 +2746,32 @@
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G55" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H55" s="23">
         <v>0</v>
       </c>
       <c r="I55" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -2790,32 +2790,32 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G56" s="22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H56" s="22">
         <v>0</v>
       </c>
       <c r="I56" s="20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -2834,32 +2834,32 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G57" s="23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H57" s="23">
         <v>0</v>
       </c>
       <c r="I57" s="21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -2878,32 +2878,32 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G58" s="22">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H58" s="22">
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -2922,32 +2922,32 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G59" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H59" s="23">
         <v>0</v>
       </c>
       <c r="I59" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G60" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H60" s="22">
         <v>0</v>
       </c>
       <c r="I60" s="20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
@@ -3010,46 +3010,46 @@
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G61" s="23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H61" s="23">
         <v>0</v>
       </c>
       <c r="I61" s="21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
@@ -3063,19 +3063,17 @@
         </is>
       </c>
       <c r="G62" s="22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H62" s="22">
+        <v>0</v>
+      </c>
+      <c r="I62" s="20">
         <v>5</v>
       </c>
-      <c r="I62" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -3100,19 +3098,19 @@
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G63" s="23">
         <v>0</v>
       </c>
       <c r="H63" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I63" s="21" t="inlineStr">
         <is>
@@ -3141,7 +3139,7 @@
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
@@ -3154,15 +3152,11 @@
           <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
-      <c r="G64" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H64" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+      <c r="G64" s="22">
+        <v>0</v>
+      </c>
+      <c r="H64" s="22">
+        <v>3</v>
       </c>
       <c r="I64" s="20" t="inlineStr">
         <is>
@@ -3191,24 +3185,28 @@
       </c>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G65" s="23">
-        <v>0</v>
-      </c>
-      <c r="H65" s="23">
-        <v>6</v>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H65" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
       </c>
       <c r="I65" s="21" t="inlineStr">
         <is>
@@ -3237,7 +3235,7 @@
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
@@ -3250,15 +3248,11 @@
           <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
-      <c r="G66" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H66" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
+      <c r="G66" s="22">
+        <v>0</v>
+      </c>
+      <c r="H66" s="22">
+        <v>6</v>
       </c>
       <c r="I66" s="20" t="inlineStr">
         <is>
@@ -3292,12 +3286,12 @@
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
@@ -3307,7 +3301,7 @@
       </c>
       <c r="H67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I67" s="21" t="inlineStr">
@@ -3342,22 +3336,22 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I68" s="20" t="inlineStr">
@@ -3392,12 +3386,12 @@
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
@@ -3407,7 +3401,7 @@
       </c>
       <c r="H69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I69" s="21" t="inlineStr">
@@ -3442,12 +3436,12 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G70" s="22" t="inlineStr">
@@ -3457,7 +3451,7 @@
       </c>
       <c r="H70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="I70" s="20" t="inlineStr">
@@ -3487,24 +3481,28 @@
       </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G71" s="23">
-        <v>0</v>
-      </c>
-      <c r="H71" s="23">
-        <v>3</v>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H71" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
       </c>
       <c r="I71" s="21" t="inlineStr">
         <is>
@@ -3533,7 +3531,7 @@
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
@@ -3546,15 +3544,11 @@
           <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
-      <c r="G72" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H72" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
+      <c r="G72" s="22">
+        <v>0</v>
+      </c>
+      <c r="H72" s="22">
+        <v>3</v>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
@@ -3583,24 +3577,28 @@
       </c>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G73" s="23">
-        <v>0</v>
-      </c>
-      <c r="H73" s="23">
-        <v>3</v>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H73" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
       </c>
       <c r="I73" s="21" t="inlineStr">
         <is>
@@ -3629,7 +3627,7 @@
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
@@ -3642,15 +3640,11 @@
           <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
-      <c r="G74" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H74" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
+      <c r="G74" s="22">
+        <v>0</v>
+      </c>
+      <c r="H74" s="22">
+        <v>3</v>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
@@ -3679,24 +3673,28 @@
       </c>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G75" s="23">
-        <v>0</v>
-      </c>
-      <c r="H75" s="23">
-        <v>5</v>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H75" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
       </c>
       <c r="I75" s="21" t="inlineStr">
         <is>
@@ -3725,7 +3723,7 @@
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
@@ -3738,15 +3736,11 @@
           <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
-      <c r="G76" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H76" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
+      <c r="G76" s="22">
+        <v>0</v>
+      </c>
+      <c r="H76" s="22">
+        <v>5</v>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
@@ -3775,24 +3769,28 @@
       </c>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="G77" s="23">
-        <v>0</v>
-      </c>
-      <c r="H77" s="23">
-        <v>9</v>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H77" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
@@ -3821,7 +3819,7 @@
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
@@ -3834,15 +3832,11 @@
           <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
-      <c r="G78" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H78" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
+      <c r="G78" s="22">
+        <v>0</v>
+      </c>
+      <c r="H78" s="22">
+        <v>9</v>
       </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
@@ -3876,12 +3870,12 @@
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -3891,7 +3885,7 @@
       </c>
       <c r="H79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I79" s="21" t="inlineStr">
@@ -3926,12 +3920,12 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G80" s="22" t="inlineStr">
@@ -3941,7 +3935,7 @@
       </c>
       <c r="H80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
@@ -3971,24 +3965,28 @@
       </c>
       <c r="D81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G81" s="23">
-        <v>0</v>
-      </c>
-      <c r="H81" s="23">
-        <v>6</v>
+          <t xml:space="preserve">وافل</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H81" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وافل</t>
+        </is>
       </c>
       <c r="I81" s="21" t="inlineStr">
         <is>
@@ -4017,7 +4015,7 @@
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
@@ -4030,15 +4028,11 @@
           <t xml:space="preserve">کوکی</t>
         </is>
       </c>
-      <c r="G82" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H82" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
+      <c r="G82" s="22">
+        <v>0</v>
+      </c>
+      <c r="H82" s="22">
+        <v>6</v>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
@@ -4067,24 +4061,28 @@
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="G83" s="23">
-        <v>0</v>
-      </c>
-      <c r="H83" s="23">
-        <v>3</v>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H83" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
@@ -4113,7 +4111,7 @@
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
@@ -4126,15 +4124,11 @@
           <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
-      <c r="G84" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H84" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
+      <c r="G84" s="22">
+        <v>0</v>
+      </c>
+      <c r="H84" s="22">
+        <v>3</v>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
@@ -4168,12 +4162,12 @@
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -4183,7 +4177,7 @@
       </c>
       <c r="H85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="I85" s="21" t="inlineStr">
@@ -4213,24 +4207,28 @@
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G86" s="22">
-        <v>0</v>
-      </c>
-      <c r="H86" s="22">
-        <v>4</v>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H86" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
@@ -4259,7 +4257,7 @@
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
@@ -4272,15 +4270,11 @@
           <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
-      <c r="G87" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H87" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
+      <c r="G87" s="23">
+        <v>0</v>
+      </c>
+      <c r="H87" s="23">
+        <v>4</v>
       </c>
       <c r="I87" s="21" t="inlineStr">
         <is>
@@ -4309,24 +4303,28 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G88" s="22">
-        <v>0</v>
-      </c>
-      <c r="H88" s="22">
-        <v>6</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H88" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
@@ -4355,7 +4353,7 @@
       </c>
       <c r="D89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
@@ -4368,15 +4366,11 @@
           <t xml:space="preserve">آجیل</t>
         </is>
       </c>
-      <c r="G89" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H89" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+      <c r="G89" s="23">
+        <v>0</v>
+      </c>
+      <c r="H89" s="23">
+        <v>6</v>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
@@ -4405,24 +4399,28 @@
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
-      </c>
-      <c r="G90" s="22">
-        <v>0</v>
-      </c>
-      <c r="H90" s="22">
-        <v>7</v>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G90" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H90" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
@@ -4451,7 +4449,7 @@
       </c>
       <c r="D91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E91" s="19" t="inlineStr">
@@ -4464,15 +4462,11 @@
           <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
-      <c r="G91" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H91" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
+      <c r="G91" s="23">
+        <v>0</v>
+      </c>
+      <c r="H91" s="23">
+        <v>7</v>
       </c>
       <c r="I91" s="21" t="inlineStr">
         <is>
@@ -4506,12 +4500,12 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F92" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G92" s="22" t="inlineStr">
@@ -4521,7 +4515,7 @@
       </c>
       <c r="H92" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I92" s="20" t="inlineStr">
@@ -4551,24 +4545,28 @@
       </c>
       <c r="D93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G93" s="23">
-        <v>0</v>
-      </c>
-      <c r="H93" s="23">
-        <v>3</v>
+          <t xml:space="preserve">رول رول</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H93" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول</t>
+        </is>
       </c>
       <c r="I93" s="21" t="inlineStr">
         <is>
@@ -4597,7 +4595,7 @@
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
@@ -4610,15 +4608,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G94" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H94" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G94" s="22">
+        <v>0</v>
+      </c>
+      <c r="H94" s="22">
+        <v>3</v>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
@@ -4652,7 +4646,7 @@
       </c>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
@@ -4702,7 +4696,7 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
@@ -4752,7 +4746,7 @@
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
@@ -4802,12 +4796,12 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F98" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G98" s="22" t="inlineStr">
@@ -4817,7 +4811,7 @@
       </c>
       <c r="H98" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I98" s="20" t="inlineStr">
@@ -4852,12 +4846,12 @@
       </c>
       <c r="E99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -4867,7 +4861,7 @@
       </c>
       <c r="H99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I99" s="21" t="inlineStr">
@@ -4902,12 +4896,12 @@
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="G100" s="22" t="inlineStr">
@@ -4917,7 +4911,7 @@
       </c>
       <c r="H100" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="I100" s="20" t="inlineStr">
@@ -4947,24 +4941,28 @@
       </c>
       <c r="D101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G101" s="23">
-        <v>0</v>
-      </c>
-      <c r="H101" s="23">
-        <v>5</v>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H101" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
       </c>
       <c r="I101" s="21" t="inlineStr">
         <is>
@@ -4993,7 +4991,7 @@
       </c>
       <c r="D102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E102" s="17" t="inlineStr">
@@ -5006,15 +5004,11 @@
           <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
-      <c r="G102" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H102" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
+      <c r="G102" s="22">
+        <v>0</v>
+      </c>
+      <c r="H102" s="22">
+        <v>5</v>
       </c>
       <c r="I102" s="20" t="inlineStr">
         <is>
@@ -5043,24 +5037,28 @@
       </c>
       <c r="D103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G103" s="23">
-        <v>0</v>
-      </c>
-      <c r="H103" s="23">
-        <v>2</v>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H103" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
       </c>
       <c r="I103" s="21" t="inlineStr">
         <is>
@@ -5089,7 +5087,7 @@
       </c>
       <c r="D104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E104" s="17" t="inlineStr">
@@ -5102,15 +5100,11 @@
           <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
-      <c r="G104" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H104" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
+      <c r="G104" s="22">
+        <v>0</v>
+      </c>
+      <c r="H104" s="22">
+        <v>2</v>
       </c>
       <c r="I104" s="20" t="inlineStr">
         <is>
@@ -5139,24 +5133,28 @@
       </c>
       <c r="D105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G105" s="23">
-        <v>0</v>
-      </c>
-      <c r="H105" s="23">
-        <v>4</v>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H105" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
       </c>
       <c r="I105" s="21" t="inlineStr">
         <is>
@@ -5185,7 +5183,7 @@
       </c>
       <c r="D106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E106" s="17" t="inlineStr">
@@ -5198,15 +5196,11 @@
           <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
-      <c r="G106" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H106" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
+      <c r="G106" s="22">
+        <v>0</v>
+      </c>
+      <c r="H106" s="22">
+        <v>4</v>
       </c>
       <c r="I106" s="20" t="inlineStr">
         <is>
@@ -5240,12 +5234,12 @@
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -5255,7 +5249,7 @@
       </c>
       <c r="H107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I107" s="21" t="inlineStr">
@@ -5290,12 +5284,12 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G108" s="22" t="inlineStr">
@@ -5305,7 +5299,7 @@
       </c>
       <c r="H108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I108" s="20" t="inlineStr">
@@ -5340,12 +5334,12 @@
       </c>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -5355,7 +5349,7 @@
       </c>
       <c r="H109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I109" s="21" t="inlineStr">
@@ -5390,12 +5384,12 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -5405,7 +5399,7 @@
       </c>
       <c r="H110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I110" s="20" t="inlineStr">
@@ -5440,12 +5434,12 @@
       </c>
       <c r="E111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -5455,7 +5449,7 @@
       </c>
       <c r="H111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I111" s="21" t="inlineStr">
@@ -5490,12 +5484,12 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G112" s="22" t="inlineStr">
@@ -5505,7 +5499,7 @@
       </c>
       <c r="H112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I112" s="20" t="inlineStr">
@@ -5540,12 +5534,12 @@
       </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -5555,7 +5549,7 @@
       </c>
       <c r="H113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="I113" s="21" t="inlineStr">
@@ -5585,24 +5579,28 @@
       </c>
       <c r="D114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G114" s="22">
-        <v>0</v>
-      </c>
-      <c r="H114" s="22">
-        <v>4</v>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="G114" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H114" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
       </c>
       <c r="I114" s="20" t="inlineStr">
         <is>
@@ -5631,7 +5629,7 @@
       </c>
       <c r="D115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E115" s="19" t="inlineStr">
@@ -5644,15 +5642,11 @@
           <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
-      <c r="G115" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H115" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
+      <c r="G115" s="23">
+        <v>0</v>
+      </c>
+      <c r="H115" s="23">
+        <v>4</v>
       </c>
       <c r="I115" s="21" t="inlineStr">
         <is>
@@ -5686,12 +5680,12 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G116" s="22" t="inlineStr">
@@ -5701,7 +5695,7 @@
       </c>
       <c r="H116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I116" s="20" t="inlineStr">
@@ -5736,12 +5730,12 @@
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -5751,7 +5745,7 @@
       </c>
       <c r="H117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I117" s="21" t="inlineStr">
@@ -5786,12 +5780,12 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G118" s="22" t="inlineStr">
@@ -5801,7 +5795,7 @@
       </c>
       <c r="H118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I118" s="20" t="inlineStr">
@@ -5836,12 +5830,12 @@
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -5851,7 +5845,7 @@
       </c>
       <c r="H119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="I119" s="21" t="inlineStr">
@@ -5881,24 +5875,28 @@
       </c>
       <c r="D120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G120" s="22">
-        <v>0</v>
-      </c>
-      <c r="H120" s="22">
-        <v>4</v>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G120" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H120" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
       </c>
       <c r="I120" s="20" t="inlineStr">
         <is>
@@ -5927,7 +5925,7 @@
       </c>
       <c r="D121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E121" s="19" t="inlineStr">
@@ -5940,15 +5938,11 @@
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G121" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H121" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
+      <c r="G121" s="23">
+        <v>0</v>
+      </c>
+      <c r="H121" s="23">
+        <v>4</v>
       </c>
       <c r="I121" s="21" t="inlineStr">
         <is>
@@ -5982,132 +5976,138 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F122" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G122" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H122" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="I122" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J122" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="28" customHeight="1">
+      <c r="A123" s="18">
+        <v>3</v>
+      </c>
+      <c r="B123" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C123" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D123" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E123" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">68</t>
         </is>
       </c>
-      <c r="F122" s="22" t="inlineStr">
+      <c r="F123" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="G122" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H122" s="22" t="inlineStr">
+      <c r="G123" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H123" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="I122" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J122" s="17" t="inlineStr">
+      <c r="I123" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J123" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="48" customHeight="1">
-      <c r="A123" s="18">
-        <v>3</v>
-      </c>
-      <c r="B123" s="19" t="inlineStr">
+    <row r="124" ht="48" customHeight="1">
+      <c r="A124" s="16">
+        <v>3</v>
+      </c>
+      <c r="B124" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
-      <c r="C123" s="19" t="inlineStr">
+      <c r="C124" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
-      <c r="D123" s="19" t="inlineStr">
+      <c r="D124" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E123" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F123" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G123" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H123" s="23" t="inlineStr">
+      <c r="E124" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F124" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G124" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H124" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="I123" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J123" s="19" t="inlineStr">
+      <c r="I124" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J124" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="28" customHeight="1">
-      <c r="A124" s="16">
-        <v>2</v>
-      </c>
-      <c r="B124" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/23</t>
-        </is>
-      </c>
-      <c r="C124" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23:16:19</t>
-        </is>
-      </c>
-      <c r="D124" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E124" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="F124" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G124" s="22">
-        <v>4</v>
-      </c>
-      <c r="H124" s="22">
-        <v>0</v>
-      </c>
-      <c r="I124" s="20">
-        <v>4</v>
-      </c>
-      <c r="J124" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
     <row r="125" ht="28" customHeight="1">
       <c r="A125" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B125" s="19" t="inlineStr">
         <is>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="C125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">23:16:19</t>
         </is>
       </c>
       <c r="D125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E125" s="19" t="inlineStr">
@@ -6135,19 +6135,17 @@
         </is>
       </c>
       <c r="G125" s="23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H125" s="23">
+        <v>0</v>
+      </c>
+      <c r="I125" s="21">
         <v>4</v>
       </c>
-      <c r="I125" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6165,7 @@
       </c>
       <c r="D126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E126" s="17" t="inlineStr">
@@ -6180,15 +6178,11 @@
           <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
-      <c r="G126" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H126" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
+      <c r="G126" s="22">
+        <v>0</v>
+      </c>
+      <c r="H126" s="22">
+        <v>4</v>
       </c>
       <c r="I126" s="20" t="inlineStr">
         <is>
@@ -6222,12 +6216,12 @@
       </c>
       <c r="E127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -6237,7 +6231,7 @@
       </c>
       <c r="H127" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="I127" s="21" t="inlineStr">
@@ -6272,7 +6266,7 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F128" s="22" t="inlineStr">
@@ -6322,30 +6316,80 @@
       </c>
       <c r="E129" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F129" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G129" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H129" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I129" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J129" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="28" customHeight="1">
+      <c r="A130" s="16">
+        <v>1</v>
+      </c>
+      <c r="B130" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C130" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D130" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E130" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F129" s="23" t="inlineStr">
+      <c r="F130" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G129" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H129" s="23" t="inlineStr">
+      <c r="G130" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H130" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I129" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J129" s="19" t="inlineStr">
+      <c r="I130" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J130" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J130" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J130"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J131" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J131"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:53</t>
+          <t xml:space="preserve">15:31:30</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -518,32 +518,32 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G6" s="22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H6" s="22">
         <v>0</v>
       </c>
       <c r="I6" s="20">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a1408f9e88</t>
+          <t xml:space="preserve">5edabb20bb</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:35</t>
+          <t xml:space="preserve">15:30:53</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G7" s="23">
@@ -581,13 +581,13 @@
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed45f1ef47</t>
+          <t xml:space="preserve">a1408f9e88</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:59</t>
+          <t xml:space="preserve">15:30:35</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -606,32 +606,32 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G8" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H8" s="22">
         <v>0</v>
       </c>
       <c r="I8" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">d659616819</t>
+          <t xml:space="preserve">ed45f1ef47</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:38</t>
+          <t xml:space="preserve">15:29:59</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G9" s="23">
@@ -669,13 +669,13 @@
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">19f5f6152e</t>
+          <t xml:space="preserve">d659616819</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:24</t>
+          <t xml:space="preserve">15:29:38</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G10" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10" s="22">
         <v>0</v>
       </c>
       <c r="I10" s="20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd714591b4</t>
+          <t xml:space="preserve">19f5f6152e</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
@@ -728,38 +728,36 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:24</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G11" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11" s="23">
         <v>0</v>
       </c>
-      <c r="I11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I11" s="21">
+        <v>4</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">bd714591b4</t>
         </is>
       </c>
     </row>
@@ -784,16 +782,16 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G12" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" s="22">
         <v>0</v>
@@ -830,16 +828,16 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G13" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" s="23">
         <v>0</v>
@@ -876,19 +874,19 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G14" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" s="22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
@@ -922,19 +920,19 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G15" s="23">
         <v>0</v>
       </c>
       <c r="H15" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I15" s="21" t="inlineStr">
         <is>
@@ -968,12 +966,12 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G16" s="22">
@@ -1014,19 +1012,19 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G17" s="23">
         <v>0</v>
       </c>
       <c r="H17" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
@@ -1060,19 +1058,19 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G18" s="22">
         <v>0</v>
       </c>
       <c r="H18" s="22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
@@ -1106,19 +1104,19 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G19" s="23">
         <v>0</v>
       </c>
       <c r="H19" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
@@ -1152,12 +1150,12 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G20" s="22">
@@ -1198,19 +1196,19 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G21" s="23">
         <v>0</v>
       </c>
       <c r="H21" s="23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
@@ -1244,19 +1242,19 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G22" s="22">
         <v>0</v>
       </c>
       <c r="H22" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
@@ -1290,12 +1288,12 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G23" s="23">
@@ -1336,19 +1334,19 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G24" s="22">
         <v>0</v>
       </c>
       <c r="H24" s="22">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -1382,19 +1380,19 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G25" s="23">
         <v>0</v>
       </c>
       <c r="H25" s="23">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
@@ -1428,19 +1426,19 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G26" s="22">
         <v>0</v>
       </c>
       <c r="H26" s="22">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
@@ -1474,19 +1472,19 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G27" s="23">
         <v>0</v>
       </c>
       <c r="H27" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
@@ -1520,19 +1518,19 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G28" s="22">
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -1566,19 +1564,19 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G29" s="23">
         <v>0</v>
       </c>
       <c r="H29" s="23">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
@@ -1612,19 +1610,19 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G30" s="22">
         <v>0</v>
       </c>
       <c r="H30" s="22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
@@ -1658,19 +1656,19 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G31" s="23">
         <v>0</v>
       </c>
       <c r="H31" s="23">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
@@ -1704,19 +1702,19 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G32" s="22">
         <v>0</v>
       </c>
       <c r="H32" s="22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
@@ -1750,19 +1748,19 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G33" s="23">
         <v>0</v>
       </c>
       <c r="H33" s="23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
@@ -1796,12 +1794,12 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G34" s="22">
@@ -1842,19 +1840,19 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G35" s="23">
         <v>0</v>
       </c>
       <c r="H35" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1888,12 +1886,12 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G36" s="22">
@@ -1934,19 +1932,19 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G37" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1961,7 +1959,7 @@
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
@@ -1970,7 +1968,7 @@
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
@@ -1980,19 +1978,19 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G38" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -2001,7 +1999,7 @@
       </c>
       <c r="J38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
@@ -2026,19 +2024,19 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G39" s="23">
         <v>0</v>
       </c>
       <c r="H39" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
@@ -2072,19 +2070,19 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G40" s="22">
         <v>0</v>
       </c>
       <c r="H40" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
@@ -2118,19 +2116,19 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G41" s="23">
         <v>0</v>
       </c>
       <c r="H41" s="23">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I41" s="21" t="inlineStr">
         <is>
@@ -2164,19 +2162,19 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G42" s="22">
         <v>0</v>
       </c>
       <c r="H42" s="22">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
@@ -2210,128 +2208,130 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G43" s="23">
+        <v>0</v>
+      </c>
+      <c r="H43" s="23">
+        <v>4</v>
+      </c>
+      <c r="I43" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="16">
+        <v>23</v>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:59:31</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">67</t>
         </is>
       </c>
-      <c r="F43" s="23" t="inlineStr">
+      <c r="F44" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G43" s="23">
-        <v>0</v>
-      </c>
-      <c r="H43" s="23">
+      <c r="G44" s="22">
+        <v>0</v>
+      </c>
+      <c r="H44" s="22">
         <v>1</v>
       </c>
-      <c r="I43" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J43" s="19" t="inlineStr">
+      <c r="I44" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J44" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="48" customHeight="1">
-      <c r="A44" s="16">
+    <row r="45" ht="48" customHeight="1">
+      <c r="A45" s="18">
         <v>22</v>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
-      <c r="C44" s="17" t="inlineStr">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="D45" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E44" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F44" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G44" s="22" t="inlineStr">
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="H44" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I44" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J44" s="17" t="inlineStr">
+      <c r="H45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I45" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J45" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">2688d62325</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="18">
-        <v>21</v>
-      </c>
-      <c r="B45" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:18:32</t>
-        </is>
-      </c>
-      <c r="D45" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E45" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G45" s="23">
-        <v>4</v>
-      </c>
-      <c r="H45" s="23">
-        <v>0</v>
-      </c>
-      <c r="I45" s="21">
-        <v>4</v>
-      </c>
-      <c r="J45" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G46" s="22">
@@ -2369,13 +2369,13 @@
       </c>
       <c r="J46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="18">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D47" s="19" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G47" s="23">
@@ -2413,13 +2413,13 @@
       </c>
       <c r="J47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -2438,32 +2438,32 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G48" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H48" s="22">
         <v>0</v>
       </c>
       <c r="I48" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
@@ -2482,32 +2482,32 @@
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G49" s="23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H49" s="23">
         <v>0</v>
       </c>
       <c r="I49" s="21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G50" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H50" s="22">
         <v>0</v>
       </c>
       <c r="I50" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G51" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H51" s="23">
         <v>0</v>
       </c>
       <c r="I51" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -2614,32 +2614,32 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G52" s="22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H52" s="22">
         <v>0</v>
       </c>
       <c r="I52" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D53" s="19" t="inlineStr">
@@ -2658,32 +2658,32 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G53" s="23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H53" s="23">
         <v>0</v>
       </c>
       <c r="I53" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -2702,32 +2702,32 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G54" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H54" s="22">
         <v>0</v>
       </c>
       <c r="I54" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -2746,32 +2746,32 @@
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G55" s="23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H55" s="23">
         <v>0</v>
       </c>
       <c r="I55" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -2790,32 +2790,32 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G56" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H56" s="22">
         <v>0</v>
       </c>
       <c r="I56" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -2834,32 +2834,32 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G57" s="23">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H57" s="23">
         <v>0</v>
       </c>
       <c r="I57" s="21">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -2878,32 +2878,32 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G58" s="22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H58" s="22">
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -2922,32 +2922,32 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G59" s="23">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H59" s="23">
         <v>0</v>
       </c>
       <c r="I59" s="21">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G60" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H60" s="22">
         <v>0</v>
       </c>
       <c r="I60" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
@@ -3010,32 +3010,32 @@
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G61" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H61" s="23">
         <v>0</v>
       </c>
       <c r="I61" s="21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
@@ -3054,46 +3054,46 @@
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G62" s="22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H62" s="22">
         <v>0</v>
       </c>
       <c r="I62" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
@@ -3107,19 +3107,17 @@
         </is>
       </c>
       <c r="G63" s="23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H63" s="23">
+        <v>0</v>
+      </c>
+      <c r="I63" s="21">
         <v>5</v>
       </c>
-      <c r="I63" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -3144,19 +3142,19 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G64" s="22">
         <v>0</v>
       </c>
       <c r="H64" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I64" s="20" t="inlineStr">
         <is>
@@ -3185,7 +3183,7 @@
       </c>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
@@ -3198,15 +3196,11 @@
           <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
-      <c r="G65" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H65" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+      <c r="G65" s="23">
+        <v>0</v>
+      </c>
+      <c r="H65" s="23">
+        <v>3</v>
       </c>
       <c r="I65" s="21" t="inlineStr">
         <is>
@@ -3235,24 +3229,28 @@
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G66" s="22">
-        <v>0</v>
-      </c>
-      <c r="H66" s="22">
-        <v>6</v>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H66" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
       </c>
       <c r="I66" s="20" t="inlineStr">
         <is>
@@ -3281,7 +3279,7 @@
       </c>
       <c r="D67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
@@ -3294,15 +3292,11 @@
           <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
-      <c r="G67" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H67" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
+      <c r="G67" s="23">
+        <v>0</v>
+      </c>
+      <c r="H67" s="23">
+        <v>6</v>
       </c>
       <c r="I67" s="21" t="inlineStr">
         <is>
@@ -3336,12 +3330,12 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G68" s="22" t="inlineStr">
@@ -3351,7 +3345,7 @@
       </c>
       <c r="H68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I68" s="20" t="inlineStr">
@@ -3386,22 +3380,22 @@
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I69" s="21" t="inlineStr">
@@ -3436,12 +3430,12 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G70" s="22" t="inlineStr">
@@ -3451,7 +3445,7 @@
       </c>
       <c r="H70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I70" s="20" t="inlineStr">
@@ -3486,12 +3480,12 @@
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
@@ -3501,7 +3495,7 @@
       </c>
       <c r="H71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="I71" s="21" t="inlineStr">
@@ -3531,24 +3525,28 @@
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G72" s="22">
-        <v>0</v>
-      </c>
-      <c r="H72" s="22">
-        <v>3</v>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H72" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
@@ -3577,7 +3575,7 @@
       </c>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
@@ -3590,15 +3588,11 @@
           <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
-      <c r="G73" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H73" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
+      <c r="G73" s="23">
+        <v>0</v>
+      </c>
+      <c r="H73" s="23">
+        <v>3</v>
       </c>
       <c r="I73" s="21" t="inlineStr">
         <is>
@@ -3627,24 +3621,28 @@
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G74" s="22">
-        <v>0</v>
-      </c>
-      <c r="H74" s="22">
-        <v>3</v>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H74" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
@@ -3673,7 +3671,7 @@
       </c>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
@@ -3686,15 +3684,11 @@
           <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
-      <c r="G75" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H75" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
+      <c r="G75" s="23">
+        <v>0</v>
+      </c>
+      <c r="H75" s="23">
+        <v>3</v>
       </c>
       <c r="I75" s="21" t="inlineStr">
         <is>
@@ -3723,24 +3717,28 @@
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G76" s="22">
-        <v>0</v>
-      </c>
-      <c r="H76" s="22">
-        <v>5</v>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H76" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
@@ -3769,7 +3767,7 @@
       </c>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
@@ -3782,15 +3780,11 @@
           <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
-      <c r="G77" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H77" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
+      <c r="G77" s="23">
+        <v>0</v>
+      </c>
+      <c r="H77" s="23">
+        <v>5</v>
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
@@ -3819,24 +3813,28 @@
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="G78" s="22">
-        <v>0</v>
-      </c>
-      <c r="H78" s="22">
-        <v>9</v>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H78" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
@@ -3865,7 +3863,7 @@
       </c>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3878,15 +3876,11 @@
           <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
-      <c r="G79" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H79" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
+      <c r="G79" s="23">
+        <v>0</v>
+      </c>
+      <c r="H79" s="23">
+        <v>9</v>
       </c>
       <c r="I79" s="21" t="inlineStr">
         <is>
@@ -3920,12 +3914,12 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G80" s="22" t="inlineStr">
@@ -3935,7 +3929,7 @@
       </c>
       <c r="H80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
@@ -3970,12 +3964,12 @@
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -3985,7 +3979,7 @@
       </c>
       <c r="H81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I81" s="21" t="inlineStr">
@@ -4015,24 +4009,28 @@
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G82" s="22">
-        <v>0</v>
-      </c>
-      <c r="H82" s="22">
-        <v>6</v>
+          <t xml:space="preserve">وافل</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H82" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وافل</t>
+        </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
@@ -4061,7 +4059,7 @@
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
@@ -4074,15 +4072,11 @@
           <t xml:space="preserve">کوکی</t>
         </is>
       </c>
-      <c r="G83" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H83" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
+      <c r="G83" s="23">
+        <v>0</v>
+      </c>
+      <c r="H83" s="23">
+        <v>6</v>
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
@@ -4111,24 +4105,28 @@
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="G84" s="22">
-        <v>0</v>
-      </c>
-      <c r="H84" s="22">
-        <v>3</v>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H84" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
@@ -4157,7 +4155,7 @@
       </c>
       <c r="D85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
@@ -4170,15 +4168,11 @@
           <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
-      <c r="G85" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H85" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
+      <c r="G85" s="23">
+        <v>0</v>
+      </c>
+      <c r="H85" s="23">
+        <v>3</v>
       </c>
       <c r="I85" s="21" t="inlineStr">
         <is>
@@ -4212,12 +4206,12 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G86" s="22" t="inlineStr">
@@ -4227,7 +4221,7 @@
       </c>
       <c r="H86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
@@ -4257,24 +4251,28 @@
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G87" s="23">
-        <v>0</v>
-      </c>
-      <c r="H87" s="23">
-        <v>4</v>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
       </c>
       <c r="I87" s="21" t="inlineStr">
         <is>
@@ -4303,7 +4301,7 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
@@ -4316,15 +4314,11 @@
           <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
-      <c r="G88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
+      <c r="G88" s="22">
+        <v>0</v>
+      </c>
+      <c r="H88" s="22">
+        <v>4</v>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
@@ -4353,24 +4347,28 @@
       </c>
       <c r="D89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G89" s="23">
-        <v>0</v>
-      </c>
-      <c r="H89" s="23">
-        <v>6</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H89" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
@@ -4399,7 +4397,7 @@
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
@@ -4412,15 +4410,11 @@
           <t xml:space="preserve">آجیل</t>
         </is>
       </c>
-      <c r="G90" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H90" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+      <c r="G90" s="22">
+        <v>0</v>
+      </c>
+      <c r="H90" s="22">
+        <v>6</v>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
@@ -4449,24 +4443,28 @@
       </c>
       <c r="D91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
-      </c>
-      <c r="G91" s="23">
-        <v>0</v>
-      </c>
-      <c r="H91" s="23">
-        <v>7</v>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H91" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
       </c>
       <c r="I91" s="21" t="inlineStr">
         <is>
@@ -4495,7 +4493,7 @@
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
@@ -4508,15 +4506,11 @@
           <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
-      <c r="G92" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H92" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
+      <c r="G92" s="22">
+        <v>0</v>
+      </c>
+      <c r="H92" s="22">
+        <v>7</v>
       </c>
       <c r="I92" s="20" t="inlineStr">
         <is>
@@ -4550,12 +4544,12 @@
       </c>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -4565,7 +4559,7 @@
       </c>
       <c r="H93" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I93" s="21" t="inlineStr">
@@ -4595,24 +4589,28 @@
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F94" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G94" s="22">
-        <v>0</v>
-      </c>
-      <c r="H94" s="22">
-        <v>3</v>
+          <t xml:space="preserve">رول رول</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H94" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول</t>
+        </is>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
@@ -4641,7 +4639,7 @@
       </c>
       <c r="D95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E95" s="19" t="inlineStr">
@@ -4654,15 +4652,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G95" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H95" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G95" s="23">
+        <v>0</v>
+      </c>
+      <c r="H95" s="23">
+        <v>3</v>
       </c>
       <c r="I95" s="21" t="inlineStr">
         <is>
@@ -4696,7 +4690,7 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
@@ -4746,7 +4740,7 @@
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
@@ -4796,7 +4790,7 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F98" s="22" t="inlineStr">
@@ -4846,12 +4840,12 @@
       </c>
       <c r="E99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -4861,7 +4855,7 @@
       </c>
       <c r="H99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I99" s="21" t="inlineStr">
@@ -4896,12 +4890,12 @@
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G100" s="22" t="inlineStr">
@@ -4911,7 +4905,7 @@
       </c>
       <c r="H100" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I100" s="20" t="inlineStr">
@@ -4946,12 +4940,12 @@
       </c>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -4961,7 +4955,7 @@
       </c>
       <c r="H101" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="I101" s="21" t="inlineStr">
@@ -4991,24 +4985,28 @@
       </c>
       <c r="D102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F102" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G102" s="22">
-        <v>0</v>
-      </c>
-      <c r="H102" s="22">
-        <v>5</v>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
+      </c>
+      <c r="G102" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H102" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
       </c>
       <c r="I102" s="20" t="inlineStr">
         <is>
@@ -5037,7 +5035,7 @@
       </c>
       <c r="D103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E103" s="19" t="inlineStr">
@@ -5050,15 +5048,11 @@
           <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
-      <c r="G103" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H103" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
+      <c r="G103" s="23">
+        <v>0</v>
+      </c>
+      <c r="H103" s="23">
+        <v>5</v>
       </c>
       <c r="I103" s="21" t="inlineStr">
         <is>
@@ -5087,24 +5081,28 @@
       </c>
       <c r="D104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G104" s="22">
-        <v>0</v>
-      </c>
-      <c r="H104" s="22">
-        <v>2</v>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G104" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H104" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
       </c>
       <c r="I104" s="20" t="inlineStr">
         <is>
@@ -5133,7 +5131,7 @@
       </c>
       <c r="D105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E105" s="19" t="inlineStr">
@@ -5146,15 +5144,11 @@
           <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
-      <c r="G105" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H105" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
+      <c r="G105" s="23">
+        <v>0</v>
+      </c>
+      <c r="H105" s="23">
+        <v>2</v>
       </c>
       <c r="I105" s="21" t="inlineStr">
         <is>
@@ -5183,24 +5177,28 @@
       </c>
       <c r="D106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G106" s="22">
-        <v>0</v>
-      </c>
-      <c r="H106" s="22">
-        <v>4</v>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G106" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H106" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
       </c>
       <c r="I106" s="20" t="inlineStr">
         <is>
@@ -5229,7 +5227,7 @@
       </c>
       <c r="D107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E107" s="19" t="inlineStr">
@@ -5242,15 +5240,11 @@
           <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
-      <c r="G107" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H107" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
+      <c r="G107" s="23">
+        <v>0</v>
+      </c>
+      <c r="H107" s="23">
+        <v>4</v>
       </c>
       <c r="I107" s="21" t="inlineStr">
         <is>
@@ -5284,12 +5278,12 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G108" s="22" t="inlineStr">
@@ -5299,7 +5293,7 @@
       </c>
       <c r="H108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I108" s="20" t="inlineStr">
@@ -5334,12 +5328,12 @@
       </c>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -5349,7 +5343,7 @@
       </c>
       <c r="H109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I109" s="21" t="inlineStr">
@@ -5384,12 +5378,12 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -5399,7 +5393,7 @@
       </c>
       <c r="H110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I110" s="20" t="inlineStr">
@@ -5434,12 +5428,12 @@
       </c>
       <c r="E111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -5449,7 +5443,7 @@
       </c>
       <c r="H111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I111" s="21" t="inlineStr">
@@ -5484,12 +5478,12 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G112" s="22" t="inlineStr">
@@ -5499,7 +5493,7 @@
       </c>
       <c r="H112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I112" s="20" t="inlineStr">
@@ -5534,12 +5528,12 @@
       </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -5549,7 +5543,7 @@
       </c>
       <c r="H113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I113" s="21" t="inlineStr">
@@ -5584,12 +5578,12 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G114" s="22" t="inlineStr">
@@ -5599,7 +5593,7 @@
       </c>
       <c r="H114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="I114" s="20" t="inlineStr">
@@ -5629,24 +5623,28 @@
       </c>
       <c r="D115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G115" s="23">
-        <v>0</v>
-      </c>
-      <c r="H115" s="23">
-        <v>4</v>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="G115" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H115" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
       </c>
       <c r="I115" s="21" t="inlineStr">
         <is>
@@ -5675,7 +5673,7 @@
       </c>
       <c r="D116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E116" s="17" t="inlineStr">
@@ -5688,15 +5686,11 @@
           <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
-      <c r="G116" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H116" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>4</v>
       </c>
       <c r="I116" s="20" t="inlineStr">
         <is>
@@ -5730,12 +5724,12 @@
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -5745,7 +5739,7 @@
       </c>
       <c r="H117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I117" s="21" t="inlineStr">
@@ -5780,12 +5774,12 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G118" s="22" t="inlineStr">
@@ -5795,7 +5789,7 @@
       </c>
       <c r="H118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I118" s="20" t="inlineStr">
@@ -5830,12 +5824,12 @@
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -5845,7 +5839,7 @@
       </c>
       <c r="H119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I119" s="21" t="inlineStr">
@@ -5880,12 +5874,12 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="G120" s="22" t="inlineStr">
@@ -5895,7 +5889,7 @@
       </c>
       <c r="H120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="I120" s="20" t="inlineStr">
@@ -5925,24 +5919,28 @@
       </c>
       <c r="D121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G121" s="23">
-        <v>0</v>
-      </c>
-      <c r="H121" s="23">
-        <v>4</v>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G121" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H121" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
       </c>
       <c r="I121" s="21" t="inlineStr">
         <is>
@@ -5971,7 +5969,7 @@
       </c>
       <c r="D122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E122" s="17" t="inlineStr">
@@ -5984,15 +5982,11 @@
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G122" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H122" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
+      <c r="G122" s="22">
+        <v>0</v>
+      </c>
+      <c r="H122" s="22">
+        <v>4</v>
       </c>
       <c r="I122" s="20" t="inlineStr">
         <is>
@@ -6026,132 +6020,138 @@
       </c>
       <c r="E123" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F123" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G123" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H123" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="I123" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J123" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="28" customHeight="1">
+      <c r="A124" s="16">
+        <v>3</v>
+      </c>
+      <c r="B124" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C124" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D124" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E124" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">68</t>
         </is>
       </c>
-      <c r="F123" s="23" t="inlineStr">
+      <c r="F124" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="G123" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H123" s="23" t="inlineStr">
+      <c r="G124" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H124" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="I123" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J123" s="19" t="inlineStr">
+      <c r="I124" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J124" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="48" customHeight="1">
-      <c r="A124" s="16">
-        <v>3</v>
-      </c>
-      <c r="B124" s="17" t="inlineStr">
+    <row r="125" ht="48" customHeight="1">
+      <c r="A125" s="18">
+        <v>3</v>
+      </c>
+      <c r="B125" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
-      <c r="C124" s="17" t="inlineStr">
+      <c r="C125" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
-      <c r="D124" s="17" t="inlineStr">
+      <c r="D125" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E124" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F124" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G124" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H124" s="22" t="inlineStr">
+      <c r="E125" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F125" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G125" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H125" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="I124" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J124" s="17" t="inlineStr">
+      <c r="I125" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J125" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="28" customHeight="1">
-      <c r="A125" s="18">
-        <v>2</v>
-      </c>
-      <c r="B125" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/23</t>
-        </is>
-      </c>
-      <c r="C125" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23:16:19</t>
-        </is>
-      </c>
-      <c r="D125" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E125" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="F125" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G125" s="23">
-        <v>4</v>
-      </c>
-      <c r="H125" s="23">
-        <v>0</v>
-      </c>
-      <c r="I125" s="21">
-        <v>4</v>
-      </c>
-      <c r="J125" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
     <row r="126" ht="28" customHeight="1">
       <c r="A126" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
@@ -6160,12 +6160,12 @@
       </c>
       <c r="C126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">23:16:19</t>
         </is>
       </c>
       <c r="D126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E126" s="17" t="inlineStr">
@@ -6179,19 +6179,17 @@
         </is>
       </c>
       <c r="G126" s="22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H126" s="22">
+        <v>0</v>
+      </c>
+      <c r="I126" s="20">
         <v>4</v>
       </c>
-      <c r="I126" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6209,7 @@
       </c>
       <c r="D127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E127" s="19" t="inlineStr">
@@ -6224,15 +6222,11 @@
           <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
-      <c r="G127" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H127" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
+      <c r="G127" s="23">
+        <v>0</v>
+      </c>
+      <c r="H127" s="23">
+        <v>4</v>
       </c>
       <c r="I127" s="21" t="inlineStr">
         <is>
@@ -6266,12 +6260,12 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F128" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G128" s="22" t="inlineStr">
@@ -6281,7 +6275,7 @@
       </c>
       <c r="H128" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="I128" s="20" t="inlineStr">
@@ -6316,7 +6310,7 @@
       </c>
       <c r="E129" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
@@ -6366,30 +6360,80 @@
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F130" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G130" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H130" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I130" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J130" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="28" customHeight="1">
+      <c r="A131" s="18">
+        <v>1</v>
+      </c>
+      <c r="B131" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C131" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D131" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E131" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F130" s="22" t="inlineStr">
+      <c r="F131" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G130" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H130" s="22" t="inlineStr">
+      <c r="G131" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H131" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I130" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J130" s="17" t="inlineStr">
+      <c r="I131" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J131" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J131" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J131"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J133" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J133"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:31:30</t>
+          <t xml:space="preserve">15:33:13</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -518,32 +518,32 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G6" s="22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H6" s="22">
         <v>0</v>
       </c>
       <c r="I6" s="20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5edabb20bb</t>
+          <t xml:space="preserve">28a1fcc537</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:53</t>
+          <t xml:space="preserve">15:33:05</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -562,32 +562,32 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G7" s="23">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H7" s="23">
         <v>0</v>
       </c>
       <c r="I7" s="21">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a1408f9e88</t>
+          <t xml:space="preserve">a734384c03</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:35</t>
+          <t xml:space="preserve">15:31:30</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -606,32 +606,32 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G8" s="22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H8" s="22">
         <v>0</v>
       </c>
       <c r="I8" s="20">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed45f1ef47</t>
+          <t xml:space="preserve">5edabb20bb</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="18">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:59</t>
+          <t xml:space="preserve">15:30:53</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -650,32 +650,32 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9" s="23">
         <v>0</v>
       </c>
       <c r="I9" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">d659616819</t>
+          <t xml:space="preserve">a1408f9e88</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:38</t>
+          <t xml:space="preserve">15:30:35</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G10" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" s="22">
         <v>0</v>
       </c>
       <c r="I10" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">19f5f6152e</t>
+          <t xml:space="preserve">ed45f1ef47</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="18">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:24</t>
+          <t xml:space="preserve">15:29:59</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -738,32 +738,32 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G11" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" s="23">
         <v>0</v>
       </c>
       <c r="I11" s="21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd714591b4</t>
+          <t xml:space="preserve">d659616819</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -772,22 +772,22 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:38</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G12" s="22">
@@ -796,20 +796,18 @@
       <c r="H12" s="22">
         <v>0</v>
       </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I12" s="20">
+        <v>2</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">19f5f6152e</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -818,22 +816,22 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:24</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G13" s="23">
@@ -842,14 +840,12 @@
       <c r="H13" s="23">
         <v>0</v>
       </c>
-      <c r="I13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I13" s="21">
+        <v>4</v>
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">bd714591b4</t>
         </is>
       </c>
     </row>
@@ -874,12 +870,12 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G14" s="22">
@@ -920,19 +916,19 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G15" s="23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H15" s="23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I15" s="21" t="inlineStr">
         <is>
@@ -966,19 +962,19 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G16" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" s="22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
@@ -1012,19 +1008,19 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G17" s="23">
         <v>0</v>
       </c>
       <c r="H17" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
@@ -1058,19 +1054,19 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G18" s="22">
         <v>0</v>
       </c>
       <c r="H18" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
@@ -1104,12 +1100,12 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G19" s="23">
@@ -1150,12 +1146,12 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G20" s="22">
@@ -1196,19 +1192,19 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G21" s="23">
         <v>0</v>
       </c>
       <c r="H21" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
@@ -1242,19 +1238,19 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G22" s="22">
         <v>0</v>
       </c>
       <c r="H22" s="22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
@@ -1288,19 +1284,19 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G23" s="23">
         <v>0</v>
       </c>
       <c r="H23" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
@@ -1334,19 +1330,19 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G24" s="22">
         <v>0</v>
       </c>
       <c r="H24" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -1380,19 +1376,19 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G25" s="23">
         <v>0</v>
       </c>
       <c r="H25" s="23">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
@@ -1426,19 +1422,19 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G26" s="22">
         <v>0</v>
       </c>
       <c r="H26" s="22">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
@@ -1472,19 +1468,19 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G27" s="23">
         <v>0</v>
       </c>
       <c r="H27" s="23">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
@@ -1518,19 +1514,19 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G28" s="22">
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -1564,19 +1560,19 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G29" s="23">
         <v>0</v>
       </c>
       <c r="H29" s="23">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
@@ -1610,19 +1606,19 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G30" s="22">
         <v>0</v>
       </c>
       <c r="H30" s="22">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
@@ -1656,19 +1652,19 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G31" s="23">
         <v>0</v>
       </c>
       <c r="H31" s="23">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
@@ -1702,19 +1698,19 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G32" s="22">
         <v>0</v>
       </c>
       <c r="H32" s="22">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
@@ -1748,19 +1744,19 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G33" s="23">
         <v>0</v>
       </c>
       <c r="H33" s="23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
@@ -1794,19 +1790,19 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G34" s="22">
         <v>0</v>
       </c>
       <c r="H34" s="22">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
@@ -1840,19 +1836,19 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G35" s="23">
         <v>0</v>
       </c>
       <c r="H35" s="23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1886,19 +1882,19 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G36" s="22">
         <v>0</v>
       </c>
       <c r="H36" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1932,19 +1928,19 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G37" s="23">
         <v>0</v>
       </c>
       <c r="H37" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1978,19 +1974,19 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G38" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -2005,7 +2001,7 @@
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
@@ -2014,7 +2010,7 @@
       </c>
       <c r="C39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
@@ -2024,12 +2020,12 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G39" s="23">
@@ -2045,13 +2041,13 @@
       </c>
       <c r="J39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
@@ -2060,7 +2056,7 @@
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D40" s="17" t="inlineStr">
@@ -2070,16 +2066,16 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G40" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="22">
         <v>4</v>
@@ -2091,7 +2087,7 @@
       </c>
       <c r="J40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
@@ -2116,12 +2112,12 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G41" s="23">
@@ -2162,19 +2158,19 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G42" s="22">
         <v>0</v>
       </c>
       <c r="H42" s="22">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
@@ -2208,19 +2204,19 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G43" s="23">
         <v>0</v>
       </c>
       <c r="H43" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I43" s="21" t="inlineStr">
         <is>
@@ -2254,19 +2250,19 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G44" s="22">
         <v>0</v>
       </c>
       <c r="H44" s="22">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
@@ -2279,9 +2275,9 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="48" customHeight="1">
+    <row r="45" ht="28" customHeight="1">
       <c r="A45" s="18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
@@ -2290,33 +2286,29 @@
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11:25:59</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">یادداشت و آمار قهوه</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G45" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
-        </is>
-      </c>
-      <c r="H45" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G45" s="23">
+        <v>0</v>
+      </c>
+      <c r="H45" s="23">
+        <v>4</v>
       </c>
       <c r="I45" s="21" t="inlineStr">
         <is>
@@ -2325,13 +2317,13 @@
       </c>
       <c r="J45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2688d62325</t>
+          <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="16">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
@@ -2340,42 +2332,44 @@
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:32</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G46" s="22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H46" s="22">
-        <v>0</v>
-      </c>
-      <c r="I46" s="20">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="I46" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">371938f24f</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28" customHeight="1">
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="48" customHeight="1">
       <c r="A47" s="18">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
@@ -2384,42 +2378,48 @@
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G47" s="23">
-        <v>4</v>
-      </c>
-      <c r="H47" s="23">
-        <v>0</v>
-      </c>
-      <c r="I47" s="21">
-        <v>4</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
+        </is>
+      </c>
+      <c r="H47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I47" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">2688d62325</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="16">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G48" s="22">
@@ -2457,13 +2457,13 @@
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="18">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
@@ -2482,32 +2482,32 @@
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G49" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H49" s="23">
         <v>0</v>
       </c>
       <c r="I49" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="16">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G50" s="22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H50" s="22">
         <v>0</v>
       </c>
       <c r="I50" s="20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="18">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G51" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H51" s="23">
         <v>0</v>
       </c>
       <c r="I51" s="21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="16">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -2614,32 +2614,32 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G52" s="22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H52" s="22">
         <v>0</v>
       </c>
       <c r="I52" s="20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="18">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D53" s="19" t="inlineStr">
@@ -2658,32 +2658,32 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G53" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H53" s="23">
         <v>0</v>
       </c>
       <c r="I53" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="16">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -2702,32 +2702,32 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G54" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H54" s="22">
         <v>0</v>
       </c>
       <c r="I54" s="20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="18">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -2746,32 +2746,32 @@
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G55" s="23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H55" s="23">
         <v>0</v>
       </c>
       <c r="I55" s="21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="16">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -2790,32 +2790,32 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G56" s="22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H56" s="22">
         <v>0</v>
       </c>
       <c r="I56" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -2834,32 +2834,32 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G57" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H57" s="23">
         <v>0</v>
       </c>
       <c r="I57" s="21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="16">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -2878,32 +2878,32 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G58" s="22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H58" s="22">
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -2922,76 +2922,76 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G59" s="23">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H59" s="23">
         <v>0</v>
       </c>
       <c r="I59" s="21">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="16">
+        <v>9</v>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:18:08</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37</t>
+        </is>
+      </c>
+      <c r="F60" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
+        </is>
+      </c>
+      <c r="G60" s="22">
         <v>7</v>
       </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:18:04</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E60" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24</t>
-        </is>
-      </c>
-      <c r="F60" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G60" s="22">
-        <v>3</v>
-      </c>
       <c r="H60" s="22">
         <v>0</v>
       </c>
       <c r="I60" s="20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
@@ -3010,32 +3010,32 @@
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G61" s="23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H61" s="23">
         <v>0</v>
       </c>
       <c r="I61" s="21">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G62" s="22">
@@ -3073,13 +3073,13 @@
       </c>
       <c r="J62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D63" s="19" t="inlineStr">
@@ -3098,118 +3098,114 @@
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G63" s="23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H63" s="23">
         <v>0</v>
       </c>
       <c r="I63" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G64" s="22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H64" s="22">
-        <v>5</v>
-      </c>
-      <c r="I64" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I64" s="20">
+        <v>3</v>
       </c>
       <c r="J64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G65" s="23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H65" s="23">
-        <v>3</v>
-      </c>
-      <c r="I65" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I65" s="21">
+        <v>5</v>
       </c>
       <c r="J65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -3229,28 +3225,24 @@
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
-      </c>
-      <c r="G66" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H66" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+          <t xml:space="preserve">تیتاپ نادری</t>
+        </is>
+      </c>
+      <c r="G66" s="22">
+        <v>0</v>
+      </c>
+      <c r="H66" s="22">
+        <v>5</v>
       </c>
       <c r="I66" s="20" t="inlineStr">
         <is>
@@ -3284,19 +3276,19 @@
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G67" s="23">
         <v>0</v>
       </c>
       <c r="H67" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I67" s="21" t="inlineStr">
         <is>
@@ -3330,12 +3322,12 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G68" s="22" t="inlineStr">
@@ -3345,7 +3337,7 @@
       </c>
       <c r="H68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="I68" s="20" t="inlineStr">
@@ -3375,28 +3367,24 @@
       </c>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H69" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
-        </is>
+          <t xml:space="preserve">ساندویچ مرغ</t>
+        </is>
+      </c>
+      <c r="G69" s="23">
+        <v>0</v>
+      </c>
+      <c r="H69" s="23">
+        <v>6</v>
       </c>
       <c r="I69" s="21" t="inlineStr">
         <is>
@@ -3430,22 +3418,22 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I70" s="20" t="inlineStr">
@@ -3480,22 +3468,22 @@
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I71" s="21" t="inlineStr">
@@ -3530,12 +3518,12 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G72" s="22" t="inlineStr">
@@ -3545,7 +3533,7 @@
       </c>
       <c r="H72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I72" s="20" t="inlineStr">
@@ -3575,24 +3563,28 @@
       </c>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G73" s="23">
-        <v>0</v>
-      </c>
-      <c r="H73" s="23">
-        <v>3</v>
+          <t xml:space="preserve">نات بار زرد</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H73" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">نات بار زرد</t>
+        </is>
       </c>
       <c r="I73" s="21" t="inlineStr">
         <is>
@@ -3626,12 +3618,12 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
         </is>
       </c>
       <c r="G74" s="22" t="inlineStr">
@@ -3641,7 +3633,7 @@
       </c>
       <c r="H74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
         </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
@@ -3676,12 +3668,12 @@
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G75" s="23">
@@ -3722,12 +3714,12 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G76" s="22" t="inlineStr">
@@ -3737,7 +3729,7 @@
       </c>
       <c r="H76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
@@ -3772,19 +3764,19 @@
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G77" s="23">
         <v>0</v>
       </c>
       <c r="H77" s="23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
@@ -3818,12 +3810,12 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G78" s="22" t="inlineStr">
@@ -3833,7 +3825,7 @@
       </c>
       <c r="H78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
@@ -3868,19 +3860,19 @@
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G79" s="23">
         <v>0</v>
       </c>
       <c r="H79" s="23">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I79" s="21" t="inlineStr">
         <is>
@@ -3914,12 +3906,12 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G80" s="22" t="inlineStr">
@@ -3929,7 +3921,7 @@
       </c>
       <c r="H80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
@@ -3959,28 +3951,24 @@
       </c>
       <c r="D81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H81" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کروسان</t>
-        </is>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
+        </is>
+      </c>
+      <c r="G81" s="23">
+        <v>0</v>
+      </c>
+      <c r="H81" s="23">
+        <v>9</v>
       </c>
       <c r="I81" s="21" t="inlineStr">
         <is>
@@ -4014,12 +4002,12 @@
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G82" s="22" t="inlineStr">
@@ -4029,7 +4017,7 @@
       </c>
       <c r="H82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
@@ -4059,24 +4047,28 @@
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G83" s="23">
-        <v>0</v>
-      </c>
-      <c r="H83" s="23">
-        <v>6</v>
+          <t xml:space="preserve">کروسان</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H83" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کروسان</t>
+        </is>
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
@@ -4110,12 +4102,12 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">وافل</t>
         </is>
       </c>
       <c r="G84" s="22" t="inlineStr">
@@ -4125,7 +4117,7 @@
       </c>
       <c r="H84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">وافل</t>
         </is>
       </c>
       <c r="I84" s="20" t="inlineStr">
@@ -4160,19 +4152,19 @@
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G85" s="23">
         <v>0</v>
       </c>
       <c r="H85" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I85" s="21" t="inlineStr">
         <is>
@@ -4206,12 +4198,12 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G86" s="22" t="inlineStr">
@@ -4221,7 +4213,7 @@
       </c>
       <c r="H86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
@@ -4251,28 +4243,24 @@
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
-        </is>
-      </c>
-      <c r="G87" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H87" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
-        </is>
+          <t xml:space="preserve">پاستیل</t>
+        </is>
+      </c>
+      <c r="G87" s="23">
+        <v>0</v>
+      </c>
+      <c r="H87" s="23">
+        <v>3</v>
       </c>
       <c r="I87" s="21" t="inlineStr">
         <is>
@@ -4301,24 +4289,28 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G88" s="22">
-        <v>0</v>
-      </c>
-      <c r="H88" s="22">
-        <v>4</v>
+          <t xml:space="preserve">پاستیل</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H88" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پاستیل</t>
+        </is>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
@@ -4352,12 +4344,12 @@
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -4367,7 +4359,7 @@
       </c>
       <c r="H89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="I89" s="21" t="inlineStr">
@@ -4402,19 +4394,19 @@
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G90" s="22">
         <v>0</v>
       </c>
       <c r="H90" s="22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
@@ -4448,12 +4440,12 @@
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -4463,7 +4455,7 @@
       </c>
       <c r="H91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="I91" s="21" t="inlineStr">
@@ -4498,19 +4490,19 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F92" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G92" s="22">
         <v>0</v>
       </c>
       <c r="H92" s="22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I92" s="20" t="inlineStr">
         <is>
@@ -4544,12 +4536,12 @@
       </c>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -4559,7 +4551,7 @@
       </c>
       <c r="H93" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="I93" s="21" t="inlineStr">
@@ -4589,28 +4581,24 @@
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F94" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
-        </is>
-      </c>
-      <c r="G94" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H94" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">رول رول</t>
-        </is>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
+        </is>
+      </c>
+      <c r="G94" s="22">
+        <v>0</v>
+      </c>
+      <c r="H94" s="22">
+        <v>7</v>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
@@ -4639,24 +4627,28 @@
       </c>
       <c r="D95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G95" s="23">
-        <v>0</v>
-      </c>
-      <c r="H95" s="23">
-        <v>3</v>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H95" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
+        </is>
       </c>
       <c r="I95" s="21" t="inlineStr">
         <is>
@@ -4690,12 +4682,12 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G96" s="22" t="inlineStr">
@@ -4705,7 +4697,7 @@
       </c>
       <c r="H96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="I96" s="20" t="inlineStr">
@@ -4735,12 +4727,12 @@
       </c>
       <c r="D97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
@@ -4748,15 +4740,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G97" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H97" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G97" s="23">
+        <v>0</v>
+      </c>
+      <c r="H97" s="23">
+        <v>3</v>
       </c>
       <c r="I97" s="21" t="inlineStr">
         <is>
@@ -4790,7 +4778,7 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F98" s="22" t="inlineStr">
@@ -4840,7 +4828,7 @@
       </c>
       <c r="E99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
@@ -4890,12 +4878,12 @@
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G100" s="22" t="inlineStr">
@@ -4905,7 +4893,7 @@
       </c>
       <c r="H100" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I100" s="20" t="inlineStr">
@@ -4940,12 +4928,12 @@
       </c>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -4955,7 +4943,7 @@
       </c>
       <c r="H101" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I101" s="21" t="inlineStr">
@@ -4990,12 +4978,12 @@
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F102" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G102" s="22" t="inlineStr">
@@ -5005,7 +4993,7 @@
       </c>
       <c r="H102" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I102" s="20" t="inlineStr">
@@ -5035,24 +5023,28 @@
       </c>
       <c r="D103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G103" s="23">
-        <v>0</v>
-      </c>
-      <c r="H103" s="23">
-        <v>5</v>
+          <t xml:space="preserve">توینکلز</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H103" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">توینکلز</t>
+        </is>
       </c>
       <c r="I103" s="21" t="inlineStr">
         <is>
@@ -5086,12 +5078,12 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G104" s="22" t="inlineStr">
@@ -5101,7 +5093,7 @@
       </c>
       <c r="H104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="I104" s="20" t="inlineStr">
@@ -5136,19 +5128,19 @@
       </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G105" s="23">
         <v>0</v>
       </c>
       <c r="H105" s="23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I105" s="21" t="inlineStr">
         <is>
@@ -5182,12 +5174,12 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G106" s="22" t="inlineStr">
@@ -5197,7 +5189,7 @@
       </c>
       <c r="H106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="I106" s="20" t="inlineStr">
@@ -5232,19 +5224,19 @@
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G107" s="23">
         <v>0</v>
       </c>
       <c r="H107" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I107" s="21" t="inlineStr">
         <is>
@@ -5278,12 +5270,12 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G108" s="22" t="inlineStr">
@@ -5293,7 +5285,7 @@
       </c>
       <c r="H108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="I108" s="20" t="inlineStr">
@@ -5323,28 +5315,24 @@
       </c>
       <c r="D109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
-        </is>
-      </c>
-      <c r="G109" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H109" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شیر شکلات</t>
-        </is>
+          <t xml:space="preserve">تیتو مزمز</t>
+        </is>
+      </c>
+      <c r="G109" s="23">
+        <v>0</v>
+      </c>
+      <c r="H109" s="23">
+        <v>4</v>
       </c>
       <c r="I109" s="21" t="inlineStr">
         <is>
@@ -5378,12 +5366,12 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -5393,7 +5381,7 @@
       </c>
       <c r="H110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I110" s="20" t="inlineStr">
@@ -5428,12 +5416,12 @@
       </c>
       <c r="E111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -5443,7 +5431,7 @@
       </c>
       <c r="H111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I111" s="21" t="inlineStr">
@@ -5478,12 +5466,12 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G112" s="22" t="inlineStr">
@@ -5493,7 +5481,7 @@
       </c>
       <c r="H112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I112" s="20" t="inlineStr">
@@ -5528,12 +5516,12 @@
       </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -5543,7 +5531,7 @@
       </c>
       <c r="H113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I113" s="21" t="inlineStr">
@@ -5578,12 +5566,12 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G114" s="22" t="inlineStr">
@@ -5593,7 +5581,7 @@
       </c>
       <c r="H114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I114" s="20" t="inlineStr">
@@ -5628,12 +5616,12 @@
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -5643,7 +5631,7 @@
       </c>
       <c r="H115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I115" s="21" t="inlineStr">
@@ -5673,24 +5661,28 @@
       </c>
       <c r="D116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G116" s="22">
-        <v>0</v>
-      </c>
-      <c r="H116" s="22">
-        <v>4</v>
+          <t xml:space="preserve">وجین</t>
+        </is>
+      </c>
+      <c r="G116" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H116" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وجین</t>
+        </is>
       </c>
       <c r="I116" s="20" t="inlineStr">
         <is>
@@ -5724,12 +5716,12 @@
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -5739,7 +5731,7 @@
       </c>
       <c r="H117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="I117" s="21" t="inlineStr">
@@ -5769,28 +5761,24 @@
       </c>
       <c r="D118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
-        </is>
-      </c>
-      <c r="G118" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H118" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
-        </is>
+          <t xml:space="preserve">پرو شیر</t>
+        </is>
+      </c>
+      <c r="G118" s="22">
+        <v>0</v>
+      </c>
+      <c r="H118" s="22">
+        <v>4</v>
       </c>
       <c r="I118" s="20" t="inlineStr">
         <is>
@@ -5824,12 +5812,12 @@
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -5839,7 +5827,7 @@
       </c>
       <c r="H119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I119" s="21" t="inlineStr">
@@ -5874,12 +5862,12 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G120" s="22" t="inlineStr">
@@ -5889,7 +5877,7 @@
       </c>
       <c r="H120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I120" s="20" t="inlineStr">
@@ -5924,12 +5912,12 @@
       </c>
       <c r="E121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -5939,7 +5927,7 @@
       </c>
       <c r="H121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I121" s="21" t="inlineStr">
@@ -5969,24 +5957,28 @@
       </c>
       <c r="D122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F122" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G122" s="22">
-        <v>0</v>
-      </c>
-      <c r="H122" s="22">
-        <v>4</v>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
+        </is>
+      </c>
+      <c r="G122" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H122" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
+        </is>
       </c>
       <c r="I122" s="20" t="inlineStr">
         <is>
@@ -6020,12 +6012,12 @@
       </c>
       <c r="E123" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -6035,7 +6027,7 @@
       </c>
       <c r="H123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="I123" s="21" t="inlineStr">
@@ -6065,67 +6057,63 @@
       </c>
       <c r="D124" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E124" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F124" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G124" s="22">
+        <v>0</v>
+      </c>
+      <c r="H124" s="22">
+        <v>4</v>
+      </c>
+      <c r="I124" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J124" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="28" customHeight="1">
+      <c r="A125" s="18">
+        <v>3</v>
+      </c>
+      <c r="B125" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C125" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D125" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
-      <c r="E124" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68</t>
-        </is>
-      </c>
-      <c r="F124" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف بدون قند</t>
-        </is>
-      </c>
-      <c r="G124" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H124" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف بدون قند</t>
-        </is>
-      </c>
-      <c r="I124" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J124" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="48" customHeight="1">
-      <c r="A125" s="18">
-        <v>3</v>
-      </c>
-      <c r="B125" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/24</t>
-        </is>
-      </c>
-      <c r="C125" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12:39:32</t>
-        </is>
-      </c>
-      <c r="D125" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">یادداشت و آمار قهوه</t>
-        </is>
-      </c>
       <c r="E125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -6135,7 +6123,7 @@
       </c>
       <c r="H125" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="I125" s="21" t="inlineStr">
@@ -6151,82 +6139,92 @@
     </row>
     <row r="126" ht="28" customHeight="1">
       <c r="A126" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/23</t>
+          <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
       <c r="C126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">23:16:19</t>
+          <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
       <c r="D126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">68</t>
         </is>
       </c>
       <c r="F126" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G126" s="22">
-        <v>4</v>
-      </c>
-      <c r="H126" s="22">
-        <v>0</v>
-      </c>
-      <c r="I126" s="20">
-        <v>4</v>
+          <t xml:space="preserve">لایف بدون قند</t>
+        </is>
+      </c>
+      <c r="G126" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H126" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف بدون قند</t>
+        </is>
+      </c>
+      <c r="I126" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">deac82c691</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="28" customHeight="1">
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="48" customHeight="1">
       <c r="A127" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/23</t>
+          <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
       <c r="C127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
       <c r="D127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
       <c r="E127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G127" s="23">
-        <v>0</v>
-      </c>
-      <c r="H127" s="23">
-        <v>4</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H127" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
+        </is>
       </c>
       <c r="I127" s="21" t="inlineStr">
         <is>
@@ -6235,13 +6233,13 @@
       </c>
       <c r="J127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
     <row r="128" ht="28" customHeight="1">
       <c r="A128" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B128" s="17" t="inlineStr">
         <is>
@@ -6250,12 +6248,12 @@
       </c>
       <c r="C128" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">23:16:19</t>
         </is>
       </c>
       <c r="D128" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E128" s="17" t="inlineStr">
@@ -6268,24 +6266,18 @@
           <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
-      <c r="G128" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H128" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="I128" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="G128" s="22">
+        <v>4</v>
+      </c>
+      <c r="H128" s="22">
+        <v>0</v>
+      </c>
+      <c r="I128" s="20">
+        <v>4</v>
       </c>
       <c r="J128" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
@@ -6305,28 +6297,24 @@
       </c>
       <c r="D129" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E129" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="G129" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H129" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
+          <t xml:space="preserve">تیتاپ نادری</t>
+        </is>
+      </c>
+      <c r="G129" s="23">
+        <v>0</v>
+      </c>
+      <c r="H129" s="23">
+        <v>4</v>
       </c>
       <c r="I129" s="21" t="inlineStr">
         <is>
@@ -6360,12 +6348,12 @@
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F130" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G130" s="22" t="inlineStr">
@@ -6375,7 +6363,7 @@
       </c>
       <c r="H130" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="I130" s="20" t="inlineStr">
@@ -6410,30 +6398,130 @@
       </c>
       <c r="E131" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="F131" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G131" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H131" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I131" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J131" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="28" customHeight="1">
+      <c r="A132" s="16">
+        <v>1</v>
+      </c>
+      <c r="B132" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C132" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D132" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E132" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F132" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G132" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H132" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I132" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J132" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="28" customHeight="1">
+      <c r="A133" s="18">
+        <v>1</v>
+      </c>
+      <c r="B133" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C133" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D133" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E133" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F131" s="23" t="inlineStr">
+      <c r="F133" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G131" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H131" s="23" t="inlineStr">
+      <c r="G133" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H133" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I131" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J131" s="19" t="inlineStr">
+      <c r="I133" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J133" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J133" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J133"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J134" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J134"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:13</t>
+          <t xml:space="preserve">15:33:18</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -518,32 +518,32 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G6" s="22">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H6" s="22">
         <v>0</v>
       </c>
       <c r="I6" s="20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">28a1fcc537</t>
+          <t xml:space="preserve">0be32d0353</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:05</t>
+          <t xml:space="preserve">15:33:13</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -562,32 +562,32 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G7" s="23">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H7" s="23">
         <v>0</v>
       </c>
       <c r="I7" s="21">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a734384c03</t>
+          <t xml:space="preserve">28a1fcc537</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:31:30</t>
+          <t xml:space="preserve">15:33:05</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -606,32 +606,32 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G8" s="22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H8" s="22">
         <v>0</v>
       </c>
       <c r="I8" s="20">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5edabb20bb</t>
+          <t xml:space="preserve">a734384c03</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="18">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:53</t>
+          <t xml:space="preserve">15:31:30</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -650,32 +650,32 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H9" s="23">
         <v>0</v>
       </c>
       <c r="I9" s="21">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a1408f9e88</t>
+          <t xml:space="preserve">5edabb20bb</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:35</t>
+          <t xml:space="preserve">15:30:53</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G10" s="22">
@@ -713,13 +713,13 @@
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed45f1ef47</t>
+          <t xml:space="preserve">a1408f9e88</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:59</t>
+          <t xml:space="preserve">15:30:35</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -738,32 +738,32 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G11" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11" s="23">
         <v>0</v>
       </c>
       <c r="I11" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">d659616819</t>
+          <t xml:space="preserve">ed45f1ef47</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:38</t>
+          <t xml:space="preserve">15:29:59</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G12" s="22">
@@ -801,13 +801,13 @@
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">19f5f6152e</t>
+          <t xml:space="preserve">d659616819</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:24</t>
+          <t xml:space="preserve">15:29:38</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -826,32 +826,32 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G13" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13" s="23">
         <v>0</v>
       </c>
       <c r="I13" s="21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd714591b4</t>
+          <t xml:space="preserve">19f5f6152e</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -860,38 +860,36 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:24</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G14" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" s="22">
         <v>0</v>
       </c>
-      <c r="I14" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I14" s="20">
+        <v>4</v>
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">bd714591b4</t>
         </is>
       </c>
     </row>
@@ -916,16 +914,16 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G15" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="23">
         <v>0</v>
@@ -962,16 +960,16 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G16" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" s="22">
         <v>0</v>
@@ -1008,19 +1006,19 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G17" s="23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" s="23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
@@ -1054,19 +1052,19 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G18" s="22">
         <v>0</v>
       </c>
       <c r="H18" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
@@ -1100,12 +1098,12 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G19" s="23">
@@ -1146,19 +1144,19 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G20" s="22">
         <v>0</v>
       </c>
       <c r="H20" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
@@ -1192,19 +1190,19 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G21" s="23">
         <v>0</v>
       </c>
       <c r="H21" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
@@ -1238,19 +1236,19 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G22" s="22">
         <v>0</v>
       </c>
       <c r="H22" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
@@ -1284,12 +1282,12 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G23" s="23">
@@ -1330,19 +1328,19 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G24" s="22">
         <v>0</v>
       </c>
       <c r="H24" s="22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -1376,19 +1374,19 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G25" s="23">
         <v>0</v>
       </c>
       <c r="H25" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
@@ -1422,12 +1420,12 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G26" s="22">
@@ -1468,19 +1466,19 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G27" s="23">
         <v>0</v>
       </c>
       <c r="H27" s="23">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
@@ -1514,19 +1512,19 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G28" s="22">
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -1560,19 +1558,19 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G29" s="23">
         <v>0</v>
       </c>
       <c r="H29" s="23">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
@@ -1606,19 +1604,19 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G30" s="22">
         <v>0</v>
       </c>
       <c r="H30" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
@@ -1652,19 +1650,19 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G31" s="23">
         <v>0</v>
       </c>
       <c r="H31" s="23">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
@@ -1698,19 +1696,19 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G32" s="22">
         <v>0</v>
       </c>
       <c r="H32" s="22">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
@@ -1744,19 +1742,19 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G33" s="23">
         <v>0</v>
       </c>
       <c r="H33" s="23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
@@ -1790,19 +1788,19 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G34" s="22">
         <v>0</v>
       </c>
       <c r="H34" s="22">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
@@ -1836,19 +1834,19 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G35" s="23">
         <v>0</v>
       </c>
       <c r="H35" s="23">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1882,19 +1880,19 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G36" s="22">
         <v>0</v>
       </c>
       <c r="H36" s="22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1928,12 +1926,12 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G37" s="23">
@@ -1974,19 +1972,19 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G38" s="22">
         <v>0</v>
       </c>
       <c r="H38" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -2020,12 +2018,12 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G39" s="23">
@@ -2066,19 +2064,19 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G40" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
@@ -2093,7 +2091,7 @@
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
@@ -2102,7 +2100,7 @@
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D41" s="19" t="inlineStr">
@@ -2112,19 +2110,19 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G41" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I41" s="21" t="inlineStr">
         <is>
@@ -2133,7 +2131,7 @@
       </c>
       <c r="J41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
@@ -2158,19 +2156,19 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G42" s="22">
         <v>0</v>
       </c>
       <c r="H42" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
@@ -2204,19 +2202,19 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G43" s="23">
         <v>0</v>
       </c>
       <c r="H43" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I43" s="21" t="inlineStr">
         <is>
@@ -2250,19 +2248,19 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G44" s="22">
         <v>0</v>
       </c>
       <c r="H44" s="22">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
@@ -2296,19 +2294,19 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G45" s="23">
         <v>0</v>
       </c>
       <c r="H45" s="23">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I45" s="21" t="inlineStr">
         <is>
@@ -2342,128 +2340,130 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="F46" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G46" s="22">
+        <v>0</v>
+      </c>
+      <c r="H46" s="22">
+        <v>4</v>
+      </c>
+      <c r="I46" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J46" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="18">
+        <v>23</v>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:59:31</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">67</t>
         </is>
       </c>
-      <c r="F46" s="22" t="inlineStr">
+      <c r="F47" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G46" s="22">
-        <v>0</v>
-      </c>
-      <c r="H46" s="22">
+      <c r="G47" s="23">
+        <v>0</v>
+      </c>
+      <c r="H47" s="23">
         <v>1</v>
       </c>
-      <c r="I46" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J46" s="17" t="inlineStr">
+      <c r="I47" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J47" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="48" customHeight="1">
-      <c r="A47" s="18">
+    <row r="48" ht="48" customHeight="1">
+      <c r="A48" s="16">
         <v>22</v>
       </c>
-      <c r="B47" s="19" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
-      <c r="C47" s="19" t="inlineStr">
+      <c r="C48" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
-      <c r="D47" s="19" t="inlineStr">
+      <c r="D48" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E47" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F47" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G47" s="23" t="inlineStr">
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="H47" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I47" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J47" s="19" t="inlineStr">
+      <c r="H48" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I48" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J48" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2688d62325</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="16">
-        <v>21</v>
-      </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:18:32</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E48" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62</t>
-        </is>
-      </c>
-      <c r="F48" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G48" s="22">
-        <v>4</v>
-      </c>
-      <c r="H48" s="22">
-        <v>0</v>
-      </c>
-      <c r="I48" s="20">
-        <v>4</v>
-      </c>
-      <c r="J48" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G49" s="23">
@@ -2501,13 +2501,13 @@
       </c>
       <c r="J49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="16">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G50" s="22">
@@ -2545,13 +2545,13 @@
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
@@ -2570,32 +2570,32 @@
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G51" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H51" s="23">
         <v>0</v>
       </c>
       <c r="I51" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -2614,32 +2614,32 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G52" s="22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H52" s="22">
         <v>0</v>
       </c>
       <c r="I52" s="20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D53" s="19" t="inlineStr">
@@ -2658,32 +2658,32 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G53" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H53" s="23">
         <v>0</v>
       </c>
       <c r="I53" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -2702,32 +2702,32 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G54" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H54" s="22">
         <v>0</v>
       </c>
       <c r="I54" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -2746,32 +2746,32 @@
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G55" s="23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H55" s="23">
         <v>0</v>
       </c>
       <c r="I55" s="21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -2790,32 +2790,32 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G56" s="22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H56" s="22">
         <v>0</v>
       </c>
       <c r="I56" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -2834,32 +2834,32 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G57" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H57" s="23">
         <v>0</v>
       </c>
       <c r="I57" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -2878,32 +2878,32 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G58" s="22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H58" s="22">
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -2922,32 +2922,32 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G59" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H59" s="23">
         <v>0</v>
       </c>
       <c r="I59" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G60" s="22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H60" s="22">
         <v>0</v>
       </c>
       <c r="I60" s="20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
@@ -3010,32 +3010,32 @@
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G61" s="23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H61" s="23">
         <v>0</v>
       </c>
       <c r="I61" s="21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
@@ -3054,32 +3054,32 @@
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G62" s="22">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H62" s="22">
         <v>0</v>
       </c>
       <c r="I62" s="20">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D63" s="19" t="inlineStr">
@@ -3098,32 +3098,32 @@
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G63" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H63" s="23">
         <v>0</v>
       </c>
       <c r="I63" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
@@ -3142,32 +3142,32 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G64" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H64" s="22">
         <v>0</v>
       </c>
       <c r="I64" s="20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -3186,46 +3186,46 @@
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G65" s="23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H65" s="23">
         <v>0</v>
       </c>
       <c r="I65" s="21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
@@ -3239,19 +3239,17 @@
         </is>
       </c>
       <c r="G66" s="22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H66" s="22">
+        <v>0</v>
+      </c>
+      <c r="I66" s="20">
         <v>5</v>
       </c>
-      <c r="I66" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -3276,19 +3274,19 @@
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G67" s="23">
         <v>0</v>
       </c>
       <c r="H67" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I67" s="21" t="inlineStr">
         <is>
@@ -3317,7 +3315,7 @@
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
@@ -3330,15 +3328,11 @@
           <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
-      <c r="G68" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H68" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+      <c r="G68" s="22">
+        <v>0</v>
+      </c>
+      <c r="H68" s="22">
+        <v>3</v>
       </c>
       <c r="I68" s="20" t="inlineStr">
         <is>
@@ -3367,24 +3361,28 @@
       </c>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G69" s="23">
-        <v>0</v>
-      </c>
-      <c r="H69" s="23">
-        <v>6</v>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H69" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
       </c>
       <c r="I69" s="21" t="inlineStr">
         <is>
@@ -3413,7 +3411,7 @@
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
@@ -3426,15 +3424,11 @@
           <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
-      <c r="G70" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H70" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
+      <c r="G70" s="22">
+        <v>0</v>
+      </c>
+      <c r="H70" s="22">
+        <v>6</v>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
@@ -3468,12 +3462,12 @@
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
@@ -3483,7 +3477,7 @@
       </c>
       <c r="H71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I71" s="21" t="inlineStr">
@@ -3518,22 +3512,22 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I72" s="20" t="inlineStr">
@@ -3568,12 +3562,12 @@
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -3583,7 +3577,7 @@
       </c>
       <c r="H73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I73" s="21" t="inlineStr">
@@ -3618,12 +3612,12 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G74" s="22" t="inlineStr">
@@ -3633,7 +3627,7 @@
       </c>
       <c r="H74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
@@ -3663,24 +3657,28 @@
       </c>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G75" s="23">
-        <v>0</v>
-      </c>
-      <c r="H75" s="23">
-        <v>3</v>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H75" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
       </c>
       <c r="I75" s="21" t="inlineStr">
         <is>
@@ -3709,7 +3707,7 @@
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
@@ -3722,15 +3720,11 @@
           <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
-      <c r="G76" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H76" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
+      <c r="G76" s="22">
+        <v>0</v>
+      </c>
+      <c r="H76" s="22">
+        <v>3</v>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
@@ -3759,24 +3753,28 @@
       </c>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G77" s="23">
-        <v>0</v>
-      </c>
-      <c r="H77" s="23">
-        <v>3</v>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H77" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
@@ -3805,7 +3803,7 @@
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
@@ -3818,15 +3816,11 @@
           <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
-      <c r="G78" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H78" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
+      <c r="G78" s="22">
+        <v>0</v>
+      </c>
+      <c r="H78" s="22">
+        <v>3</v>
       </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
@@ -3855,24 +3849,28 @@
       </c>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G79" s="23">
-        <v>0</v>
-      </c>
-      <c r="H79" s="23">
-        <v>5</v>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H79" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
       </c>
       <c r="I79" s="21" t="inlineStr">
         <is>
@@ -3901,7 +3899,7 @@
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
@@ -3914,15 +3912,11 @@
           <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
-      <c r="G80" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H80" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
+      <c r="G80" s="22">
+        <v>0</v>
+      </c>
+      <c r="H80" s="22">
+        <v>5</v>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
@@ -3951,24 +3945,28 @@
       </c>
       <c r="D81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="G81" s="23">
-        <v>0</v>
-      </c>
-      <c r="H81" s="23">
-        <v>9</v>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H81" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
       </c>
       <c r="I81" s="21" t="inlineStr">
         <is>
@@ -3997,7 +3995,7 @@
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
@@ -4010,15 +4008,11 @@
           <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
-      <c r="G82" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H82" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
+      <c r="G82" s="22">
+        <v>0</v>
+      </c>
+      <c r="H82" s="22">
+        <v>9</v>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
@@ -4052,12 +4046,12 @@
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -4067,7 +4061,7 @@
       </c>
       <c r="H83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I83" s="21" t="inlineStr">
@@ -4102,12 +4096,12 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G84" s="22" t="inlineStr">
@@ -4117,7 +4111,7 @@
       </c>
       <c r="H84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I84" s="20" t="inlineStr">
@@ -4147,24 +4141,28 @@
       </c>
       <c r="D85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G85" s="23">
-        <v>0</v>
-      </c>
-      <c r="H85" s="23">
-        <v>6</v>
+          <t xml:space="preserve">وافل</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H85" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وافل</t>
+        </is>
       </c>
       <c r="I85" s="21" t="inlineStr">
         <is>
@@ -4193,7 +4191,7 @@
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
@@ -4206,15 +4204,11 @@
           <t xml:space="preserve">کوکی</t>
         </is>
       </c>
-      <c r="G86" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H86" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
+      <c r="G86" s="22">
+        <v>0</v>
+      </c>
+      <c r="H86" s="22">
+        <v>6</v>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
@@ -4243,24 +4237,28 @@
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="G87" s="23">
-        <v>0</v>
-      </c>
-      <c r="H87" s="23">
-        <v>3</v>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
       </c>
       <c r="I87" s="21" t="inlineStr">
         <is>
@@ -4289,7 +4287,7 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
@@ -4302,15 +4300,11 @@
           <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
-      <c r="G88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
+      <c r="G88" s="22">
+        <v>0</v>
+      </c>
+      <c r="H88" s="22">
+        <v>3</v>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
@@ -4344,12 +4338,12 @@
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -4359,7 +4353,7 @@
       </c>
       <c r="H89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="I89" s="21" t="inlineStr">
@@ -4389,24 +4383,28 @@
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G90" s="22">
-        <v>0</v>
-      </c>
-      <c r="H90" s="22">
-        <v>4</v>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
+      </c>
+      <c r="G90" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H90" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
@@ -4435,7 +4433,7 @@
       </c>
       <c r="D91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E91" s="19" t="inlineStr">
@@ -4448,15 +4446,11 @@
           <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
-      <c r="G91" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H91" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
+      <c r="G91" s="23">
+        <v>0</v>
+      </c>
+      <c r="H91" s="23">
+        <v>4</v>
       </c>
       <c r="I91" s="21" t="inlineStr">
         <is>
@@ -4485,24 +4479,28 @@
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F92" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G92" s="22">
-        <v>0</v>
-      </c>
-      <c r="H92" s="22">
-        <v>6</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G92" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H92" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I92" s="20" t="inlineStr">
         <is>
@@ -4531,7 +4529,7 @@
       </c>
       <c r="D93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E93" s="19" t="inlineStr">
@@ -4544,15 +4542,11 @@
           <t xml:space="preserve">آجیل</t>
         </is>
       </c>
-      <c r="G93" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H93" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+      <c r="G93" s="23">
+        <v>0</v>
+      </c>
+      <c r="H93" s="23">
+        <v>6</v>
       </c>
       <c r="I93" s="21" t="inlineStr">
         <is>
@@ -4581,24 +4575,28 @@
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F94" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
-      </c>
-      <c r="G94" s="22">
-        <v>0</v>
-      </c>
-      <c r="H94" s="22">
-        <v>7</v>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H94" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
@@ -4627,7 +4625,7 @@
       </c>
       <c r="D95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E95" s="19" t="inlineStr">
@@ -4640,15 +4638,11 @@
           <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
-      <c r="G95" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H95" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
+      <c r="G95" s="23">
+        <v>0</v>
+      </c>
+      <c r="H95" s="23">
+        <v>7</v>
       </c>
       <c r="I95" s="21" t="inlineStr">
         <is>
@@ -4682,12 +4676,12 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G96" s="22" t="inlineStr">
@@ -4697,7 +4691,7 @@
       </c>
       <c r="H96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I96" s="20" t="inlineStr">
@@ -4727,24 +4721,28 @@
       </c>
       <c r="D97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G97" s="23">
-        <v>0</v>
-      </c>
-      <c r="H97" s="23">
-        <v>3</v>
+          <t xml:space="preserve">رول رول</t>
+        </is>
+      </c>
+      <c r="G97" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H97" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول</t>
+        </is>
       </c>
       <c r="I97" s="21" t="inlineStr">
         <is>
@@ -4773,7 +4771,7 @@
       </c>
       <c r="D98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E98" s="17" t="inlineStr">
@@ -4786,15 +4784,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G98" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H98" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G98" s="22">
+        <v>0</v>
+      </c>
+      <c r="H98" s="22">
+        <v>3</v>
       </c>
       <c r="I98" s="20" t="inlineStr">
         <is>
@@ -4828,7 +4822,7 @@
       </c>
       <c r="E99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
@@ -4878,7 +4872,7 @@
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F100" s="22" t="inlineStr">
@@ -4928,7 +4922,7 @@
       </c>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
@@ -4978,12 +4972,12 @@
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F102" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G102" s="22" t="inlineStr">
@@ -4993,7 +4987,7 @@
       </c>
       <c r="H102" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I102" s="20" t="inlineStr">
@@ -5028,12 +5022,12 @@
       </c>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -5043,7 +5037,7 @@
       </c>
       <c r="H103" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I103" s="21" t="inlineStr">
@@ -5078,12 +5072,12 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="G104" s="22" t="inlineStr">
@@ -5093,7 +5087,7 @@
       </c>
       <c r="H104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="I104" s="20" t="inlineStr">
@@ -5123,24 +5117,28 @@
       </c>
       <c r="D105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G105" s="23">
-        <v>0</v>
-      </c>
-      <c r="H105" s="23">
-        <v>5</v>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H105" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
       </c>
       <c r="I105" s="21" t="inlineStr">
         <is>
@@ -5169,7 +5167,7 @@
       </c>
       <c r="D106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E106" s="17" t="inlineStr">
@@ -5182,15 +5180,11 @@
           <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
-      <c r="G106" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H106" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
+      <c r="G106" s="22">
+        <v>0</v>
+      </c>
+      <c r="H106" s="22">
+        <v>5</v>
       </c>
       <c r="I106" s="20" t="inlineStr">
         <is>
@@ -5219,24 +5213,28 @@
       </c>
       <c r="D107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G107" s="23">
-        <v>0</v>
-      </c>
-      <c r="H107" s="23">
-        <v>2</v>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H107" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
       </c>
       <c r="I107" s="21" t="inlineStr">
         <is>
@@ -5265,7 +5263,7 @@
       </c>
       <c r="D108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E108" s="17" t="inlineStr">
@@ -5278,15 +5276,11 @@
           <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
-      <c r="G108" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H108" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>2</v>
       </c>
       <c r="I108" s="20" t="inlineStr">
         <is>
@@ -5315,24 +5309,28 @@
       </c>
       <c r="D109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G109" s="23">
-        <v>0</v>
-      </c>
-      <c r="H109" s="23">
-        <v>4</v>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G109" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H109" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
       </c>
       <c r="I109" s="21" t="inlineStr">
         <is>
@@ -5361,7 +5359,7 @@
       </c>
       <c r="D110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E110" s="17" t="inlineStr">
@@ -5374,15 +5372,11 @@
           <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
-      <c r="G110" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H110" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>4</v>
       </c>
       <c r="I110" s="20" t="inlineStr">
         <is>
@@ -5416,12 +5410,12 @@
       </c>
       <c r="E111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -5431,7 +5425,7 @@
       </c>
       <c r="H111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I111" s="21" t="inlineStr">
@@ -5466,12 +5460,12 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G112" s="22" t="inlineStr">
@@ -5481,7 +5475,7 @@
       </c>
       <c r="H112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I112" s="20" t="inlineStr">
@@ -5516,12 +5510,12 @@
       </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -5531,7 +5525,7 @@
       </c>
       <c r="H113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I113" s="21" t="inlineStr">
@@ -5566,12 +5560,12 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G114" s="22" t="inlineStr">
@@ -5581,7 +5575,7 @@
       </c>
       <c r="H114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I114" s="20" t="inlineStr">
@@ -5616,12 +5610,12 @@
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -5631,7 +5625,7 @@
       </c>
       <c r="H115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I115" s="21" t="inlineStr">
@@ -5666,12 +5660,12 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G116" s="22" t="inlineStr">
@@ -5681,7 +5675,7 @@
       </c>
       <c r="H116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I116" s="20" t="inlineStr">
@@ -5716,12 +5710,12 @@
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -5731,7 +5725,7 @@
       </c>
       <c r="H117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="I117" s="21" t="inlineStr">
@@ -5761,24 +5755,28 @@
       </c>
       <c r="D118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G118" s="22">
-        <v>0</v>
-      </c>
-      <c r="H118" s="22">
-        <v>4</v>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="G118" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H118" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
       </c>
       <c r="I118" s="20" t="inlineStr">
         <is>
@@ -5807,7 +5805,7 @@
       </c>
       <c r="D119" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E119" s="19" t="inlineStr">
@@ -5820,15 +5818,11 @@
           <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
-      <c r="G119" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H119" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
+      <c r="G119" s="23">
+        <v>0</v>
+      </c>
+      <c r="H119" s="23">
+        <v>4</v>
       </c>
       <c r="I119" s="21" t="inlineStr">
         <is>
@@ -5862,12 +5856,12 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G120" s="22" t="inlineStr">
@@ -5877,7 +5871,7 @@
       </c>
       <c r="H120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I120" s="20" t="inlineStr">
@@ -5912,12 +5906,12 @@
       </c>
       <c r="E121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -5927,7 +5921,7 @@
       </c>
       <c r="H121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I121" s="21" t="inlineStr">
@@ -5962,12 +5956,12 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F122" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G122" s="22" t="inlineStr">
@@ -5977,7 +5971,7 @@
       </c>
       <c r="H122" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I122" s="20" t="inlineStr">
@@ -6012,12 +6006,12 @@
       </c>
       <c r="E123" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -6027,7 +6021,7 @@
       </c>
       <c r="H123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="I123" s="21" t="inlineStr">
@@ -6057,24 +6051,28 @@
       </c>
       <c r="D124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F124" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G124" s="22">
-        <v>0</v>
-      </c>
-      <c r="H124" s="22">
-        <v>4</v>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G124" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H124" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
       </c>
       <c r="I124" s="20" t="inlineStr">
         <is>
@@ -6103,7 +6101,7 @@
       </c>
       <c r="D125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E125" s="19" t="inlineStr">
@@ -6116,15 +6114,11 @@
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G125" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H125" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
+      <c r="G125" s="23">
+        <v>0</v>
+      </c>
+      <c r="H125" s="23">
+        <v>4</v>
       </c>
       <c r="I125" s="21" t="inlineStr">
         <is>
@@ -6158,132 +6152,138 @@
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F126" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G126" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H126" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="I126" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J126" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="28" customHeight="1">
+      <c r="A127" s="18">
+        <v>3</v>
+      </c>
+      <c r="B127" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C127" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D127" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E127" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">68</t>
         </is>
       </c>
-      <c r="F126" s="22" t="inlineStr">
+      <c r="F127" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="G126" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H126" s="22" t="inlineStr">
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H127" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="I126" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J126" s="17" t="inlineStr">
+      <c r="I127" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J127" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="48" customHeight="1">
-      <c r="A127" s="18">
-        <v>3</v>
-      </c>
-      <c r="B127" s="19" t="inlineStr">
+    <row r="128" ht="48" customHeight="1">
+      <c r="A128" s="16">
+        <v>3</v>
+      </c>
+      <c r="B128" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
-      <c r="C127" s="19" t="inlineStr">
+      <c r="C128" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
-      <c r="D127" s="19" t="inlineStr">
+      <c r="D128" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E127" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F127" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G127" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H127" s="23" t="inlineStr">
+      <c r="E128" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F128" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G128" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H128" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="I127" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J127" s="19" t="inlineStr">
+      <c r="I128" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J128" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="28" customHeight="1">
-      <c r="A128" s="16">
-        <v>2</v>
-      </c>
-      <c r="B128" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/23</t>
-        </is>
-      </c>
-      <c r="C128" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23:16:19</t>
-        </is>
-      </c>
-      <c r="D128" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E128" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="F128" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G128" s="22">
-        <v>4</v>
-      </c>
-      <c r="H128" s="22">
-        <v>0</v>
-      </c>
-      <c r="I128" s="20">
-        <v>4</v>
-      </c>
-      <c r="J128" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
     <row r="129" ht="28" customHeight="1">
       <c r="A129" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B129" s="19" t="inlineStr">
         <is>
@@ -6292,12 +6292,12 @@
       </c>
       <c r="C129" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">23:16:19</t>
         </is>
       </c>
       <c r="D129" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E129" s="19" t="inlineStr">
@@ -6311,19 +6311,17 @@
         </is>
       </c>
       <c r="G129" s="23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H129" s="23">
+        <v>0</v>
+      </c>
+      <c r="I129" s="21">
         <v>4</v>
       </c>
-      <c r="I129" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J129" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6341,7 @@
       </c>
       <c r="D130" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E130" s="17" t="inlineStr">
@@ -6356,15 +6354,11 @@
           <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
-      <c r="G130" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H130" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
+      <c r="G130" s="22">
+        <v>0</v>
+      </c>
+      <c r="H130" s="22">
+        <v>4</v>
       </c>
       <c r="I130" s="20" t="inlineStr">
         <is>
@@ -6398,12 +6392,12 @@
       </c>
       <c r="E131" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -6413,7 +6407,7 @@
       </c>
       <c r="H131" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="I131" s="21" t="inlineStr">
@@ -6448,7 +6442,7 @@
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F132" s="22" t="inlineStr">
@@ -6498,30 +6492,80 @@
       </c>
       <c r="E133" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F133" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G133" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H133" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I133" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J133" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="28" customHeight="1">
+      <c r="A134" s="16">
+        <v>1</v>
+      </c>
+      <c r="B134" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C134" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D134" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E134" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F133" s="23" t="inlineStr">
+      <c r="F134" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G133" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H133" s="23" t="inlineStr">
+      <c r="G134" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H134" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I133" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J133" s="19" t="inlineStr">
+      <c r="I134" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J134" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J134" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J134"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J135" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J135"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:18</t>
+          <t xml:space="preserve">15:35:52</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -518,32 +518,32 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G6" s="22">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H6" s="22">
         <v>0</v>
       </c>
       <c r="I6" s="20">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">0be32d0353</t>
+          <t xml:space="preserve">751f8a7696</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:13</t>
+          <t xml:space="preserve">15:33:18</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -562,32 +562,32 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G7" s="23">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H7" s="23">
         <v>0</v>
       </c>
       <c r="I7" s="21">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">28a1fcc537</t>
+          <t xml:space="preserve">0be32d0353</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:05</t>
+          <t xml:space="preserve">15:33:13</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -606,32 +606,32 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G8" s="22">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H8" s="22">
         <v>0</v>
       </c>
       <c r="I8" s="20">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a734384c03</t>
+          <t xml:space="preserve">28a1fcc537</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="18">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:31:30</t>
+          <t xml:space="preserve">15:33:05</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -650,32 +650,32 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H9" s="23">
         <v>0</v>
       </c>
       <c r="I9" s="21">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5edabb20bb</t>
+          <t xml:space="preserve">a734384c03</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:53</t>
+          <t xml:space="preserve">15:31:30</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G10" s="22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H10" s="22">
         <v>0</v>
       </c>
       <c r="I10" s="20">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a1408f9e88</t>
+          <t xml:space="preserve">5edabb20bb</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="18">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:35</t>
+          <t xml:space="preserve">15:30:53</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G11" s="23">
@@ -757,13 +757,13 @@
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed45f1ef47</t>
+          <t xml:space="preserve">a1408f9e88</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:59</t>
+          <t xml:space="preserve">15:30:35</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
@@ -782,32 +782,32 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G12" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12" s="22">
         <v>0</v>
       </c>
       <c r="I12" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">d659616819</t>
+          <t xml:space="preserve">ed45f1ef47</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:38</t>
+          <t xml:space="preserve">15:29:59</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -826,12 +826,12 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G13" s="23">
@@ -845,13 +845,13 @@
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">19f5f6152e</t>
+          <t xml:space="preserve">d659616819</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:24</t>
+          <t xml:space="preserve">15:29:38</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
@@ -870,32 +870,32 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G14" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H14" s="22">
         <v>0</v>
       </c>
       <c r="I14" s="20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd714591b4</t>
+          <t xml:space="preserve">19f5f6152e</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
@@ -904,38 +904,36 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:24</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G15" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="23">
         <v>0</v>
       </c>
-      <c r="I15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I15" s="21">
+        <v>4</v>
       </c>
       <c r="J15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">bd714591b4</t>
         </is>
       </c>
     </row>
@@ -960,16 +958,16 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G16" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" s="22">
         <v>0</v>
@@ -1006,16 +1004,16 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G17" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" s="23">
         <v>0</v>
@@ -1052,19 +1050,19 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G18" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" s="22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
@@ -1098,19 +1096,19 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G19" s="23">
         <v>0</v>
       </c>
       <c r="H19" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
@@ -1144,12 +1142,12 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G20" s="22">
@@ -1190,19 +1188,19 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G21" s="23">
         <v>0</v>
       </c>
       <c r="H21" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
@@ -1236,19 +1234,19 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G22" s="22">
         <v>0</v>
       </c>
       <c r="H22" s="22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
@@ -1282,19 +1280,19 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G23" s="23">
         <v>0</v>
       </c>
       <c r="H23" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
@@ -1328,12 +1326,12 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G24" s="22">
@@ -1374,19 +1372,19 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G25" s="23">
         <v>0</v>
       </c>
       <c r="H25" s="23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
@@ -1420,19 +1418,19 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G26" s="22">
         <v>0</v>
       </c>
       <c r="H26" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
@@ -1466,12 +1464,12 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G27" s="23">
@@ -1512,19 +1510,19 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G28" s="22">
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -1558,19 +1556,19 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G29" s="23">
         <v>0</v>
       </c>
       <c r="H29" s="23">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
@@ -1604,19 +1602,19 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G30" s="22">
         <v>0</v>
       </c>
       <c r="H30" s="22">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
@@ -1650,19 +1648,19 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G31" s="23">
         <v>0</v>
       </c>
       <c r="H31" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
@@ -1696,19 +1694,19 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G32" s="22">
         <v>0</v>
       </c>
       <c r="H32" s="22">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
@@ -1742,19 +1740,19 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G33" s="23">
         <v>0</v>
       </c>
       <c r="H33" s="23">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
@@ -1788,19 +1786,19 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G34" s="22">
         <v>0</v>
       </c>
       <c r="H34" s="22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
@@ -1834,19 +1832,19 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G35" s="23">
         <v>0</v>
       </c>
       <c r="H35" s="23">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1880,19 +1878,19 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G36" s="22">
         <v>0</v>
       </c>
       <c r="H36" s="22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1926,19 +1924,19 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G37" s="23">
         <v>0</v>
       </c>
       <c r="H37" s="23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1972,12 +1970,12 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G38" s="22">
@@ -2018,19 +2016,19 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G39" s="23">
         <v>0</v>
       </c>
       <c r="H39" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
@@ -2064,12 +2062,12 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G40" s="22">
@@ -2110,19 +2108,19 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G41" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I41" s="21" t="inlineStr">
         <is>
@@ -2137,7 +2135,7 @@
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
@@ -2146,7 +2144,7 @@
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D42" s="17" t="inlineStr">
@@ -2156,19 +2154,19 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G42" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
@@ -2177,7 +2175,7 @@
       </c>
       <c r="J42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
@@ -2202,19 +2200,19 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G43" s="23">
         <v>0</v>
       </c>
       <c r="H43" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I43" s="21" t="inlineStr">
         <is>
@@ -2248,19 +2246,19 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G44" s="22">
         <v>0</v>
       </c>
       <c r="H44" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
@@ -2294,19 +2292,19 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G45" s="23">
         <v>0</v>
       </c>
       <c r="H45" s="23">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I45" s="21" t="inlineStr">
         <is>
@@ -2340,19 +2338,19 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G46" s="22">
         <v>0</v>
       </c>
       <c r="H46" s="22">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
@@ -2386,128 +2384,130 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G47" s="23">
+        <v>0</v>
+      </c>
+      <c r="H47" s="23">
+        <v>4</v>
+      </c>
+      <c r="I47" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J47" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="16">
+        <v>23</v>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:59:31</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">67</t>
         </is>
       </c>
-      <c r="F47" s="23" t="inlineStr">
+      <c r="F48" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G47" s="23">
-        <v>0</v>
-      </c>
-      <c r="H47" s="23">
+      <c r="G48" s="22">
+        <v>0</v>
+      </c>
+      <c r="H48" s="22">
         <v>1</v>
       </c>
-      <c r="I47" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J47" s="19" t="inlineStr">
+      <c r="I48" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J48" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="48" customHeight="1">
-      <c r="A48" s="16">
+    <row r="49" ht="48" customHeight="1">
+      <c r="A49" s="18">
         <v>22</v>
       </c>
-      <c r="B48" s="17" t="inlineStr">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
-      <c r="C48" s="17" t="inlineStr">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D49" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E48" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F48" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G48" s="22" t="inlineStr">
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="H48" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I48" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J48" s="17" t="inlineStr">
+      <c r="H49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I49" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">2688d62325</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="18">
-        <v>21</v>
-      </c>
-      <c r="B49" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C49" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:18:32</t>
-        </is>
-      </c>
-      <c r="D49" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E49" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62</t>
-        </is>
-      </c>
-      <c r="F49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G49" s="23">
-        <v>4</v>
-      </c>
-      <c r="H49" s="23">
-        <v>0</v>
-      </c>
-      <c r="I49" s="21">
-        <v>4</v>
-      </c>
-      <c r="J49" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G50" s="22">
@@ -2545,13 +2545,13 @@
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="18">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G51" s="23">
@@ -2589,13 +2589,13 @@
       </c>
       <c r="J51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -2614,32 +2614,32 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G52" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H52" s="22">
         <v>0</v>
       </c>
       <c r="I52" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D53" s="19" t="inlineStr">
@@ -2658,32 +2658,32 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G53" s="23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H53" s="23">
         <v>0</v>
       </c>
       <c r="I53" s="21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -2702,32 +2702,32 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G54" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H54" s="22">
         <v>0</v>
       </c>
       <c r="I54" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -2746,32 +2746,32 @@
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G55" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H55" s="23">
         <v>0</v>
       </c>
       <c r="I55" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -2790,32 +2790,32 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G56" s="22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H56" s="22">
         <v>0</v>
       </c>
       <c r="I56" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -2834,32 +2834,32 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G57" s="23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H57" s="23">
         <v>0</v>
       </c>
       <c r="I57" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -2878,32 +2878,32 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G58" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H58" s="22">
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -2922,32 +2922,32 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G59" s="23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H59" s="23">
         <v>0</v>
       </c>
       <c r="I59" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G60" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H60" s="22">
         <v>0</v>
       </c>
       <c r="I60" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
@@ -3010,32 +3010,32 @@
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G61" s="23">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H61" s="23">
         <v>0</v>
       </c>
       <c r="I61" s="21">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
@@ -3054,32 +3054,32 @@
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G62" s="22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H62" s="22">
         <v>0</v>
       </c>
       <c r="I62" s="20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D63" s="19" t="inlineStr">
@@ -3098,32 +3098,32 @@
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G63" s="23">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H63" s="23">
         <v>0</v>
       </c>
       <c r="I63" s="21">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
@@ -3142,32 +3142,32 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G64" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H64" s="22">
         <v>0</v>
       </c>
       <c r="I64" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -3186,32 +3186,32 @@
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G65" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H65" s="23">
         <v>0</v>
       </c>
       <c r="I65" s="21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
@@ -3230,46 +3230,46 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G66" s="22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H66" s="22">
         <v>0</v>
       </c>
       <c r="I66" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
@@ -3283,19 +3283,17 @@
         </is>
       </c>
       <c r="G67" s="23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H67" s="23">
+        <v>0</v>
+      </c>
+      <c r="I67" s="21">
         <v>5</v>
       </c>
-      <c r="I67" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -3320,19 +3318,19 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G68" s="22">
         <v>0</v>
       </c>
       <c r="H68" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I68" s="20" t="inlineStr">
         <is>
@@ -3361,7 +3359,7 @@
       </c>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
@@ -3374,15 +3372,11 @@
           <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
-      <c r="G69" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H69" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+      <c r="G69" s="23">
+        <v>0</v>
+      </c>
+      <c r="H69" s="23">
+        <v>3</v>
       </c>
       <c r="I69" s="21" t="inlineStr">
         <is>
@@ -3411,24 +3405,28 @@
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G70" s="22">
-        <v>0</v>
-      </c>
-      <c r="H70" s="22">
-        <v>6</v>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H70" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
@@ -3457,7 +3455,7 @@
       </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
@@ -3470,15 +3468,11 @@
           <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
-      <c r="G71" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H71" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
+      <c r="G71" s="23">
+        <v>0</v>
+      </c>
+      <c r="H71" s="23">
+        <v>6</v>
       </c>
       <c r="I71" s="21" t="inlineStr">
         <is>
@@ -3512,12 +3506,12 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G72" s="22" t="inlineStr">
@@ -3527,7 +3521,7 @@
       </c>
       <c r="H72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I72" s="20" t="inlineStr">
@@ -3562,22 +3556,22 @@
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I73" s="21" t="inlineStr">
@@ -3612,12 +3606,12 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G74" s="22" t="inlineStr">
@@ -3627,7 +3621,7 @@
       </c>
       <c r="H74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
@@ -3662,12 +3656,12 @@
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -3677,7 +3671,7 @@
       </c>
       <c r="H75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="I75" s="21" t="inlineStr">
@@ -3707,24 +3701,28 @@
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G76" s="22">
-        <v>0</v>
-      </c>
-      <c r="H76" s="22">
-        <v>3</v>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H76" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
@@ -3753,7 +3751,7 @@
       </c>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
@@ -3766,15 +3764,11 @@
           <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
-      <c r="G77" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H77" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
+      <c r="G77" s="23">
+        <v>0</v>
+      </c>
+      <c r="H77" s="23">
+        <v>3</v>
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
@@ -3803,24 +3797,28 @@
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G78" s="22">
-        <v>0</v>
-      </c>
-      <c r="H78" s="22">
-        <v>3</v>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H78" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
@@ -3849,7 +3847,7 @@
       </c>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3862,15 +3860,11 @@
           <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
-      <c r="G79" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H79" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
+      <c r="G79" s="23">
+        <v>0</v>
+      </c>
+      <c r="H79" s="23">
+        <v>3</v>
       </c>
       <c r="I79" s="21" t="inlineStr">
         <is>
@@ -3899,24 +3893,28 @@
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G80" s="22">
-        <v>0</v>
-      </c>
-      <c r="H80" s="22">
-        <v>5</v>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H80" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
@@ -3945,7 +3943,7 @@
       </c>
       <c r="D81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
@@ -3958,15 +3956,11 @@
           <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
-      <c r="G81" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H81" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
+      <c r="G81" s="23">
+        <v>0</v>
+      </c>
+      <c r="H81" s="23">
+        <v>5</v>
       </c>
       <c r="I81" s="21" t="inlineStr">
         <is>
@@ -3995,24 +3989,28 @@
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="G82" s="22">
-        <v>0</v>
-      </c>
-      <c r="H82" s="22">
-        <v>9</v>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H82" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
@@ -4041,7 +4039,7 @@
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
@@ -4054,15 +4052,11 @@
           <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
-      <c r="G83" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H83" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
+      <c r="G83" s="23">
+        <v>0</v>
+      </c>
+      <c r="H83" s="23">
+        <v>9</v>
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
@@ -4096,12 +4090,12 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G84" s="22" t="inlineStr">
@@ -4111,7 +4105,7 @@
       </c>
       <c r="H84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I84" s="20" t="inlineStr">
@@ -4146,12 +4140,12 @@
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -4161,7 +4155,7 @@
       </c>
       <c r="H85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I85" s="21" t="inlineStr">
@@ -4191,24 +4185,28 @@
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G86" s="22">
-        <v>0</v>
-      </c>
-      <c r="H86" s="22">
-        <v>6</v>
+          <t xml:space="preserve">وافل</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H86" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وافل</t>
+        </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
@@ -4237,7 +4235,7 @@
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
@@ -4250,15 +4248,11 @@
           <t xml:space="preserve">کوکی</t>
         </is>
       </c>
-      <c r="G87" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H87" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
+      <c r="G87" s="23">
+        <v>0</v>
+      </c>
+      <c r="H87" s="23">
+        <v>6</v>
       </c>
       <c r="I87" s="21" t="inlineStr">
         <is>
@@ -4287,24 +4281,28 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="G88" s="22">
-        <v>0</v>
-      </c>
-      <c r="H88" s="22">
-        <v>3</v>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H88" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
@@ -4333,7 +4331,7 @@
       </c>
       <c r="D89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
@@ -4346,15 +4344,11 @@
           <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
-      <c r="G89" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H89" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
+      <c r="G89" s="23">
+        <v>0</v>
+      </c>
+      <c r="H89" s="23">
+        <v>3</v>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
@@ -4388,12 +4382,12 @@
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G90" s="22" t="inlineStr">
@@ -4403,7 +4397,7 @@
       </c>
       <c r="H90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="I90" s="20" t="inlineStr">
@@ -4433,24 +4427,28 @@
       </c>
       <c r="D91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G91" s="23">
-        <v>0</v>
-      </c>
-      <c r="H91" s="23">
-        <v>4</v>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H91" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
       </c>
       <c r="I91" s="21" t="inlineStr">
         <is>
@@ -4479,7 +4477,7 @@
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
@@ -4492,15 +4490,11 @@
           <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
-      <c r="G92" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H92" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
+      <c r="G92" s="22">
+        <v>0</v>
+      </c>
+      <c r="H92" s="22">
+        <v>4</v>
       </c>
       <c r="I92" s="20" t="inlineStr">
         <is>
@@ -4529,24 +4523,28 @@
       </c>
       <c r="D93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G93" s="23">
-        <v>0</v>
-      </c>
-      <c r="H93" s="23">
-        <v>6</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H93" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I93" s="21" t="inlineStr">
         <is>
@@ -4575,7 +4573,7 @@
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
@@ -4588,15 +4586,11 @@
           <t xml:space="preserve">آجیل</t>
         </is>
       </c>
-      <c r="G94" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H94" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+      <c r="G94" s="22">
+        <v>0</v>
+      </c>
+      <c r="H94" s="22">
+        <v>6</v>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
@@ -4625,24 +4619,28 @@
       </c>
       <c r="D95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
-      </c>
-      <c r="G95" s="23">
-        <v>0</v>
-      </c>
-      <c r="H95" s="23">
-        <v>7</v>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H95" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
       </c>
       <c r="I95" s="21" t="inlineStr">
         <is>
@@ -4671,7 +4669,7 @@
       </c>
       <c r="D96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E96" s="17" t="inlineStr">
@@ -4684,15 +4682,11 @@
           <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
-      <c r="G96" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H96" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
+      <c r="G96" s="22">
+        <v>0</v>
+      </c>
+      <c r="H96" s="22">
+        <v>7</v>
       </c>
       <c r="I96" s="20" t="inlineStr">
         <is>
@@ -4726,12 +4720,12 @@
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -4741,7 +4735,7 @@
       </c>
       <c r="H97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I97" s="21" t="inlineStr">
@@ -4771,24 +4765,28 @@
       </c>
       <c r="D98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F98" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G98" s="22">
-        <v>0</v>
-      </c>
-      <c r="H98" s="22">
-        <v>3</v>
+          <t xml:space="preserve">رول رول</t>
+        </is>
+      </c>
+      <c r="G98" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H98" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول</t>
+        </is>
       </c>
       <c r="I98" s="20" t="inlineStr">
         <is>
@@ -4817,7 +4815,7 @@
       </c>
       <c r="D99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E99" s="19" t="inlineStr">
@@ -4830,15 +4828,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G99" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H99" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G99" s="23">
+        <v>0</v>
+      </c>
+      <c r="H99" s="23">
+        <v>3</v>
       </c>
       <c r="I99" s="21" t="inlineStr">
         <is>
@@ -4872,7 +4866,7 @@
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F100" s="22" t="inlineStr">
@@ -4922,7 +4916,7 @@
       </c>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
@@ -4972,7 +4966,7 @@
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F102" s="22" t="inlineStr">
@@ -5022,12 +5016,12 @@
       </c>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -5037,7 +5031,7 @@
       </c>
       <c r="H103" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I103" s="21" t="inlineStr">
@@ -5072,12 +5066,12 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G104" s="22" t="inlineStr">
@@ -5087,7 +5081,7 @@
       </c>
       <c r="H104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I104" s="20" t="inlineStr">
@@ -5122,12 +5116,12 @@
       </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -5137,7 +5131,7 @@
       </c>
       <c r="H105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="I105" s="21" t="inlineStr">
@@ -5167,24 +5161,28 @@
       </c>
       <c r="D106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G106" s="22">
-        <v>0</v>
-      </c>
-      <c r="H106" s="22">
-        <v>5</v>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
+      </c>
+      <c r="G106" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H106" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
       </c>
       <c r="I106" s="20" t="inlineStr">
         <is>
@@ -5213,7 +5211,7 @@
       </c>
       <c r="D107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E107" s="19" t="inlineStr">
@@ -5226,15 +5224,11 @@
           <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
-      <c r="G107" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H107" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
+      <c r="G107" s="23">
+        <v>0</v>
+      </c>
+      <c r="H107" s="23">
+        <v>5</v>
       </c>
       <c r="I107" s="21" t="inlineStr">
         <is>
@@ -5263,24 +5257,28 @@
       </c>
       <c r="D108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G108" s="22">
-        <v>0</v>
-      </c>
-      <c r="H108" s="22">
-        <v>2</v>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G108" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H108" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
       </c>
       <c r="I108" s="20" t="inlineStr">
         <is>
@@ -5309,7 +5307,7 @@
       </c>
       <c r="D109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E109" s="19" t="inlineStr">
@@ -5322,15 +5320,11 @@
           <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
-      <c r="G109" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H109" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
+      <c r="G109" s="23">
+        <v>0</v>
+      </c>
+      <c r="H109" s="23">
+        <v>2</v>
       </c>
       <c r="I109" s="21" t="inlineStr">
         <is>
@@ -5359,24 +5353,28 @@
       </c>
       <c r="D110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G110" s="22">
-        <v>0</v>
-      </c>
-      <c r="H110" s="22">
-        <v>4</v>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G110" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H110" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
       </c>
       <c r="I110" s="20" t="inlineStr">
         <is>
@@ -5405,7 +5403,7 @@
       </c>
       <c r="D111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E111" s="19" t="inlineStr">
@@ -5418,15 +5416,11 @@
           <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
-      <c r="G111" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H111" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
+      <c r="G111" s="23">
+        <v>0</v>
+      </c>
+      <c r="H111" s="23">
+        <v>4</v>
       </c>
       <c r="I111" s="21" t="inlineStr">
         <is>
@@ -5460,12 +5454,12 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G112" s="22" t="inlineStr">
@@ -5475,7 +5469,7 @@
       </c>
       <c r="H112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I112" s="20" t="inlineStr">
@@ -5510,12 +5504,12 @@
       </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -5525,7 +5519,7 @@
       </c>
       <c r="H113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I113" s="21" t="inlineStr">
@@ -5560,12 +5554,12 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G114" s="22" t="inlineStr">
@@ -5575,7 +5569,7 @@
       </c>
       <c r="H114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I114" s="20" t="inlineStr">
@@ -5610,12 +5604,12 @@
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -5625,7 +5619,7 @@
       </c>
       <c r="H115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I115" s="21" t="inlineStr">
@@ -5660,12 +5654,12 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G116" s="22" t="inlineStr">
@@ -5675,7 +5669,7 @@
       </c>
       <c r="H116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I116" s="20" t="inlineStr">
@@ -5710,12 +5704,12 @@
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -5725,7 +5719,7 @@
       </c>
       <c r="H117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I117" s="21" t="inlineStr">
@@ -5760,12 +5754,12 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G118" s="22" t="inlineStr">
@@ -5775,7 +5769,7 @@
       </c>
       <c r="H118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="I118" s="20" t="inlineStr">
@@ -5805,24 +5799,28 @@
       </c>
       <c r="D119" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G119" s="23">
-        <v>0</v>
-      </c>
-      <c r="H119" s="23">
-        <v>4</v>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="G119" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H119" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
       </c>
       <c r="I119" s="21" t="inlineStr">
         <is>
@@ -5851,7 +5849,7 @@
       </c>
       <c r="D120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E120" s="17" t="inlineStr">
@@ -5864,15 +5862,11 @@
           <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
-      <c r="G120" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H120" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
+      <c r="G120" s="22">
+        <v>0</v>
+      </c>
+      <c r="H120" s="22">
+        <v>4</v>
       </c>
       <c r="I120" s="20" t="inlineStr">
         <is>
@@ -5906,12 +5900,12 @@
       </c>
       <c r="E121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -5921,7 +5915,7 @@
       </c>
       <c r="H121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I121" s="21" t="inlineStr">
@@ -5956,12 +5950,12 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F122" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G122" s="22" t="inlineStr">
@@ -5971,7 +5965,7 @@
       </c>
       <c r="H122" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I122" s="20" t="inlineStr">
@@ -6006,12 +6000,12 @@
       </c>
       <c r="E123" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -6021,7 +6015,7 @@
       </c>
       <c r="H123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I123" s="21" t="inlineStr">
@@ -6056,12 +6050,12 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F124" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="G124" s="22" t="inlineStr">
@@ -6071,7 +6065,7 @@
       </c>
       <c r="H124" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="I124" s="20" t="inlineStr">
@@ -6101,24 +6095,28 @@
       </c>
       <c r="D125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G125" s="23">
-        <v>0</v>
-      </c>
-      <c r="H125" s="23">
-        <v>4</v>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G125" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H125" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
       </c>
       <c r="I125" s="21" t="inlineStr">
         <is>
@@ -6147,7 +6145,7 @@
       </c>
       <c r="D126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E126" s="17" t="inlineStr">
@@ -6160,15 +6158,11 @@
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G126" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H126" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
+      <c r="G126" s="22">
+        <v>0</v>
+      </c>
+      <c r="H126" s="22">
+        <v>4</v>
       </c>
       <c r="I126" s="20" t="inlineStr">
         <is>
@@ -6202,132 +6196,138 @@
       </c>
       <c r="E127" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F127" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H127" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="I127" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J127" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="28" customHeight="1">
+      <c r="A128" s="16">
+        <v>3</v>
+      </c>
+      <c r="B128" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C128" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D128" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E128" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">68</t>
         </is>
       </c>
-      <c r="F127" s="23" t="inlineStr">
+      <c r="F128" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="G127" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H127" s="23" t="inlineStr">
+      <c r="G128" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H128" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="I127" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J127" s="19" t="inlineStr">
+      <c r="I128" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J128" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="48" customHeight="1">
-      <c r="A128" s="16">
-        <v>3</v>
-      </c>
-      <c r="B128" s="17" t="inlineStr">
+    <row r="129" ht="48" customHeight="1">
+      <c r="A129" s="18">
+        <v>3</v>
+      </c>
+      <c r="B129" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
-      <c r="C128" s="17" t="inlineStr">
+      <c r="C129" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
-      <c r="D128" s="17" t="inlineStr">
+      <c r="D129" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E128" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F128" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G128" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H128" s="22" t="inlineStr">
+      <c r="E129" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F129" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G129" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H129" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="I128" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J128" s="17" t="inlineStr">
+      <c r="I129" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J129" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="28" customHeight="1">
-      <c r="A129" s="18">
-        <v>2</v>
-      </c>
-      <c r="B129" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/23</t>
-        </is>
-      </c>
-      <c r="C129" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23:16:19</t>
-        </is>
-      </c>
-      <c r="D129" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E129" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="F129" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G129" s="23">
-        <v>4</v>
-      </c>
-      <c r="H129" s="23">
-        <v>0</v>
-      </c>
-      <c r="I129" s="21">
-        <v>4</v>
-      </c>
-      <c r="J129" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
     <row r="130" ht="28" customHeight="1">
       <c r="A130" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B130" s="17" t="inlineStr">
         <is>
@@ -6336,12 +6336,12 @@
       </c>
       <c r="C130" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">23:16:19</t>
         </is>
       </c>
       <c r="D130" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E130" s="17" t="inlineStr">
@@ -6355,19 +6355,17 @@
         </is>
       </c>
       <c r="G130" s="22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H130" s="22">
+        <v>0</v>
+      </c>
+      <c r="I130" s="20">
         <v>4</v>
       </c>
-      <c r="I130" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J130" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
@@ -6387,7 +6385,7 @@
       </c>
       <c r="D131" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E131" s="19" t="inlineStr">
@@ -6400,15 +6398,11 @@
           <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
-      <c r="G131" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H131" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
+      <c r="G131" s="23">
+        <v>0</v>
+      </c>
+      <c r="H131" s="23">
+        <v>4</v>
       </c>
       <c r="I131" s="21" t="inlineStr">
         <is>
@@ -6442,12 +6436,12 @@
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F132" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G132" s="22" t="inlineStr">
@@ -6457,7 +6451,7 @@
       </c>
       <c r="H132" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="I132" s="20" t="inlineStr">
@@ -6492,7 +6486,7 @@
       </c>
       <c r="E133" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
@@ -6542,30 +6536,80 @@
       </c>
       <c r="E134" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F134" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G134" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H134" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I134" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J134" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="28" customHeight="1">
+      <c r="A135" s="18">
+        <v>1</v>
+      </c>
+      <c r="B135" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C135" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D135" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E135" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F134" s="22" t="inlineStr">
+      <c r="F135" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G134" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H134" s="22" t="inlineStr">
+      <c r="G135" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H135" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I134" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J134" s="17" t="inlineStr">
+      <c r="I135" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J135" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J135" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J135"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J136" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J136"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:35:52</t>
+          <t xml:space="preserve">15:36:21</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -518,32 +518,32 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G6" s="22">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H6" s="22">
         <v>0</v>
       </c>
       <c r="I6" s="20">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">751f8a7696</t>
+          <t xml:space="preserve">b665f084da</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:18</t>
+          <t xml:space="preserve">15:35:52</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -562,32 +562,32 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G7" s="23">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H7" s="23">
         <v>0</v>
       </c>
       <c r="I7" s="21">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0be32d0353</t>
+          <t xml:space="preserve">751f8a7696</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:13</t>
+          <t xml:space="preserve">15:33:18</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -606,32 +606,32 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G8" s="22">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H8" s="22">
         <v>0</v>
       </c>
       <c r="I8" s="20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">28a1fcc537</t>
+          <t xml:space="preserve">0be32d0353</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="18">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:05</t>
+          <t xml:space="preserve">15:33:13</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -650,32 +650,32 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H9" s="23">
         <v>0</v>
       </c>
       <c r="I9" s="21">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a734384c03</t>
+          <t xml:space="preserve">28a1fcc537</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:31:30</t>
+          <t xml:space="preserve">15:33:05</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G10" s="22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H10" s="22">
         <v>0</v>
       </c>
       <c r="I10" s="20">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5edabb20bb</t>
+          <t xml:space="preserve">a734384c03</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="18">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:53</t>
+          <t xml:space="preserve">15:31:30</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -738,32 +738,32 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G11" s="23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H11" s="23">
         <v>0</v>
       </c>
       <c r="I11" s="21">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a1408f9e88</t>
+          <t xml:space="preserve">5edabb20bb</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:35</t>
+          <t xml:space="preserve">15:30:53</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G12" s="22">
@@ -801,13 +801,13 @@
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed45f1ef47</t>
+          <t xml:space="preserve">a1408f9e88</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:59</t>
+          <t xml:space="preserve">15:30:35</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -826,32 +826,32 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G13" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" s="23">
         <v>0</v>
       </c>
       <c r="I13" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">d659616819</t>
+          <t xml:space="preserve">ed45f1ef47</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:38</t>
+          <t xml:space="preserve">15:29:59</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G14" s="22">
@@ -889,13 +889,13 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">19f5f6152e</t>
+          <t xml:space="preserve">d659616819</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:24</t>
+          <t xml:space="preserve">15:29:38</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -914,32 +914,32 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G15" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="23">
         <v>0</v>
       </c>
       <c r="I15" s="21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd714591b4</t>
+          <t xml:space="preserve">19f5f6152e</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
@@ -948,38 +948,36 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:24</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G16" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" s="22">
         <v>0</v>
       </c>
-      <c r="I16" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I16" s="20">
+        <v>4</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">bd714591b4</t>
         </is>
       </c>
     </row>
@@ -1004,16 +1002,16 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G17" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H17" s="23">
         <v>0</v>
@@ -1050,16 +1048,16 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G18" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H18" s="22">
         <v>0</v>
@@ -1096,19 +1094,19 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G19" s="23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" s="23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
@@ -1142,19 +1140,19 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G20" s="22">
         <v>0</v>
       </c>
       <c r="H20" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
@@ -1188,12 +1186,12 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G21" s="23">
@@ -1234,19 +1232,19 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G22" s="22">
         <v>0</v>
       </c>
       <c r="H22" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
@@ -1280,19 +1278,19 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G23" s="23">
         <v>0</v>
       </c>
       <c r="H23" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
@@ -1326,19 +1324,19 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G24" s="22">
         <v>0</v>
       </c>
       <c r="H24" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -1372,12 +1370,12 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G25" s="23">
@@ -1418,19 +1416,19 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G26" s="22">
         <v>0</v>
       </c>
       <c r="H26" s="22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
@@ -1464,19 +1462,19 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G27" s="23">
         <v>0</v>
       </c>
       <c r="H27" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
@@ -1510,12 +1508,12 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G28" s="22">
@@ -1556,19 +1554,19 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G29" s="23">
         <v>0</v>
       </c>
       <c r="H29" s="23">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
@@ -1602,19 +1600,19 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G30" s="22">
         <v>0</v>
       </c>
       <c r="H30" s="22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
@@ -1648,19 +1646,19 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G31" s="23">
         <v>0</v>
       </c>
       <c r="H31" s="23">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
@@ -1694,19 +1692,19 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G32" s="22">
         <v>0</v>
       </c>
       <c r="H32" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
@@ -1740,19 +1738,19 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G33" s="23">
         <v>0</v>
       </c>
       <c r="H33" s="23">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
@@ -1786,19 +1784,19 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G34" s="22">
         <v>0</v>
       </c>
       <c r="H34" s="22">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
@@ -1832,19 +1830,19 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G35" s="23">
         <v>0</v>
       </c>
       <c r="H35" s="23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1878,19 +1876,19 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G36" s="22">
         <v>0</v>
       </c>
       <c r="H36" s="22">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1924,19 +1922,19 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G37" s="23">
         <v>0</v>
       </c>
       <c r="H37" s="23">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1970,19 +1968,19 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G38" s="22">
         <v>0</v>
       </c>
       <c r="H38" s="22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -2016,12 +2014,12 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G39" s="23">
@@ -2062,19 +2060,19 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G40" s="22">
         <v>0</v>
       </c>
       <c r="H40" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
@@ -2108,12 +2106,12 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G41" s="23">
@@ -2154,19 +2152,19 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G42" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
@@ -2181,7 +2179,7 @@
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
@@ -2190,7 +2188,7 @@
       </c>
       <c r="C43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D43" s="19" t="inlineStr">
@@ -2200,19 +2198,19 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G43" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I43" s="21" t="inlineStr">
         <is>
@@ -2221,7 +2219,7 @@
       </c>
       <c r="J43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
@@ -2246,19 +2244,19 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G44" s="22">
         <v>0</v>
       </c>
       <c r="H44" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
@@ -2292,19 +2290,19 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G45" s="23">
         <v>0</v>
       </c>
       <c r="H45" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I45" s="21" t="inlineStr">
         <is>
@@ -2338,19 +2336,19 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G46" s="22">
         <v>0</v>
       </c>
       <c r="H46" s="22">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
@@ -2384,19 +2382,19 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G47" s="23">
         <v>0</v>
       </c>
       <c r="H47" s="23">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I47" s="21" t="inlineStr">
         <is>
@@ -2430,128 +2428,130 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G48" s="22">
+        <v>0</v>
+      </c>
+      <c r="H48" s="22">
+        <v>4</v>
+      </c>
+      <c r="I48" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J48" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="18">
+        <v>23</v>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:59:31</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">67</t>
         </is>
       </c>
-      <c r="F48" s="22" t="inlineStr">
+      <c r="F49" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G48" s="22">
-        <v>0</v>
-      </c>
-      <c r="H48" s="22">
+      <c r="G49" s="23">
+        <v>0</v>
+      </c>
+      <c r="H49" s="23">
         <v>1</v>
       </c>
-      <c r="I48" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J48" s="17" t="inlineStr">
+      <c r="I49" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="48" customHeight="1">
-      <c r="A49" s="18">
+    <row r="50" ht="48" customHeight="1">
+      <c r="A50" s="16">
         <v>22</v>
       </c>
-      <c r="B49" s="19" t="inlineStr">
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
-      <c r="C49" s="19" t="inlineStr">
+      <c r="C50" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
-      <c r="D49" s="19" t="inlineStr">
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E49" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G49" s="23" t="inlineStr">
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="H49" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I49" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J49" s="19" t="inlineStr">
+      <c r="H50" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I50" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J50" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2688d62325</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="16">
-        <v>21</v>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:18:32</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E50" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62</t>
-        </is>
-      </c>
-      <c r="F50" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G50" s="22">
-        <v>4</v>
-      </c>
-      <c r="H50" s="22">
-        <v>0</v>
-      </c>
-      <c r="I50" s="20">
-        <v>4</v>
-      </c>
-      <c r="J50" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G51" s="23">
@@ -2589,13 +2589,13 @@
       </c>
       <c r="J51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="16">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G52" s="22">
@@ -2633,13 +2633,13 @@
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D53" s="19" t="inlineStr">
@@ -2658,32 +2658,32 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G53" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H53" s="23">
         <v>0</v>
       </c>
       <c r="I53" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -2702,32 +2702,32 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G54" s="22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H54" s="22">
         <v>0</v>
       </c>
       <c r="I54" s="20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -2746,32 +2746,32 @@
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G55" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H55" s="23">
         <v>0</v>
       </c>
       <c r="I55" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -2790,32 +2790,32 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G56" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H56" s="22">
         <v>0</v>
       </c>
       <c r="I56" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -2834,32 +2834,32 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G57" s="23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H57" s="23">
         <v>0</v>
       </c>
       <c r="I57" s="21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -2878,32 +2878,32 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G58" s="22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H58" s="22">
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -2922,32 +2922,32 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G59" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H59" s="23">
         <v>0</v>
       </c>
       <c r="I59" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G60" s="22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H60" s="22">
         <v>0</v>
       </c>
       <c r="I60" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
@@ -3010,32 +3010,32 @@
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G61" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H61" s="23">
         <v>0</v>
       </c>
       <c r="I61" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
@@ -3054,32 +3054,32 @@
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G62" s="22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H62" s="22">
         <v>0</v>
       </c>
       <c r="I62" s="20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D63" s="19" t="inlineStr">
@@ -3098,32 +3098,32 @@
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G63" s="23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H63" s="23">
         <v>0</v>
       </c>
       <c r="I63" s="21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
@@ -3142,32 +3142,32 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G64" s="22">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H64" s="22">
         <v>0</v>
       </c>
       <c r="I64" s="20">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -3186,32 +3186,32 @@
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G65" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H65" s="23">
         <v>0</v>
       </c>
       <c r="I65" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
@@ -3230,32 +3230,32 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G66" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H66" s="22">
         <v>0</v>
       </c>
       <c r="I66" s="20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D67" s="19" t="inlineStr">
@@ -3274,46 +3274,46 @@
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G67" s="23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H67" s="23">
         <v>0</v>
       </c>
       <c r="I67" s="21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
@@ -3327,19 +3327,17 @@
         </is>
       </c>
       <c r="G68" s="22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H68" s="22">
+        <v>0</v>
+      </c>
+      <c r="I68" s="20">
         <v>5</v>
       </c>
-      <c r="I68" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -3364,19 +3362,19 @@
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G69" s="23">
         <v>0</v>
       </c>
       <c r="H69" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I69" s="21" t="inlineStr">
         <is>
@@ -3405,7 +3403,7 @@
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
@@ -3418,15 +3416,11 @@
           <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
-      <c r="G70" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H70" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+      <c r="G70" s="22">
+        <v>0</v>
+      </c>
+      <c r="H70" s="22">
+        <v>3</v>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
@@ -3455,24 +3449,28 @@
       </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G71" s="23">
-        <v>0</v>
-      </c>
-      <c r="H71" s="23">
-        <v>6</v>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H71" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
       </c>
       <c r="I71" s="21" t="inlineStr">
         <is>
@@ -3501,7 +3499,7 @@
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
@@ -3514,15 +3512,11 @@
           <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
-      <c r="G72" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H72" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
+      <c r="G72" s="22">
+        <v>0</v>
+      </c>
+      <c r="H72" s="22">
+        <v>6</v>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
@@ -3556,12 +3550,12 @@
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -3571,7 +3565,7 @@
       </c>
       <c r="H73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I73" s="21" t="inlineStr">
@@ -3606,22 +3600,22 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
@@ -3656,12 +3650,12 @@
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -3671,7 +3665,7 @@
       </c>
       <c r="H75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I75" s="21" t="inlineStr">
@@ -3706,12 +3700,12 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G76" s="22" t="inlineStr">
@@ -3721,7 +3715,7 @@
       </c>
       <c r="H76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
@@ -3751,24 +3745,28 @@
       </c>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G77" s="23">
-        <v>0</v>
-      </c>
-      <c r="H77" s="23">
-        <v>3</v>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H77" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
@@ -3797,7 +3795,7 @@
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
@@ -3810,15 +3808,11 @@
           <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
-      <c r="G78" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H78" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
+      <c r="G78" s="22">
+        <v>0</v>
+      </c>
+      <c r="H78" s="22">
+        <v>3</v>
       </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
@@ -3847,24 +3841,28 @@
       </c>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G79" s="23">
-        <v>0</v>
-      </c>
-      <c r="H79" s="23">
-        <v>3</v>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H79" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
       </c>
       <c r="I79" s="21" t="inlineStr">
         <is>
@@ -3893,7 +3891,7 @@
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
@@ -3906,15 +3904,11 @@
           <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
-      <c r="G80" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H80" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
+      <c r="G80" s="22">
+        <v>0</v>
+      </c>
+      <c r="H80" s="22">
+        <v>3</v>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
@@ -3943,24 +3937,28 @@
       </c>
       <c r="D81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G81" s="23">
-        <v>0</v>
-      </c>
-      <c r="H81" s="23">
-        <v>5</v>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H81" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
       </c>
       <c r="I81" s="21" t="inlineStr">
         <is>
@@ -3989,7 +3987,7 @@
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
@@ -4002,15 +4000,11 @@
           <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
-      <c r="G82" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H82" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
+      <c r="G82" s="22">
+        <v>0</v>
+      </c>
+      <c r="H82" s="22">
+        <v>5</v>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
@@ -4039,24 +4033,28 @@
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="G83" s="23">
-        <v>0</v>
-      </c>
-      <c r="H83" s="23">
-        <v>9</v>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H83" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
@@ -4085,7 +4083,7 @@
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
@@ -4098,15 +4096,11 @@
           <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
-      <c r="G84" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H84" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
+      <c r="G84" s="22">
+        <v>0</v>
+      </c>
+      <c r="H84" s="22">
+        <v>9</v>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
@@ -4140,12 +4134,12 @@
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -4155,7 +4149,7 @@
       </c>
       <c r="H85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I85" s="21" t="inlineStr">
@@ -4190,12 +4184,12 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G86" s="22" t="inlineStr">
@@ -4205,7 +4199,7 @@
       </c>
       <c r="H86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
@@ -4235,24 +4229,28 @@
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G87" s="23">
-        <v>0</v>
-      </c>
-      <c r="H87" s="23">
-        <v>6</v>
+          <t xml:space="preserve">وافل</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وافل</t>
+        </is>
       </c>
       <c r="I87" s="21" t="inlineStr">
         <is>
@@ -4281,7 +4279,7 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
@@ -4294,15 +4292,11 @@
           <t xml:space="preserve">کوکی</t>
         </is>
       </c>
-      <c r="G88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
+      <c r="G88" s="22">
+        <v>0</v>
+      </c>
+      <c r="H88" s="22">
+        <v>6</v>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
@@ -4331,24 +4325,28 @@
       </c>
       <c r="D89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="G89" s="23">
-        <v>0</v>
-      </c>
-      <c r="H89" s="23">
-        <v>3</v>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H89" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
@@ -4377,7 +4375,7 @@
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
@@ -4390,15 +4388,11 @@
           <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
-      <c r="G90" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H90" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
+      <c r="G90" s="22">
+        <v>0</v>
+      </c>
+      <c r="H90" s="22">
+        <v>3</v>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
@@ -4432,12 +4426,12 @@
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -4447,7 +4441,7 @@
       </c>
       <c r="H91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="I91" s="21" t="inlineStr">
@@ -4477,24 +4471,28 @@
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F92" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G92" s="22">
-        <v>0</v>
-      </c>
-      <c r="H92" s="22">
-        <v>4</v>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
+      </c>
+      <c r="G92" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H92" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
       </c>
       <c r="I92" s="20" t="inlineStr">
         <is>
@@ -4523,7 +4521,7 @@
       </c>
       <c r="D93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E93" s="19" t="inlineStr">
@@ -4536,15 +4534,11 @@
           <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
-      <c r="G93" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H93" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
+      <c r="G93" s="23">
+        <v>0</v>
+      </c>
+      <c r="H93" s="23">
+        <v>4</v>
       </c>
       <c r="I93" s="21" t="inlineStr">
         <is>
@@ -4573,24 +4567,28 @@
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F94" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G94" s="22">
-        <v>0</v>
-      </c>
-      <c r="H94" s="22">
-        <v>6</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H94" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
@@ -4619,7 +4617,7 @@
       </c>
       <c r="D95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E95" s="19" t="inlineStr">
@@ -4632,15 +4630,11 @@
           <t xml:space="preserve">آجیل</t>
         </is>
       </c>
-      <c r="G95" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H95" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+      <c r="G95" s="23">
+        <v>0</v>
+      </c>
+      <c r="H95" s="23">
+        <v>6</v>
       </c>
       <c r="I95" s="21" t="inlineStr">
         <is>
@@ -4669,24 +4663,28 @@
       </c>
       <c r="D96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
-      </c>
-      <c r="G96" s="22">
-        <v>0</v>
-      </c>
-      <c r="H96" s="22">
-        <v>7</v>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H96" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
       </c>
       <c r="I96" s="20" t="inlineStr">
         <is>
@@ -4715,7 +4713,7 @@
       </c>
       <c r="D97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E97" s="19" t="inlineStr">
@@ -4728,15 +4726,11 @@
           <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
-      <c r="G97" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H97" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
+      <c r="G97" s="23">
+        <v>0</v>
+      </c>
+      <c r="H97" s="23">
+        <v>7</v>
       </c>
       <c r="I97" s="21" t="inlineStr">
         <is>
@@ -4770,12 +4764,12 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F98" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G98" s="22" t="inlineStr">
@@ -4785,7 +4779,7 @@
       </c>
       <c r="H98" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I98" s="20" t="inlineStr">
@@ -4815,24 +4809,28 @@
       </c>
       <c r="D99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G99" s="23">
-        <v>0</v>
-      </c>
-      <c r="H99" s="23">
-        <v>3</v>
+          <t xml:space="preserve">رول رول</t>
+        </is>
+      </c>
+      <c r="G99" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H99" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول</t>
+        </is>
       </c>
       <c r="I99" s="21" t="inlineStr">
         <is>
@@ -4861,7 +4859,7 @@
       </c>
       <c r="D100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
@@ -4874,15 +4872,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G100" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H100" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G100" s="22">
+        <v>0</v>
+      </c>
+      <c r="H100" s="22">
+        <v>3</v>
       </c>
       <c r="I100" s="20" t="inlineStr">
         <is>
@@ -4916,7 +4910,7 @@
       </c>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
@@ -4966,7 +4960,7 @@
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F102" s="22" t="inlineStr">
@@ -5016,7 +5010,7 @@
       </c>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
@@ -5066,12 +5060,12 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G104" s="22" t="inlineStr">
@@ -5081,7 +5075,7 @@
       </c>
       <c r="H104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I104" s="20" t="inlineStr">
@@ -5116,12 +5110,12 @@
       </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -5131,7 +5125,7 @@
       </c>
       <c r="H105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I105" s="21" t="inlineStr">
@@ -5166,12 +5160,12 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="G106" s="22" t="inlineStr">
@@ -5181,7 +5175,7 @@
       </c>
       <c r="H106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="I106" s="20" t="inlineStr">
@@ -5211,24 +5205,28 @@
       </c>
       <c r="D107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G107" s="23">
-        <v>0</v>
-      </c>
-      <c r="H107" s="23">
-        <v>5</v>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H107" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
       </c>
       <c r="I107" s="21" t="inlineStr">
         <is>
@@ -5257,7 +5255,7 @@
       </c>
       <c r="D108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E108" s="17" t="inlineStr">
@@ -5270,15 +5268,11 @@
           <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
-      <c r="G108" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H108" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
+      <c r="G108" s="22">
+        <v>0</v>
+      </c>
+      <c r="H108" s="22">
+        <v>5</v>
       </c>
       <c r="I108" s="20" t="inlineStr">
         <is>
@@ -5307,24 +5301,28 @@
       </c>
       <c r="D109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G109" s="23">
-        <v>0</v>
-      </c>
-      <c r="H109" s="23">
-        <v>2</v>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G109" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H109" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
       </c>
       <c r="I109" s="21" t="inlineStr">
         <is>
@@ -5353,7 +5351,7 @@
       </c>
       <c r="D110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E110" s="17" t="inlineStr">
@@ -5366,15 +5364,11 @@
           <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
-      <c r="G110" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H110" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>2</v>
       </c>
       <c r="I110" s="20" t="inlineStr">
         <is>
@@ -5403,24 +5397,28 @@
       </c>
       <c r="D111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G111" s="23">
-        <v>0</v>
-      </c>
-      <c r="H111" s="23">
-        <v>4</v>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H111" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
       </c>
       <c r="I111" s="21" t="inlineStr">
         <is>
@@ -5449,7 +5447,7 @@
       </c>
       <c r="D112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E112" s="17" t="inlineStr">
@@ -5462,15 +5460,11 @@
           <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
-      <c r="G112" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H112" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>4</v>
       </c>
       <c r="I112" s="20" t="inlineStr">
         <is>
@@ -5504,12 +5498,12 @@
       </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -5519,7 +5513,7 @@
       </c>
       <c r="H113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I113" s="21" t="inlineStr">
@@ -5554,12 +5548,12 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G114" s="22" t="inlineStr">
@@ -5569,7 +5563,7 @@
       </c>
       <c r="H114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I114" s="20" t="inlineStr">
@@ -5604,12 +5598,12 @@
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -5619,7 +5613,7 @@
       </c>
       <c r="H115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I115" s="21" t="inlineStr">
@@ -5654,12 +5648,12 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G116" s="22" t="inlineStr">
@@ -5669,7 +5663,7 @@
       </c>
       <c r="H116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I116" s="20" t="inlineStr">
@@ -5704,12 +5698,12 @@
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -5719,7 +5713,7 @@
       </c>
       <c r="H117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I117" s="21" t="inlineStr">
@@ -5754,12 +5748,12 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G118" s="22" t="inlineStr">
@@ -5769,7 +5763,7 @@
       </c>
       <c r="H118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I118" s="20" t="inlineStr">
@@ -5804,12 +5798,12 @@
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -5819,7 +5813,7 @@
       </c>
       <c r="H119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="I119" s="21" t="inlineStr">
@@ -5849,24 +5843,28 @@
       </c>
       <c r="D120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G120" s="22">
-        <v>0</v>
-      </c>
-      <c r="H120" s="22">
-        <v>4</v>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="G120" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H120" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
       </c>
       <c r="I120" s="20" t="inlineStr">
         <is>
@@ -5895,7 +5893,7 @@
       </c>
       <c r="D121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E121" s="19" t="inlineStr">
@@ -5908,15 +5906,11 @@
           <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
-      <c r="G121" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H121" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
+      <c r="G121" s="23">
+        <v>0</v>
+      </c>
+      <c r="H121" s="23">
+        <v>4</v>
       </c>
       <c r="I121" s="21" t="inlineStr">
         <is>
@@ -5950,12 +5944,12 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F122" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G122" s="22" t="inlineStr">
@@ -5965,7 +5959,7 @@
       </c>
       <c r="H122" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I122" s="20" t="inlineStr">
@@ -6000,12 +5994,12 @@
       </c>
       <c r="E123" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -6015,7 +6009,7 @@
       </c>
       <c r="H123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I123" s="21" t="inlineStr">
@@ -6050,12 +6044,12 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F124" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G124" s="22" t="inlineStr">
@@ -6065,7 +6059,7 @@
       </c>
       <c r="H124" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I124" s="20" t="inlineStr">
@@ -6100,12 +6094,12 @@
       </c>
       <c r="E125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -6115,7 +6109,7 @@
       </c>
       <c r="H125" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="I125" s="21" t="inlineStr">
@@ -6145,24 +6139,28 @@
       </c>
       <c r="D126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F126" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G126" s="22">
-        <v>0</v>
-      </c>
-      <c r="H126" s="22">
-        <v>4</v>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G126" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H126" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
       </c>
       <c r="I126" s="20" t="inlineStr">
         <is>
@@ -6191,7 +6189,7 @@
       </c>
       <c r="D127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E127" s="19" t="inlineStr">
@@ -6204,15 +6202,11 @@
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G127" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H127" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
+      <c r="G127" s="23">
+        <v>0</v>
+      </c>
+      <c r="H127" s="23">
+        <v>4</v>
       </c>
       <c r="I127" s="21" t="inlineStr">
         <is>
@@ -6246,132 +6240,138 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F128" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G128" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H128" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="I128" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J128" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="28" customHeight="1">
+      <c r="A129" s="18">
+        <v>3</v>
+      </c>
+      <c r="B129" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C129" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D129" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E129" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">68</t>
         </is>
       </c>
-      <c r="F128" s="22" t="inlineStr">
+      <c r="F129" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="G128" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H128" s="22" t="inlineStr">
+      <c r="G129" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H129" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="I128" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J128" s="17" t="inlineStr">
+      <c r="I129" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J129" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="48" customHeight="1">
-      <c r="A129" s="18">
-        <v>3</v>
-      </c>
-      <c r="B129" s="19" t="inlineStr">
+    <row r="130" ht="48" customHeight="1">
+      <c r="A130" s="16">
+        <v>3</v>
+      </c>
+      <c r="B130" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
-      <c r="C129" s="19" t="inlineStr">
+      <c r="C130" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
-      <c r="D129" s="19" t="inlineStr">
+      <c r="D130" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E129" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F129" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G129" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H129" s="23" t="inlineStr">
+      <c r="E130" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F130" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G130" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H130" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="I129" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J129" s="19" t="inlineStr">
+      <c r="I130" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J130" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="28" customHeight="1">
-      <c r="A130" s="16">
-        <v>2</v>
-      </c>
-      <c r="B130" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/23</t>
-        </is>
-      </c>
-      <c r="C130" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23:16:19</t>
-        </is>
-      </c>
-      <c r="D130" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E130" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="F130" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G130" s="22">
-        <v>4</v>
-      </c>
-      <c r="H130" s="22">
-        <v>0</v>
-      </c>
-      <c r="I130" s="20">
-        <v>4</v>
-      </c>
-      <c r="J130" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
     <row r="131" ht="28" customHeight="1">
       <c r="A131" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B131" s="19" t="inlineStr">
         <is>
@@ -6380,12 +6380,12 @@
       </c>
       <c r="C131" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">23:16:19</t>
         </is>
       </c>
       <c r="D131" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E131" s="19" t="inlineStr">
@@ -6399,19 +6399,17 @@
         </is>
       </c>
       <c r="G131" s="23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H131" s="23">
+        <v>0</v>
+      </c>
+      <c r="I131" s="21">
         <v>4</v>
       </c>
-      <c r="I131" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J131" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6429,7 @@
       </c>
       <c r="D132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E132" s="17" t="inlineStr">
@@ -6444,15 +6442,11 @@
           <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
-      <c r="G132" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H132" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
+      <c r="G132" s="22">
+        <v>0</v>
+      </c>
+      <c r="H132" s="22">
+        <v>4</v>
       </c>
       <c r="I132" s="20" t="inlineStr">
         <is>
@@ -6486,12 +6480,12 @@
       </c>
       <c r="E133" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -6501,7 +6495,7 @@
       </c>
       <c r="H133" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="I133" s="21" t="inlineStr">
@@ -6536,7 +6530,7 @@
       </c>
       <c r="E134" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F134" s="22" t="inlineStr">
@@ -6586,30 +6580,80 @@
       </c>
       <c r="E135" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F135" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G135" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H135" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I135" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J135" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="28" customHeight="1">
+      <c r="A136" s="16">
+        <v>1</v>
+      </c>
+      <c r="B136" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C136" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D136" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E136" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F135" s="23" t="inlineStr">
+      <c r="F136" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G135" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H135" s="23" t="inlineStr">
+      <c r="G136" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H136" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I135" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J135" s="19" t="inlineStr">
+      <c r="I136" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J136" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J136" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J136"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J137" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J137"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:36:21</t>
+          <t xml:space="preserve">15:36:57</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -518,32 +518,32 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G6" s="22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6" s="22">
         <v>0</v>
       </c>
       <c r="I6" s="20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">b665f084da</t>
+          <t xml:space="preserve">424ffdd738</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:35:52</t>
+          <t xml:space="preserve">15:36:21</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -562,32 +562,32 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G7" s="23">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H7" s="23">
         <v>0</v>
       </c>
       <c r="I7" s="21">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">751f8a7696</t>
+          <t xml:space="preserve">b665f084da</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:18</t>
+          <t xml:space="preserve">15:35:52</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -606,32 +606,32 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G8" s="22">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H8" s="22">
         <v>0</v>
       </c>
       <c r="I8" s="20">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">0be32d0353</t>
+          <t xml:space="preserve">751f8a7696</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="18">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:13</t>
+          <t xml:space="preserve">15:33:18</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -650,32 +650,32 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H9" s="23">
         <v>0</v>
       </c>
       <c r="I9" s="21">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">28a1fcc537</t>
+          <t xml:space="preserve">0be32d0353</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:05</t>
+          <t xml:space="preserve">15:33:13</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G10" s="22">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H10" s="22">
         <v>0</v>
       </c>
       <c r="I10" s="20">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a734384c03</t>
+          <t xml:space="preserve">28a1fcc537</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="18">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:31:30</t>
+          <t xml:space="preserve">15:33:05</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -738,32 +738,32 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G11" s="23">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H11" s="23">
         <v>0</v>
       </c>
       <c r="I11" s="21">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5edabb20bb</t>
+          <t xml:space="preserve">a734384c03</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="16">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:53</t>
+          <t xml:space="preserve">15:31:30</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
@@ -782,32 +782,32 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G12" s="22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H12" s="22">
         <v>0</v>
       </c>
       <c r="I12" s="20">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a1408f9e88</t>
+          <t xml:space="preserve">5edabb20bb</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="18">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:35</t>
+          <t xml:space="preserve">15:30:53</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -826,12 +826,12 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G13" s="23">
@@ -845,13 +845,13 @@
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed45f1ef47</t>
+          <t xml:space="preserve">a1408f9e88</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:59</t>
+          <t xml:space="preserve">15:30:35</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
@@ -870,32 +870,32 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G14" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" s="22">
         <v>0</v>
       </c>
       <c r="I14" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">d659616819</t>
+          <t xml:space="preserve">ed45f1ef47</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:38</t>
+          <t xml:space="preserve">15:29:59</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G15" s="23">
@@ -933,13 +933,13 @@
       </c>
       <c r="J15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">19f5f6152e</t>
+          <t xml:space="preserve">d659616819</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:24</t>
+          <t xml:space="preserve">15:29:38</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
@@ -958,32 +958,32 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G16" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" s="22">
         <v>0</v>
       </c>
       <c r="I16" s="20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd714591b4</t>
+          <t xml:space="preserve">19f5f6152e</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
@@ -992,38 +992,36 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:24</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G17" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" s="23">
         <v>0</v>
       </c>
-      <c r="I17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I17" s="21">
+        <v>4</v>
       </c>
       <c r="J17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">bd714591b4</t>
         </is>
       </c>
     </row>
@@ -1048,16 +1046,16 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G18" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H18" s="22">
         <v>0</v>
@@ -1094,16 +1092,16 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G19" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" s="23">
         <v>0</v>
@@ -1140,19 +1138,19 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G20" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" s="22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
@@ -1186,19 +1184,19 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G21" s="23">
         <v>0</v>
       </c>
       <c r="H21" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
@@ -1232,12 +1230,12 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G22" s="22">
@@ -1278,19 +1276,19 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G23" s="23">
         <v>0</v>
       </c>
       <c r="H23" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
@@ -1324,19 +1322,19 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G24" s="22">
         <v>0</v>
       </c>
       <c r="H24" s="22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -1370,19 +1368,19 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G25" s="23">
         <v>0</v>
       </c>
       <c r="H25" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
@@ -1416,12 +1414,12 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G26" s="22">
@@ -1462,19 +1460,19 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G27" s="23">
         <v>0</v>
       </c>
       <c r="H27" s="23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
@@ -1508,19 +1506,19 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G28" s="22">
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -1554,12 +1552,12 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G29" s="23">
@@ -1600,19 +1598,19 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G30" s="22">
         <v>0</v>
       </c>
       <c r="H30" s="22">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
@@ -1646,19 +1644,19 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G31" s="23">
         <v>0</v>
       </c>
       <c r="H31" s="23">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
@@ -1692,19 +1690,19 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G32" s="22">
         <v>0</v>
       </c>
       <c r="H32" s="22">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
@@ -1738,19 +1736,19 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G33" s="23">
         <v>0</v>
       </c>
       <c r="H33" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
@@ -1784,19 +1782,19 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G34" s="22">
         <v>0</v>
       </c>
       <c r="H34" s="22">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
@@ -1830,19 +1828,19 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G35" s="23">
         <v>0</v>
       </c>
       <c r="H35" s="23">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1876,19 +1874,19 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G36" s="22">
         <v>0</v>
       </c>
       <c r="H36" s="22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1922,19 +1920,19 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G37" s="23">
         <v>0</v>
       </c>
       <c r="H37" s="23">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1968,19 +1966,19 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G38" s="22">
         <v>0</v>
       </c>
       <c r="H38" s="22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -2014,19 +2012,19 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G39" s="23">
         <v>0</v>
       </c>
       <c r="H39" s="23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
@@ -2060,12 +2058,12 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G40" s="22">
@@ -2106,19 +2104,19 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G41" s="23">
         <v>0</v>
       </c>
       <c r="H41" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I41" s="21" t="inlineStr">
         <is>
@@ -2152,12 +2150,12 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G42" s="22">
@@ -2198,19 +2196,19 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G43" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I43" s="21" t="inlineStr">
         <is>
@@ -2225,7 +2223,7 @@
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
@@ -2234,7 +2232,7 @@
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
@@ -2244,19 +2242,19 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G44" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
@@ -2265,7 +2263,7 @@
       </c>
       <c r="J44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
@@ -2290,19 +2288,19 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G45" s="23">
         <v>0</v>
       </c>
       <c r="H45" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I45" s="21" t="inlineStr">
         <is>
@@ -2336,19 +2334,19 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G46" s="22">
         <v>0</v>
       </c>
       <c r="H46" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
@@ -2382,19 +2380,19 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G47" s="23">
         <v>0</v>
       </c>
       <c r="H47" s="23">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I47" s="21" t="inlineStr">
         <is>
@@ -2428,19 +2426,19 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G48" s="22">
         <v>0</v>
       </c>
       <c r="H48" s="22">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I48" s="20" t="inlineStr">
         <is>
@@ -2474,128 +2472,130 @@
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G49" s="23">
+        <v>0</v>
+      </c>
+      <c r="H49" s="23">
+        <v>4</v>
+      </c>
+      <c r="I49" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="16">
+        <v>23</v>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:59:31</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">67</t>
         </is>
       </c>
-      <c r="F49" s="23" t="inlineStr">
+      <c r="F50" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G49" s="23">
-        <v>0</v>
-      </c>
-      <c r="H49" s="23">
+      <c r="G50" s="22">
+        <v>0</v>
+      </c>
+      <c r="H50" s="22">
         <v>1</v>
       </c>
-      <c r="I49" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J49" s="19" t="inlineStr">
+      <c r="I50" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J50" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="48" customHeight="1">
-      <c r="A50" s="16">
+    <row r="51" ht="48" customHeight="1">
+      <c r="A51" s="18">
         <v>22</v>
       </c>
-      <c r="B50" s="17" t="inlineStr">
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
-      <c r="C50" s="17" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="D51" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E50" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F50" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G50" s="22" t="inlineStr">
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="H50" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I50" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J50" s="17" t="inlineStr">
+      <c r="H51" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I51" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J51" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">2688d62325</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="18">
-        <v>21</v>
-      </c>
-      <c r="B51" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C51" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:18:32</t>
-        </is>
-      </c>
-      <c r="D51" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E51" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62</t>
-        </is>
-      </c>
-      <c r="F51" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G51" s="23">
-        <v>4</v>
-      </c>
-      <c r="H51" s="23">
-        <v>0</v>
-      </c>
-      <c r="I51" s="21">
-        <v>4</v>
-      </c>
-      <c r="J51" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G52" s="22">
@@ -2633,13 +2633,13 @@
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="18">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D53" s="19" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G53" s="23">
@@ -2677,13 +2677,13 @@
       </c>
       <c r="J53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -2702,32 +2702,32 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G54" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H54" s="22">
         <v>0</v>
       </c>
       <c r="I54" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -2746,32 +2746,32 @@
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G55" s="23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H55" s="23">
         <v>0</v>
       </c>
       <c r="I55" s="21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -2790,32 +2790,32 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G56" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H56" s="22">
         <v>0</v>
       </c>
       <c r="I56" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -2834,32 +2834,32 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G57" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H57" s="23">
         <v>0</v>
       </c>
       <c r="I57" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -2878,32 +2878,32 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G58" s="22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H58" s="22">
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -2922,32 +2922,32 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G59" s="23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H59" s="23">
         <v>0</v>
       </c>
       <c r="I59" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G60" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H60" s="22">
         <v>0</v>
       </c>
       <c r="I60" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
@@ -3010,32 +3010,32 @@
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G61" s="23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H61" s="23">
         <v>0</v>
       </c>
       <c r="I61" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
@@ -3054,32 +3054,32 @@
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G62" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H62" s="22">
         <v>0</v>
       </c>
       <c r="I62" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D63" s="19" t="inlineStr">
@@ -3098,32 +3098,32 @@
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G63" s="23">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H63" s="23">
         <v>0</v>
       </c>
       <c r="I63" s="21">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
@@ -3142,32 +3142,32 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G64" s="22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H64" s="22">
         <v>0</v>
       </c>
       <c r="I64" s="20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -3186,32 +3186,32 @@
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G65" s="23">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H65" s="23">
         <v>0</v>
       </c>
       <c r="I65" s="21">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
@@ -3230,32 +3230,32 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G66" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H66" s="22">
         <v>0</v>
       </c>
       <c r="I66" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D67" s="19" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G67" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H67" s="23">
         <v>0</v>
       </c>
       <c r="I67" s="21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
@@ -3318,46 +3318,46 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G68" s="22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H68" s="22">
         <v>0</v>
       </c>
       <c r="I68" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1">
       <c r="A69" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
@@ -3371,19 +3371,17 @@
         </is>
       </c>
       <c r="G69" s="23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H69" s="23">
+        <v>0</v>
+      </c>
+      <c r="I69" s="21">
         <v>5</v>
       </c>
-      <c r="I69" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -3408,19 +3406,19 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G70" s="22">
         <v>0</v>
       </c>
       <c r="H70" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
@@ -3449,7 +3447,7 @@
       </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
@@ -3462,15 +3460,11 @@
           <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
-      <c r="G71" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H71" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+      <c r="G71" s="23">
+        <v>0</v>
+      </c>
+      <c r="H71" s="23">
+        <v>3</v>
       </c>
       <c r="I71" s="21" t="inlineStr">
         <is>
@@ -3499,24 +3493,28 @@
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G72" s="22">
-        <v>0</v>
-      </c>
-      <c r="H72" s="22">
-        <v>6</v>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H72" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
@@ -3545,7 +3543,7 @@
       </c>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
@@ -3558,15 +3556,11 @@
           <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
-      <c r="G73" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H73" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
+      <c r="G73" s="23">
+        <v>0</v>
+      </c>
+      <c r="H73" s="23">
+        <v>6</v>
       </c>
       <c r="I73" s="21" t="inlineStr">
         <is>
@@ -3600,12 +3594,12 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G74" s="22" t="inlineStr">
@@ -3615,7 +3609,7 @@
       </c>
       <c r="H74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
@@ -3650,22 +3644,22 @@
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I75" s="21" t="inlineStr">
@@ -3700,12 +3694,12 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G76" s="22" t="inlineStr">
@@ -3715,7 +3709,7 @@
       </c>
       <c r="H76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
@@ -3750,12 +3744,12 @@
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
@@ -3765,7 +3759,7 @@
       </c>
       <c r="H77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="I77" s="21" t="inlineStr">
@@ -3795,24 +3789,28 @@
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G78" s="22">
-        <v>0</v>
-      </c>
-      <c r="H78" s="22">
-        <v>3</v>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H78" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
@@ -3841,7 +3839,7 @@
       </c>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3854,15 +3852,11 @@
           <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
-      <c r="G79" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H79" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
+      <c r="G79" s="23">
+        <v>0</v>
+      </c>
+      <c r="H79" s="23">
+        <v>3</v>
       </c>
       <c r="I79" s="21" t="inlineStr">
         <is>
@@ -3891,24 +3885,28 @@
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G80" s="22">
-        <v>0</v>
-      </c>
-      <c r="H80" s="22">
-        <v>3</v>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H80" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
@@ -3937,7 +3935,7 @@
       </c>
       <c r="D81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
@@ -3950,15 +3948,11 @@
           <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
-      <c r="G81" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H81" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
+      <c r="G81" s="23">
+        <v>0</v>
+      </c>
+      <c r="H81" s="23">
+        <v>3</v>
       </c>
       <c r="I81" s="21" t="inlineStr">
         <is>
@@ -3987,24 +3981,28 @@
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G82" s="22">
-        <v>0</v>
-      </c>
-      <c r="H82" s="22">
-        <v>5</v>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H82" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
@@ -4033,7 +4031,7 @@
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
@@ -4046,15 +4044,11 @@
           <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
-      <c r="G83" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H83" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
+      <c r="G83" s="23">
+        <v>0</v>
+      </c>
+      <c r="H83" s="23">
+        <v>5</v>
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
@@ -4083,24 +4077,28 @@
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="G84" s="22">
-        <v>0</v>
-      </c>
-      <c r="H84" s="22">
-        <v>9</v>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H84" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
@@ -4129,7 +4127,7 @@
       </c>
       <c r="D85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
@@ -4142,15 +4140,11 @@
           <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
-      <c r="G85" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H85" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
+      <c r="G85" s="23">
+        <v>0</v>
+      </c>
+      <c r="H85" s="23">
+        <v>9</v>
       </c>
       <c r="I85" s="21" t="inlineStr">
         <is>
@@ -4184,12 +4178,12 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G86" s="22" t="inlineStr">
@@ -4199,7 +4193,7 @@
       </c>
       <c r="H86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
@@ -4234,12 +4228,12 @@
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -4249,7 +4243,7 @@
       </c>
       <c r="H87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I87" s="21" t="inlineStr">
@@ -4279,24 +4273,28 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G88" s="22">
-        <v>0</v>
-      </c>
-      <c r="H88" s="22">
-        <v>6</v>
+          <t xml:space="preserve">وافل</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H88" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وافل</t>
+        </is>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
@@ -4325,7 +4323,7 @@
       </c>
       <c r="D89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
@@ -4338,15 +4336,11 @@
           <t xml:space="preserve">کوکی</t>
         </is>
       </c>
-      <c r="G89" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H89" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
+      <c r="G89" s="23">
+        <v>0</v>
+      </c>
+      <c r="H89" s="23">
+        <v>6</v>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
@@ -4375,24 +4369,28 @@
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="G90" s="22">
-        <v>0</v>
-      </c>
-      <c r="H90" s="22">
-        <v>3</v>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G90" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H90" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
@@ -4421,7 +4419,7 @@
       </c>
       <c r="D91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E91" s="19" t="inlineStr">
@@ -4434,15 +4432,11 @@
           <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
-      <c r="G91" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H91" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
+      <c r="G91" s="23">
+        <v>0</v>
+      </c>
+      <c r="H91" s="23">
+        <v>3</v>
       </c>
       <c r="I91" s="21" t="inlineStr">
         <is>
@@ -4476,12 +4470,12 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F92" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G92" s="22" t="inlineStr">
@@ -4491,7 +4485,7 @@
       </c>
       <c r="H92" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="I92" s="20" t="inlineStr">
@@ -4521,24 +4515,28 @@
       </c>
       <c r="D93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G93" s="23">
-        <v>0</v>
-      </c>
-      <c r="H93" s="23">
-        <v>4</v>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H93" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
       </c>
       <c r="I93" s="21" t="inlineStr">
         <is>
@@ -4567,7 +4565,7 @@
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
@@ -4580,15 +4578,11 @@
           <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
-      <c r="G94" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H94" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
+      <c r="G94" s="22">
+        <v>0</v>
+      </c>
+      <c r="H94" s="22">
+        <v>4</v>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
@@ -4617,24 +4611,28 @@
       </c>
       <c r="D95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G95" s="23">
-        <v>0</v>
-      </c>
-      <c r="H95" s="23">
-        <v>6</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H95" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I95" s="21" t="inlineStr">
         <is>
@@ -4663,7 +4661,7 @@
       </c>
       <c r="D96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E96" s="17" t="inlineStr">
@@ -4676,15 +4674,11 @@
           <t xml:space="preserve">آجیل</t>
         </is>
       </c>
-      <c r="G96" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H96" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+      <c r="G96" s="22">
+        <v>0</v>
+      </c>
+      <c r="H96" s="22">
+        <v>6</v>
       </c>
       <c r="I96" s="20" t="inlineStr">
         <is>
@@ -4713,24 +4707,28 @@
       </c>
       <c r="D97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
-      </c>
-      <c r="G97" s="23">
-        <v>0</v>
-      </c>
-      <c r="H97" s="23">
-        <v>7</v>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G97" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H97" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
       </c>
       <c r="I97" s="21" t="inlineStr">
         <is>
@@ -4759,7 +4757,7 @@
       </c>
       <c r="D98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E98" s="17" t="inlineStr">
@@ -4772,15 +4770,11 @@
           <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
-      <c r="G98" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H98" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
+      <c r="G98" s="22">
+        <v>0</v>
+      </c>
+      <c r="H98" s="22">
+        <v>7</v>
       </c>
       <c r="I98" s="20" t="inlineStr">
         <is>
@@ -4814,12 +4808,12 @@
       </c>
       <c r="E99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -4829,7 +4823,7 @@
       </c>
       <c r="H99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I99" s="21" t="inlineStr">
@@ -4859,24 +4853,28 @@
       </c>
       <c r="D100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G100" s="22">
-        <v>0</v>
-      </c>
-      <c r="H100" s="22">
-        <v>3</v>
+          <t xml:space="preserve">رول رول</t>
+        </is>
+      </c>
+      <c r="G100" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H100" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول</t>
+        </is>
       </c>
       <c r="I100" s="20" t="inlineStr">
         <is>
@@ -4905,7 +4903,7 @@
       </c>
       <c r="D101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E101" s="19" t="inlineStr">
@@ -4918,15 +4916,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G101" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H101" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G101" s="23">
+        <v>0</v>
+      </c>
+      <c r="H101" s="23">
+        <v>3</v>
       </c>
       <c r="I101" s="21" t="inlineStr">
         <is>
@@ -4960,7 +4954,7 @@
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F102" s="22" t="inlineStr">
@@ -5010,7 +5004,7 @@
       </c>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
@@ -5060,7 +5054,7 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
@@ -5110,12 +5104,12 @@
       </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -5125,7 +5119,7 @@
       </c>
       <c r="H105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I105" s="21" t="inlineStr">
@@ -5160,12 +5154,12 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G106" s="22" t="inlineStr">
@@ -5175,7 +5169,7 @@
       </c>
       <c r="H106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I106" s="20" t="inlineStr">
@@ -5210,12 +5204,12 @@
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -5225,7 +5219,7 @@
       </c>
       <c r="H107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="I107" s="21" t="inlineStr">
@@ -5255,24 +5249,28 @@
       </c>
       <c r="D108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G108" s="22">
-        <v>0</v>
-      </c>
-      <c r="H108" s="22">
-        <v>5</v>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
+      </c>
+      <c r="G108" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H108" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
       </c>
       <c r="I108" s="20" t="inlineStr">
         <is>
@@ -5301,7 +5299,7 @@
       </c>
       <c r="D109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E109" s="19" t="inlineStr">
@@ -5314,15 +5312,11 @@
           <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
-      <c r="G109" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H109" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
+      <c r="G109" s="23">
+        <v>0</v>
+      </c>
+      <c r="H109" s="23">
+        <v>5</v>
       </c>
       <c r="I109" s="21" t="inlineStr">
         <is>
@@ -5351,24 +5345,28 @@
       </c>
       <c r="D110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G110" s="22">
-        <v>0</v>
-      </c>
-      <c r="H110" s="22">
-        <v>2</v>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G110" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H110" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
       </c>
       <c r="I110" s="20" t="inlineStr">
         <is>
@@ -5397,7 +5395,7 @@
       </c>
       <c r="D111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E111" s="19" t="inlineStr">
@@ -5410,15 +5408,11 @@
           <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
-      <c r="G111" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H111" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
+      <c r="G111" s="23">
+        <v>0</v>
+      </c>
+      <c r="H111" s="23">
+        <v>2</v>
       </c>
       <c r="I111" s="21" t="inlineStr">
         <is>
@@ -5447,24 +5441,28 @@
       </c>
       <c r="D112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G112" s="22">
-        <v>0</v>
-      </c>
-      <c r="H112" s="22">
-        <v>4</v>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G112" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H112" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
       </c>
       <c r="I112" s="20" t="inlineStr">
         <is>
@@ -5493,7 +5491,7 @@
       </c>
       <c r="D113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E113" s="19" t="inlineStr">
@@ -5506,15 +5504,11 @@
           <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
-      <c r="G113" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H113" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
+      <c r="G113" s="23">
+        <v>0</v>
+      </c>
+      <c r="H113" s="23">
+        <v>4</v>
       </c>
       <c r="I113" s="21" t="inlineStr">
         <is>
@@ -5548,12 +5542,12 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G114" s="22" t="inlineStr">
@@ -5563,7 +5557,7 @@
       </c>
       <c r="H114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I114" s="20" t="inlineStr">
@@ -5598,12 +5592,12 @@
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -5613,7 +5607,7 @@
       </c>
       <c r="H115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I115" s="21" t="inlineStr">
@@ -5648,12 +5642,12 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G116" s="22" t="inlineStr">
@@ -5663,7 +5657,7 @@
       </c>
       <c r="H116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I116" s="20" t="inlineStr">
@@ -5698,12 +5692,12 @@
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -5713,7 +5707,7 @@
       </c>
       <c r="H117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I117" s="21" t="inlineStr">
@@ -5748,12 +5742,12 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G118" s="22" t="inlineStr">
@@ -5763,7 +5757,7 @@
       </c>
       <c r="H118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I118" s="20" t="inlineStr">
@@ -5798,12 +5792,12 @@
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -5813,7 +5807,7 @@
       </c>
       <c r="H119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I119" s="21" t="inlineStr">
@@ -5848,12 +5842,12 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G120" s="22" t="inlineStr">
@@ -5863,7 +5857,7 @@
       </c>
       <c r="H120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="I120" s="20" t="inlineStr">
@@ -5893,24 +5887,28 @@
       </c>
       <c r="D121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G121" s="23">
-        <v>0</v>
-      </c>
-      <c r="H121" s="23">
-        <v>4</v>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="G121" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H121" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
       </c>
       <c r="I121" s="21" t="inlineStr">
         <is>
@@ -5939,7 +5937,7 @@
       </c>
       <c r="D122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E122" s="17" t="inlineStr">
@@ -5952,15 +5950,11 @@
           <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
-      <c r="G122" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H122" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
+      <c r="G122" s="22">
+        <v>0</v>
+      </c>
+      <c r="H122" s="22">
+        <v>4</v>
       </c>
       <c r="I122" s="20" t="inlineStr">
         <is>
@@ -5994,12 +5988,12 @@
       </c>
       <c r="E123" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -6009,7 +6003,7 @@
       </c>
       <c r="H123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I123" s="21" t="inlineStr">
@@ -6044,12 +6038,12 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F124" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G124" s="22" t="inlineStr">
@@ -6059,7 +6053,7 @@
       </c>
       <c r="H124" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I124" s="20" t="inlineStr">
@@ -6094,12 +6088,12 @@
       </c>
       <c r="E125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -6109,7 +6103,7 @@
       </c>
       <c r="H125" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I125" s="21" t="inlineStr">
@@ -6144,12 +6138,12 @@
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F126" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="G126" s="22" t="inlineStr">
@@ -6159,7 +6153,7 @@
       </c>
       <c r="H126" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="I126" s="20" t="inlineStr">
@@ -6189,24 +6183,28 @@
       </c>
       <c r="D127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G127" s="23">
-        <v>0</v>
-      </c>
-      <c r="H127" s="23">
-        <v>4</v>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H127" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
       </c>
       <c r="I127" s="21" t="inlineStr">
         <is>
@@ -6235,7 +6233,7 @@
       </c>
       <c r="D128" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E128" s="17" t="inlineStr">
@@ -6248,15 +6246,11 @@
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G128" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H128" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
+      <c r="G128" s="22">
+        <v>0</v>
+      </c>
+      <c r="H128" s="22">
+        <v>4</v>
       </c>
       <c r="I128" s="20" t="inlineStr">
         <is>
@@ -6290,132 +6284,138 @@
       </c>
       <c r="E129" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F129" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G129" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H129" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="I129" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J129" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="28" customHeight="1">
+      <c r="A130" s="16">
+        <v>3</v>
+      </c>
+      <c r="B130" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C130" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D130" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E130" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">68</t>
         </is>
       </c>
-      <c r="F129" s="23" t="inlineStr">
+      <c r="F130" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="G129" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H129" s="23" t="inlineStr">
+      <c r="G130" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H130" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="I129" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J129" s="19" t="inlineStr">
+      <c r="I130" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J130" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="48" customHeight="1">
-      <c r="A130" s="16">
-        <v>3</v>
-      </c>
-      <c r="B130" s="17" t="inlineStr">
+    <row r="131" ht="48" customHeight="1">
+      <c r="A131" s="18">
+        <v>3</v>
+      </c>
+      <c r="B131" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
-      <c r="C130" s="17" t="inlineStr">
+      <c r="C131" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
-      <c r="D130" s="17" t="inlineStr">
+      <c r="D131" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E130" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F130" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G130" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H130" s="22" t="inlineStr">
+      <c r="E131" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F131" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G131" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H131" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="I130" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J130" s="17" t="inlineStr">
+      <c r="I131" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J131" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="28" customHeight="1">
-      <c r="A131" s="18">
-        <v>2</v>
-      </c>
-      <c r="B131" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/23</t>
-        </is>
-      </c>
-      <c r="C131" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23:16:19</t>
-        </is>
-      </c>
-      <c r="D131" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E131" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="F131" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G131" s="23">
-        <v>4</v>
-      </c>
-      <c r="H131" s="23">
-        <v>0</v>
-      </c>
-      <c r="I131" s="21">
-        <v>4</v>
-      </c>
-      <c r="J131" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
     <row r="132" ht="28" customHeight="1">
       <c r="A132" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B132" s="17" t="inlineStr">
         <is>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="C132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">23:16:19</t>
         </is>
       </c>
       <c r="D132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E132" s="17" t="inlineStr">
@@ -6443,19 +6443,17 @@
         </is>
       </c>
       <c r="G132" s="22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H132" s="22">
+        <v>0</v>
+      </c>
+      <c r="I132" s="20">
         <v>4</v>
       </c>
-      <c r="I132" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6473,7 @@
       </c>
       <c r="D133" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E133" s="19" t="inlineStr">
@@ -6488,15 +6486,11 @@
           <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
-      <c r="G133" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H133" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
+      <c r="G133" s="23">
+        <v>0</v>
+      </c>
+      <c r="H133" s="23">
+        <v>4</v>
       </c>
       <c r="I133" s="21" t="inlineStr">
         <is>
@@ -6530,12 +6524,12 @@
       </c>
       <c r="E134" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F134" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G134" s="22" t="inlineStr">
@@ -6545,7 +6539,7 @@
       </c>
       <c r="H134" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="I134" s="20" t="inlineStr">
@@ -6580,7 +6574,7 @@
       </c>
       <c r="E135" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
@@ -6630,30 +6624,80 @@
       </c>
       <c r="E136" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F136" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G136" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H136" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I136" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J136" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="28" customHeight="1">
+      <c r="A137" s="18">
+        <v>1</v>
+      </c>
+      <c r="B137" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C137" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D137" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E137" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F136" s="22" t="inlineStr">
+      <c r="F137" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G136" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H136" s="22" t="inlineStr">
+      <c r="G137" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H137" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I136" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J136" s="17" t="inlineStr">
+      <c r="I137" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J137" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J137" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J137"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J139" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J139"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:36:57</t>
+          <t xml:space="preserve">15:38:05</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -518,32 +518,32 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G6" s="22">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H6" s="22">
         <v>0</v>
       </c>
       <c r="I6" s="20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">424ffdd738</t>
+          <t xml:space="preserve">c36d03e545</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:36:21</t>
+          <t xml:space="preserve">15:38:01</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -562,32 +562,32 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G7" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H7" s="23">
         <v>0</v>
       </c>
       <c r="I7" s="21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">b665f084da</t>
+          <t xml:space="preserve">02e6345647</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:35:52</t>
+          <t xml:space="preserve">15:36:57</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -606,32 +606,32 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G8" s="22">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H8" s="22">
         <v>0</v>
       </c>
       <c r="I8" s="20">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">751f8a7696</t>
+          <t xml:space="preserve">424ffdd738</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="18">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:18</t>
+          <t xml:space="preserve">15:36:21</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -650,32 +650,32 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" s="23">
         <v>0</v>
       </c>
       <c r="I9" s="21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0be32d0353</t>
+          <t xml:space="preserve">b665f084da</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:13</t>
+          <t xml:space="preserve">15:35:52</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G10" s="22">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H10" s="22">
         <v>0</v>
       </c>
       <c r="I10" s="20">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">28a1fcc537</t>
+          <t xml:space="preserve">751f8a7696</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="18">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:05</t>
+          <t xml:space="preserve">15:33:18</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -738,32 +738,32 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G11" s="23">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H11" s="23">
         <v>0</v>
       </c>
       <c r="I11" s="21">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a734384c03</t>
+          <t xml:space="preserve">0be32d0353</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:31:30</t>
+          <t xml:space="preserve">15:33:13</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
@@ -782,32 +782,32 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G12" s="22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H12" s="22">
         <v>0</v>
       </c>
       <c r="I12" s="20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5edabb20bb</t>
+          <t xml:space="preserve">28a1fcc537</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="18">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:53</t>
+          <t xml:space="preserve">15:33:05</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -826,32 +826,32 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G13" s="23">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H13" s="23">
         <v>0</v>
       </c>
       <c r="I13" s="21">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a1408f9e88</t>
+          <t xml:space="preserve">a734384c03</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:35</t>
+          <t xml:space="preserve">15:31:30</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
@@ -870,32 +870,32 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G14" s="22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H14" s="22">
         <v>0</v>
       </c>
       <c r="I14" s="20">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed45f1ef47</t>
+          <t xml:space="preserve">5edabb20bb</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="18">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:59</t>
+          <t xml:space="preserve">15:30:53</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -914,32 +914,32 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G15" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="23">
         <v>0</v>
       </c>
       <c r="I15" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">d659616819</t>
+          <t xml:space="preserve">a1408f9e88</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="16">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:38</t>
+          <t xml:space="preserve">15:30:35</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
@@ -958,32 +958,32 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G16" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" s="22">
         <v>0</v>
       </c>
       <c r="I16" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">19f5f6152e</t>
+          <t xml:space="preserve">ed45f1ef47</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="18">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:24</t>
+          <t xml:space="preserve">15:29:59</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -1002,32 +1002,32 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G17" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H17" s="23">
         <v>0</v>
       </c>
       <c r="I17" s="21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd714591b4</t>
+          <t xml:space="preserve">d659616819</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
@@ -1036,22 +1036,22 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:38</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G18" s="22">
@@ -1060,20 +1060,18 @@
       <c r="H18" s="22">
         <v>0</v>
       </c>
-      <c r="I18" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I18" s="20">
+        <v>2</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">19f5f6152e</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
@@ -1082,22 +1080,22 @@
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:24</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G19" s="23">
@@ -1106,14 +1104,12 @@
       <c r="H19" s="23">
         <v>0</v>
       </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I19" s="21">
+        <v>4</v>
       </c>
       <c r="J19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">bd714591b4</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1134,12 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G20" s="22">
@@ -1184,19 +1180,19 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G21" s="23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H21" s="23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
@@ -1230,19 +1226,19 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G22" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" s="22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
@@ -1276,19 +1272,19 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G23" s="23">
         <v>0</v>
       </c>
       <c r="H23" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
@@ -1322,19 +1318,19 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G24" s="22">
         <v>0</v>
       </c>
       <c r="H24" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -1368,12 +1364,12 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G25" s="23">
@@ -1414,12 +1410,12 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G26" s="22">
@@ -1460,19 +1456,19 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G27" s="23">
         <v>0</v>
       </c>
       <c r="H27" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
@@ -1506,19 +1502,19 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G28" s="22">
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -1552,19 +1548,19 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G29" s="23">
         <v>0</v>
       </c>
       <c r="H29" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
@@ -1598,19 +1594,19 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G30" s="22">
         <v>0</v>
       </c>
       <c r="H30" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
@@ -1644,19 +1640,19 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G31" s="23">
         <v>0</v>
       </c>
       <c r="H31" s="23">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
@@ -1690,19 +1686,19 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G32" s="22">
         <v>0</v>
       </c>
       <c r="H32" s="22">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
@@ -1736,19 +1732,19 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G33" s="23">
         <v>0</v>
       </c>
       <c r="H33" s="23">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
@@ -1782,19 +1778,19 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G34" s="22">
         <v>0</v>
       </c>
       <c r="H34" s="22">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
@@ -1828,19 +1824,19 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G35" s="23">
         <v>0</v>
       </c>
       <c r="H35" s="23">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1874,19 +1870,19 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G36" s="22">
         <v>0</v>
       </c>
       <c r="H36" s="22">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1920,19 +1916,19 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G37" s="23">
         <v>0</v>
       </c>
       <c r="H37" s="23">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1966,19 +1962,19 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G38" s="22">
         <v>0</v>
       </c>
       <c r="H38" s="22">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -2012,19 +2008,19 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G39" s="23">
         <v>0</v>
       </c>
       <c r="H39" s="23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
@@ -2058,19 +2054,19 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G40" s="22">
         <v>0</v>
       </c>
       <c r="H40" s="22">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
@@ -2104,19 +2100,19 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G41" s="23">
         <v>0</v>
       </c>
       <c r="H41" s="23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I41" s="21" t="inlineStr">
         <is>
@@ -2150,19 +2146,19 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G42" s="22">
         <v>0</v>
       </c>
       <c r="H42" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
@@ -2196,19 +2192,19 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G43" s="23">
         <v>0</v>
       </c>
       <c r="H43" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I43" s="21" t="inlineStr">
         <is>
@@ -2242,19 +2238,19 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G44" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
@@ -2269,7 +2265,7 @@
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
@@ -2278,7 +2274,7 @@
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D45" s="19" t="inlineStr">
@@ -2288,12 +2284,12 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G45" s="23">
@@ -2309,13 +2305,13 @@
       </c>
       <c r="J45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
@@ -2324,7 +2320,7 @@
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
@@ -2334,16 +2330,16 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G46" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="22">
         <v>4</v>
@@ -2355,7 +2351,7 @@
       </c>
       <c r="J46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
@@ -2380,12 +2376,12 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G47" s="23">
@@ -2426,19 +2422,19 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G48" s="22">
         <v>0</v>
       </c>
       <c r="H48" s="22">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I48" s="20" t="inlineStr">
         <is>
@@ -2472,19 +2468,19 @@
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G49" s="23">
         <v>0</v>
       </c>
       <c r="H49" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I49" s="21" t="inlineStr">
         <is>
@@ -2518,19 +2514,19 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G50" s="22">
         <v>0</v>
       </c>
       <c r="H50" s="22">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I50" s="20" t="inlineStr">
         <is>
@@ -2543,9 +2539,9 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="48" customHeight="1">
+    <row r="51" ht="28" customHeight="1">
       <c r="A51" s="18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
@@ -2554,33 +2550,29 @@
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11:25:59</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">یادداشت و آمار قهوه</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G51" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
-        </is>
-      </c>
-      <c r="H51" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G51" s="23">
+        <v>0</v>
+      </c>
+      <c r="H51" s="23">
+        <v>4</v>
       </c>
       <c r="I51" s="21" t="inlineStr">
         <is>
@@ -2589,13 +2581,13 @@
       </c>
       <c r="J51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2688d62325</t>
+          <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="16">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
@@ -2604,42 +2596,44 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:32</t>
+          <t xml:space="preserve">12:59:31</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G52" s="22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H52" s="22">
-        <v>0</v>
-      </c>
-      <c r="I52" s="20">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="I52" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">371938f24f</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28" customHeight="1">
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="48" customHeight="1">
       <c r="A53" s="18">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
@@ -2648,42 +2642,48 @@
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G53" s="23">
-        <v>4</v>
-      </c>
-      <c r="H53" s="23">
-        <v>0</v>
-      </c>
-      <c r="I53" s="21">
-        <v>4</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
+        </is>
+      </c>
+      <c r="H53" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I53" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">2688d62325</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="16">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F54" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G54" s="22">
@@ -2721,13 +2721,13 @@
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="18">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -2746,32 +2746,32 @@
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G55" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H55" s="23">
         <v>0</v>
       </c>
       <c r="I55" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="16">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -2790,32 +2790,32 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G56" s="22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H56" s="22">
         <v>0</v>
       </c>
       <c r="I56" s="20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -2834,32 +2834,32 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G57" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57" s="23">
         <v>0</v>
       </c>
       <c r="I57" s="21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="16">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -2878,32 +2878,32 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G58" s="22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H58" s="22">
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="18">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -2922,32 +2922,32 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G59" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H59" s="23">
         <v>0</v>
       </c>
       <c r="I59" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="16">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G60" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H60" s="22">
         <v>0</v>
       </c>
       <c r="I60" s="20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="18">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
@@ -3010,32 +3010,32 @@
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G61" s="23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H61" s="23">
         <v>0</v>
       </c>
       <c r="I61" s="21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="16">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
@@ -3054,32 +3054,32 @@
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G62" s="22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H62" s="22">
         <v>0</v>
       </c>
       <c r="I62" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="18">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D63" s="19" t="inlineStr">
@@ -3098,32 +3098,32 @@
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G63" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H63" s="23">
         <v>0</v>
       </c>
       <c r="I63" s="21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="16">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
@@ -3142,32 +3142,32 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G64" s="22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H64" s="22">
         <v>0</v>
       </c>
       <c r="I64" s="20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -3186,76 +3186,76 @@
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G65" s="23">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H65" s="23">
         <v>0</v>
       </c>
       <c r="I65" s="21">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="16">
+        <v>9</v>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:18:08</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37</t>
+        </is>
+      </c>
+      <c r="F66" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
+        </is>
+      </c>
+      <c r="G66" s="22">
         <v>7</v>
       </c>
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C66" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:18:04</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E66" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24</t>
-        </is>
-      </c>
-      <c r="F66" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G66" s="22">
-        <v>3</v>
-      </c>
       <c r="H66" s="22">
         <v>0</v>
       </c>
       <c r="I66" s="20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D67" s="19" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G67" s="23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H67" s="23">
         <v>0</v>
       </c>
       <c r="I67" s="21">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G68" s="22">
@@ -3337,13 +3337,13 @@
       </c>
       <c r="J68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1">
       <c r="A69" s="18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D69" s="19" t="inlineStr">
@@ -3362,118 +3362,114 @@
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G69" s="23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H69" s="23">
         <v>0</v>
       </c>
       <c r="I69" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1">
       <c r="A70" s="16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G70" s="22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H70" s="22">
-        <v>5</v>
-      </c>
-      <c r="I70" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I70" s="20">
+        <v>3</v>
       </c>
       <c r="J70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1">
       <c r="A71" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G71" s="23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H71" s="23">
-        <v>3</v>
-      </c>
-      <c r="I71" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I71" s="21">
+        <v>5</v>
       </c>
       <c r="J71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -3493,28 +3489,24 @@
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
-      </c>
-      <c r="G72" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H72" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+          <t xml:space="preserve">تیتاپ نادری</t>
+        </is>
+      </c>
+      <c r="G72" s="22">
+        <v>0</v>
+      </c>
+      <c r="H72" s="22">
+        <v>5</v>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
@@ -3548,19 +3540,19 @@
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G73" s="23">
         <v>0</v>
       </c>
       <c r="H73" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I73" s="21" t="inlineStr">
         <is>
@@ -3594,12 +3586,12 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G74" s="22" t="inlineStr">
@@ -3609,7 +3601,7 @@
       </c>
       <c r="H74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
@@ -3639,28 +3631,24 @@
       </c>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
-        </is>
-      </c>
-      <c r="G75" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H75" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
-        </is>
+          <t xml:space="preserve">ساندویچ مرغ</t>
+        </is>
+      </c>
+      <c r="G75" s="23">
+        <v>0</v>
+      </c>
+      <c r="H75" s="23">
+        <v>6</v>
       </c>
       <c r="I75" s="21" t="inlineStr">
         <is>
@@ -3694,22 +3682,22 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
@@ -3744,22 +3732,22 @@
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I77" s="21" t="inlineStr">
@@ -3794,12 +3782,12 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G78" s="22" t="inlineStr">
@@ -3809,7 +3797,7 @@
       </c>
       <c r="H78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
@@ -3839,24 +3827,28 @@
       </c>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G79" s="23">
-        <v>0</v>
-      </c>
-      <c r="H79" s="23">
-        <v>3</v>
+          <t xml:space="preserve">نات بار زرد</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H79" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">نات بار زرد</t>
+        </is>
       </c>
       <c r="I79" s="21" t="inlineStr">
         <is>
@@ -3890,12 +3882,12 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
         </is>
       </c>
       <c r="G80" s="22" t="inlineStr">
@@ -3905,7 +3897,7 @@
       </c>
       <c r="H80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
@@ -3940,12 +3932,12 @@
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G81" s="23">
@@ -3986,12 +3978,12 @@
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G82" s="22" t="inlineStr">
@@ -4001,7 +3993,7 @@
       </c>
       <c r="H82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
@@ -4036,19 +4028,19 @@
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G83" s="23">
         <v>0</v>
       </c>
       <c r="H83" s="23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
@@ -4082,12 +4074,12 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G84" s="22" t="inlineStr">
@@ -4097,7 +4089,7 @@
       </c>
       <c r="H84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="I84" s="20" t="inlineStr">
@@ -4132,19 +4124,19 @@
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G85" s="23">
         <v>0</v>
       </c>
       <c r="H85" s="23">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I85" s="21" t="inlineStr">
         <is>
@@ -4178,12 +4170,12 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G86" s="22" t="inlineStr">
@@ -4193,7 +4185,7 @@
       </c>
       <c r="H86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
@@ -4223,28 +4215,24 @@
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
-        </is>
-      </c>
-      <c r="G87" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H87" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کروسان</t>
-        </is>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
+        </is>
+      </c>
+      <c r="G87" s="23">
+        <v>0</v>
+      </c>
+      <c r="H87" s="23">
+        <v>9</v>
       </c>
       <c r="I87" s="21" t="inlineStr">
         <is>
@@ -4278,12 +4266,12 @@
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G88" s="22" t="inlineStr">
@@ -4293,7 +4281,7 @@
       </c>
       <c r="H88" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I88" s="20" t="inlineStr">
@@ -4323,24 +4311,28 @@
       </c>
       <c r="D89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G89" s="23">
-        <v>0</v>
-      </c>
-      <c r="H89" s="23">
-        <v>6</v>
+          <t xml:space="preserve">کروسان</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H89" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کروسان</t>
+        </is>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
@@ -4374,12 +4366,12 @@
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">وافل</t>
         </is>
       </c>
       <c r="G90" s="22" t="inlineStr">
@@ -4389,7 +4381,7 @@
       </c>
       <c r="H90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">وافل</t>
         </is>
       </c>
       <c r="I90" s="20" t="inlineStr">
@@ -4424,19 +4416,19 @@
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G91" s="23">
         <v>0</v>
       </c>
       <c r="H91" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I91" s="21" t="inlineStr">
         <is>
@@ -4470,12 +4462,12 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F92" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G92" s="22" t="inlineStr">
@@ -4485,7 +4477,7 @@
       </c>
       <c r="H92" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="I92" s="20" t="inlineStr">
@@ -4515,28 +4507,24 @@
       </c>
       <c r="D93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
-        </is>
-      </c>
-      <c r="G93" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H93" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
-        </is>
+          <t xml:space="preserve">پاستیل</t>
+        </is>
+      </c>
+      <c r="G93" s="23">
+        <v>0</v>
+      </c>
+      <c r="H93" s="23">
+        <v>3</v>
       </c>
       <c r="I93" s="21" t="inlineStr">
         <is>
@@ -4565,24 +4553,28 @@
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F94" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G94" s="22">
-        <v>0</v>
-      </c>
-      <c r="H94" s="22">
-        <v>4</v>
+          <t xml:space="preserve">پاستیل</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H94" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پاستیل</t>
+        </is>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
@@ -4616,12 +4608,12 @@
       </c>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -4631,7 +4623,7 @@
       </c>
       <c r="H95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="I95" s="21" t="inlineStr">
@@ -4666,19 +4658,19 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G96" s="22">
         <v>0</v>
       </c>
       <c r="H96" s="22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I96" s="20" t="inlineStr">
         <is>
@@ -4712,12 +4704,12 @@
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -4727,7 +4719,7 @@
       </c>
       <c r="H97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="I97" s="21" t="inlineStr">
@@ -4762,19 +4754,19 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F98" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G98" s="22">
         <v>0</v>
       </c>
       <c r="H98" s="22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I98" s="20" t="inlineStr">
         <is>
@@ -4808,12 +4800,12 @@
       </c>
       <c r="E99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -4823,7 +4815,7 @@
       </c>
       <c r="H99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="I99" s="21" t="inlineStr">
@@ -4853,28 +4845,24 @@
       </c>
       <c r="D100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
-        </is>
-      </c>
-      <c r="G100" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H100" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">رول رول</t>
-        </is>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
+        </is>
+      </c>
+      <c r="G100" s="22">
+        <v>0</v>
+      </c>
+      <c r="H100" s="22">
+        <v>7</v>
       </c>
       <c r="I100" s="20" t="inlineStr">
         <is>
@@ -4903,24 +4891,28 @@
       </c>
       <c r="D101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G101" s="23">
-        <v>0</v>
-      </c>
-      <c r="H101" s="23">
-        <v>3</v>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H101" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
+        </is>
       </c>
       <c r="I101" s="21" t="inlineStr">
         <is>
@@ -4954,12 +4946,12 @@
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F102" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G102" s="22" t="inlineStr">
@@ -4969,7 +4961,7 @@
       </c>
       <c r="H102" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="I102" s="20" t="inlineStr">
@@ -4999,12 +4991,12 @@
       </c>
       <c r="D103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
@@ -5012,15 +5004,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G103" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H103" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G103" s="23">
+        <v>0</v>
+      </c>
+      <c r="H103" s="23">
+        <v>3</v>
       </c>
       <c r="I103" s="21" t="inlineStr">
         <is>
@@ -5054,7 +5042,7 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
@@ -5104,7 +5092,7 @@
       </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
@@ -5154,12 +5142,12 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G106" s="22" t="inlineStr">
@@ -5169,7 +5157,7 @@
       </c>
       <c r="H106" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I106" s="20" t="inlineStr">
@@ -5204,12 +5192,12 @@
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -5219,7 +5207,7 @@
       </c>
       <c r="H107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I107" s="21" t="inlineStr">
@@ -5254,12 +5242,12 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G108" s="22" t="inlineStr">
@@ -5269,7 +5257,7 @@
       </c>
       <c r="H108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I108" s="20" t="inlineStr">
@@ -5299,24 +5287,28 @@
       </c>
       <c r="D109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G109" s="23">
-        <v>0</v>
-      </c>
-      <c r="H109" s="23">
-        <v>5</v>
+          <t xml:space="preserve">توینکلز</t>
+        </is>
+      </c>
+      <c r="G109" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H109" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">توینکلز</t>
+        </is>
       </c>
       <c r="I109" s="21" t="inlineStr">
         <is>
@@ -5350,12 +5342,12 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -5365,7 +5357,7 @@
       </c>
       <c r="H110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="I110" s="20" t="inlineStr">
@@ -5400,19 +5392,19 @@
       </c>
       <c r="E111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G111" s="23">
         <v>0</v>
       </c>
       <c r="H111" s="23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I111" s="21" t="inlineStr">
         <is>
@@ -5446,12 +5438,12 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G112" s="22" t="inlineStr">
@@ -5461,7 +5453,7 @@
       </c>
       <c r="H112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="I112" s="20" t="inlineStr">
@@ -5496,19 +5488,19 @@
       </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G113" s="23">
         <v>0</v>
       </c>
       <c r="H113" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I113" s="21" t="inlineStr">
         <is>
@@ -5542,12 +5534,12 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G114" s="22" t="inlineStr">
@@ -5557,7 +5549,7 @@
       </c>
       <c r="H114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="I114" s="20" t="inlineStr">
@@ -5587,28 +5579,24 @@
       </c>
       <c r="D115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
-        </is>
-      </c>
-      <c r="G115" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H115" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شیر شکلات</t>
-        </is>
+          <t xml:space="preserve">تیتو مزمز</t>
+        </is>
+      </c>
+      <c r="G115" s="23">
+        <v>0</v>
+      </c>
+      <c r="H115" s="23">
+        <v>4</v>
       </c>
       <c r="I115" s="21" t="inlineStr">
         <is>
@@ -5642,12 +5630,12 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G116" s="22" t="inlineStr">
@@ -5657,7 +5645,7 @@
       </c>
       <c r="H116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I116" s="20" t="inlineStr">
@@ -5692,12 +5680,12 @@
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -5707,7 +5695,7 @@
       </c>
       <c r="H117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I117" s="21" t="inlineStr">
@@ -5742,12 +5730,12 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G118" s="22" t="inlineStr">
@@ -5757,7 +5745,7 @@
       </c>
       <c r="H118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I118" s="20" t="inlineStr">
@@ -5792,12 +5780,12 @@
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -5807,7 +5795,7 @@
       </c>
       <c r="H119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I119" s="21" t="inlineStr">
@@ -5842,12 +5830,12 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G120" s="22" t="inlineStr">
@@ -5857,7 +5845,7 @@
       </c>
       <c r="H120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I120" s="20" t="inlineStr">
@@ -5892,12 +5880,12 @@
       </c>
       <c r="E121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -5907,7 +5895,7 @@
       </c>
       <c r="H121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I121" s="21" t="inlineStr">
@@ -5937,24 +5925,28 @@
       </c>
       <c r="D122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F122" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G122" s="22">
-        <v>0</v>
-      </c>
-      <c r="H122" s="22">
-        <v>4</v>
+          <t xml:space="preserve">وجین</t>
+        </is>
+      </c>
+      <c r="G122" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H122" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وجین</t>
+        </is>
       </c>
       <c r="I122" s="20" t="inlineStr">
         <is>
@@ -5988,12 +5980,12 @@
       </c>
       <c r="E123" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -6003,7 +5995,7 @@
       </c>
       <c r="H123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="I123" s="21" t="inlineStr">
@@ -6033,28 +6025,24 @@
       </c>
       <c r="D124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F124" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
-        </is>
-      </c>
-      <c r="G124" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H124" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
-        </is>
+          <t xml:space="preserve">پرو شیر</t>
+        </is>
+      </c>
+      <c r="G124" s="22">
+        <v>0</v>
+      </c>
+      <c r="H124" s="22">
+        <v>4</v>
       </c>
       <c r="I124" s="20" t="inlineStr">
         <is>
@@ -6088,12 +6076,12 @@
       </c>
       <c r="E125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -6103,7 +6091,7 @@
       </c>
       <c r="H125" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I125" s="21" t="inlineStr">
@@ -6138,12 +6126,12 @@
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F126" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G126" s="22" t="inlineStr">
@@ -6153,7 +6141,7 @@
       </c>
       <c r="H126" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I126" s="20" t="inlineStr">
@@ -6188,12 +6176,12 @@
       </c>
       <c r="E127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -6203,7 +6191,7 @@
       </c>
       <c r="H127" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I127" s="21" t="inlineStr">
@@ -6233,24 +6221,28 @@
       </c>
       <c r="D128" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F128" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G128" s="22">
-        <v>0</v>
-      </c>
-      <c r="H128" s="22">
-        <v>4</v>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
+        </is>
+      </c>
+      <c r="G128" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H128" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
+        </is>
       </c>
       <c r="I128" s="20" t="inlineStr">
         <is>
@@ -6284,12 +6276,12 @@
       </c>
       <c r="E129" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -6299,7 +6291,7 @@
       </c>
       <c r="H129" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="I129" s="21" t="inlineStr">
@@ -6329,67 +6321,63 @@
       </c>
       <c r="D130" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E130" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F130" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G130" s="22">
+        <v>0</v>
+      </c>
+      <c r="H130" s="22">
+        <v>4</v>
+      </c>
+      <c r="I130" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J130" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="28" customHeight="1">
+      <c r="A131" s="18">
+        <v>3</v>
+      </c>
+      <c r="B131" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C131" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D131" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
-      <c r="E130" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68</t>
-        </is>
-      </c>
-      <c r="F130" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف بدون قند</t>
-        </is>
-      </c>
-      <c r="G130" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H130" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف بدون قند</t>
-        </is>
-      </c>
-      <c r="I130" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J130" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="48" customHeight="1">
-      <c r="A131" s="18">
-        <v>3</v>
-      </c>
-      <c r="B131" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/24</t>
-        </is>
-      </c>
-      <c r="C131" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12:39:32</t>
-        </is>
-      </c>
-      <c r="D131" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">یادداشت و آمار قهوه</t>
-        </is>
-      </c>
       <c r="E131" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -6399,7 +6387,7 @@
       </c>
       <c r="H131" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="I131" s="21" t="inlineStr">
@@ -6415,82 +6403,92 @@
     </row>
     <row r="132" ht="28" customHeight="1">
       <c r="A132" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/23</t>
+          <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
       <c r="C132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">23:16:19</t>
+          <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
       <c r="D132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">68</t>
         </is>
       </c>
       <c r="F132" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G132" s="22">
-        <v>4</v>
-      </c>
-      <c r="H132" s="22">
-        <v>0</v>
-      </c>
-      <c r="I132" s="20">
-        <v>4</v>
+          <t xml:space="preserve">لایف بدون قند</t>
+        </is>
+      </c>
+      <c r="G132" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H132" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف بدون قند</t>
+        </is>
+      </c>
+      <c r="I132" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="J132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">deac82c691</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="28" customHeight="1">
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="48" customHeight="1">
       <c r="A133" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B133" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/23</t>
+          <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
       <c r="C133" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
       <c r="D133" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
       <c r="E133" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G133" s="23">
-        <v>0</v>
-      </c>
-      <c r="H133" s="23">
-        <v>4</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G133" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H133" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
+        </is>
       </c>
       <c r="I133" s="21" t="inlineStr">
         <is>
@@ -6499,13 +6497,13 @@
       </c>
       <c r="J133" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
     <row r="134" ht="28" customHeight="1">
       <c r="A134" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B134" s="17" t="inlineStr">
         <is>
@@ -6514,12 +6512,12 @@
       </c>
       <c r="C134" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">23:16:19</t>
         </is>
       </c>
       <c r="D134" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E134" s="17" t="inlineStr">
@@ -6532,24 +6530,18 @@
           <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
-      <c r="G134" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H134" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="I134" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="G134" s="22">
+        <v>4</v>
+      </c>
+      <c r="H134" s="22">
+        <v>0</v>
+      </c>
+      <c r="I134" s="20">
+        <v>4</v>
       </c>
       <c r="J134" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
@@ -6569,28 +6561,24 @@
       </c>
       <c r="D135" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E135" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="G135" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H135" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
+          <t xml:space="preserve">تیتاپ نادری</t>
+        </is>
+      </c>
+      <c r="G135" s="23">
+        <v>0</v>
+      </c>
+      <c r="H135" s="23">
+        <v>4</v>
       </c>
       <c r="I135" s="21" t="inlineStr">
         <is>
@@ -6624,12 +6612,12 @@
       </c>
       <c r="E136" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F136" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G136" s="22" t="inlineStr">
@@ -6639,7 +6627,7 @@
       </c>
       <c r="H136" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="I136" s="20" t="inlineStr">
@@ -6674,30 +6662,130 @@
       </c>
       <c r="E137" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="F137" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G137" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H137" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I137" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J137" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="28" customHeight="1">
+      <c r="A138" s="16">
+        <v>1</v>
+      </c>
+      <c r="B138" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C138" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D138" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E138" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F138" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G138" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H138" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I138" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J138" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="28" customHeight="1">
+      <c r="A139" s="18">
+        <v>1</v>
+      </c>
+      <c r="B139" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C139" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D139" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E139" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F137" s="23" t="inlineStr">
+      <c r="F139" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G137" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H137" s="23" t="inlineStr">
+      <c r="G139" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H139" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I137" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J137" s="19" t="inlineStr">
+      <c r="I139" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J139" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J139" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J139"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J140" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J140"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:38:05</t>
+          <t xml:space="preserve">15:39:21</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -518,32 +518,32 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G6" s="22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H6" s="22">
         <v>0</v>
       </c>
       <c r="I6" s="20">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">c36d03e545</t>
+          <t xml:space="preserve">fde35723ac</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:38:01</t>
+          <t xml:space="preserve">15:38:05</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -562,32 +562,32 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G7" s="23">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H7" s="23">
         <v>0</v>
       </c>
       <c r="I7" s="21">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">02e6345647</t>
+          <t xml:space="preserve">c36d03e545</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:36:57</t>
+          <t xml:space="preserve">15:38:01</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -606,32 +606,32 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G8" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="22">
         <v>0</v>
       </c>
       <c r="I8" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">424ffdd738</t>
+          <t xml:space="preserve">02e6345647</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="18">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:36:21</t>
+          <t xml:space="preserve">15:36:57</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -650,32 +650,32 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H9" s="23">
         <v>0</v>
       </c>
       <c r="I9" s="21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">b665f084da</t>
+          <t xml:space="preserve">424ffdd738</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:35:52</t>
+          <t xml:space="preserve">15:36:21</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G10" s="22">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H10" s="22">
         <v>0</v>
       </c>
       <c r="I10" s="20">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">751f8a7696</t>
+          <t xml:space="preserve">b665f084da</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="18">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:18</t>
+          <t xml:space="preserve">15:35:52</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -738,32 +738,32 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G11" s="23">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H11" s="23">
         <v>0</v>
       </c>
       <c r="I11" s="21">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0be32d0353</t>
+          <t xml:space="preserve">751f8a7696</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:13</t>
+          <t xml:space="preserve">15:33:18</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
@@ -782,32 +782,32 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G12" s="22">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H12" s="22">
         <v>0</v>
       </c>
       <c r="I12" s="20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">28a1fcc537</t>
+          <t xml:space="preserve">0be32d0353</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="18">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:05</t>
+          <t xml:space="preserve">15:33:13</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -826,32 +826,32 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G13" s="23">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H13" s="23">
         <v>0</v>
       </c>
       <c r="I13" s="21">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a734384c03</t>
+          <t xml:space="preserve">28a1fcc537</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:31:30</t>
+          <t xml:space="preserve">15:33:05</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
@@ -870,32 +870,32 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G14" s="22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H14" s="22">
         <v>0</v>
       </c>
       <c r="I14" s="20">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5edabb20bb</t>
+          <t xml:space="preserve">a734384c03</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="18">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:53</t>
+          <t xml:space="preserve">15:31:30</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -914,32 +914,32 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G15" s="23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H15" s="23">
         <v>0</v>
       </c>
       <c r="I15" s="21">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a1408f9e88</t>
+          <t xml:space="preserve">5edabb20bb</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:35</t>
+          <t xml:space="preserve">15:30:53</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G16" s="22">
@@ -977,13 +977,13 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed45f1ef47</t>
+          <t xml:space="preserve">a1408f9e88</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:59</t>
+          <t xml:space="preserve">15:30:35</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -1002,32 +1002,32 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G17" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" s="23">
         <v>0</v>
       </c>
       <c r="I17" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">d659616819</t>
+          <t xml:space="preserve">ed45f1ef47</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:38</t>
+          <t xml:space="preserve">15:29:59</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G18" s="22">
@@ -1065,13 +1065,13 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">19f5f6152e</t>
+          <t xml:space="preserve">d659616819</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:24</t>
+          <t xml:space="preserve">15:29:38</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -1090,32 +1090,32 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G19" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19" s="23">
         <v>0</v>
       </c>
       <c r="I19" s="21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd714591b4</t>
+          <t xml:space="preserve">19f5f6152e</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
@@ -1124,38 +1124,36 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:24</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G20" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" s="22">
         <v>0</v>
       </c>
-      <c r="I20" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I20" s="20">
+        <v>4</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">bd714591b4</t>
         </is>
       </c>
     </row>
@@ -1180,16 +1178,16 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G21" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H21" s="23">
         <v>0</v>
@@ -1226,16 +1224,16 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G22" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="22">
         <v>0</v>
@@ -1272,19 +1270,19 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G23" s="23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" s="23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
@@ -1318,19 +1316,19 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G24" s="22">
         <v>0</v>
       </c>
       <c r="H24" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -1364,12 +1362,12 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G25" s="23">
@@ -1410,19 +1408,19 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G26" s="22">
         <v>0</v>
       </c>
       <c r="H26" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
@@ -1456,19 +1454,19 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G27" s="23">
         <v>0</v>
       </c>
       <c r="H27" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
@@ -1502,19 +1500,19 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G28" s="22">
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -1548,12 +1546,12 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G29" s="23">
@@ -1594,19 +1592,19 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G30" s="22">
         <v>0</v>
       </c>
       <c r="H30" s="22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
@@ -1640,19 +1638,19 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G31" s="23">
         <v>0</v>
       </c>
       <c r="H31" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
@@ -1686,12 +1684,12 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G32" s="22">
@@ -1732,19 +1730,19 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G33" s="23">
         <v>0</v>
       </c>
       <c r="H33" s="23">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
@@ -1778,19 +1776,19 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G34" s="22">
         <v>0</v>
       </c>
       <c r="H34" s="22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
@@ -1824,19 +1822,19 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G35" s="23">
         <v>0</v>
       </c>
       <c r="H35" s="23">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1870,19 +1868,19 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G36" s="22">
         <v>0</v>
       </c>
       <c r="H36" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1916,19 +1914,19 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G37" s="23">
         <v>0</v>
       </c>
       <c r="H37" s="23">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1962,19 +1960,19 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G38" s="22">
         <v>0</v>
       </c>
       <c r="H38" s="22">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -2008,19 +2006,19 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G39" s="23">
         <v>0</v>
       </c>
       <c r="H39" s="23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
@@ -2054,19 +2052,19 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G40" s="22">
         <v>0</v>
       </c>
       <c r="H40" s="22">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
@@ -2100,19 +2098,19 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G41" s="23">
         <v>0</v>
       </c>
       <c r="H41" s="23">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I41" s="21" t="inlineStr">
         <is>
@@ -2146,19 +2144,19 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G42" s="22">
         <v>0</v>
       </c>
       <c r="H42" s="22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
@@ -2192,12 +2190,12 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G43" s="23">
@@ -2238,19 +2236,19 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G44" s="22">
         <v>0</v>
       </c>
       <c r="H44" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
@@ -2284,12 +2282,12 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G45" s="23">
@@ -2330,19 +2328,19 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G46" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
@@ -2357,7 +2355,7 @@
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
@@ -2366,7 +2364,7 @@
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D47" s="19" t="inlineStr">
@@ -2376,19 +2374,19 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G47" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I47" s="21" t="inlineStr">
         <is>
@@ -2397,7 +2395,7 @@
       </c>
       <c r="J47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
@@ -2422,19 +2420,19 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G48" s="22">
         <v>0</v>
       </c>
       <c r="H48" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I48" s="20" t="inlineStr">
         <is>
@@ -2468,19 +2466,19 @@
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G49" s="23">
         <v>0</v>
       </c>
       <c r="H49" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I49" s="21" t="inlineStr">
         <is>
@@ -2514,19 +2512,19 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G50" s="22">
         <v>0</v>
       </c>
       <c r="H50" s="22">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I50" s="20" t="inlineStr">
         <is>
@@ -2560,19 +2558,19 @@
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G51" s="23">
         <v>0</v>
       </c>
       <c r="H51" s="23">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I51" s="21" t="inlineStr">
         <is>
@@ -2606,128 +2604,130 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G52" s="22">
+        <v>0</v>
+      </c>
+      <c r="H52" s="22">
+        <v>4</v>
+      </c>
+      <c r="I52" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J52" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="18">
+        <v>23</v>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:59:31</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">67</t>
         </is>
       </c>
-      <c r="F52" s="22" t="inlineStr">
+      <c r="F53" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G52" s="22">
-        <v>0</v>
-      </c>
-      <c r="H52" s="22">
+      <c r="G53" s="23">
+        <v>0</v>
+      </c>
+      <c r="H53" s="23">
         <v>1</v>
       </c>
-      <c r="I52" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J52" s="17" t="inlineStr">
+      <c r="I53" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J53" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="48" customHeight="1">
-      <c r="A53" s="18">
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="16">
         <v>22</v>
       </c>
-      <c r="B53" s="19" t="inlineStr">
+      <c r="B54" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
-      <c r="C53" s="19" t="inlineStr">
+      <c r="C54" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
-      <c r="D53" s="19" t="inlineStr">
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E53" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F53" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G53" s="23" t="inlineStr">
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G54" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="H53" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I53" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J53" s="19" t="inlineStr">
+      <c r="H54" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I54" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J54" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2688d62325</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="16">
-        <v>21</v>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:18:32</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E54" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62</t>
-        </is>
-      </c>
-      <c r="F54" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G54" s="22">
-        <v>4</v>
-      </c>
-      <c r="H54" s="22">
-        <v>0</v>
-      </c>
-      <c r="I54" s="20">
-        <v>4</v>
-      </c>
-      <c r="J54" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G55" s="23">
@@ -2765,13 +2765,13 @@
       </c>
       <c r="J55" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="16">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G56" s="22">
@@ -2809,13 +2809,13 @@
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -2834,32 +2834,32 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G57" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H57" s="23">
         <v>0</v>
       </c>
       <c r="I57" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -2878,32 +2878,32 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G58" s="22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H58" s="22">
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -2922,32 +2922,32 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G59" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H59" s="23">
         <v>0</v>
       </c>
       <c r="I59" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G60" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H60" s="22">
         <v>0</v>
       </c>
       <c r="I60" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
@@ -3010,32 +3010,32 @@
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G61" s="23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H61" s="23">
         <v>0</v>
       </c>
       <c r="I61" s="21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
@@ -3054,32 +3054,32 @@
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G62" s="22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H62" s="22">
         <v>0</v>
       </c>
       <c r="I62" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D63" s="19" t="inlineStr">
@@ -3098,32 +3098,32 @@
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G63" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H63" s="23">
         <v>0</v>
       </c>
       <c r="I63" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
@@ -3142,32 +3142,32 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G64" s="22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H64" s="22">
         <v>0</v>
       </c>
       <c r="I64" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -3186,32 +3186,32 @@
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G65" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H65" s="23">
         <v>0</v>
       </c>
       <c r="I65" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
@@ -3230,32 +3230,32 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G66" s="22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H66" s="22">
         <v>0</v>
       </c>
       <c r="I66" s="20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D67" s="19" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G67" s="23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H67" s="23">
         <v>0</v>
       </c>
       <c r="I67" s="21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
@@ -3318,32 +3318,32 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G68" s="22">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H68" s="22">
         <v>0</v>
       </c>
       <c r="I68" s="20">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1">
       <c r="A69" s="18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D69" s="19" t="inlineStr">
@@ -3362,32 +3362,32 @@
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G69" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H69" s="23">
         <v>0</v>
       </c>
       <c r="I69" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1">
       <c r="A70" s="16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G70" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H70" s="22">
         <v>0</v>
       </c>
       <c r="I70" s="20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1">
       <c r="A71" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B71" s="19" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="C71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D71" s="19" t="inlineStr">
@@ -3450,46 +3450,46 @@
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G71" s="23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H71" s="23">
         <v>0</v>
       </c>
       <c r="I71" s="21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
@@ -3503,19 +3503,17 @@
         </is>
       </c>
       <c r="G72" s="22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H72" s="22">
+        <v>0</v>
+      </c>
+      <c r="I72" s="20">
         <v>5</v>
       </c>
-      <c r="I72" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -3540,19 +3538,19 @@
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G73" s="23">
         <v>0</v>
       </c>
       <c r="H73" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I73" s="21" t="inlineStr">
         <is>
@@ -3581,7 +3579,7 @@
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
@@ -3594,15 +3592,11 @@
           <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
-      <c r="G74" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H74" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+      <c r="G74" s="22">
+        <v>0</v>
+      </c>
+      <c r="H74" s="22">
+        <v>3</v>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
@@ -3631,24 +3625,28 @@
       </c>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G75" s="23">
-        <v>0</v>
-      </c>
-      <c r="H75" s="23">
-        <v>6</v>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H75" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
       </c>
       <c r="I75" s="21" t="inlineStr">
         <is>
@@ -3677,7 +3675,7 @@
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
@@ -3690,15 +3688,11 @@
           <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
-      <c r="G76" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H76" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
+      <c r="G76" s="22">
+        <v>0</v>
+      </c>
+      <c r="H76" s="22">
+        <v>6</v>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
@@ -3732,12 +3726,12 @@
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
@@ -3747,7 +3741,7 @@
       </c>
       <c r="H77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I77" s="21" t="inlineStr">
@@ -3782,22 +3776,22 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
@@ -3832,12 +3826,12 @@
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -3847,7 +3841,7 @@
       </c>
       <c r="H79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I79" s="21" t="inlineStr">
@@ -3882,12 +3876,12 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G80" s="22" t="inlineStr">
@@ -3897,7 +3891,7 @@
       </c>
       <c r="H80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
@@ -3927,24 +3921,28 @@
       </c>
       <c r="D81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G81" s="23">
-        <v>0</v>
-      </c>
-      <c r="H81" s="23">
-        <v>3</v>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H81" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
       </c>
       <c r="I81" s="21" t="inlineStr">
         <is>
@@ -3973,7 +3971,7 @@
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
@@ -3986,15 +3984,11 @@
           <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
-      <c r="G82" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H82" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
+      <c r="G82" s="22">
+        <v>0</v>
+      </c>
+      <c r="H82" s="22">
+        <v>3</v>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
@@ -4023,24 +4017,28 @@
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G83" s="23">
-        <v>0</v>
-      </c>
-      <c r="H83" s="23">
-        <v>3</v>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H83" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
@@ -4069,7 +4067,7 @@
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
@@ -4082,15 +4080,11 @@
           <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
-      <c r="G84" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H84" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
+      <c r="G84" s="22">
+        <v>0</v>
+      </c>
+      <c r="H84" s="22">
+        <v>3</v>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
@@ -4119,24 +4113,28 @@
       </c>
       <c r="D85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G85" s="23">
-        <v>0</v>
-      </c>
-      <c r="H85" s="23">
-        <v>5</v>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H85" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
       </c>
       <c r="I85" s="21" t="inlineStr">
         <is>
@@ -4165,7 +4163,7 @@
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
@@ -4178,15 +4176,11 @@
           <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
-      <c r="G86" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H86" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
+      <c r="G86" s="22">
+        <v>0</v>
+      </c>
+      <c r="H86" s="22">
+        <v>5</v>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
@@ -4215,24 +4209,28 @@
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="G87" s="23">
-        <v>0</v>
-      </c>
-      <c r="H87" s="23">
-        <v>9</v>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
       </c>
       <c r="I87" s="21" t="inlineStr">
         <is>
@@ -4261,7 +4259,7 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
@@ -4274,15 +4272,11 @@
           <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
-      <c r="G88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
+      <c r="G88" s="22">
+        <v>0</v>
+      </c>
+      <c r="H88" s="22">
+        <v>9</v>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
@@ -4316,12 +4310,12 @@
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -4331,7 +4325,7 @@
       </c>
       <c r="H89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I89" s="21" t="inlineStr">
@@ -4366,12 +4360,12 @@
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G90" s="22" t="inlineStr">
@@ -4381,7 +4375,7 @@
       </c>
       <c r="H90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I90" s="20" t="inlineStr">
@@ -4411,24 +4405,28 @@
       </c>
       <c r="D91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G91" s="23">
-        <v>0</v>
-      </c>
-      <c r="H91" s="23">
-        <v>6</v>
+          <t xml:space="preserve">وافل</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H91" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وافل</t>
+        </is>
       </c>
       <c r="I91" s="21" t="inlineStr">
         <is>
@@ -4457,7 +4455,7 @@
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
@@ -4470,15 +4468,11 @@
           <t xml:space="preserve">کوکی</t>
         </is>
       </c>
-      <c r="G92" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H92" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
+      <c r="G92" s="22">
+        <v>0</v>
+      </c>
+      <c r="H92" s="22">
+        <v>6</v>
       </c>
       <c r="I92" s="20" t="inlineStr">
         <is>
@@ -4507,24 +4501,28 @@
       </c>
       <c r="D93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="G93" s="23">
-        <v>0</v>
-      </c>
-      <c r="H93" s="23">
-        <v>3</v>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H93" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
       </c>
       <c r="I93" s="21" t="inlineStr">
         <is>
@@ -4553,7 +4551,7 @@
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
@@ -4566,15 +4564,11 @@
           <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
-      <c r="G94" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H94" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
+      <c r="G94" s="22">
+        <v>0</v>
+      </c>
+      <c r="H94" s="22">
+        <v>3</v>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
@@ -4608,12 +4602,12 @@
       </c>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -4623,7 +4617,7 @@
       </c>
       <c r="H95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="I95" s="21" t="inlineStr">
@@ -4653,24 +4647,28 @@
       </c>
       <c r="D96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G96" s="22">
-        <v>0</v>
-      </c>
-      <c r="H96" s="22">
-        <v>4</v>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H96" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
       </c>
       <c r="I96" s="20" t="inlineStr">
         <is>
@@ -4699,7 +4697,7 @@
       </c>
       <c r="D97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E97" s="19" t="inlineStr">
@@ -4712,15 +4710,11 @@
           <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
-      <c r="G97" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H97" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
+      <c r="G97" s="23">
+        <v>0</v>
+      </c>
+      <c r="H97" s="23">
+        <v>4</v>
       </c>
       <c r="I97" s="21" t="inlineStr">
         <is>
@@ -4749,24 +4743,28 @@
       </c>
       <c r="D98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F98" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G98" s="22">
-        <v>0</v>
-      </c>
-      <c r="H98" s="22">
-        <v>6</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G98" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H98" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I98" s="20" t="inlineStr">
         <is>
@@ -4795,7 +4793,7 @@
       </c>
       <c r="D99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E99" s="19" t="inlineStr">
@@ -4808,15 +4806,11 @@
           <t xml:space="preserve">آجیل</t>
         </is>
       </c>
-      <c r="G99" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H99" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+      <c r="G99" s="23">
+        <v>0</v>
+      </c>
+      <c r="H99" s="23">
+        <v>6</v>
       </c>
       <c r="I99" s="21" t="inlineStr">
         <is>
@@ -4845,24 +4839,28 @@
       </c>
       <c r="D100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
-      </c>
-      <c r="G100" s="22">
-        <v>0</v>
-      </c>
-      <c r="H100" s="22">
-        <v>7</v>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G100" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H100" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
       </c>
       <c r="I100" s="20" t="inlineStr">
         <is>
@@ -4891,7 +4889,7 @@
       </c>
       <c r="D101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E101" s="19" t="inlineStr">
@@ -4904,15 +4902,11 @@
           <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
-      <c r="G101" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H101" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
+      <c r="G101" s="23">
+        <v>0</v>
+      </c>
+      <c r="H101" s="23">
+        <v>7</v>
       </c>
       <c r="I101" s="21" t="inlineStr">
         <is>
@@ -4946,12 +4940,12 @@
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F102" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G102" s="22" t="inlineStr">
@@ -4961,7 +4955,7 @@
       </c>
       <c r="H102" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I102" s="20" t="inlineStr">
@@ -4991,24 +4985,28 @@
       </c>
       <c r="D103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G103" s="23">
-        <v>0</v>
-      </c>
-      <c r="H103" s="23">
-        <v>3</v>
+          <t xml:space="preserve">رول رول</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H103" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول</t>
+        </is>
       </c>
       <c r="I103" s="21" t="inlineStr">
         <is>
@@ -5037,7 +5035,7 @@
       </c>
       <c r="D104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E104" s="17" t="inlineStr">
@@ -5050,15 +5048,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G104" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H104" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G104" s="22">
+        <v>0</v>
+      </c>
+      <c r="H104" s="22">
+        <v>3</v>
       </c>
       <c r="I104" s="20" t="inlineStr">
         <is>
@@ -5092,7 +5086,7 @@
       </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
@@ -5142,7 +5136,7 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
@@ -5192,7 +5186,7 @@
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
@@ -5242,12 +5236,12 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G108" s="22" t="inlineStr">
@@ -5257,7 +5251,7 @@
       </c>
       <c r="H108" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I108" s="20" t="inlineStr">
@@ -5292,12 +5286,12 @@
       </c>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -5307,7 +5301,7 @@
       </c>
       <c r="H109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I109" s="21" t="inlineStr">
@@ -5342,12 +5336,12 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -5357,7 +5351,7 @@
       </c>
       <c r="H110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="I110" s="20" t="inlineStr">
@@ -5387,24 +5381,28 @@
       </c>
       <c r="D111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G111" s="23">
-        <v>0</v>
-      </c>
-      <c r="H111" s="23">
-        <v>5</v>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H111" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
       </c>
       <c r="I111" s="21" t="inlineStr">
         <is>
@@ -5433,7 +5431,7 @@
       </c>
       <c r="D112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E112" s="17" t="inlineStr">
@@ -5446,15 +5444,11 @@
           <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
-      <c r="G112" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H112" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>5</v>
       </c>
       <c r="I112" s="20" t="inlineStr">
         <is>
@@ -5483,24 +5477,28 @@
       </c>
       <c r="D113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G113" s="23">
-        <v>0</v>
-      </c>
-      <c r="H113" s="23">
-        <v>2</v>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G113" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H113" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
       </c>
       <c r="I113" s="21" t="inlineStr">
         <is>
@@ -5529,7 +5527,7 @@
       </c>
       <c r="D114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E114" s="17" t="inlineStr">
@@ -5542,15 +5540,11 @@
           <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
-      <c r="G114" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H114" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
+      <c r="G114" s="22">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22">
+        <v>2</v>
       </c>
       <c r="I114" s="20" t="inlineStr">
         <is>
@@ -5579,24 +5573,28 @@
       </c>
       <c r="D115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G115" s="23">
-        <v>0</v>
-      </c>
-      <c r="H115" s="23">
-        <v>4</v>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G115" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H115" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
       </c>
       <c r="I115" s="21" t="inlineStr">
         <is>
@@ -5625,7 +5623,7 @@
       </c>
       <c r="D116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E116" s="17" t="inlineStr">
@@ -5638,15 +5636,11 @@
           <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
-      <c r="G116" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H116" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>4</v>
       </c>
       <c r="I116" s="20" t="inlineStr">
         <is>
@@ -5680,12 +5674,12 @@
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -5695,7 +5689,7 @@
       </c>
       <c r="H117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I117" s="21" t="inlineStr">
@@ -5730,12 +5724,12 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G118" s="22" t="inlineStr">
@@ -5745,7 +5739,7 @@
       </c>
       <c r="H118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I118" s="20" t="inlineStr">
@@ -5780,12 +5774,12 @@
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -5795,7 +5789,7 @@
       </c>
       <c r="H119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I119" s="21" t="inlineStr">
@@ -5830,12 +5824,12 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G120" s="22" t="inlineStr">
@@ -5845,7 +5839,7 @@
       </c>
       <c r="H120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I120" s="20" t="inlineStr">
@@ -5880,12 +5874,12 @@
       </c>
       <c r="E121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -5895,7 +5889,7 @@
       </c>
       <c r="H121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I121" s="21" t="inlineStr">
@@ -5930,12 +5924,12 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F122" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G122" s="22" t="inlineStr">
@@ -5945,7 +5939,7 @@
       </c>
       <c r="H122" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I122" s="20" t="inlineStr">
@@ -5980,12 +5974,12 @@
       </c>
       <c r="E123" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -5995,7 +5989,7 @@
       </c>
       <c r="H123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="I123" s="21" t="inlineStr">
@@ -6025,24 +6019,28 @@
       </c>
       <c r="D124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F124" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G124" s="22">
-        <v>0</v>
-      </c>
-      <c r="H124" s="22">
-        <v>4</v>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="G124" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H124" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
       </c>
       <c r="I124" s="20" t="inlineStr">
         <is>
@@ -6071,7 +6069,7 @@
       </c>
       <c r="D125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E125" s="19" t="inlineStr">
@@ -6084,15 +6082,11 @@
           <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
-      <c r="G125" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H125" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
+      <c r="G125" s="23">
+        <v>0</v>
+      </c>
+      <c r="H125" s="23">
+        <v>4</v>
       </c>
       <c r="I125" s="21" t="inlineStr">
         <is>
@@ -6126,12 +6120,12 @@
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F126" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G126" s="22" t="inlineStr">
@@ -6141,7 +6135,7 @@
       </c>
       <c r="H126" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I126" s="20" t="inlineStr">
@@ -6176,12 +6170,12 @@
       </c>
       <c r="E127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -6191,7 +6185,7 @@
       </c>
       <c r="H127" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I127" s="21" t="inlineStr">
@@ -6226,12 +6220,12 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F128" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G128" s="22" t="inlineStr">
@@ -6241,7 +6235,7 @@
       </c>
       <c r="H128" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I128" s="20" t="inlineStr">
@@ -6276,12 +6270,12 @@
       </c>
       <c r="E129" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -6291,7 +6285,7 @@
       </c>
       <c r="H129" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="I129" s="21" t="inlineStr">
@@ -6321,24 +6315,28 @@
       </c>
       <c r="D130" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F130" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G130" s="22">
-        <v>0</v>
-      </c>
-      <c r="H130" s="22">
-        <v>4</v>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G130" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H130" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
       </c>
       <c r="I130" s="20" t="inlineStr">
         <is>
@@ -6367,7 +6365,7 @@
       </c>
       <c r="D131" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E131" s="19" t="inlineStr">
@@ -6380,15 +6378,11 @@
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G131" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H131" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
+      <c r="G131" s="23">
+        <v>0</v>
+      </c>
+      <c r="H131" s="23">
+        <v>4</v>
       </c>
       <c r="I131" s="21" t="inlineStr">
         <is>
@@ -6422,132 +6416,138 @@
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F132" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G132" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H132" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="I132" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J132" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="28" customHeight="1">
+      <c r="A133" s="18">
+        <v>3</v>
+      </c>
+      <c r="B133" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C133" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D133" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E133" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">68</t>
         </is>
       </c>
-      <c r="F132" s="22" t="inlineStr">
+      <c r="F133" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="G132" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H132" s="22" t="inlineStr">
+      <c r="G133" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H133" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="I132" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J132" s="17" t="inlineStr">
+      <c r="I133" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J133" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="48" customHeight="1">
-      <c r="A133" s="18">
-        <v>3</v>
-      </c>
-      <c r="B133" s="19" t="inlineStr">
+    <row r="134" ht="48" customHeight="1">
+      <c r="A134" s="16">
+        <v>3</v>
+      </c>
+      <c r="B134" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
-      <c r="C133" s="19" t="inlineStr">
+      <c r="C134" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
-      <c r="D133" s="19" t="inlineStr">
+      <c r="D134" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E133" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F133" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G133" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H133" s="23" t="inlineStr">
+      <c r="E134" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F134" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G134" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H134" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="I133" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J133" s="19" t="inlineStr">
+      <c r="I134" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J134" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="28" customHeight="1">
-      <c r="A134" s="16">
-        <v>2</v>
-      </c>
-      <c r="B134" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/23</t>
-        </is>
-      </c>
-      <c r="C134" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23:16:19</t>
-        </is>
-      </c>
-      <c r="D134" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E134" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="F134" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G134" s="22">
-        <v>4</v>
-      </c>
-      <c r="H134" s="22">
-        <v>0</v>
-      </c>
-      <c r="I134" s="20">
-        <v>4</v>
-      </c>
-      <c r="J134" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
     <row r="135" ht="28" customHeight="1">
       <c r="A135" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B135" s="19" t="inlineStr">
         <is>
@@ -6556,12 +6556,12 @@
       </c>
       <c r="C135" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">23:16:19</t>
         </is>
       </c>
       <c r="D135" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E135" s="19" t="inlineStr">
@@ -6575,19 +6575,17 @@
         </is>
       </c>
       <c r="G135" s="23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H135" s="23">
+        <v>0</v>
+      </c>
+      <c r="I135" s="21">
         <v>4</v>
       </c>
-      <c r="I135" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J135" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6605,7 @@
       </c>
       <c r="D136" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E136" s="17" t="inlineStr">
@@ -6620,15 +6618,11 @@
           <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
-      <c r="G136" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H136" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
+      <c r="G136" s="22">
+        <v>0</v>
+      </c>
+      <c r="H136" s="22">
+        <v>4</v>
       </c>
       <c r="I136" s="20" t="inlineStr">
         <is>
@@ -6662,12 +6656,12 @@
       </c>
       <c r="E137" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F137" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G137" s="23" t="inlineStr">
@@ -6677,7 +6671,7 @@
       </c>
       <c r="H137" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="I137" s="21" t="inlineStr">
@@ -6712,7 +6706,7 @@
       </c>
       <c r="E138" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F138" s="22" t="inlineStr">
@@ -6762,30 +6756,80 @@
       </c>
       <c r="E139" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F139" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G139" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H139" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I139" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J139" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="28" customHeight="1">
+      <c r="A140" s="16">
+        <v>1</v>
+      </c>
+      <c r="B140" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C140" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D140" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E140" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F139" s="23" t="inlineStr">
+      <c r="F140" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G139" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H139" s="23" t="inlineStr">
+      <c r="G140" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H140" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I139" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J139" s="19" t="inlineStr">
+      <c r="I140" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J140" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J140" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J140"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J141" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J141"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:39:21</t>
+          <t xml:space="preserve">15:40:03</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -518,32 +518,32 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G6" s="22">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H6" s="22">
         <v>0</v>
       </c>
       <c r="I6" s="20">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">fde35723ac</t>
+          <t xml:space="preserve">a58157ef0e</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:38:05</t>
+          <t xml:space="preserve">15:39:21</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -562,32 +562,32 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G7" s="23">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H7" s="23">
         <v>0</v>
       </c>
       <c r="I7" s="21">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">c36d03e545</t>
+          <t xml:space="preserve">fde35723ac</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:38:01</t>
+          <t xml:space="preserve">15:38:05</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -606,32 +606,32 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G8" s="22">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H8" s="22">
         <v>0</v>
       </c>
       <c r="I8" s="20">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">02e6345647</t>
+          <t xml:space="preserve">c36d03e545</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="18">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:36:57</t>
+          <t xml:space="preserve">15:38:01</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -650,32 +650,32 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="23">
         <v>0</v>
       </c>
       <c r="I9" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">424ffdd738</t>
+          <t xml:space="preserve">02e6345647</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:36:21</t>
+          <t xml:space="preserve">15:36:57</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G10" s="22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H10" s="22">
         <v>0</v>
       </c>
       <c r="I10" s="20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">b665f084da</t>
+          <t xml:space="preserve">424ffdd738</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="18">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:35:52</t>
+          <t xml:space="preserve">15:36:21</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -738,32 +738,32 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G11" s="23">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H11" s="23">
         <v>0</v>
       </c>
       <c r="I11" s="21">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">751f8a7696</t>
+          <t xml:space="preserve">b665f084da</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:18</t>
+          <t xml:space="preserve">15:35:52</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
@@ -782,32 +782,32 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G12" s="22">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H12" s="22">
         <v>0</v>
       </c>
       <c r="I12" s="20">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">0be32d0353</t>
+          <t xml:space="preserve">751f8a7696</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="18">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:13</t>
+          <t xml:space="preserve">15:33:18</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -826,32 +826,32 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G13" s="23">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H13" s="23">
         <v>0</v>
       </c>
       <c r="I13" s="21">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">28a1fcc537</t>
+          <t xml:space="preserve">0be32d0353</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:05</t>
+          <t xml:space="preserve">15:33:13</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
@@ -870,32 +870,32 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G14" s="22">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H14" s="22">
         <v>0</v>
       </c>
       <c r="I14" s="20">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a734384c03</t>
+          <t xml:space="preserve">28a1fcc537</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="18">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:31:30</t>
+          <t xml:space="preserve">15:33:05</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -914,32 +914,32 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G15" s="23">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H15" s="23">
         <v>0</v>
       </c>
       <c r="I15" s="21">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5edabb20bb</t>
+          <t xml:space="preserve">a734384c03</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="16">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:53</t>
+          <t xml:space="preserve">15:31:30</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
@@ -958,32 +958,32 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G16" s="22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H16" s="22">
         <v>0</v>
       </c>
       <c r="I16" s="20">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a1408f9e88</t>
+          <t xml:space="preserve">5edabb20bb</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="18">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:35</t>
+          <t xml:space="preserve">15:30:53</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G17" s="23">
@@ -1021,13 +1021,13 @@
       </c>
       <c r="J17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed45f1ef47</t>
+          <t xml:space="preserve">a1408f9e88</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:59</t>
+          <t xml:space="preserve">15:30:35</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
@@ -1046,32 +1046,32 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G18" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H18" s="22">
         <v>0</v>
       </c>
       <c r="I18" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">d659616819</t>
+          <t xml:space="preserve">ed45f1ef47</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:38</t>
+          <t xml:space="preserve">15:29:59</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G19" s="23">
@@ -1109,13 +1109,13 @@
       </c>
       <c r="J19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">19f5f6152e</t>
+          <t xml:space="preserve">d659616819</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:24</t>
+          <t xml:space="preserve">15:29:38</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G20" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H20" s="22">
         <v>0</v>
       </c>
       <c r="I20" s="20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd714591b4</t>
+          <t xml:space="preserve">19f5f6152e</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
@@ -1168,38 +1168,36 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:24</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G21" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H21" s="23">
         <v>0</v>
       </c>
-      <c r="I21" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I21" s="21">
+        <v>4</v>
       </c>
       <c r="J21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">bd714591b4</t>
         </is>
       </c>
     </row>
@@ -1224,16 +1222,16 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G22" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" s="22">
         <v>0</v>
@@ -1270,16 +1268,16 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G23" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" s="23">
         <v>0</v>
@@ -1316,19 +1314,19 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G24" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" s="22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
@@ -1362,19 +1360,19 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G25" s="23">
         <v>0</v>
       </c>
       <c r="H25" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
@@ -1408,12 +1406,12 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G26" s="22">
@@ -1454,19 +1452,19 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G27" s="23">
         <v>0</v>
       </c>
       <c r="H27" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
@@ -1500,19 +1498,19 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G28" s="22">
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -1546,19 +1544,19 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G29" s="23">
         <v>0</v>
       </c>
       <c r="H29" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
@@ -1592,12 +1590,12 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G30" s="22">
@@ -1638,19 +1636,19 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G31" s="23">
         <v>0</v>
       </c>
       <c r="H31" s="23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
@@ -1684,19 +1682,19 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G32" s="22">
         <v>0</v>
       </c>
       <c r="H32" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
@@ -1730,12 +1728,12 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G33" s="23">
@@ -1776,19 +1774,19 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G34" s="22">
         <v>0</v>
       </c>
       <c r="H34" s="22">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
@@ -1822,19 +1820,19 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G35" s="23">
         <v>0</v>
       </c>
       <c r="H35" s="23">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1868,19 +1866,19 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G36" s="22">
         <v>0</v>
       </c>
       <c r="H36" s="22">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1914,19 +1912,19 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G37" s="23">
         <v>0</v>
       </c>
       <c r="H37" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1960,19 +1958,19 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G38" s="22">
         <v>0</v>
       </c>
       <c r="H38" s="22">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -2006,19 +2004,19 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G39" s="23">
         <v>0</v>
       </c>
       <c r="H39" s="23">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
@@ -2052,19 +2050,19 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G40" s="22">
         <v>0</v>
       </c>
       <c r="H40" s="22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
@@ -2098,19 +2096,19 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G41" s="23">
         <v>0</v>
       </c>
       <c r="H41" s="23">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I41" s="21" t="inlineStr">
         <is>
@@ -2144,19 +2142,19 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G42" s="22">
         <v>0</v>
       </c>
       <c r="H42" s="22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
@@ -2190,19 +2188,19 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G43" s="23">
         <v>0</v>
       </c>
       <c r="H43" s="23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I43" s="21" t="inlineStr">
         <is>
@@ -2236,12 +2234,12 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G44" s="22">
@@ -2282,19 +2280,19 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G45" s="23">
         <v>0</v>
       </c>
       <c r="H45" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I45" s="21" t="inlineStr">
         <is>
@@ -2328,12 +2326,12 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G46" s="22">
@@ -2374,19 +2372,19 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G47" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I47" s="21" t="inlineStr">
         <is>
@@ -2401,7 +2399,7 @@
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
@@ -2410,7 +2408,7 @@
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -2420,19 +2418,19 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G48" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I48" s="20" t="inlineStr">
         <is>
@@ -2441,7 +2439,7 @@
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
@@ -2466,19 +2464,19 @@
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G49" s="23">
         <v>0</v>
       </c>
       <c r="H49" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I49" s="21" t="inlineStr">
         <is>
@@ -2512,19 +2510,19 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G50" s="22">
         <v>0</v>
       </c>
       <c r="H50" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I50" s="20" t="inlineStr">
         <is>
@@ -2558,19 +2556,19 @@
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G51" s="23">
         <v>0</v>
       </c>
       <c r="H51" s="23">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I51" s="21" t="inlineStr">
         <is>
@@ -2604,19 +2602,19 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G52" s="22">
         <v>0</v>
       </c>
       <c r="H52" s="22">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I52" s="20" t="inlineStr">
         <is>
@@ -2650,128 +2648,130 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G53" s="23">
+        <v>0</v>
+      </c>
+      <c r="H53" s="23">
+        <v>4</v>
+      </c>
+      <c r="I53" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J53" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="16">
+        <v>23</v>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:59:31</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">67</t>
         </is>
       </c>
-      <c r="F53" s="23" t="inlineStr">
+      <c r="F54" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G53" s="23">
-        <v>0</v>
-      </c>
-      <c r="H53" s="23">
+      <c r="G54" s="22">
+        <v>0</v>
+      </c>
+      <c r="H54" s="22">
         <v>1</v>
       </c>
-      <c r="I53" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J53" s="19" t="inlineStr">
+      <c r="I54" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J54" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="48" customHeight="1">
-      <c r="A54" s="16">
+    <row r="55" ht="48" customHeight="1">
+      <c r="A55" s="18">
         <v>22</v>
       </c>
-      <c r="B54" s="17" t="inlineStr">
+      <c r="B55" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
-      <c r="C54" s="17" t="inlineStr">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
-      <c r="D54" s="17" t="inlineStr">
+      <c r="D55" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E54" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F54" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G54" s="22" t="inlineStr">
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="H54" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I54" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J54" s="17" t="inlineStr">
+      <c r="H55" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I55" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J55" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">2688d62325</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="18">
-        <v>21</v>
-      </c>
-      <c r="B55" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C55" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:18:32</t>
-        </is>
-      </c>
-      <c r="D55" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E55" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62</t>
-        </is>
-      </c>
-      <c r="F55" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G55" s="23">
-        <v>4</v>
-      </c>
-      <c r="H55" s="23">
-        <v>0</v>
-      </c>
-      <c r="I55" s="21">
-        <v>4</v>
-      </c>
-      <c r="J55" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G56" s="22">
@@ -2809,13 +2809,13 @@
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G57" s="23">
@@ -2853,13 +2853,13 @@
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -2878,32 +2878,32 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G58" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H58" s="22">
         <v>0</v>
       </c>
       <c r="I58" s="20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -2922,32 +2922,32 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G59" s="23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H59" s="23">
         <v>0</v>
       </c>
       <c r="I59" s="21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G60" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H60" s="22">
         <v>0</v>
       </c>
       <c r="I60" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
@@ -3010,32 +3010,32 @@
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G61" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H61" s="23">
         <v>0</v>
       </c>
       <c r="I61" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
@@ -3054,32 +3054,32 @@
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G62" s="22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H62" s="22">
         <v>0</v>
       </c>
       <c r="I62" s="20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D63" s="19" t="inlineStr">
@@ -3098,32 +3098,32 @@
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G63" s="23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H63" s="23">
         <v>0</v>
       </c>
       <c r="I63" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
@@ -3142,32 +3142,32 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G64" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H64" s="22">
         <v>0</v>
       </c>
       <c r="I64" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -3186,32 +3186,32 @@
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G65" s="23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H65" s="23">
         <v>0</v>
       </c>
       <c r="I65" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
@@ -3230,32 +3230,32 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G66" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H66" s="22">
         <v>0</v>
       </c>
       <c r="I66" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D67" s="19" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G67" s="23">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H67" s="23">
         <v>0</v>
       </c>
       <c r="I67" s="21">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
@@ -3318,32 +3318,32 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G68" s="22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H68" s="22">
         <v>0</v>
       </c>
       <c r="I68" s="20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1">
       <c r="A69" s="18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D69" s="19" t="inlineStr">
@@ -3362,32 +3362,32 @@
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G69" s="23">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H69" s="23">
         <v>0</v>
       </c>
       <c r="I69" s="21">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1">
       <c r="A70" s="16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G70" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H70" s="22">
         <v>0</v>
       </c>
       <c r="I70" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1">
       <c r="A71" s="18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B71" s="19" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="C71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D71" s="19" t="inlineStr">
@@ -3450,32 +3450,32 @@
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G71" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H71" s="23">
         <v>0</v>
       </c>
       <c r="I71" s="21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
@@ -3494,46 +3494,46 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G72" s="22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H72" s="22">
         <v>0</v>
       </c>
       <c r="I72" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="73" ht="28" customHeight="1">
       <c r="A73" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
@@ -3547,19 +3547,17 @@
         </is>
       </c>
       <c r="G73" s="23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H73" s="23">
+        <v>0</v>
+      </c>
+      <c r="I73" s="21">
         <v>5</v>
       </c>
-      <c r="I73" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -3584,19 +3582,19 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F74" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G74" s="22">
         <v>0</v>
       </c>
       <c r="H74" s="22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
@@ -3625,7 +3623,7 @@
       </c>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
@@ -3638,15 +3636,11 @@
           <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
-      <c r="G75" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H75" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+      <c r="G75" s="23">
+        <v>0</v>
+      </c>
+      <c r="H75" s="23">
+        <v>3</v>
       </c>
       <c r="I75" s="21" t="inlineStr">
         <is>
@@ -3675,24 +3669,28 @@
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F76" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G76" s="22">
-        <v>0</v>
-      </c>
-      <c r="H76" s="22">
-        <v>6</v>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H76" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
@@ -3721,7 +3719,7 @@
       </c>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
@@ -3734,15 +3732,11 @@
           <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
-      <c r="G77" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H77" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
+      <c r="G77" s="23">
+        <v>0</v>
+      </c>
+      <c r="H77" s="23">
+        <v>6</v>
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
@@ -3776,12 +3770,12 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G78" s="22" t="inlineStr">
@@ -3791,7 +3785,7 @@
       </c>
       <c r="H78" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
@@ -3826,22 +3820,22 @@
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I79" s="21" t="inlineStr">
@@ -3876,12 +3870,12 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G80" s="22" t="inlineStr">
@@ -3891,7 +3885,7 @@
       </c>
       <c r="H80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
@@ -3926,12 +3920,12 @@
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -3941,7 +3935,7 @@
       </c>
       <c r="H81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="I81" s="21" t="inlineStr">
@@ -3971,24 +3965,28 @@
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G82" s="22">
-        <v>0</v>
-      </c>
-      <c r="H82" s="22">
-        <v>3</v>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H82" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
@@ -4017,7 +4015,7 @@
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
@@ -4030,15 +4028,11 @@
           <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
-      <c r="G83" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H83" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
+      <c r="G83" s="23">
+        <v>0</v>
+      </c>
+      <c r="H83" s="23">
+        <v>3</v>
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
@@ -4067,24 +4061,28 @@
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F84" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G84" s="22">
-        <v>0</v>
-      </c>
-      <c r="H84" s="22">
-        <v>3</v>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H84" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
@@ -4113,7 +4111,7 @@
       </c>
       <c r="D85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
@@ -4126,15 +4124,11 @@
           <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
-      <c r="G85" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H85" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
+      <c r="G85" s="23">
+        <v>0</v>
+      </c>
+      <c r="H85" s="23">
+        <v>3</v>
       </c>
       <c r="I85" s="21" t="inlineStr">
         <is>
@@ -4163,24 +4157,28 @@
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F86" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G86" s="22">
-        <v>0</v>
-      </c>
-      <c r="H86" s="22">
-        <v>5</v>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H86" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
@@ -4209,7 +4207,7 @@
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
@@ -4222,15 +4220,11 @@
           <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
-      <c r="G87" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H87" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
+      <c r="G87" s="23">
+        <v>0</v>
+      </c>
+      <c r="H87" s="23">
+        <v>5</v>
       </c>
       <c r="I87" s="21" t="inlineStr">
         <is>
@@ -4259,24 +4253,28 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="G88" s="22">
-        <v>0</v>
-      </c>
-      <c r="H88" s="22">
-        <v>9</v>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H88" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
@@ -4305,7 +4303,7 @@
       </c>
       <c r="D89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
@@ -4318,15 +4316,11 @@
           <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
-      <c r="G89" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H89" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
+      <c r="G89" s="23">
+        <v>0</v>
+      </c>
+      <c r="H89" s="23">
+        <v>9</v>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
@@ -4360,12 +4354,12 @@
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G90" s="22" t="inlineStr">
@@ -4375,7 +4369,7 @@
       </c>
       <c r="H90" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I90" s="20" t="inlineStr">
@@ -4410,12 +4404,12 @@
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -4425,7 +4419,7 @@
       </c>
       <c r="H91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I91" s="21" t="inlineStr">
@@ -4455,24 +4449,28 @@
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F92" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G92" s="22">
-        <v>0</v>
-      </c>
-      <c r="H92" s="22">
-        <v>6</v>
+          <t xml:space="preserve">وافل</t>
+        </is>
+      </c>
+      <c r="G92" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H92" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وافل</t>
+        </is>
       </c>
       <c r="I92" s="20" t="inlineStr">
         <is>
@@ -4501,7 +4499,7 @@
       </c>
       <c r="D93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E93" s="19" t="inlineStr">
@@ -4514,15 +4512,11 @@
           <t xml:space="preserve">کوکی</t>
         </is>
       </c>
-      <c r="G93" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H93" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
+      <c r="G93" s="23">
+        <v>0</v>
+      </c>
+      <c r="H93" s="23">
+        <v>6</v>
       </c>
       <c r="I93" s="21" t="inlineStr">
         <is>
@@ -4551,24 +4545,28 @@
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F94" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="G94" s="22">
-        <v>0</v>
-      </c>
-      <c r="H94" s="22">
-        <v>3</v>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H94" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
@@ -4597,7 +4595,7 @@
       </c>
       <c r="D95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E95" s="19" t="inlineStr">
@@ -4610,15 +4608,11 @@
           <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
-      <c r="G95" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H95" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
+      <c r="G95" s="23">
+        <v>0</v>
+      </c>
+      <c r="H95" s="23">
+        <v>3</v>
       </c>
       <c r="I95" s="21" t="inlineStr">
         <is>
@@ -4652,12 +4646,12 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G96" s="22" t="inlineStr">
@@ -4667,7 +4661,7 @@
       </c>
       <c r="H96" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="I96" s="20" t="inlineStr">
@@ -4697,24 +4691,28 @@
       </c>
       <c r="D97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G97" s="23">
-        <v>0</v>
-      </c>
-      <c r="H97" s="23">
-        <v>4</v>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
+      </c>
+      <c r="G97" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H97" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
       </c>
       <c r="I97" s="21" t="inlineStr">
         <is>
@@ -4743,7 +4741,7 @@
       </c>
       <c r="D98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E98" s="17" t="inlineStr">
@@ -4756,15 +4754,11 @@
           <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
-      <c r="G98" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H98" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
+      <c r="G98" s="22">
+        <v>0</v>
+      </c>
+      <c r="H98" s="22">
+        <v>4</v>
       </c>
       <c r="I98" s="20" t="inlineStr">
         <is>
@@ -4793,24 +4787,28 @@
       </c>
       <c r="D99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G99" s="23">
-        <v>0</v>
-      </c>
-      <c r="H99" s="23">
-        <v>6</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G99" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H99" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I99" s="21" t="inlineStr">
         <is>
@@ -4839,7 +4837,7 @@
       </c>
       <c r="D100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
@@ -4852,15 +4850,11 @@
           <t xml:space="preserve">آجیل</t>
         </is>
       </c>
-      <c r="G100" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H100" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+      <c r="G100" s="22">
+        <v>0</v>
+      </c>
+      <c r="H100" s="22">
+        <v>6</v>
       </c>
       <c r="I100" s="20" t="inlineStr">
         <is>
@@ -4889,24 +4883,28 @@
       </c>
       <c r="D101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
-      </c>
-      <c r="G101" s="23">
-        <v>0</v>
-      </c>
-      <c r="H101" s="23">
-        <v>7</v>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H101" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
       </c>
       <c r="I101" s="21" t="inlineStr">
         <is>
@@ -4935,7 +4933,7 @@
       </c>
       <c r="D102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E102" s="17" t="inlineStr">
@@ -4948,15 +4946,11 @@
           <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
-      <c r="G102" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H102" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
+      <c r="G102" s="22">
+        <v>0</v>
+      </c>
+      <c r="H102" s="22">
+        <v>7</v>
       </c>
       <c r="I102" s="20" t="inlineStr">
         <is>
@@ -4990,12 +4984,12 @@
       </c>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -5005,7 +4999,7 @@
       </c>
       <c r="H103" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I103" s="21" t="inlineStr">
@@ -5035,24 +5029,28 @@
       </c>
       <c r="D104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G104" s="22">
-        <v>0</v>
-      </c>
-      <c r="H104" s="22">
-        <v>3</v>
+          <t xml:space="preserve">رول رول</t>
+        </is>
+      </c>
+      <c r="G104" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H104" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول</t>
+        </is>
       </c>
       <c r="I104" s="20" t="inlineStr">
         <is>
@@ -5081,7 +5079,7 @@
       </c>
       <c r="D105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E105" s="19" t="inlineStr">
@@ -5094,15 +5092,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G105" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H105" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G105" s="23">
+        <v>0</v>
+      </c>
+      <c r="H105" s="23">
+        <v>3</v>
       </c>
       <c r="I105" s="21" t="inlineStr">
         <is>
@@ -5136,7 +5130,7 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F106" s="22" t="inlineStr">
@@ -5186,7 +5180,7 @@
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
@@ -5236,7 +5230,7 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
@@ -5286,12 +5280,12 @@
       </c>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -5301,7 +5295,7 @@
       </c>
       <c r="H109" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I109" s="21" t="inlineStr">
@@ -5336,12 +5330,12 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -5351,7 +5345,7 @@
       </c>
       <c r="H110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I110" s="20" t="inlineStr">
@@ -5386,12 +5380,12 @@
       </c>
       <c r="E111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -5401,7 +5395,7 @@
       </c>
       <c r="H111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="I111" s="21" t="inlineStr">
@@ -5431,24 +5425,28 @@
       </c>
       <c r="D112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G112" s="22">
-        <v>0</v>
-      </c>
-      <c r="H112" s="22">
-        <v>5</v>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
+      </c>
+      <c r="G112" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H112" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
       </c>
       <c r="I112" s="20" t="inlineStr">
         <is>
@@ -5477,7 +5475,7 @@
       </c>
       <c r="D113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E113" s="19" t="inlineStr">
@@ -5490,15 +5488,11 @@
           <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
-      <c r="G113" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H113" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
+      <c r="G113" s="23">
+        <v>0</v>
+      </c>
+      <c r="H113" s="23">
+        <v>5</v>
       </c>
       <c r="I113" s="21" t="inlineStr">
         <is>
@@ -5527,24 +5521,28 @@
       </c>
       <c r="D114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F114" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G114" s="22">
-        <v>0</v>
-      </c>
-      <c r="H114" s="22">
-        <v>2</v>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G114" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H114" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
       </c>
       <c r="I114" s="20" t="inlineStr">
         <is>
@@ -5573,7 +5571,7 @@
       </c>
       <c r="D115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E115" s="19" t="inlineStr">
@@ -5586,15 +5584,11 @@
           <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
-      <c r="G115" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H115" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
+      <c r="G115" s="23">
+        <v>0</v>
+      </c>
+      <c r="H115" s="23">
+        <v>2</v>
       </c>
       <c r="I115" s="21" t="inlineStr">
         <is>
@@ -5623,24 +5617,28 @@
       </c>
       <c r="D116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F116" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G116" s="22">
-        <v>0</v>
-      </c>
-      <c r="H116" s="22">
-        <v>4</v>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G116" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H116" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
       </c>
       <c r="I116" s="20" t="inlineStr">
         <is>
@@ -5669,7 +5667,7 @@
       </c>
       <c r="D117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E117" s="19" t="inlineStr">
@@ -5682,15 +5680,11 @@
           <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
-      <c r="G117" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H117" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
+      <c r="G117" s="23">
+        <v>0</v>
+      </c>
+      <c r="H117" s="23">
+        <v>4</v>
       </c>
       <c r="I117" s="21" t="inlineStr">
         <is>
@@ -5724,12 +5718,12 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G118" s="22" t="inlineStr">
@@ -5739,7 +5733,7 @@
       </c>
       <c r="H118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I118" s="20" t="inlineStr">
@@ -5774,12 +5768,12 @@
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -5789,7 +5783,7 @@
       </c>
       <c r="H119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I119" s="21" t="inlineStr">
@@ -5824,12 +5818,12 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G120" s="22" t="inlineStr">
@@ -5839,7 +5833,7 @@
       </c>
       <c r="H120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I120" s="20" t="inlineStr">
@@ -5874,12 +5868,12 @@
       </c>
       <c r="E121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -5889,7 +5883,7 @@
       </c>
       <c r="H121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I121" s="21" t="inlineStr">
@@ -5924,12 +5918,12 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F122" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G122" s="22" t="inlineStr">
@@ -5939,7 +5933,7 @@
       </c>
       <c r="H122" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I122" s="20" t="inlineStr">
@@ -5974,12 +5968,12 @@
       </c>
       <c r="E123" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -5989,7 +5983,7 @@
       </c>
       <c r="H123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I123" s="21" t="inlineStr">
@@ -6024,12 +6018,12 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F124" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G124" s="22" t="inlineStr">
@@ -6039,7 +6033,7 @@
       </c>
       <c r="H124" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="I124" s="20" t="inlineStr">
@@ -6069,24 +6063,28 @@
       </c>
       <c r="D125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G125" s="23">
-        <v>0</v>
-      </c>
-      <c r="H125" s="23">
-        <v>4</v>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="G125" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H125" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
       </c>
       <c r="I125" s="21" t="inlineStr">
         <is>
@@ -6115,7 +6113,7 @@
       </c>
       <c r="D126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E126" s="17" t="inlineStr">
@@ -6128,15 +6126,11 @@
           <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
-      <c r="G126" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H126" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
+      <c r="G126" s="22">
+        <v>0</v>
+      </c>
+      <c r="H126" s="22">
+        <v>4</v>
       </c>
       <c r="I126" s="20" t="inlineStr">
         <is>
@@ -6170,12 +6164,12 @@
       </c>
       <c r="E127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -6185,7 +6179,7 @@
       </c>
       <c r="H127" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I127" s="21" t="inlineStr">
@@ -6220,12 +6214,12 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F128" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G128" s="22" t="inlineStr">
@@ -6235,7 +6229,7 @@
       </c>
       <c r="H128" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I128" s="20" t="inlineStr">
@@ -6270,12 +6264,12 @@
       </c>
       <c r="E129" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -6285,7 +6279,7 @@
       </c>
       <c r="H129" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I129" s="21" t="inlineStr">
@@ -6320,12 +6314,12 @@
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F130" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="G130" s="22" t="inlineStr">
@@ -6335,7 +6329,7 @@
       </c>
       <c r="H130" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="I130" s="20" t="inlineStr">
@@ -6365,24 +6359,28 @@
       </c>
       <c r="D131" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E131" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G131" s="23">
-        <v>0</v>
-      </c>
-      <c r="H131" s="23">
-        <v>4</v>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G131" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H131" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
       </c>
       <c r="I131" s="21" t="inlineStr">
         <is>
@@ -6411,7 +6409,7 @@
       </c>
       <c r="D132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E132" s="17" t="inlineStr">
@@ -6424,15 +6422,11 @@
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G132" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H132" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
+      <c r="G132" s="22">
+        <v>0</v>
+      </c>
+      <c r="H132" s="22">
+        <v>4</v>
       </c>
       <c r="I132" s="20" t="inlineStr">
         <is>
@@ -6466,132 +6460,138 @@
       </c>
       <c r="E133" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F133" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G133" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H133" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="I133" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J133" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="28" customHeight="1">
+      <c r="A134" s="16">
+        <v>3</v>
+      </c>
+      <c r="B134" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C134" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D134" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E134" s="17" t="inlineStr">
+        <is>
           <t xml:space="preserve">68</t>
         </is>
       </c>
-      <c r="F133" s="23" t="inlineStr">
+      <c r="F134" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="G133" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H133" s="23" t="inlineStr">
+      <c r="G134" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H134" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف بدون قند</t>
         </is>
       </c>
-      <c r="I133" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J133" s="19" t="inlineStr">
+      <c r="I134" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J134" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="48" customHeight="1">
-      <c r="A134" s="16">
-        <v>3</v>
-      </c>
-      <c r="B134" s="17" t="inlineStr">
+    <row r="135" ht="48" customHeight="1">
+      <c r="A135" s="18">
+        <v>3</v>
+      </c>
+      <c r="B135" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/24</t>
         </is>
       </c>
-      <c r="C134" s="17" t="inlineStr">
+      <c r="C135" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">12:39:32</t>
         </is>
       </c>
-      <c r="D134" s="17" t="inlineStr">
+      <c r="D135" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E134" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F134" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G134" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H134" s="22" t="inlineStr">
+      <c r="E135" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F135" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G135" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H135" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="I134" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J134" s="17" t="inlineStr">
+      <c r="I135" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J135" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">9422c9aa7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="28" customHeight="1">
-      <c r="A135" s="18">
-        <v>2</v>
-      </c>
-      <c r="B135" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/23</t>
-        </is>
-      </c>
-      <c r="C135" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23:16:19</t>
-        </is>
-      </c>
-      <c r="D135" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E135" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="F135" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
-      </c>
-      <c r="G135" s="23">
-        <v>4</v>
-      </c>
-      <c r="H135" s="23">
-        <v>0</v>
-      </c>
-      <c r="I135" s="21">
-        <v>4</v>
-      </c>
-      <c r="J135" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
     <row r="136" ht="28" customHeight="1">
       <c r="A136" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
@@ -6600,12 +6600,12 @@
       </c>
       <c r="C136" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22:41:53</t>
+          <t xml:space="preserve">23:16:19</t>
         </is>
       </c>
       <c r="D136" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E136" s="17" t="inlineStr">
@@ -6619,19 +6619,17 @@
         </is>
       </c>
       <c r="G136" s="22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H136" s="22">
+        <v>0</v>
+      </c>
+      <c r="I136" s="20">
         <v>4</v>
       </c>
-      <c r="I136" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J136" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a58237bc2</t>
+          <t xml:space="preserve">deac82c691</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6649,7 @@
       </c>
       <c r="D137" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E137" s="19" t="inlineStr">
@@ -6664,15 +6662,11 @@
           <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
-      <c r="G137" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H137" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
-        </is>
+      <c r="G137" s="23">
+        <v>0</v>
+      </c>
+      <c r="H137" s="23">
+        <v>4</v>
       </c>
       <c r="I137" s="21" t="inlineStr">
         <is>
@@ -6706,12 +6700,12 @@
       </c>
       <c r="E138" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F138" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G138" s="22" t="inlineStr">
@@ -6721,7 +6715,7 @@
       </c>
       <c r="H138" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="I138" s="20" t="inlineStr">
@@ -6756,7 +6750,7 @@
       </c>
       <c r="E139" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F139" s="23" t="inlineStr">
@@ -6806,30 +6800,80 @@
       </c>
       <c r="E140" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F140" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="G140" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H140" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="I140" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J140" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a58237bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="28" customHeight="1">
+      <c r="A141" s="18">
+        <v>1</v>
+      </c>
+      <c r="B141" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/23</t>
+        </is>
+      </c>
+      <c r="C141" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:41:53</t>
+        </is>
+      </c>
+      <c r="D141" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تغییر نام محصول</t>
+        </is>
+      </c>
+      <c r="E141" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F140" s="22" t="inlineStr">
+      <c r="F141" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="G140" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H140" s="22" t="inlineStr">
+      <c r="G141" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H141" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
-      <c r="I140" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J140" s="17" t="inlineStr">
+      <c r="I141" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J141" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">3a58237bc2</t>
         </is>

--- a/data/unicafe-history.xlsx
+++ b/data/unicafe-history.xlsx
@@ -181,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J141" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A5:J141"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UniCafeHistory" displayName="UniCafeHistory" ref="A5:J142" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:J142"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ردیف ثبت"/>
     <tableColumn id="2" name="تاریخ شمسی"/>
@@ -499,7 +499,7 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:40:03</t>
+          <t xml:space="preserve">15:40:28</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
@@ -518,12 +518,12 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G6" s="22">
@@ -537,13 +537,13 @@
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a58157ef0e</t>
+          <t xml:space="preserve">94cab5e732</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="18">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:39:21</t>
+          <t xml:space="preserve">15:40:03</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -562,32 +562,32 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G7" s="23">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H7" s="23">
         <v>0</v>
       </c>
       <c r="I7" s="21">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">fde35723ac</t>
+          <t xml:space="preserve">a58157ef0e</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:38:05</t>
+          <t xml:space="preserve">15:39:21</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -606,32 +606,32 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G8" s="22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H8" s="22">
         <v>0</v>
       </c>
       <c r="I8" s="20">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">c36d03e545</t>
+          <t xml:space="preserve">fde35723ac</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="18">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:38:01</t>
+          <t xml:space="preserve">15:38:05</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -650,32 +650,32 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G9" s="23">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H9" s="23">
         <v>0</v>
       </c>
       <c r="I9" s="21">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">02e6345647</t>
+          <t xml:space="preserve">c36d03e545</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:36:57</t>
+          <t xml:space="preserve">15:38:01</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G10" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="22">
         <v>0</v>
       </c>
       <c r="I10" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">424ffdd738</t>
+          <t xml:space="preserve">02e6345647</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="18">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:36:21</t>
+          <t xml:space="preserve">15:36:57</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -738,32 +738,32 @@
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G11" s="23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H11" s="23">
         <v>0</v>
       </c>
       <c r="I11" s="21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">b665f084da</t>
+          <t xml:space="preserve">424ffdd738</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="16">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:35:52</t>
+          <t xml:space="preserve">15:36:21</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
@@ -782,32 +782,32 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G12" s="22">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H12" s="22">
         <v>0</v>
       </c>
       <c r="I12" s="20">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">751f8a7696</t>
+          <t xml:space="preserve">b665f084da</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="18">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:18</t>
+          <t xml:space="preserve">15:35:52</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -826,32 +826,32 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G13" s="23">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H13" s="23">
         <v>0</v>
       </c>
       <c r="I13" s="21">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0be32d0353</t>
+          <t xml:space="preserve">751f8a7696</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:13</t>
+          <t xml:space="preserve">15:33:18</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
@@ -870,32 +870,32 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G14" s="22">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H14" s="22">
         <v>0</v>
       </c>
       <c r="I14" s="20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">28a1fcc537</t>
+          <t xml:space="preserve">0be32d0353</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="18">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:33:05</t>
+          <t xml:space="preserve">15:33:13</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -914,32 +914,32 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G15" s="23">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H15" s="23">
         <v>0</v>
       </c>
       <c r="I15" s="21">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a734384c03</t>
+          <t xml:space="preserve">28a1fcc537</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="16">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:31:30</t>
+          <t xml:space="preserve">15:33:05</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
@@ -958,32 +958,32 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G16" s="22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H16" s="22">
         <v>0</v>
       </c>
       <c r="I16" s="20">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5edabb20bb</t>
+          <t xml:space="preserve">a734384c03</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="18">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:53</t>
+          <t xml:space="preserve">15:31:30</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -1002,32 +1002,32 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G17" s="23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H17" s="23">
         <v>0</v>
       </c>
       <c r="I17" s="21">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J17" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a1408f9e88</t>
+          <t xml:space="preserve">5edabb20bb</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:30:35</t>
+          <t xml:space="preserve">15:30:53</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G18" s="22">
@@ -1065,13 +1065,13 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed45f1ef47</t>
+          <t xml:space="preserve">a1408f9e88</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:59</t>
+          <t xml:space="preserve">15:30:35</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -1090,32 +1090,32 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G19" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" s="23">
         <v>0</v>
       </c>
       <c r="I19" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">d659616819</t>
+          <t xml:space="preserve">ed45f1ef47</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:38</t>
+          <t xml:space="preserve">15:29:59</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G20" s="22">
@@ -1153,13 +1153,13 @@
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">19f5f6152e</t>
+          <t xml:space="preserve">d659616819</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:29:24</t>
+          <t xml:space="preserve">15:29:38</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -1178,32 +1178,32 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G21" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H21" s="23">
         <v>0</v>
       </c>
       <c r="I21" s="21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J21" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd714591b4</t>
+          <t xml:space="preserve">19f5f6152e</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
@@ -1212,38 +1212,36 @@
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15:27:49</t>
+          <t xml:space="preserve">15:29:24</t>
         </is>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G22" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="22">
         <v>0</v>
       </c>
-      <c r="I22" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="I22" s="20">
+        <v>4</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea4946ef39</t>
+          <t xml:space="preserve">bd714591b4</t>
         </is>
       </c>
     </row>
@@ -1268,16 +1266,16 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G23" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" s="23">
         <v>0</v>
@@ -1314,16 +1312,16 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G24" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H24" s="22">
         <v>0</v>
@@ -1360,19 +1358,19 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G25" s="23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" s="23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
@@ -1406,19 +1404,19 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G26" s="22">
         <v>0</v>
       </c>
       <c r="H26" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
@@ -1452,12 +1450,12 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G27" s="23">
@@ -1498,19 +1496,19 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G28" s="22">
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
@@ -1544,19 +1542,19 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G29" s="23">
         <v>0</v>
       </c>
       <c r="H29" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
@@ -1590,19 +1588,19 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G30" s="22">
         <v>0</v>
       </c>
       <c r="H30" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
@@ -1636,12 +1634,12 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G31" s="23">
@@ -1682,19 +1680,19 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
         </is>
       </c>
       <c r="G32" s="22">
         <v>0</v>
       </c>
       <c r="H32" s="22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
@@ -1728,19 +1726,19 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G33" s="23">
         <v>0</v>
       </c>
       <c r="H33" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
@@ -1774,12 +1772,12 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">رول رول</t>
         </is>
       </c>
       <c r="G34" s="22">
@@ -1820,19 +1818,19 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G35" s="23">
         <v>0</v>
       </c>
       <c r="H35" s="23">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -1866,19 +1864,19 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G36" s="22">
         <v>0</v>
       </c>
       <c r="H36" s="22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
@@ -1912,19 +1910,19 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">معینی پور</t>
         </is>
       </c>
       <c r="G37" s="23">
         <v>0</v>
       </c>
       <c r="H37" s="23">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -1958,19 +1956,19 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G38" s="22">
         <v>0</v>
       </c>
       <c r="H38" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
@@ -2004,19 +2002,19 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G39" s="23">
         <v>0</v>
       </c>
       <c r="H39" s="23">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
@@ -2050,19 +2048,19 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G40" s="22">
         <v>0</v>
       </c>
       <c r="H40" s="22">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
@@ -2096,19 +2094,19 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G41" s="23">
         <v>0</v>
       </c>
       <c r="H41" s="23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I41" s="21" t="inlineStr">
         <is>
@@ -2142,19 +2140,19 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G42" s="22">
         <v>0</v>
       </c>
       <c r="H42" s="22">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
@@ -2188,19 +2186,19 @@
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G43" s="23">
         <v>0</v>
       </c>
       <c r="H43" s="23">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I43" s="21" t="inlineStr">
         <is>
@@ -2234,19 +2232,19 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G44" s="22">
         <v>0</v>
       </c>
       <c r="H44" s="22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
@@ -2280,12 +2278,12 @@
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
+          <t xml:space="preserve">الوئه ورا</t>
         </is>
       </c>
       <c r="G45" s="23">
@@ -2326,19 +2324,19 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G46" s="22">
         <v>0</v>
       </c>
       <c r="H46" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
@@ -2372,12 +2370,12 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G47" s="23">
@@ -2418,19 +2416,19 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">رانی</t>
         </is>
       </c>
       <c r="G48" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I48" s="20" t="inlineStr">
         <is>
@@ -2445,7 +2443,7 @@
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
@@ -2454,7 +2452,7 @@
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:59:31</t>
+          <t xml:space="preserve">15:27:49</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
@@ -2464,19 +2462,19 @@
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G49" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I49" s="21" t="inlineStr">
         <is>
@@ -2485,7 +2483,7 @@
       </c>
       <c r="J49" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">e824170718</t>
+          <t xml:space="preserve">ea4946ef39</t>
         </is>
       </c>
     </row>
@@ -2510,19 +2508,19 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G50" s="22">
         <v>0</v>
       </c>
       <c r="H50" s="22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I50" s="20" t="inlineStr">
         <is>
@@ -2556,19 +2554,19 @@
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G51" s="23">
         <v>0</v>
       </c>
       <c r="H51" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I51" s="21" t="inlineStr">
         <is>
@@ -2602,19 +2600,19 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G52" s="22">
         <v>0</v>
       </c>
       <c r="H52" s="22">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I52" s="20" t="inlineStr">
         <is>
@@ -2648,19 +2646,19 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G53" s="23">
         <v>0</v>
       </c>
       <c r="H53" s="23">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I53" s="21" t="inlineStr">
         <is>
@@ -2694,128 +2692,130 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول با کلاس</t>
+        </is>
+      </c>
+      <c r="G54" s="22">
+        <v>0</v>
+      </c>
+      <c r="H54" s="22">
+        <v>4</v>
+      </c>
+      <c r="I54" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J54" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e824170718</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="18">
+        <v>23</v>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/25</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:59:31</t>
+        </is>
+      </c>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ثبت آمار</t>
+        </is>
+      </c>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">67</t>
         </is>
       </c>
-      <c r="F54" s="22" t="inlineStr">
+      <c r="F55" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G54" s="22">
-        <v>0</v>
-      </c>
-      <c r="H54" s="22">
+      <c r="G55" s="23">
+        <v>0</v>
+      </c>
+      <c r="H55" s="23">
         <v>1</v>
       </c>
-      <c r="I54" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J54" s="17" t="inlineStr">
+      <c r="I55" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J55" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">e824170718</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="48" customHeight="1">
-      <c r="A55" s="18">
+    <row r="56" ht="48" customHeight="1">
+      <c r="A56" s="16">
         <v>22</v>
       </c>
-      <c r="B55" s="19" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
-      <c r="C55" s="19" t="inlineStr">
+      <c r="C56" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">11:25:59</t>
         </is>
       </c>
-      <c r="D55" s="19" t="inlineStr">
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">یادداشت و آمار قهوه</t>
         </is>
       </c>
-      <c r="E55" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F55" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G55" s="23" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F56" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">وجین رو یکم ردیفشو خالی کردم به نظر بیاد دوتا فروش رفته خیلی وقته ثابته</t>
         </is>
       </c>
-      <c r="H55" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I55" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J55" s="19" t="inlineStr">
+      <c r="H56" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I56" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J56" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2688d62325</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="16">
-        <v>21</v>
-      </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1405/07/25</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09:18:32</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">شارژ و خروج از انبار</t>
-        </is>
-      </c>
-      <c r="E56" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62</t>
-        </is>
-      </c>
-      <c r="F56" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G56" s="22">
-        <v>4</v>
-      </c>
-      <c r="H56" s="22">
-        <v>0</v>
-      </c>
-      <c r="I56" s="20">
-        <v>4</v>
-      </c>
-      <c r="J56" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:29</t>
+          <t xml:space="preserve">09:18:32</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G57" s="23">
@@ -2853,13 +2853,13 @@
       </c>
       <c r="J57" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42a5348cd6</t>
+          <t xml:space="preserve">371938f24f</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="16">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:27</t>
+          <t xml:space="preserve">09:18:29</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
+          <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
       <c r="G58" s="22">
@@ -2897,13 +2897,13 @@
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">326a06b821</t>
+          <t xml:space="preserve">42a5348cd6</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:24</t>
+          <t xml:space="preserve">09:18:27</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -2922,32 +2922,32 @@
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G59" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H59" s="23">
         <v>0</v>
       </c>
       <c r="I59" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J59" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad336a97ef</t>
+          <t xml:space="preserve">326a06b821</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:22</t>
+          <t xml:space="preserve">09:18:24</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
+          <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
       <c r="G60" s="22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H60" s="22">
         <v>0</v>
       </c>
       <c r="I60" s="20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">a805c9c231</t>
+          <t xml:space="preserve">ad336a97ef</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:20</t>
+          <t xml:space="preserve">09:18:22</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
@@ -3010,32 +3010,32 @@
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
+          <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
       <c r="G61" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H61" s="23">
         <v>0</v>
       </c>
       <c r="I61" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J61" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">a8ff3d619f</t>
+          <t xml:space="preserve">a805c9c231</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:18</t>
+          <t xml:space="preserve">09:18:20</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
@@ -3054,32 +3054,32 @@
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F62" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G62" s="22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H62" s="22">
         <v>0</v>
       </c>
       <c r="I62" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11722c1ea0</t>
+          <t xml:space="preserve">a8ff3d619f</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:16</t>
+          <t xml:space="preserve">09:18:18</t>
         </is>
       </c>
       <c r="D63" s="19" t="inlineStr">
@@ -3098,32 +3098,32 @@
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
+          <t xml:space="preserve">آجیل</t>
         </is>
       </c>
       <c r="G63" s="23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H63" s="23">
         <v>0</v>
       </c>
       <c r="I63" s="21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891938adf</t>
+          <t xml:space="preserve">11722c1ea0</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:14</t>
+          <t xml:space="preserve">09:18:16</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
@@ -3142,32 +3142,32 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
       <c r="G64" s="22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H64" s="22">
         <v>0</v>
       </c>
       <c r="I64" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaaf8a4c01</t>
+          <t xml:space="preserve">5891938adf</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:12</t>
+          <t xml:space="preserve">09:18:14</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -3186,32 +3186,32 @@
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G65" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H65" s="23">
         <v>0</v>
       </c>
       <c r="I65" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf94ca7aef</t>
+          <t xml:space="preserve">eaaf8a4c01</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:11</t>
+          <t xml:space="preserve">09:18:12</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
@@ -3230,32 +3230,32 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F66" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+          <t xml:space="preserve">کوکی</t>
         </is>
       </c>
       <c r="G66" s="22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H66" s="22">
         <v>0</v>
       </c>
       <c r="I66" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J66" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">c72c97e061</t>
+          <t xml:space="preserve">bf94ca7aef</t>
         </is>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:09</t>
+          <t xml:space="preserve">09:18:11</t>
         </is>
       </c>
       <c r="D67" s="19" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
       <c r="G67" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H67" s="23">
         <v>0</v>
       </c>
       <c r="I67" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J67" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">39ac61bdf4</t>
+          <t xml:space="preserve">c72c97e061</t>
         </is>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:08</t>
+          <t xml:space="preserve">09:18:09</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
@@ -3318,32 +3318,32 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F68" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
+          <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
       <c r="G68" s="22">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H68" s="22">
         <v>0</v>
       </c>
       <c r="I68" s="20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42fdd74805</t>
+          <t xml:space="preserve">39ac61bdf4</t>
         </is>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1">
       <c r="A69" s="18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:06</t>
+          <t xml:space="preserve">09:18:08</t>
         </is>
       </c>
       <c r="D69" s="19" t="inlineStr">
@@ -3362,32 +3362,32 @@
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G69" s="23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H69" s="23">
         <v>0</v>
       </c>
       <c r="I69" s="21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J69" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">84e74cfe9c</t>
+          <t xml:space="preserve">42fdd74805</t>
         </is>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1">
       <c r="A70" s="16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:04</t>
+          <t xml:space="preserve">09:18:06</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F70" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G70" s="22">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H70" s="22">
         <v>0</v>
       </c>
       <c r="I70" s="20">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">723667cd28</t>
+          <t xml:space="preserve">84e74cfe9c</t>
         </is>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1">
       <c r="A71" s="18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B71" s="19" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="C71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:18:01</t>
+          <t xml:space="preserve">09:18:04</t>
         </is>
       </c>
       <c r="D71" s="19" t="inlineStr">
@@ -3450,32 +3450,32 @@
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
+          <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
       <c r="G71" s="23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H71" s="23">
         <v>0</v>
       </c>
       <c r="I71" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8cbfef9090</t>
+          <t xml:space="preserve">723667cd28</t>
         </is>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:58</t>
+          <t xml:space="preserve">09:18:01</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
@@ -3494,32 +3494,32 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F72" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G72" s="22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H72" s="22">
         <v>0</v>
       </c>
       <c r="I72" s="20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J72" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">86145ae381</t>
+          <t xml:space="preserve">8cbfef9090</t>
         </is>
       </c>
     </row>
     <row r="73" ht="28" customHeight="1">
       <c r="A73" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B73" s="19" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="C73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">09:17:53</t>
+          <t xml:space="preserve">09:17:58</t>
         </is>
       </c>
       <c r="D73" s="19" t="inlineStr">
@@ -3538,46 +3538,46 @@
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتاپ نادری</t>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
       <c r="G73" s="23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H73" s="23">
         <v>0</v>
       </c>
       <c r="I73" s="21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J73" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7a5cbafc23</t>
+          <t xml:space="preserve">86145ae381</t>
         </is>
       </c>
     </row>
     <row r="74" ht="28" customHeight="1">
       <c r="A74" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405/07/24</t>
+          <t xml:space="preserve">1405/07/25</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:39:32</t>
+          <t xml:space="preserve">09:17:53</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">شارژ و خروج از انبار</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
@@ -3591,19 +3591,17 @@
         </is>
       </c>
       <c r="G74" s="22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H74" s="22">
+        <v>0</v>
+      </c>
+      <c r="I74" s="20">
         <v>5</v>
       </c>
-      <c r="I74" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422c9aa7d</t>
+          <t xml:space="preserve">7a5cbafc23</t>
         </is>
       </c>
     </row>
@@ -3628,19 +3626,19 @@
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
+          <t xml:space="preserve">تیتاپ نادری</t>
         </is>
       </c>
       <c r="G75" s="23">
         <v>0</v>
       </c>
       <c r="H75" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I75" s="21" t="inlineStr">
         <is>
@@ -3669,7 +3667,7 @@
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
@@ -3682,15 +3680,11 @@
           <t xml:space="preserve">ساندویچ انار گردو</t>
         </is>
       </c>
-      <c r="G76" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H76" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ انار گردو</t>
-        </is>
+      <c r="G76" s="22">
+        <v>0</v>
+      </c>
+      <c r="H76" s="22">
+        <v>3</v>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
@@ -3719,24 +3713,28 @@
       </c>
       <c r="D77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
-      </c>
-      <c r="G77" s="23">
-        <v>0</v>
-      </c>
-      <c r="H77" s="23">
-        <v>6</v>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ</t>
+        </is>
+      </c>
+      <c r="H77" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ساندویچ انار گردو</t>
+        </is>
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
@@ -3765,7 +3763,7 @@
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
@@ -3778,15 +3776,11 @@
           <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
-      <c r="G78" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ</t>
-        </is>
-      </c>
-      <c r="H78" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ساندویچ مرغ</t>
-        </is>
+      <c r="G78" s="22">
+        <v>0</v>
+      </c>
+      <c r="H78" s="22">
+        <v>6</v>
       </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
@@ -3820,12 +3814,12 @@
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -3835,7 +3829,7 @@
       </c>
       <c r="H79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ساندویچ بندری</t>
+          <t xml:space="preserve">ساندویچ مرغ</t>
         </is>
       </c>
       <c r="I79" s="21" t="inlineStr">
@@ -3870,22 +3864,22 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="G80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ساندویچ</t>
         </is>
       </c>
       <c r="H80" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت نعناع</t>
+          <t xml:space="preserve">ساندویچ بندری</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
@@ -3920,12 +3914,12 @@
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -3935,7 +3929,7 @@
       </c>
       <c r="H81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">نات بار زرد</t>
+          <t xml:space="preserve">بایودنت نعناع</t>
         </is>
       </c>
       <c r="I81" s="21" t="inlineStr">
@@ -3970,12 +3964,12 @@
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="G82" s="22" t="inlineStr">
@@ -3985,7 +3979,7 @@
       </c>
       <c r="H82" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بایودنت توتی فروتی</t>
+          <t xml:space="preserve">نات بار زرد</t>
         </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
@@ -4015,24 +4009,28 @@
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
-      </c>
-      <c r="G83" s="23">
-        <v>0</v>
-      </c>
-      <c r="H83" s="23">
-        <v>3</v>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H83" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بایودنت توتی فروتی</t>
+        </is>
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
@@ -4061,7 +4059,7 @@
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
@@ -4074,15 +4072,11 @@
           <t xml:space="preserve">همپا دراز</t>
         </is>
       </c>
-      <c r="G84" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H84" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا دراز</t>
-        </is>
+      <c r="G84" s="22">
+        <v>0</v>
+      </c>
+      <c r="H84" s="22">
+        <v>3</v>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
@@ -4111,24 +4105,28 @@
       </c>
       <c r="D85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
-      </c>
-      <c r="G85" s="23">
-        <v>0</v>
-      </c>
-      <c r="H85" s="23">
-        <v>3</v>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H85" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا دراز</t>
+        </is>
       </c>
       <c r="I85" s="21" t="inlineStr">
         <is>
@@ -4157,7 +4155,7 @@
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
@@ -4170,15 +4168,11 @@
           <t xml:space="preserve">همپا ادامسی</t>
         </is>
       </c>
-      <c r="G86" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H86" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">همپا ادامسی</t>
-        </is>
+      <c r="G86" s="22">
+        <v>0</v>
+      </c>
+      <c r="H86" s="22">
+        <v>3</v>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
@@ -4207,24 +4201,28 @@
       </c>
       <c r="D87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
-      </c>
-      <c r="G87" s="23">
-        <v>0</v>
-      </c>
-      <c r="H87" s="23">
-        <v>5</v>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H87" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">همپا ادامسی</t>
+        </is>
       </c>
       <c r="I87" s="21" t="inlineStr">
         <is>
@@ -4253,7 +4251,7 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
@@ -4266,15 +4264,11 @@
           <t xml:space="preserve">کلوچه نادری نارگیلی</t>
         </is>
       </c>
-      <c r="G88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H88" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
-        </is>
+      <c r="G88" s="22">
+        <v>0</v>
+      </c>
+      <c r="H88" s="22">
+        <v>5</v>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
@@ -4303,24 +4297,28 @@
       </c>
       <c r="D89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
-      </c>
-      <c r="G89" s="23">
-        <v>0</v>
-      </c>
-      <c r="H89" s="23">
-        <v>9</v>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H89" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوچه نادری نارگیلی</t>
+        </is>
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
@@ -4349,7 +4347,7 @@
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
@@ -4362,15 +4360,11 @@
           <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
-      <c r="G90" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H90" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوچه نادری گردویی</t>
-        </is>
+      <c r="G90" s="22">
+        <v>0</v>
+      </c>
+      <c r="H90" s="22">
+        <v>9</v>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
@@ -4404,12 +4398,12 @@
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -4419,7 +4413,7 @@
       </c>
       <c r="H91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کروسان</t>
+          <t xml:space="preserve">کلوچه نادری گردویی</t>
         </is>
       </c>
       <c r="I91" s="21" t="inlineStr">
@@ -4454,12 +4448,12 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F92" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="G92" s="22" t="inlineStr">
@@ -4469,7 +4463,7 @@
       </c>
       <c r="H92" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وافل</t>
+          <t xml:space="preserve">کروسان</t>
         </is>
       </c>
       <c r="I92" s="20" t="inlineStr">
@@ -4499,24 +4493,28 @@
       </c>
       <c r="D93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
-      </c>
-      <c r="G93" s="23">
-        <v>0</v>
-      </c>
-      <c r="H93" s="23">
-        <v>6</v>
+          <t xml:space="preserve">وافل</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H93" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">وافل</t>
+        </is>
       </c>
       <c r="I93" s="21" t="inlineStr">
         <is>
@@ -4545,7 +4543,7 @@
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
@@ -4558,15 +4556,11 @@
           <t xml:space="preserve">کوکی</t>
         </is>
       </c>
-      <c r="G94" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H94" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کوکی</t>
-        </is>
+      <c r="G94" s="22">
+        <v>0</v>
+      </c>
+      <c r="H94" s="22">
+        <v>6</v>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
@@ -4595,24 +4589,28 @@
       </c>
       <c r="D95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
-      </c>
-      <c r="G95" s="23">
-        <v>0</v>
-      </c>
-      <c r="H95" s="23">
-        <v>3</v>
+          <t xml:space="preserve">کوکی</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H95" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کوکی</t>
+        </is>
       </c>
       <c r="I95" s="21" t="inlineStr">
         <is>
@@ -4641,7 +4639,7 @@
       </c>
       <c r="D96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E96" s="17" t="inlineStr">
@@ -4654,15 +4652,11 @@
           <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
-      <c r="G96" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H96" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پاستیل</t>
-        </is>
+      <c r="G96" s="22">
+        <v>0</v>
+      </c>
+      <c r="H96" s="22">
+        <v>3</v>
       </c>
       <c r="I96" s="20" t="inlineStr">
         <is>
@@ -4696,12 +4690,12 @@
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -4711,7 +4705,7 @@
       </c>
       <c r="H97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ویفر نادری کوچیک</t>
+          <t xml:space="preserve">پاستیل</t>
         </is>
       </c>
       <c r="I97" s="21" t="inlineStr">
@@ -4741,24 +4735,28 @@
       </c>
       <c r="D98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F98" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
-      </c>
-      <c r="G98" s="22">
-        <v>0</v>
-      </c>
-      <c r="H98" s="22">
-        <v>4</v>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
+      </c>
+      <c r="G98" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H98" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ویفر نادری کوچیک</t>
+        </is>
       </c>
       <c r="I98" s="20" t="inlineStr">
         <is>
@@ -4787,7 +4785,7 @@
       </c>
       <c r="D99" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E99" s="19" t="inlineStr">
@@ -4800,15 +4798,11 @@
           <t xml:space="preserve">کلوجه کاکائویی</t>
         </is>
       </c>
-      <c r="G99" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H99" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کلوجه کاکائویی</t>
-        </is>
+      <c r="G99" s="23">
+        <v>0</v>
+      </c>
+      <c r="H99" s="23">
+        <v>4</v>
       </c>
       <c r="I99" s="21" t="inlineStr">
         <is>
@@ -4837,24 +4831,28 @@
       </c>
       <c r="D100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F100" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
-      </c>
-      <c r="G100" s="22">
-        <v>0</v>
-      </c>
-      <c r="H100" s="22">
-        <v>6</v>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
+      </c>
+      <c r="G100" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H100" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کلوجه کاکائویی</t>
+        </is>
       </c>
       <c r="I100" s="20" t="inlineStr">
         <is>
@@ -4883,7 +4881,7 @@
       </c>
       <c r="D101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E101" s="19" t="inlineStr">
@@ -4896,15 +4894,11 @@
           <t xml:space="preserve">آجیل</t>
         </is>
       </c>
-      <c r="G101" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H101" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">آجیل</t>
-        </is>
+      <c r="G101" s="23">
+        <v>0</v>
+      </c>
+      <c r="H101" s="23">
+        <v>6</v>
       </c>
       <c r="I101" s="21" t="inlineStr">
         <is>
@@ -4933,24 +4927,28 @@
       </c>
       <c r="D102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F102" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
-      </c>
-      <c r="G102" s="22">
-        <v>0</v>
-      </c>
-      <c r="H102" s="22">
-        <v>7</v>
+          <t xml:space="preserve">آجیل</t>
+        </is>
+      </c>
+      <c r="G102" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H102" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">آجیل</t>
+        </is>
       </c>
       <c r="I102" s="20" t="inlineStr">
         <is>
@@ -4979,7 +4977,7 @@
       </c>
       <c r="D103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E103" s="19" t="inlineStr">
@@ -4992,15 +4990,11 @@
           <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
-      <c r="G103" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H103" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بادوم زمینی سرکه</t>
-        </is>
+      <c r="G103" s="23">
+        <v>0</v>
+      </c>
+      <c r="H103" s="23">
+        <v>7</v>
       </c>
       <c r="I103" s="21" t="inlineStr">
         <is>
@@ -5034,12 +5028,12 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="G104" s="22" t="inlineStr">
@@ -5049,7 +5043,7 @@
       </c>
       <c r="H104" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول</t>
+          <t xml:space="preserve">بادوم زمینی سرکه</t>
         </is>
       </c>
       <c r="I104" s="20" t="inlineStr">
@@ -5079,24 +5073,28 @@
       </c>
       <c r="D105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
-      </c>
-      <c r="G105" s="23">
-        <v>0</v>
-      </c>
-      <c r="H105" s="23">
-        <v>3</v>
+          <t xml:space="preserve">رول رول</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H105" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رول رول</t>
+        </is>
       </c>
       <c r="I105" s="21" t="inlineStr">
         <is>
@@ -5125,7 +5123,7 @@
       </c>
       <c r="D106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E106" s="17" t="inlineStr">
@@ -5138,15 +5136,11 @@
           <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
-      <c r="G106" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H106" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اب معدنی</t>
-        </is>
+      <c r="G106" s="22">
+        <v>0</v>
+      </c>
+      <c r="H106" s="22">
+        <v>3</v>
       </c>
       <c r="I106" s="20" t="inlineStr">
         <is>
@@ -5180,7 +5174,7 @@
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
@@ -5230,7 +5224,7 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F108" s="22" t="inlineStr">
@@ -5280,7 +5274,7 @@
       </c>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
@@ -5330,12 +5324,12 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="G110" s="22" t="inlineStr">
@@ -5345,7 +5339,7 @@
       </c>
       <c r="H110" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">های بای نادری</t>
+          <t xml:space="preserve">اب معدنی</t>
         </is>
       </c>
       <c r="I110" s="20" t="inlineStr">
@@ -5380,12 +5374,12 @@
       </c>
       <c r="E111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -5395,7 +5389,7 @@
       </c>
       <c r="H111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">توینکلز</t>
+          <t xml:space="preserve">های بای نادری</t>
         </is>
       </c>
       <c r="I111" s="21" t="inlineStr">
@@ -5430,12 +5424,12 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">46</t>
         </is>
       </c>
       <c r="F112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="G112" s="22" t="inlineStr">
@@ -5445,7 +5439,7 @@
       </c>
       <c r="H112" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">معینی پور</t>
+          <t xml:space="preserve">توینکلز</t>
         </is>
       </c>
       <c r="I112" s="20" t="inlineStr">
@@ -5475,24 +5469,28 @@
       </c>
       <c r="D113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
-      </c>
-      <c r="G113" s="23">
-        <v>0</v>
-      </c>
-      <c r="H113" s="23">
-        <v>5</v>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
+      </c>
+      <c r="G113" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H113" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">معینی پور</t>
+        </is>
       </c>
       <c r="I113" s="21" t="inlineStr">
         <is>
@@ -5521,7 +5519,7 @@
       </c>
       <c r="D114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E114" s="17" t="inlineStr">
@@ -5534,15 +5532,11 @@
           <t xml:space="preserve">پتی بور</t>
         </is>
       </c>
-      <c r="G114" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H114" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پتی بور</t>
-        </is>
+      <c r="G114" s="22">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22">
+        <v>5</v>
       </c>
       <c r="I114" s="20" t="inlineStr">
         <is>
@@ -5571,24 +5565,28 @@
       </c>
       <c r="D115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
-      </c>
-      <c r="G115" s="23">
-        <v>0</v>
-      </c>
-      <c r="H115" s="23">
-        <v>2</v>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
+      </c>
+      <c r="G115" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H115" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">پتی بور</t>
+        </is>
       </c>
       <c r="I115" s="21" t="inlineStr">
         <is>
@@ -5617,7 +5615,7 @@
       </c>
       <c r="D116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E116" s="17" t="inlineStr">
@@ -5630,15 +5628,11 @@
           <t xml:space="preserve">کیک میک شیفون</t>
         </is>
       </c>
-      <c r="G116" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H116" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">کیک میک شیفون</t>
-        </is>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>2</v>
       </c>
       <c r="I116" s="20" t="inlineStr">
         <is>
@@ -5667,24 +5661,28 @@
       </c>
       <c r="D117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
-      </c>
-      <c r="G117" s="23">
-        <v>0</v>
-      </c>
-      <c r="H117" s="23">
-        <v>4</v>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
+      </c>
+      <c r="G117" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H117" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">کیک میک شیفون</t>
+        </is>
       </c>
       <c r="I117" s="21" t="inlineStr">
         <is>
@@ -5713,7 +5711,7 @@
       </c>
       <c r="D118" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E118" s="17" t="inlineStr">
@@ -5726,15 +5724,11 @@
           <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
-      <c r="G118" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H118" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تیتو مزمز</t>
-        </is>
+      <c r="G118" s="22">
+        <v>0</v>
+      </c>
+      <c r="H118" s="22">
+        <v>4</v>
       </c>
       <c r="I118" s="20" t="inlineStr">
         <is>
@@ -5768,12 +5762,12 @@
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -5783,7 +5777,7 @@
       </c>
       <c r="H119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر شکلات</t>
+          <t xml:space="preserve">تیتو مزمز</t>
         </is>
       </c>
       <c r="I119" s="21" t="inlineStr">
@@ -5818,12 +5812,12 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="F120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="G120" s="22" t="inlineStr">
@@ -5833,7 +5827,7 @@
       </c>
       <c r="H120" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">رول رول با کلاس</t>
+          <t xml:space="preserve">شیر شکلات</t>
         </is>
       </c>
       <c r="I120" s="20" t="inlineStr">
@@ -5868,12 +5862,12 @@
       </c>
       <c r="E121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -5883,7 +5877,7 @@
       </c>
       <c r="H121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">شیر قهوه</t>
+          <t xml:space="preserve">رول رول با کلاس</t>
         </is>
       </c>
       <c r="I121" s="21" t="inlineStr">
@@ -5918,12 +5912,12 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="F122" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="G122" s="22" t="inlineStr">
@@ -5933,7 +5927,7 @@
       </c>
       <c r="H122" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار انبه</t>
+          <t xml:space="preserve">شیر قهوه</t>
         </is>
       </c>
       <c r="I122" s="20" t="inlineStr">
@@ -5968,12 +5962,12 @@
       </c>
       <c r="E123" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -5983,7 +5977,7 @@
       </c>
       <c r="H123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">سان استار پرتقال</t>
+          <t xml:space="preserve">سان استار انبه</t>
         </is>
       </c>
       <c r="I123" s="21" t="inlineStr">
@@ -6018,12 +6012,12 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F124" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="G124" s="22" t="inlineStr">
@@ -6033,7 +6027,7 @@
       </c>
       <c r="H124" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">وجین</t>
+          <t xml:space="preserve">سان استار پرتقال</t>
         </is>
       </c>
       <c r="I124" s="20" t="inlineStr">
@@ -6068,12 +6062,12 @@
       </c>
       <c r="E125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -6083,7 +6077,7 @@
       </c>
       <c r="H125" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">الوئه ورا</t>
+          <t xml:space="preserve">وجین</t>
         </is>
       </c>
       <c r="I125" s="21" t="inlineStr">
@@ -6113,24 +6107,28 @@
       </c>
       <c r="D126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F126" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
-      </c>
-      <c r="G126" s="22">
-        <v>0</v>
-      </c>
-      <c r="H126" s="22">
-        <v>4</v>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
+      </c>
+      <c r="G126" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H126" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الوئه ورا</t>
+        </is>
       </c>
       <c r="I126" s="20" t="inlineStr">
         <is>
@@ -6159,7 +6157,7 @@
       </c>
       <c r="D127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E127" s="19" t="inlineStr">
@@ -6172,15 +6170,11 @@
           <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
-      <c r="G127" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H127" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">پرو شیر</t>
-        </is>
+      <c r="G127" s="23">
+        <v>0</v>
+      </c>
+      <c r="H127" s="23">
+        <v>4</v>
       </c>
       <c r="I127" s="21" t="inlineStr">
         <is>
@@ -6214,12 +6208,12 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="F128" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="G128" s="22" t="inlineStr">
@@ -6229,7 +6223,7 @@
       </c>
       <c r="H128" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">سن ایچ پت پرتقال</t>
+          <t xml:space="preserve">پرو شیر</t>
         </is>
       </c>
       <c r="I128" s="20" t="inlineStr">
@@ -6264,12 +6258,12 @@
       </c>
       <c r="E129" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -6279,7 +6273,7 @@
       </c>
       <c r="H129" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کاکتوس</t>
+          <t xml:space="preserve">سن ایچ پت پرتقال</t>
         </is>
       </c>
       <c r="I129" s="21" t="inlineStr">
@@ -6314,12 +6308,12 @@
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="F130" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="G130" s="22" t="inlineStr">
@@ -6329,7 +6323,7 @@
       </c>
       <c r="H130" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ایس مانکی کیوی</t>
+          <t xml:space="preserve">ایس مانکی کاکتوس</t>
         </is>
       </c>
       <c r="I130" s="20" t="inlineStr">
@@ -6364,12 +6358,12 @@
       </c>
       <c r="E131" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -6379,7 +6373,7 @@
       </c>
       <c r="H131" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">رانی</t>
+          <t xml:space="preserve">ایس مانکی کیوی</t>
         </is>
       </c>
       <c r="I131" s="21" t="inlineStr">
@@ -6409,24 +6403,28 @@
       </c>
       <c r="D132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ثبت آمار</t>
+          <t xml:space="preserve">تغییر نام محصول</t>
         </is>
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="F132" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
-      </c>
-      <c r="G132" s="22">
-        <v>0</v>
-      </c>
-      <c r="H132" s="22">
-        <v>4</v>
+          <t xml:space="preserve">رانی</t>
+        </is>
+      </c>
+      <c r="G132" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H132" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رانی</t>
+        </is>
       </c>
       <c r="I132" s="20" t="inlineStr">
         <is>
@@ -6455,7 +6453,7 @@
       </c>
       <c r="D133" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">تغییر نام محصول</t>
+          <t xml:space="preserve">ثبت آمار</t>
         </is>
       </c>
       <c r="E133" s="19" t="inlineStr">
@@ -6468,15 +6466,11 @@
           <t xml:space="preserve">لایف با قند</t>
         </is>
       </c>
-      <c r="G133" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H133" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لایف با قند</t>
-        </is>
+      <c r="G133" s="23">
+        <v>0</v>
+      </c>
+      <c r="H133" s="23">
+        <v>4</v>
       </c>
       <c r="I133" s="21" t="inlineStr">
         <is>
@@ -6510,132 +6504,138 @@
       </c>
       <c r="E134" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="F134" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="G134" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H134" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لایف با قند</t>
+        </is>
+      </c>
+      <c r="I134" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J134" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9422c9aa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="28" customHeight="1">
+      <c r="A135" s="18">
+        <v>3</v>
+      </c>
+      <c r="B135" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1405/07/24</t>
+        </is>
+      </c>
+      <c r="C135" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:39:32</t>
+        </is>
+      </c>
+      <c r="D135" s="19" t="inlineStr">
+   